--- a/Data/Stats/2023 results and national trend model.xlsx
+++ b/Data/Stats/2023 results and national trend model.xlsx
@@ -35,6 +35,9 @@
     <sheet name="National" sheetId="25" state="visible" r:id="rId27"/>
     <sheet name="Summary" sheetId="26" state="visible" r:id="rId28"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="true" localSheetId="25" name="_xlnm._FilterDatabase" vbProcedure="false">Summary!$A$1:$K$187</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -45,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="430">
   <si>
     <t xml:space="preserve">Electorate (registered electors)</t>
   </si>
@@ -746,6 +749,15 @@
     <t xml:space="preserve">Projected Votes – # Votes Cast – 2023</t>
   </si>
   <si>
+    <t xml:space="preserve">Average Projection Per Party</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% Projected Vote Share Per Party</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projected Vote Share Per Party</t>
+  </si>
+  <si>
     <t xml:space="preserve">All Saints</t>
   </si>
   <si>
@@ -1326,33 +1338,6 @@
   </si>
   <si>
     <t xml:space="preserve">Steve Tanner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">David Finch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">John Vye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carolyn Hart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doug Bray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liubov Nestorova</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rizvi Rawoof</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saboor Ahmed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Onyx Rist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roshan Bhunnoo</t>
   </si>
 </sst>
 </file>
@@ -1633,10 +1618,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1646,6 +1627,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="172" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1707,6 +1692,39 @@
     <cellStyle name="Currency [0]" xfId="23"/>
     <cellStyle name="Percent" xfId="24"/>
   </cellStyles>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF274EC0"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF5649A0"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0000FF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1768,6 +1786,10 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2045,7 +2067,7 @@
         <v>3.55452844723231</v>
       </c>
     </row>
-    <row r="9" s="18" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
         <v>16</v>
       </c>
@@ -2127,28 +2149,28 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="19" t="n">
         <v>295</v>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="20" t="n">
         <f aca="false">C12*100/SUM($C$7:$C$13)</f>
         <v>30.7291666666667</v>
       </c>
-      <c r="E12" s="21" t="n">
+      <c r="E12" s="20" t="n">
         <f aca="false">C12*100/$B$1</f>
         <v>8.44062947067239</v>
       </c>
-      <c r="F12" s="20" t="n">
+      <c r="F12" s="19" t="n">
         <f aca="false">C12*IF(ISNUMBER(SEARCH("Labour",B12)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B12)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B12)),ISNUMBER(SEARCH("RefUK",B12))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B12)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B12)),ISNUMBER(SEARCH("Lib Dem",B12))),National!$L$8,National!$L$9)))))</f>
         <v>337.142857142857</v>
       </c>
-      <c r="G12" s="21" t="n">
+      <c r="G12" s="20" t="n">
         <f aca="false">F12*100/$B$1</f>
         <v>9.64643368076844</v>
       </c>
@@ -2232,13 +2254,18 @@
       </c>
       <c r="C2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" s="21" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>0.2758</v>
       </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
@@ -2359,87 +2386,87 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="19" t="n">
         <v>1752</v>
       </c>
-      <c r="D10" s="21" t="n">
+      <c r="D10" s="20" t="n">
         <f aca="false">C10*100/SUM($C$7:$C$14)</f>
         <v>21.3138686131387</v>
       </c>
-      <c r="E10" s="21" t="n">
+      <c r="E10" s="20" t="n">
         <f aca="false">C10*100/$B$1</f>
         <v>16.1370544349268</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="19" t="n">
         <f aca="false">C10*IF(ISNUMBER(SEARCH("Labour",B10)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B10)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B10)),ISNUMBER(SEARCH("RefUK",B10))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B10)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B10)),ISNUMBER(SEARCH("Lib Dem",B10))),National!$L$8,National!$L$9)))))</f>
         <v>1145.53846153846</v>
       </c>
-      <c r="G10" s="21" t="n">
+      <c r="G10" s="20" t="n">
         <f aca="false">F10*100/$B$1</f>
         <v>10.5511509766829</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="19" t="n">
         <v>1728</v>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="20" t="n">
         <f aca="false">C11*100/SUM($C$7:$C$14)</f>
         <v>21.021897810219</v>
       </c>
-      <c r="E11" s="21" t="n">
+      <c r="E11" s="20" t="n">
         <f aca="false">C11*100/$B$1</f>
         <v>15.9159988947223</v>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F11" s="19" t="n">
         <f aca="false">C11*IF(ISNUMBER(SEARCH("Labour",B11)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B11)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B11)),ISNUMBER(SEARCH("RefUK",B11))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B11)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B11)),ISNUMBER(SEARCH("Lib Dem",B11))),National!$L$8,National!$L$9)))))</f>
         <v>1129.84615384615</v>
       </c>
-      <c r="G11" s="21" t="n">
+      <c r="G11" s="20" t="n">
         <f aca="false">F11*100/$B$1</f>
         <v>10.4066146619338</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="19" t="n">
         <v>1618</v>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="20" t="n">
         <f aca="false">C12*100/SUM($C$7:$C$14)</f>
         <v>19.683698296837</v>
       </c>
-      <c r="E12" s="21" t="n">
+      <c r="E12" s="20" t="n">
         <f aca="false">C12*100/$B$1</f>
         <v>14.9028276687851</v>
       </c>
-      <c r="F12" s="20" t="n">
+      <c r="F12" s="19" t="n">
         <f aca="false">C12*IF(ISNUMBER(SEARCH("Labour",B12)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B12)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B12)),ISNUMBER(SEARCH("RefUK",B12))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B12)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B12)),ISNUMBER(SEARCH("Lib Dem",B12))),National!$L$8,National!$L$9)))))</f>
         <v>1057.92307692308</v>
       </c>
-      <c r="G12" s="21" t="n">
+      <c r="G12" s="20" t="n">
         <f aca="false">F12*100/$B$1</f>
         <v>9.74415655266719</v>
       </c>
     </row>
-    <row r="13" s="18" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
         <v>100</v>
       </c>
@@ -2590,20 +2617,20 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="19" t="n">
         <v>796</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="20" t="n">
         <f aca="false">C7*100/SUM($C$7:$C$12)</f>
         <v>27.3727647867951</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="20" t="n">
         <f aca="false">C7*100/$B$1</f>
         <v>11.5849221365158</v>
       </c>
@@ -2617,20 +2644,20 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="19" t="n">
         <v>751</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="20" t="n">
         <f aca="false">C8*100/SUM($C$7:$C$12)</f>
         <v>25.8253094910591</v>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="E8" s="20" t="n">
         <f aca="false">C8*100/$B$1</f>
         <v>10.9299956338233</v>
       </c>
@@ -2697,7 +2724,7 @@
         <v>4.85317331482373</v>
       </c>
     </row>
-    <row r="11" s="18" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
         <v>106</v>
       </c>
@@ -2902,60 +2929,60 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="19" t="n">
         <v>938</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="20" t="n">
         <f aca="false">C9*100/SUM($C$7:$C$12)</f>
         <v>30.7138179436804</v>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="20" t="n">
         <f aca="false">C9*100/$B$1</f>
         <v>14.1158765989466</v>
       </c>
-      <c r="F9" s="20" t="n">
+      <c r="F9" s="19" t="n">
         <f aca="false">C9*IF(ISNUMBER(SEARCH("Labour",B9)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B9)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B9)),ISNUMBER(SEARCH("RefUK",B9))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B9)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B9)),ISNUMBER(SEARCH("Lib Dem",B9))),National!$L$8,National!$L$9)))))</f>
         <v>613.307692307692</v>
       </c>
-      <c r="G9" s="21" t="n">
+      <c r="G9" s="20" t="n">
         <f aca="false">F9*100/$B$1</f>
         <v>9.22961162238815</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="19" t="n">
         <v>933</v>
       </c>
-      <c r="D10" s="21" t="n">
+      <c r="D10" s="20" t="n">
         <f aca="false">C10*100/SUM($C$7:$C$12)</f>
         <v>30.5500982318271</v>
       </c>
-      <c r="E10" s="21" t="n">
+      <c r="E10" s="20" t="n">
         <f aca="false">C10*100/$B$1</f>
         <v>14.0406320541761</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="19" t="n">
         <f aca="false">C10*IF(ISNUMBER(SEARCH("Labour",B10)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B10)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B10)),ISNUMBER(SEARCH("RefUK",B10))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B10)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B10)),ISNUMBER(SEARCH("Lib Dem",B10))),National!$L$8,National!$L$9)))))</f>
         <v>610.038461538462</v>
       </c>
-      <c r="G10" s="21" t="n">
+      <c r="G10" s="20" t="n">
         <f aca="false">F10*100/$B$1</f>
         <v>9.18041326619205</v>
       </c>
     </row>
-    <row r="11" s="18" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
         <v>112</v>
       </c>
@@ -3060,13 +3087,18 @@
       </c>
       <c r="C2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" s="21" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>0.2873</v>
       </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
@@ -3187,20 +3219,20 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="19" t="n">
         <v>1210</v>
       </c>
-      <c r="D10" s="21" t="n">
+      <c r="D10" s="20" t="n">
         <f aca="false">C10*100/SUM($C$7:$C$16)</f>
         <v>14.7705078125</v>
       </c>
-      <c r="E10" s="21" t="n">
+      <c r="E10" s="20" t="n">
         <f aca="false">C10*100/$B$1</f>
         <v>11.7009960351997</v>
       </c>
@@ -3214,20 +3246,20 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="19" t="n">
         <v>1138</v>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="20" t="n">
         <f aca="false">C11*100/SUM($C$7:$C$16)</f>
         <v>13.8916015625</v>
       </c>
-      <c r="E11" s="21" t="n">
+      <c r="E11" s="20" t="n">
         <f aca="false">C11*100/$B$1</f>
         <v>11.004738419882</v>
       </c>
@@ -3241,20 +3273,20 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="19" t="n">
         <v>1124</v>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="20" t="n">
         <f aca="false">C12*100/SUM($C$7:$C$16)</f>
         <v>13.720703125</v>
       </c>
-      <c r="E12" s="21" t="n">
+      <c r="E12" s="20" t="n">
         <f aca="false">C12*100/$B$1</f>
         <v>10.8693549946814</v>
       </c>
@@ -3267,7 +3299,7 @@
         <v>7.10688595806089</v>
       </c>
     </row>
-    <row r="13" s="18" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
         <v>120</v>
       </c>
@@ -3426,13 +3458,18 @@
       </c>
       <c r="C2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" s="21" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>0.2715</v>
       </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
@@ -3553,20 +3590,20 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="19" t="n">
         <v>1455</v>
       </c>
-      <c r="D10" s="21" t="n">
+      <c r="D10" s="20" t="n">
         <f aca="false">C10*100/SUM($C$7:$C$15)</f>
         <v>18.7186414511772</v>
       </c>
-      <c r="E10" s="21" t="n">
+      <c r="E10" s="20" t="n">
         <f aca="false">C10*100/$B$1</f>
         <v>13.9021593732085</v>
       </c>
@@ -3580,20 +3617,20 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="19" t="n">
         <v>1448</v>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="20" t="n">
         <f aca="false">C11*100/SUM($C$7:$C$15)</f>
         <v>18.6285861314808</v>
       </c>
-      <c r="E11" s="21" t="n">
+      <c r="E11" s="20" t="n">
         <f aca="false">C11*100/$B$1</f>
         <v>13.8352761322377</v>
       </c>
@@ -3607,20 +3644,20 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="19" t="n">
         <v>1430</v>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="20" t="n">
         <f aca="false">C12*100/SUM($C$7:$C$15)</f>
         <v>18.3970153094044</v>
       </c>
-      <c r="E12" s="21" t="n">
+      <c r="E12" s="20" t="n">
         <f aca="false">C12*100/$B$1</f>
         <v>13.6632906554558</v>
       </c>
@@ -3633,7 +3670,7 @@
         <v>8.93369004395184</v>
       </c>
     </row>
-    <row r="13" s="18" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
         <v>130</v>
       </c>
@@ -3865,20 +3902,20 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="19" t="n">
         <v>1177</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="20" t="n">
         <f aca="false">C9*100/SUM($C$7:$C$14)</f>
         <v>26.8476277372263</v>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="20" t="n">
         <f aca="false">C9*100/$B$1</f>
         <v>16.103434122315</v>
       </c>
@@ -3892,20 +3929,20 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="19" t="n">
         <v>1027</v>
       </c>
-      <c r="D10" s="21" t="n">
+      <c r="D10" s="20" t="n">
         <f aca="false">C10*100/SUM($C$7:$C$14)</f>
         <v>23.426094890511</v>
       </c>
-      <c r="E10" s="21" t="n">
+      <c r="E10" s="20" t="n">
         <f aca="false">C10*100/$B$1</f>
         <v>14.051169790669</v>
       </c>
@@ -3918,7 +3955,7 @@
         <v>9.18730332466822</v>
       </c>
     </row>
-    <row r="11" s="18" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
         <v>137</v>
       </c>
@@ -4077,13 +4114,18 @@
       </c>
       <c r="C2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" s="21" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>0.2815</v>
       </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
@@ -4123,20 +4165,20 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="19" t="n">
         <v>1658</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="20" t="n">
         <f aca="false">C7*100/SUM($C$7:$C$14)</f>
         <v>22.7061079156396</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="20" t="n">
         <f aca="false">C7*100/$B$1</f>
         <v>17.7079995727865</v>
       </c>
@@ -4150,20 +4192,20 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="19" t="n">
         <v>1517</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="20" t="n">
         <f aca="false">C8*100/SUM($C$7:$C$14)</f>
         <v>20.7751301013421</v>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="E8" s="20" t="n">
         <f aca="false">C8*100/$B$1</f>
         <v>16.2020719854747</v>
       </c>
@@ -4177,20 +4219,20 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="19" t="n">
         <v>1347</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="20" t="n">
         <f aca="false">C9*100/SUM($C$7:$C$14)</f>
         <v>18.4470008216927</v>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="20" t="n">
         <f aca="false">C9*100/$B$1</f>
         <v>14.3864146107017</v>
       </c>
@@ -4284,7 +4326,7 @@
         <v>4.64389290086182</v>
       </c>
     </row>
-    <row r="13" s="18" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
         <v>147</v>
       </c>
@@ -4389,13 +4431,18 @@
       </c>
       <c r="C2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" s="21" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>0.389</v>
       </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
@@ -4435,20 +4482,20 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="19" t="n">
         <v>1807</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="20" t="n">
         <f aca="false">C7*100/SUM($C$7:$C$14)</f>
         <v>19.2931881272688</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="20" t="n">
         <f aca="false">C7*100/$B$1</f>
         <v>20.8877586406196</v>
       </c>
@@ -4462,20 +4509,20 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="19" t="n">
         <v>1670</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="20" t="n">
         <f aca="false">C8*100/SUM($C$7:$C$14)</f>
         <v>17.8304505658766</v>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="E8" s="20" t="n">
         <f aca="false">C8*100/$B$1</f>
         <v>19.304126690556</v>
       </c>
@@ -4489,20 +4536,20 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="19" t="n">
         <v>1624</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="20" t="n">
         <f aca="false">C9*100/SUM($C$7:$C$14)</f>
         <v>17.339312406577</v>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="20" t="n">
         <f aca="false">C9*100/$B$1</f>
         <v>18.7723962547682</v>
       </c>
@@ -4596,7 +4643,7 @@
         <v>7.63362172447827</v>
       </c>
     </row>
-    <row r="13" s="18" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
         <v>155</v>
       </c>
@@ -4774,20 +4821,20 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="19" t="n">
         <v>479</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="20" t="n">
         <f aca="false">C8*100/SUM($C$7:$C$10)</f>
         <v>44.641192917055</v>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="E8" s="20" t="n">
         <f aca="false">C8*100/$B$1</f>
         <v>14.5858708891596</v>
       </c>
@@ -4800,7 +4847,7 @@
         <v>9.53691558137356</v>
       </c>
     </row>
-    <row r="9" s="18" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
         <v>159</v>
       </c>
@@ -4845,11 +4892,11 @@
         <f aca="false">C10*100/$B$1</f>
         <v>9.83556638246041</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="19" t="n">
         <f aca="false">C10*IF(ISNUMBER(SEARCH("Labour",B10)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B10)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B10)),ISNUMBER(SEARCH("RefUK",B10))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B10)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B10)),ISNUMBER(SEARCH("Lib Dem",B10))),National!$L$8,National!$L$9)))))</f>
         <v>452.2</v>
       </c>
-      <c r="G10" s="21" t="n">
+      <c r="G10" s="20" t="n">
         <f aca="false">F10*100/$B$1</f>
         <v>13.7697929354446</v>
       </c>
@@ -4905,13 +4952,18 @@
       </c>
       <c r="C2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" s="21" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>0.319</v>
       </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
@@ -4951,20 +5003,20 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="19" t="n">
         <v>1774</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="20" t="n">
         <f aca="false">C7*100/SUM($C$7:$C$15)</f>
         <v>18.8362709704821</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="20" t="n">
         <f aca="false">C7*100/$B$1</f>
         <v>17.0282203877904</v>
       </c>
@@ -4978,20 +5030,20 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="19" t="n">
         <v>1758</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="20" t="n">
         <f aca="false">C8*100/SUM($C$7:$C$15)</f>
         <v>18.6663835209174</v>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="E8" s="20" t="n">
         <f aca="false">C8*100/$B$1</f>
         <v>16.8746400460741</v>
       </c>
@@ -5005,20 +5057,20 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="19" t="n">
         <v>1682</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="20" t="n">
         <f aca="false">C9*100/SUM($C$7:$C$15)</f>
         <v>17.8594181354852</v>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="20" t="n">
         <f aca="false">C9*100/$B$1</f>
         <v>16.1451334229219</v>
       </c>
@@ -5112,7 +5164,7 @@
         <v>6.70917199521538</v>
       </c>
     </row>
-    <row r="13" s="18" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
         <v>167</v>
       </c>
@@ -5240,13 +5292,18 @@
       </c>
       <c r="C2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" s="21" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>0.2091</v>
       </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
@@ -5291,20 +5348,20 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="19" t="n">
         <v>1394</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="20" t="n">
         <f aca="false">C7*100/SUM($C$7:$C$14)</f>
         <v>23.595125253893</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="20" t="n">
         <f aca="false">C7*100/$B$1</f>
         <v>13.2446555819477</v>
       </c>
@@ -5318,20 +5375,20 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="19" t="n">
         <v>1211</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="20" t="n">
         <f aca="false">C8*100/SUM($C$7:$C$14)</f>
         <v>20.4976303317536</v>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="E8" s="20" t="n">
         <f aca="false">C8*100/$B$1</f>
         <v>11.5059382422803</v>
       </c>
@@ -5345,20 +5402,20 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="19" t="n">
         <v>1136</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="20" t="n">
         <f aca="false">C9*100/SUM($C$7:$C$14)</f>
         <v>19.2281651997292</v>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="20" t="n">
         <f aca="false">C9*100/$B$1</f>
         <v>10.7933491686461</v>
       </c>
@@ -5452,7 +5509,7 @@
         <v>2.90115110542664</v>
       </c>
     </row>
-    <row r="13" s="18" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
         <v>33</v>
       </c>
@@ -5558,13 +5615,18 @@
       </c>
       <c r="C2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" s="21" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>0.2791</v>
       </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
@@ -5685,87 +5747,87 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="19" t="n">
         <v>1458</v>
       </c>
-      <c r="D10" s="21" t="n">
+      <c r="D10" s="20" t="n">
         <f aca="false">C10*100/SUM($C$7:$C$16)</f>
         <v>18.5166370332741</v>
       </c>
-      <c r="E10" s="21" t="n">
+      <c r="E10" s="20" t="n">
         <f aca="false">C10*100/$B$1</f>
         <v>14.2689371697005</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="19" t="n">
         <f aca="false">C10*IF(ISNUMBER(SEARCH("Labour",B10)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B10)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B10)),ISNUMBER(SEARCH("RefUK",B10))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B10)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B10)),ISNUMBER(SEARCH("Lib Dem",B10))),National!$L$8,National!$L$9)))))</f>
         <v>953.307692307692</v>
       </c>
-      <c r="G10" s="21" t="n">
+      <c r="G10" s="20" t="n">
         <f aca="false">F10*100/$B$1</f>
         <v>9.32968968788111</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="19" t="n">
         <v>1446</v>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="20" t="n">
         <f aca="false">C11*100/SUM($C$7:$C$16)</f>
         <v>18.3642367284735</v>
       </c>
-      <c r="E11" s="21" t="n">
+      <c r="E11" s="20" t="n">
         <f aca="false">C11*100/$B$1</f>
         <v>14.1514973576042</v>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F11" s="19" t="n">
         <f aca="false">C11*IF(ISNUMBER(SEARCH("Labour",B11)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B11)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B11)),ISNUMBER(SEARCH("RefUK",B11))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B11)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B11)),ISNUMBER(SEARCH("Lib Dem",B11))),National!$L$8,National!$L$9)))))</f>
         <v>945.461538461539</v>
       </c>
-      <c r="G11" s="21" t="n">
+      <c r="G11" s="20" t="n">
         <f aca="false">F11*100/$B$1</f>
         <v>9.25290211843353</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="19" t="n">
         <v>1409</v>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="20" t="n">
         <f aca="false">C12*100/SUM($C$7:$C$16)</f>
         <v>17.8943357886716</v>
       </c>
-      <c r="E12" s="21" t="n">
+      <c r="E12" s="20" t="n">
         <f aca="false">C12*100/$B$1</f>
         <v>13.7893912703073</v>
       </c>
-      <c r="F12" s="20" t="n">
+      <c r="F12" s="19" t="n">
         <f aca="false">C12*IF(ISNUMBER(SEARCH("Labour",B12)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B12)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B12)),ISNUMBER(SEARCH("RefUK",B12))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B12)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B12)),ISNUMBER(SEARCH("Lib Dem",B12))),National!$L$8,National!$L$9)))))</f>
         <v>921.269230769231</v>
       </c>
-      <c r="G12" s="21" t="n">
+      <c r="G12" s="20" t="n">
         <f aca="false">F12*100/$B$1</f>
         <v>9.01614044597016</v>
       </c>
     </row>
-    <row r="13" s="18" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
         <v>177</v>
       </c>
@@ -5924,13 +5986,18 @@
       </c>
       <c r="C2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" s="21" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>0.2617</v>
       </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
@@ -5970,20 +6037,20 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="19" t="n">
         <v>1338</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="20" t="n">
         <f aca="false">C7*100/SUM($C$7:$C$15)</f>
         <v>18.1448331977217</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="20" t="n">
         <f aca="false">C7*100/$B$1</f>
         <v>13.1822660098522</v>
       </c>
@@ -5997,20 +6064,20 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="19" t="n">
         <v>1291</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="20" t="n">
         <f aca="false">C8*100/SUM($C$7:$C$15)</f>
         <v>17.5074586384595</v>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="E8" s="20" t="n">
         <f aca="false">C8*100/$B$1</f>
         <v>12.7192118226601</v>
       </c>
@@ -6024,20 +6091,20 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="19" t="n">
         <v>1236</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="20" t="n">
         <f aca="false">C9*100/SUM($C$7:$C$15)</f>
         <v>16.7615947925142</v>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="20" t="n">
         <f aca="false">C9*100/$B$1</f>
         <v>12.1773399014778</v>
       </c>
@@ -6068,11 +6135,11 @@
         <f aca="false">C10*100/$B$1</f>
         <v>9.76354679802956</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="19" t="n">
         <f aca="false">C10*IF(ISNUMBER(SEARCH("Labour",B10)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B10)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B10)),ISNUMBER(SEARCH("RefUK",B10))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B10)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B10)),ISNUMBER(SEARCH("Lib Dem",B10))),National!$L$8,National!$L$9)))))</f>
         <v>647.961538461539</v>
       </c>
-      <c r="G10" s="21" t="n">
+      <c r="G10" s="20" t="n">
         <f aca="false">F10*100/$B$1</f>
         <v>6.38385752178856</v>
       </c>
@@ -6095,11 +6162,11 @@
         <f aca="false">C11*100/$B$1</f>
         <v>9.57635467980296</v>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F11" s="19" t="n">
         <f aca="false">C11*IF(ISNUMBER(SEARCH("Labour",B11)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B11)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B11)),ISNUMBER(SEARCH("RefUK",B11))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B11)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B11)),ISNUMBER(SEARCH("Lib Dem",B11))),National!$L$8,National!$L$9)))))</f>
         <v>635.538461538462</v>
       </c>
-      <c r="G11" s="21" t="n">
+      <c r="G11" s="20" t="n">
         <f aca="false">F11*100/$B$1</f>
         <v>6.26146267525578</v>
       </c>
@@ -6122,16 +6189,16 @@
         <f aca="false">C12*100/$B$1</f>
         <v>9.55665024630542</v>
       </c>
-      <c r="F12" s="20" t="n">
+      <c r="F12" s="19" t="n">
         <f aca="false">C12*IF(ISNUMBER(SEARCH("Labour",B12)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B12)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B12)),ISNUMBER(SEARCH("RefUK",B12))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B12)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B12)),ISNUMBER(SEARCH("Lib Dem",B12))),National!$L$8,National!$L$9)))))</f>
         <v>634.230769230769</v>
       </c>
-      <c r="G12" s="21" t="n">
+      <c r="G12" s="20" t="n">
         <f aca="false">F12*100/$B$1</f>
         <v>6.2485790071997</v>
       </c>
     </row>
-    <row r="13" s="18" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
         <v>187</v>
       </c>
@@ -6309,20 +6376,20 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="19" t="n">
         <v>967</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="20" t="n">
         <f aca="false">C7*100/SUM($C$7:$C$12)</f>
         <v>30.21875</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="20" t="n">
         <f aca="false">C7*100/$B$1</f>
         <v>13.5814606741573</v>
       </c>
@@ -6336,20 +6403,20 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="19" t="n">
         <v>869</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="20" t="n">
         <f aca="false">C8*100/SUM($C$7:$C$12)</f>
         <v>27.15625</v>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="E8" s="20" t="n">
         <f aca="false">C8*100/$B$1</f>
         <v>12.2050561797753</v>
       </c>
@@ -6416,7 +6483,7 @@
         <v>4.49060069144339</v>
       </c>
     </row>
-    <row r="11" s="18" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
         <v>194</v>
       </c>
@@ -6521,13 +6588,18 @@
       </c>
       <c r="C2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" s="21" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>0.3255</v>
       </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
@@ -6567,20 +6639,20 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="19" t="n">
         <v>1998</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="20" t="n">
         <f aca="false">C7*100/SUM($C$7:$C$14)</f>
         <v>21.999559568377</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="20" t="n">
         <f aca="false">C7*100/$B$1</f>
         <v>19.6866686373042</v>
       </c>
@@ -6594,20 +6666,20 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="19" t="n">
         <v>1977</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="20" t="n">
         <f aca="false">C8*100/SUM($C$7:$C$14)</f>
         <v>21.768332966307</v>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="E8" s="20" t="n">
         <f aca="false">C8*100/$B$1</f>
         <v>19.4797516996748</v>
       </c>
@@ -6621,20 +6693,20 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="19" t="n">
         <v>1823</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="20" t="n">
         <f aca="false">C9*100/SUM($C$7:$C$14)</f>
         <v>20.0726712177934</v>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="20" t="n">
         <f aca="false">C9*100/$B$1</f>
         <v>17.9623608237265</v>
       </c>
@@ -6728,7 +6800,7 @@
         <v>5.20551475325345</v>
       </c>
     </row>
-    <row r="13" s="18" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
         <v>202</v>
       </c>
@@ -6879,20 +6951,20 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="19" t="n">
         <v>986</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="20" t="n">
         <f aca="false">C7*100/SUM($C$7:$C$13)</f>
         <v>26.7063921993499</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="20" t="n">
         <f aca="false">C7*100/$B$1</f>
         <v>13.8037239255215</v>
       </c>
@@ -6906,20 +6978,20 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="19" t="n">
         <v>915</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="20" t="n">
         <f aca="false">C8*100/SUM($C$7:$C$13)</f>
         <v>24.783315276273</v>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="E8" s="20" t="n">
         <f aca="false">C8*100/$B$1</f>
         <v>12.8097438051239</v>
       </c>
@@ -6950,11 +7022,11 @@
         <f aca="false">C9*100/$B$1</f>
         <v>11.1857762844743</v>
       </c>
-      <c r="F9" s="20" t="n">
+      <c r="F9" s="19" t="n">
         <f aca="false">C9*IF(ISNUMBER(SEARCH("Labour",B9)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B9)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B9)),ISNUMBER(SEARCH("RefUK",B9))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B9)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B9)),ISNUMBER(SEARCH("Lib Dem",B9))),National!$L$8,National!$L$9)))))</f>
         <v>522.423076923077</v>
       </c>
-      <c r="G9" s="21" t="n">
+      <c r="G9" s="20" t="n">
         <f aca="false">F9*100/$B$1</f>
         <v>7.31377680138705</v>
       </c>
@@ -6977,16 +7049,16 @@
         <f aca="false">C10*100/$B$1</f>
         <v>9.64580708385832</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="19" t="n">
         <f aca="false">C10*IF(ISNUMBER(SEARCH("Labour",B10)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B10)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B10)),ISNUMBER(SEARCH("RefUK",B10))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B10)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B10)),ISNUMBER(SEARCH("Lib Dem",B10))),National!$L$8,National!$L$9)))))</f>
         <v>450.5</v>
       </c>
-      <c r="G10" s="21" t="n">
+      <c r="G10" s="20" t="n">
         <f aca="false">F10*100/$B$1</f>
         <v>6.30687386252275</v>
       </c>
     </row>
-    <row r="11" s="18" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
         <v>208</v>
       </c>
@@ -7448,7 +7520,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J205"/>
+  <dimension ref="A1:M187"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="27.78"/>
@@ -7461,7 +7533,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="26" width="17.19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="25" width="16.19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="24" width="34.08"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="24" width="20.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="25" width="27.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="25.64"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="14" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7492,19 +7567,28 @@
       <c r="I1" s="25" t="s">
         <v>231</v>
       </c>
-      <c r="J1" s="24" t="s">
+      <c r="J1" s="1" t="s">
         <v>232</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="L1" s="25" t="s">
+        <v>234</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B2" s="27" t="s">
         <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>295</v>
@@ -7529,10 +7613,22 @@
         <f aca="false">ROUND(I2*SUMIF(A:A,A2,D:D),0)</f>
         <v>291</v>
       </c>
+      <c r="K2" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A2,B:B,B2)/COUNTIFS(B:B,B2,A:A,A2),0)</f>
+        <v>135</v>
+      </c>
+      <c r="L2" s="25" t="n">
+        <f aca="false">K2/SUMIF(A:A,A2,K:K)</f>
+        <v>0.195652173913044</v>
+      </c>
+      <c r="M2" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A2,J:J)*L2,0)</f>
+        <v>188</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B3" s="27" t="s">
         <v>23</v>
@@ -7563,16 +7659,28 @@
         <f aca="false">ROUND(I3*SUMIF(A:A,A3,D:D),0)</f>
         <v>249</v>
       </c>
+      <c r="K3" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A3,B:B,B3)/COUNTIFS(B:B,B3,A:A,A3),0)</f>
+        <v>135</v>
+      </c>
+      <c r="L3" s="25" t="n">
+        <f aca="false">K3/SUMIF(A:A,A3,K:K)</f>
+        <v>0.195652173913044</v>
+      </c>
+      <c r="M3" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A3,J:J)*L3,0)</f>
+        <v>188</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>190</v>
@@ -7597,16 +7705,28 @@
         <f aca="false">ROUND(I4*SUMIF(A:A,A4,D:D),0)</f>
         <v>107</v>
       </c>
+      <c r="K4" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A4,B:B,B4)/COUNTIFS(B:B,B4,A:A,A4),0)</f>
+        <v>107</v>
+      </c>
+      <c r="L4" s="25" t="n">
+        <f aca="false">K4/SUMIF(A:A,A4,K:K)</f>
+        <v>0.155072463768116</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A4,J:J)*L4,0)</f>
+        <v>149</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B5" s="27" t="s">
         <v>216</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>118</v>
@@ -7631,16 +7751,28 @@
         <f aca="false">ROUND(I5*SUMIF(A:A,A5,D:D),0)</f>
         <v>40</v>
       </c>
+      <c r="K5" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A5,B:B,B5)/COUNTIFS(B:B,B5,A:A,A5),0)</f>
+        <v>40</v>
+      </c>
+      <c r="L5" s="25" t="n">
+        <f aca="false">K5/SUMIF(A:A,A5,K:K)</f>
+        <v>0.0579710144927536</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A5,J:J)*L5,0)</f>
+        <v>56</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>49</v>
@@ -7665,16 +7797,28 @@
         <f aca="false">ROUND(I6*SUMIF(A:A,A6,D:D),0)</f>
         <v>176</v>
       </c>
+      <c r="K6" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A6,B:B,B6)/COUNTIFS(B:B,B6,A:A,A6),0)</f>
+        <v>176</v>
+      </c>
+      <c r="L6" s="25" t="n">
+        <f aca="false">K6/SUMIF(A:A,A6,K:K)</f>
+        <v>0.255072463768116</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A6,J:J)*L6,0)</f>
+        <v>245</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B7" s="30" t="s">
         <v>219</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>34</v>
@@ -7699,16 +7843,28 @@
         <f aca="false">ROUND(I7*SUMIF(A:A,A7,D:D),0)</f>
         <v>70</v>
       </c>
+      <c r="K7" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A7,B:B,B7)/COUNTIFS(B:B,B7,A:A,A7),0)</f>
+        <v>70</v>
+      </c>
+      <c r="L7" s="25" t="n">
+        <f aca="false">K7/SUMIF(A:A,A7,K:K)</f>
+        <v>0.101449275362319</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A7,J:J)*L7,0)</f>
+        <v>97</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B8" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>22</v>
@@ -7733,16 +7889,28 @@
         <f aca="false">ROUND(I8*SUMIF(A:A,A8,D:D),0)</f>
         <v>27</v>
       </c>
+      <c r="K8" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A8,B:B,B8)/COUNTIFS(B:B,B8,A:A,A8),0)</f>
+        <v>27</v>
+      </c>
+      <c r="L8" s="25" t="n">
+        <f aca="false">K8/SUMIF(A:A,A8,K:K)</f>
+        <v>0.0391304347826087</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A8,J:J)*L8,0)</f>
+        <v>38</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>1394</v>
@@ -7767,13 +7935,25 @@
         <f aca="false">ROUND(I9*SUMIF(A:A,A9,D:D),0)</f>
         <v>881</v>
       </c>
+      <c r="K9" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A9,B:B,B9)/COUNTIFS(B:B,B9,A:A,A9),0)</f>
+        <v>263</v>
+      </c>
+      <c r="L9" s="25" t="n">
+        <f aca="false">K9/SUMIF(A:A,A9,K:K)</f>
+        <v>0.0806996011046333</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A9,J:J)*L9,0)</f>
+        <v>477</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>28</v>
@@ -7801,16 +7981,28 @@
         <f aca="false">ROUND(I10*SUMIF(A:A,A10,D:D),0)</f>
         <v>766</v>
       </c>
+      <c r="K10" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A10,B:B,B10)/COUNTIFS(B:B,B10,A:A,A10),0)</f>
+        <v>263</v>
+      </c>
+      <c r="L10" s="25" t="n">
+        <f aca="false">K10/SUMIF(A:A,A10,K:K)</f>
+        <v>0.0806996011046333</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A10,J:J)*L10,0)</f>
+        <v>477</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>1136</v>
@@ -7835,16 +8027,28 @@
         <f aca="false">ROUND(I11*SUMIF(A:A,A11,D:D),0)</f>
         <v>718</v>
       </c>
+      <c r="K11" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A11,B:B,B11)/COUNTIFS(B:B,B11,A:A,A11),0)</f>
+        <v>263</v>
+      </c>
+      <c r="L11" s="25" t="n">
+        <f aca="false">K11/SUMIF(A:A,A11,K:K)</f>
+        <v>0.0806996011046333</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A11,J:J)*L11,0)</f>
+        <v>477</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>552</v>
@@ -7869,16 +8073,28 @@
         <f aca="false">ROUND(I12*SUMIF(A:A,A12,D:D),0)</f>
         <v>577</v>
       </c>
+      <c r="K12" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A12,B:B,B12)/COUNTIFS(B:B,B12,A:A,A12),0)</f>
+        <v>178</v>
+      </c>
+      <c r="L12" s="25" t="n">
+        <f aca="false">K12/SUMIF(A:A,A12,K:K)</f>
+        <v>0.0546179809757594</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A12,J:J)*L12,0)</f>
+        <v>323</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>517</v>
@@ -7903,16 +8119,28 @@
         <f aca="false">ROUND(I13*SUMIF(A:A,A13,D:D),0)</f>
         <v>541</v>
       </c>
+      <c r="K13" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A13,B:B,B13)/COUNTIFS(B:B,B13,A:A,A13),0)</f>
+        <v>178</v>
+      </c>
+      <c r="L13" s="25" t="n">
+        <f aca="false">K13/SUMIF(A:A,A13,K:K)</f>
+        <v>0.0546179809757594</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A13,J:J)*L13,0)</f>
+        <v>323</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>467</v>
@@ -7937,16 +8165,28 @@
         <f aca="false">ROUND(I14*SUMIF(A:A,A14,D:D),0)</f>
         <v>488</v>
       </c>
+      <c r="K14" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A14,B:B,B14)/COUNTIFS(B:B,B14,A:A,A14),0)</f>
+        <v>178</v>
+      </c>
+      <c r="L14" s="25" t="n">
+        <f aca="false">K14/SUMIF(A:A,A14,K:K)</f>
+        <v>0.0546179809757594</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A14,J:J)*L14,0)</f>
+        <v>323</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B15" s="30" t="s">
         <v>219</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>336</v>
@@ -7971,16 +8211,28 @@
         <f aca="false">ROUND(I15*SUMIF(A:A,A15,D:D),0)</f>
         <v>1276</v>
       </c>
+      <c r="K15" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A15,B:B,B15)/COUNTIFS(B:B,B15,A:A,A15),0)</f>
+        <v>1276</v>
+      </c>
+      <c r="L15" s="25" t="n">
+        <f aca="false">K15/SUMIF(A:A,A15,K:K)</f>
+        <v>0.39153114452286</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A15,J:J)*L15,0)</f>
+        <v>2313</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B16" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>295</v>
@@ -8005,16 +8257,28 @@
         <f aca="false">ROUND(I16*SUMIF(A:A,A16,D:D),0)</f>
         <v>660</v>
       </c>
+      <c r="K16" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A16,B:B,B16)/COUNTIFS(B:B,B16,A:A,A16),0)</f>
+        <v>660</v>
+      </c>
+      <c r="L16" s="25" t="n">
+        <f aca="false">K16/SUMIF(A:A,A16,K:K)</f>
+        <v>0.202516109235962</v>
+      </c>
+      <c r="M16" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A16,J:J)*L16,0)</f>
+        <v>1196</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>880</v>
@@ -8039,16 +8303,28 @@
         <f aca="false">ROUND(I17*SUMIF(A:A,A17,D:D),0)</f>
         <v>498</v>
       </c>
+      <c r="K17" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A17,B:B,B17)/COUNTIFS(B:B,B17,A:A,A17),0)</f>
+        <v>221</v>
+      </c>
+      <c r="L17" s="25" t="n">
+        <f aca="false">K17/SUMIF(A:A,A17,K:K)</f>
+        <v>0.119459459459459</v>
+      </c>
+      <c r="M17" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A17,J:J)*L17,0)</f>
+        <v>431</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>685</v>
@@ -8073,16 +8349,28 @@
         <f aca="false">ROUND(I18*SUMIF(A:A,A18,D:D),0)</f>
         <v>387</v>
       </c>
+      <c r="K18" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A18,B:B,B18)/COUNTIFS(B:B,B18,A:A,A18),0)</f>
+        <v>221</v>
+      </c>
+      <c r="L18" s="25" t="n">
+        <f aca="false">K18/SUMIF(A:A,A18,K:K)</f>
+        <v>0.119459459459459</v>
+      </c>
+      <c r="M18" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A18,J:J)*L18,0)</f>
+        <v>431</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B19" s="30" t="s">
         <v>219</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>641</v>
@@ -8107,16 +8395,28 @@
         <f aca="false">ROUND(I19*SUMIF(A:A,A19,D:D),0)</f>
         <v>1317</v>
       </c>
+      <c r="K19" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A19,B:B,B19)/COUNTIFS(B:B,B19,A:A,A19),0)</f>
+        <v>587</v>
+      </c>
+      <c r="L19" s="25" t="n">
+        <f aca="false">K19/SUMIF(A:A,A19,K:K)</f>
+        <v>0.317297297297297</v>
+      </c>
+      <c r="M19" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A19,J:J)*L19,0)</f>
+        <v>1144</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B20" s="30" t="s">
         <v>219</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>502</v>
@@ -8141,16 +8441,28 @@
         <f aca="false">ROUND(I20*SUMIF(A:A,A20,D:D),0)</f>
         <v>1031</v>
       </c>
+      <c r="K20" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A20,B:B,B20)/COUNTIFS(B:B,B20,A:A,A20),0)</f>
+        <v>587</v>
+      </c>
+      <c r="L20" s="25" t="n">
+        <f aca="false">K20/SUMIF(A:A,A20,K:K)</f>
+        <v>0.317297297297297</v>
+      </c>
+      <c r="M20" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A20,J:J)*L20,0)</f>
+        <v>1144</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B21" s="27" t="s">
         <v>216</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>414</v>
@@ -8175,16 +8487,28 @@
         <f aca="false">ROUND(I21*SUMIF(A:A,A21,D:D),0)</f>
         <v>142</v>
       </c>
+      <c r="K21" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A21,B:B,B21)/COUNTIFS(B:B,B21,A:A,A21),0)</f>
+        <v>71</v>
+      </c>
+      <c r="L21" s="25" t="n">
+        <f aca="false">K21/SUMIF(A:A,A21,K:K)</f>
+        <v>0.0383783783783784</v>
+      </c>
+      <c r="M21" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A21,J:J)*L21,0)</f>
+        <v>138</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B22" s="27" t="s">
         <v>216</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>408</v>
@@ -8209,16 +8533,28 @@
         <f aca="false">ROUND(I22*SUMIF(A:A,A22,D:D),0)</f>
         <v>140</v>
       </c>
+      <c r="K22" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A22,B:B,B22)/COUNTIFS(B:B,B22,A:A,A22),0)</f>
+        <v>71</v>
+      </c>
+      <c r="L22" s="25" t="n">
+        <f aca="false">K22/SUMIF(A:A,A22,K:K)</f>
+        <v>0.0383783783783784</v>
+      </c>
+      <c r="M22" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A22,J:J)*L22,0)</f>
+        <v>138</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B23" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>76</v>
@@ -8243,16 +8579,28 @@
         <f aca="false">ROUND(I23*SUMIF(A:A,A23,D:D),0)</f>
         <v>92</v>
       </c>
+      <c r="K23" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A23,B:B,B23)/COUNTIFS(B:B,B23,A:A,A23),0)</f>
+        <v>92</v>
+      </c>
+      <c r="L23" s="25" t="n">
+        <f aca="false">K23/SUMIF(A:A,A23,K:K)</f>
+        <v>0.0497297297297297</v>
+      </c>
+      <c r="M23" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A23,J:J)*L23,0)</f>
+        <v>179</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>489</v>
@@ -8277,16 +8625,28 @@
         <f aca="false">ROUND(I24*SUMIF(A:A,A24,D:D),0)</f>
         <v>356</v>
       </c>
+      <c r="K24" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A24,B:B,B24)/COUNTIFS(B:B,B24,A:A,A24),0)</f>
+        <v>356</v>
+      </c>
+      <c r="L24" s="25" t="n">
+        <f aca="false">K24/SUMIF(A:A,A24,K:K)</f>
+        <v>0.328716528162512</v>
+      </c>
+      <c r="M24" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A24,J:J)*L24,0)</f>
+        <v>356</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B25" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>344</v>
@@ -8311,16 +8671,28 @@
         <f aca="false">ROUND(I25*SUMIF(A:A,A25,D:D),0)</f>
         <v>536</v>
       </c>
+      <c r="K25" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A25,B:B,B25)/COUNTIFS(B:B,B25,A:A,A25),0)</f>
+        <v>536</v>
+      </c>
+      <c r="L25" s="25" t="n">
+        <f aca="false">K25/SUMIF(A:A,A25,K:K)</f>
+        <v>0.494921514312096</v>
+      </c>
+      <c r="M25" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A25,J:J)*L25,0)</f>
+        <v>536</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B26" s="27" t="s">
         <v>216</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D26" s="1" t="n">
         <v>212</v>
@@ -8345,16 +8717,28 @@
         <f aca="false">ROUND(I26*SUMIF(A:A,A26,D:D),0)</f>
         <v>93</v>
       </c>
+      <c r="K26" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A26,B:B,B26)/COUNTIFS(B:B,B26,A:A,A26),0)</f>
+        <v>93</v>
+      </c>
+      <c r="L26" s="25" t="n">
+        <f aca="false">K26/SUMIF(A:A,A26,K:K)</f>
+        <v>0.0858725761772853</v>
+      </c>
+      <c r="M26" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A26,J:J)*L26,0)</f>
+        <v>93</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B27" s="30" t="s">
         <v>219</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>37</v>
@@ -8379,13 +8763,25 @@
         <f aca="false">ROUND(I27*SUMIF(A:A,A27,D:D),0)</f>
         <v>98</v>
       </c>
+      <c r="K27" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A27,B:B,B27)/COUNTIFS(B:B,B27,A:A,A27),0)</f>
+        <v>98</v>
+      </c>
+      <c r="L27" s="25" t="n">
+        <f aca="false">K27/SUMIF(A:A,A27,K:K)</f>
+        <v>0.0904893813481071</v>
+      </c>
+      <c r="M27" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A27,J:J)*L27,0)</f>
+        <v>98</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>47</v>
@@ -8413,16 +8809,28 @@
         <f aca="false">ROUND(I28*SUMIF(A:A,A28,D:D),0)</f>
         <v>1079</v>
       </c>
+      <c r="K28" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A28,B:B,B28)/COUNTIFS(B:B,B28,A:A,A28),0)</f>
+        <v>343</v>
+      </c>
+      <c r="L28" s="25" t="n">
+        <f aca="false">K28/SUMIF(A:A,A28,K:K)</f>
+        <v>0.0753514938488576</v>
+      </c>
+      <c r="M28" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A28,J:J)*L28,0)</f>
+        <v>647</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D29" s="1" t="n">
         <v>1634</v>
@@ -8447,16 +8855,28 @@
         <f aca="false">ROUND(I29*SUMIF(A:A,A29,D:D),0)</f>
         <v>1021</v>
       </c>
+      <c r="K29" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A29,B:B,B29)/COUNTIFS(B:B,B29,A:A,A29),0)</f>
+        <v>343</v>
+      </c>
+      <c r="L29" s="25" t="n">
+        <f aca="false">K29/SUMIF(A:A,A29,K:K)</f>
+        <v>0.0753514938488576</v>
+      </c>
+      <c r="M29" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A29,J:J)*L29,0)</f>
+        <v>647</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D30" s="1" t="n">
         <v>1577</v>
@@ -8481,16 +8901,28 @@
         <f aca="false">ROUND(I30*SUMIF(A:A,A30,D:D),0)</f>
         <v>986</v>
       </c>
+      <c r="K30" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A30,B:B,B30)/COUNTIFS(B:B,B30,A:A,A30),0)</f>
+        <v>343</v>
+      </c>
+      <c r="L30" s="25" t="n">
+        <f aca="false">K30/SUMIF(A:A,A30,K:K)</f>
+        <v>0.0753514938488576</v>
+      </c>
+      <c r="M30" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A30,J:J)*L30,0)</f>
+        <v>647</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D31" s="1" t="n">
         <v>1028</v>
@@ -8515,16 +8947,28 @@
         <f aca="false">ROUND(I31*SUMIF(A:A,A31,D:D),0)</f>
         <v>1063</v>
       </c>
+      <c r="K31" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A31,B:B,B31)/COUNTIFS(B:B,B31,A:A,A31),0)</f>
+        <v>331</v>
+      </c>
+      <c r="L31" s="25" t="n">
+        <f aca="false">K31/SUMIF(A:A,A31,K:K)</f>
+        <v>0.0727152899824253</v>
+      </c>
+      <c r="M31" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A31,J:J)*L31,0)</f>
+        <v>625</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B32" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D32" s="1" t="n">
         <v>951</v>
@@ -8549,16 +8993,28 @@
         <f aca="false">ROUND(I32*SUMIF(A:A,A32,D:D),0)</f>
         <v>983</v>
       </c>
+      <c r="K32" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A32,B:B,B32)/COUNTIFS(B:B,B32,A:A,A32),0)</f>
+        <v>331</v>
+      </c>
+      <c r="L32" s="25" t="n">
+        <f aca="false">K32/SUMIF(A:A,A32,K:K)</f>
+        <v>0.0727152899824253</v>
+      </c>
+      <c r="M32" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A32,J:J)*L32,0)</f>
+        <v>625</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D33" s="1" t="n">
         <v>901</v>
@@ -8583,10 +9039,22 @@
         <f aca="false">ROUND(I33*SUMIF(A:A,A33,D:D),0)</f>
         <v>931</v>
       </c>
+      <c r="K33" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A33,B:B,B33)/COUNTIFS(B:B,B33,A:A,A33),0)</f>
+        <v>331</v>
+      </c>
+      <c r="L33" s="25" t="n">
+        <f aca="false">K33/SUMIF(A:A,A33,K:K)</f>
+        <v>0.0727152899824253</v>
+      </c>
+      <c r="M33" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A33,J:J)*L33,0)</f>
+        <v>625</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B34" s="30" t="s">
         <v>219</v>
@@ -8617,10 +9085,22 @@
         <f aca="false">ROUND(I34*SUMIF(A:A,A34,D:D),0)</f>
         <v>1979</v>
       </c>
+      <c r="K34" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A34,B:B,B34)/COUNTIFS(B:B,B34,A:A,A34),0)</f>
+        <v>1979</v>
+      </c>
+      <c r="L34" s="25" t="n">
+        <f aca="false">K34/SUMIF(A:A,A34,K:K)</f>
+        <v>0.4347539543058</v>
+      </c>
+      <c r="M34" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A34,J:J)*L34,0)</f>
+        <v>3736</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B35" s="27" t="s">
         <v>19</v>
@@ -8651,16 +9131,28 @@
         <f aca="false">ROUND(I35*SUMIF(A:A,A35,D:D),0)</f>
         <v>551</v>
       </c>
+      <c r="K35" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A35,B:B,B35)/COUNTIFS(B:B,B35,A:A,A35),0)</f>
+        <v>551</v>
+      </c>
+      <c r="L35" s="25" t="n">
+        <f aca="false">K35/SUMIF(A:A,A35,K:K)</f>
+        <v>0.121045694200352</v>
+      </c>
+      <c r="M35" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A35,J:J)*L35,0)</f>
+        <v>1040</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B36" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D36" s="1" t="n">
         <v>1419</v>
@@ -8685,16 +9177,28 @@
         <f aca="false">ROUND(I36*SUMIF(A:A,A36,D:D),0)</f>
         <v>925</v>
       </c>
+      <c r="K36" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A36,B:B,B36)/COUNTIFS(B:B,B36,A:A,A36),0)</f>
+        <v>298</v>
+      </c>
+      <c r="L36" s="25" t="n">
+        <f aca="false">K36/SUMIF(A:A,A36,K:K)</f>
+        <v>0.0901118838826731</v>
+      </c>
+      <c r="M36" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A36,J:J)*L36,0)</f>
+        <v>548</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D37" s="1" t="n">
         <v>1355</v>
@@ -8719,16 +9223,28 @@
         <f aca="false">ROUND(I37*SUMIF(A:A,A37,D:D),0)</f>
         <v>883</v>
       </c>
+      <c r="K37" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A37,B:B,B37)/COUNTIFS(B:B,B37,A:A,A37),0)</f>
+        <v>298</v>
+      </c>
+      <c r="L37" s="25" t="n">
+        <f aca="false">K37/SUMIF(A:A,A37,K:K)</f>
+        <v>0.0901118838826731</v>
+      </c>
+      <c r="M37" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A37,J:J)*L37,0)</f>
+        <v>548</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D38" s="1" t="n">
         <v>1339</v>
@@ -8753,13 +9269,25 @@
         <f aca="false">ROUND(I38*SUMIF(A:A,A38,D:D),0)</f>
         <v>873</v>
       </c>
+      <c r="K38" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A38,B:B,B38)/COUNTIFS(B:B,B38,A:A,A38),0)</f>
+        <v>298</v>
+      </c>
+      <c r="L38" s="25" t="n">
+        <f aca="false">K38/SUMIF(A:A,A38,K:K)</f>
+        <v>0.0901118838826731</v>
+      </c>
+      <c r="M38" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A38,J:J)*L38,0)</f>
+        <v>548</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>58</v>
@@ -8787,16 +9315,28 @@
         <f aca="false">ROUND(I39*SUMIF(A:A,A39,D:D),0)</f>
         <v>571</v>
       </c>
+      <c r="K39" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A39,B:B,B39)/COUNTIFS(B:B,B39,A:A,A39),0)</f>
+        <v>165</v>
+      </c>
+      <c r="L39" s="25" t="n">
+        <f aca="false">K39/SUMIF(A:A,A39,K:K)</f>
+        <v>0.0498941638947687</v>
+      </c>
+      <c r="M39" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A39,J:J)*L39,0)</f>
+        <v>304</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B40" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D40" s="1" t="n">
         <v>439</v>
@@ -8821,16 +9361,28 @@
         <f aca="false">ROUND(I40*SUMIF(A:A,A40,D:D),0)</f>
         <v>473</v>
       </c>
+      <c r="K40" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A40,B:B,B40)/COUNTIFS(B:B,B40,A:A,A40),0)</f>
+        <v>165</v>
+      </c>
+      <c r="L40" s="25" t="n">
+        <f aca="false">K40/SUMIF(A:A,A40,K:K)</f>
+        <v>0.0498941638947687</v>
+      </c>
+      <c r="M40" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A40,J:J)*L40,0)</f>
+        <v>304</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D41" s="1" t="n">
         <v>410</v>
@@ -8855,10 +9407,22 @@
         <f aca="false">ROUND(I41*SUMIF(A:A,A41,D:D),0)</f>
         <v>442</v>
       </c>
+      <c r="K41" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A41,B:B,B41)/COUNTIFS(B:B,B41,A:A,A41),0)</f>
+        <v>165</v>
+      </c>
+      <c r="L41" s="25" t="n">
+        <f aca="false">K41/SUMIF(A:A,A41,K:K)</f>
+        <v>0.0498941638947687</v>
+      </c>
+      <c r="M41" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A41,J:J)*L41,0)</f>
+        <v>304</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B42" s="30" t="s">
         <v>219</v>
@@ -8889,16 +9453,28 @@
         <f aca="false">ROUND(I42*SUMIF(A:A,A42,D:D),0)</f>
         <v>1332</v>
       </c>
+      <c r="K42" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A42,B:B,B42)/COUNTIFS(B:B,B42,A:A,A42),0)</f>
+        <v>1332</v>
+      </c>
+      <c r="L42" s="25" t="n">
+        <f aca="false">K42/SUMIF(A:A,A42,K:K)</f>
+        <v>0.402781977623224</v>
+      </c>
+      <c r="M42" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A42,J:J)*L42,0)</f>
+        <v>2451</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B43" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D43" s="1" t="n">
         <v>254</v>
@@ -8923,16 +9499,28 @@
         <f aca="false">ROUND(I43*SUMIF(A:A,A43,D:D),0)</f>
         <v>586</v>
       </c>
+      <c r="K43" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A43,B:B,B43)/COUNTIFS(B:B,B43,A:A,A43),0)</f>
+        <v>586</v>
+      </c>
+      <c r="L43" s="25" t="n">
+        <f aca="false">K43/SUMIF(A:A,A43,K:K)</f>
+        <v>0.177199879044451</v>
+      </c>
+      <c r="M43" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A43,J:J)*L43,0)</f>
+        <v>1078</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B44" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D44" s="1" t="n">
         <v>1617</v>
@@ -8955,18 +9543,30 @@
       </c>
       <c r="J44" s="29" t="n">
         <f aca="false">ROUND(I44*SUMIF(A:A,A44,D:D),0)</f>
-        <v>752</v>
+        <v>587</v>
+      </c>
+      <c r="K44" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A44,B:B,B44)/COUNTIFS(B:B,B44,A:A,A44),0)</f>
+        <v>187</v>
+      </c>
+      <c r="L44" s="25" t="n">
+        <f aca="false">K44/SUMIF(A:A,A44,K:K)</f>
+        <v>0.0908649173955296</v>
+      </c>
+      <c r="M44" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A44,J:J)*L44,0)</f>
+        <v>338</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D45" s="1" t="n">
         <v>1531</v>
@@ -8989,18 +9589,30 @@
       </c>
       <c r="J45" s="29" t="n">
         <f aca="false">ROUND(I45*SUMIF(A:A,A45,D:D),0)</f>
-        <v>712</v>
+        <v>555</v>
+      </c>
+      <c r="K45" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A45,B:B,B45)/COUNTIFS(B:B,B45,A:A,A45),0)</f>
+        <v>187</v>
+      </c>
+      <c r="L45" s="25" t="n">
+        <f aca="false">K45/SUMIF(A:A,A45,K:K)</f>
+        <v>0.0908649173955296</v>
+      </c>
+      <c r="M45" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A45,J:J)*L45,0)</f>
+        <v>338</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B46" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D46" s="1" t="n">
         <v>1491</v>
@@ -9023,15 +9635,27 @@
       </c>
       <c r="J46" s="29" t="n">
         <f aca="false">ROUND(I46*SUMIF(A:A,A46,D:D),0)</f>
-        <v>694</v>
+        <v>541</v>
+      </c>
+      <c r="K46" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A46,B:B,B46)/COUNTIFS(B:B,B46,A:A,A46),0)</f>
+        <v>187</v>
+      </c>
+      <c r="L46" s="25" t="n">
+        <f aca="false">K46/SUMIF(A:A,A46,K:K)</f>
+        <v>0.0908649173955296</v>
+      </c>
+      <c r="M46" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A46,J:J)*L46,0)</f>
+        <v>338</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>67</v>
@@ -9057,18 +9681,30 @@
       </c>
       <c r="J47" s="29" t="n">
         <f aca="false">ROUND(I47*SUMIF(A:A,A47,D:D),0)</f>
-        <v>392</v>
+        <v>305</v>
+      </c>
+      <c r="K47" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A47,B:B,B47)/COUNTIFS(B:B,B47,A:A,A47),0)</f>
+        <v>90</v>
+      </c>
+      <c r="L47" s="25" t="n">
+        <f aca="false">K47/SUMIF(A:A,A47,K:K)</f>
+        <v>0.043731778425656</v>
+      </c>
+      <c r="M47" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A47,J:J)*L47,0)</f>
+        <v>163</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B48" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D48" s="1" t="n">
         <v>471</v>
@@ -9091,18 +9727,30 @@
       </c>
       <c r="J48" s="29" t="n">
         <f aca="false">ROUND(I48*SUMIF(A:A,A48,D:D),0)</f>
-        <v>362</v>
+        <v>283</v>
+      </c>
+      <c r="K48" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A48,B:B,B48)/COUNTIFS(B:B,B48,A:A,A48),0)</f>
+        <v>90</v>
+      </c>
+      <c r="L48" s="25" t="n">
+        <f aca="false">K48/SUMIF(A:A,A48,K:K)</f>
+        <v>0.043731778425656</v>
+      </c>
+      <c r="M48" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A48,J:J)*L48,0)</f>
+        <v>163</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B49" s="30" t="s">
         <v>219</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D49" s="1" t="n">
         <v>373</v>
@@ -9125,15 +9773,27 @@
       </c>
       <c r="J49" s="29" t="n">
         <f aca="false">ROUND(I49*SUMIF(A:A,A49,D:D),0)</f>
-        <v>1043</v>
+        <v>813</v>
+      </c>
+      <c r="K49" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A49,B:B,B49)/COUNTIFS(B:B,B49,A:A,A49),0)</f>
+        <v>813</v>
+      </c>
+      <c r="L49" s="25" t="n">
+        <f aca="false">K49/SUMIF(A:A,A49,K:K)</f>
+        <v>0.395043731778426</v>
+      </c>
+      <c r="M49" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A49,J:J)*L49,0)</f>
+        <v>1470</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B50" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>69</v>
@@ -9159,18 +9819,30 @@
       </c>
       <c r="J50" s="29" t="n">
         <f aca="false">ROUND(I50*SUMIF(A:A,A50,D:D),0)</f>
-        <v>287</v>
+        <v>224</v>
+      </c>
+      <c r="K50" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A50,B:B,B50)/COUNTIFS(B:B,B50,A:A,A50),0)</f>
+        <v>90</v>
+      </c>
+      <c r="L50" s="25" t="n">
+        <f aca="false">K50/SUMIF(A:A,A50,K:K)</f>
+        <v>0.043731778425656</v>
+      </c>
+      <c r="M50" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A50,J:J)*L50,0)</f>
+        <v>163</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B51" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D51" s="1" t="n">
         <v>322</v>
@@ -9193,18 +9865,30 @@
       </c>
       <c r="J51" s="29" t="n">
         <f aca="false">ROUND(I51*SUMIF(A:A,A51,D:D),0)</f>
-        <v>531</v>
+        <v>414</v>
+      </c>
+      <c r="K51" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A51,B:B,B51)/COUNTIFS(B:B,B51,A:A,A51),0)</f>
+        <v>414</v>
+      </c>
+      <c r="L51" s="25" t="n">
+        <f aca="false">K51/SUMIF(A:A,A51,K:K)</f>
+        <v>0.201166180758017</v>
+      </c>
+      <c r="M51" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A51,J:J)*L51,0)</f>
+        <v>749</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B52" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D52" s="1" t="n">
         <v>1709</v>
@@ -9229,16 +9913,28 @@
         <f aca="false">ROUND(I52*SUMIF(A:A,A52,D:D),0)</f>
         <v>1540</v>
       </c>
+      <c r="K52" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A52,B:B,B52)/COUNTIFS(B:B,B52,A:A,A52),0)</f>
+        <v>749</v>
+      </c>
+      <c r="L52" s="25" t="n">
+        <f aca="false">K52/SUMIF(A:A,A52,K:K)</f>
+        <v>0.237025316455696</v>
+      </c>
+      <c r="M52" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A52,J:J)*L52,0)</f>
+        <v>1172</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D53" s="1" t="n">
         <v>1617</v>
@@ -9263,16 +9959,28 @@
         <f aca="false">ROUND(I53*SUMIF(A:A,A53,D:D),0)</f>
         <v>1457</v>
       </c>
+      <c r="K53" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A53,B:B,B53)/COUNTIFS(B:B,B53,A:A,A53),0)</f>
+        <v>749</v>
+      </c>
+      <c r="L53" s="25" t="n">
+        <f aca="false">K53/SUMIF(A:A,A53,K:K)</f>
+        <v>0.237025316455696</v>
+      </c>
+      <c r="M53" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A53,J:J)*L53,0)</f>
+        <v>1172</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B54" s="27" t="s">
         <v>216</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D54" s="1" t="n">
         <v>603</v>
@@ -9297,16 +10005,28 @@
         <f aca="false">ROUND(I54*SUMIF(A:A,A54,D:D),0)</f>
         <v>329</v>
       </c>
+      <c r="K54" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A54,B:B,B54)/COUNTIFS(B:B,B54,A:A,A54),0)</f>
+        <v>144</v>
+      </c>
+      <c r="L54" s="25" t="n">
+        <f aca="false">K54/SUMIF(A:A,A54,K:K)</f>
+        <v>0.0455696202531646</v>
+      </c>
+      <c r="M54" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A54,J:J)*L54,0)</f>
+        <v>225</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B55" s="27" t="s">
         <v>216</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D55" s="1" t="n">
         <v>450</v>
@@ -9331,16 +10051,28 @@
         <f aca="false">ROUND(I55*SUMIF(A:A,A55,D:D),0)</f>
         <v>245</v>
       </c>
+      <c r="K55" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A55,B:B,B55)/COUNTIFS(B:B,B55,A:A,A55),0)</f>
+        <v>144</v>
+      </c>
+      <c r="L55" s="25" t="n">
+        <f aca="false">K55/SUMIF(A:A,A55,K:K)</f>
+        <v>0.0455696202531646</v>
+      </c>
+      <c r="M55" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A55,J:J)*L55,0)</f>
+        <v>225</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B56" s="30" t="s">
         <v>219</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D56" s="1" t="n">
         <v>237</v>
@@ -9365,16 +10097,28 @@
         <f aca="false">ROUND(I56*SUMIF(A:A,A56,D:D),0)</f>
         <v>776</v>
       </c>
+      <c r="K56" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A56,B:B,B56)/COUNTIFS(B:B,B56,A:A,A56),0)</f>
+        <v>776</v>
+      </c>
+      <c r="L56" s="25" t="n">
+        <f aca="false">K56/SUMIF(A:A,A56,K:K)</f>
+        <v>0.245569620253165</v>
+      </c>
+      <c r="M56" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A56,J:J)*L56,0)</f>
+        <v>1214</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B57" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D57" s="1" t="n">
         <v>222</v>
@@ -9399,16 +10143,28 @@
         <f aca="false">ROUND(I57*SUMIF(A:A,A57,D:D),0)</f>
         <v>428</v>
       </c>
+      <c r="K57" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A57,B:B,B57)/COUNTIFS(B:B,B57,A:A,A57),0)</f>
+        <v>428</v>
+      </c>
+      <c r="L57" s="25" t="n">
+        <f aca="false">K57/SUMIF(A:A,A57,K:K)</f>
+        <v>0.135443037974684</v>
+      </c>
+      <c r="M57" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A57,J:J)*L57,0)</f>
+        <v>670</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B58" s="27" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D58" s="1" t="n">
         <v>58</v>
@@ -9433,16 +10189,28 @@
         <f aca="false">ROUND(I58*SUMIF(A:A,A58,D:D),0)</f>
         <v>91</v>
       </c>
+      <c r="K58" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A58,B:B,B58)/COUNTIFS(B:B,B58,A:A,A58),0)</f>
+        <v>91</v>
+      </c>
+      <c r="L58" s="25" t="n">
+        <f aca="false">K58/SUMIF(A:A,A58,K:K)</f>
+        <v>0.0287974683544304</v>
+      </c>
+      <c r="M58" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A58,J:J)*L58,0)</f>
+        <v>142</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D59" s="1" t="n">
         <v>50</v>
@@ -9467,16 +10235,28 @@
         <f aca="false">ROUND(I59*SUMIF(A:A,A59,D:D),0)</f>
         <v>79</v>
       </c>
+      <c r="K59" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A59,B:B,B59)/COUNTIFS(B:B,B59,A:A,A59),0)</f>
+        <v>79</v>
+      </c>
+      <c r="L59" s="25" t="n">
+        <f aca="false">K59/SUMIF(A:A,A59,K:K)</f>
+        <v>0.025</v>
+      </c>
+      <c r="M59" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A59,J:J)*L59,0)</f>
+        <v>124</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B60" s="27" t="s">
         <v>23</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D60" s="1" t="n">
         <v>2388</v>
@@ -9501,16 +10281,28 @@
         <f aca="false">ROUND(I60*SUMIF(A:A,A60,D:D),0)</f>
         <v>2604</v>
       </c>
+      <c r="K60" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A60,B:B,B60)/COUNTIFS(B:B,B60,A:A,A60),0)</f>
+        <v>836</v>
+      </c>
+      <c r="L60" s="25" t="n">
+        <f aca="false">K60/SUMIF(A:A,A60,K:K)</f>
+        <v>0.228415300546448</v>
+      </c>
+      <c r="M60" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A60,J:J)*L60,0)</f>
+        <v>2161</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B61" s="27" t="s">
         <v>23</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D61" s="1" t="n">
         <v>2279</v>
@@ -9535,16 +10327,28 @@
         <f aca="false">ROUND(I61*SUMIF(A:A,A61,D:D),0)</f>
         <v>2486</v>
       </c>
+      <c r="K61" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A61,B:B,B61)/COUNTIFS(B:B,B61,A:A,A61),0)</f>
+        <v>836</v>
+      </c>
+      <c r="L61" s="25" t="n">
+        <f aca="false">K61/SUMIF(A:A,A61,K:K)</f>
+        <v>0.228415300546448</v>
+      </c>
+      <c r="M61" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A61,J:J)*L61,0)</f>
+        <v>2161</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B62" s="27" t="s">
         <v>23</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D62" s="1" t="n">
         <v>2230</v>
@@ -9569,16 +10373,28 @@
         <f aca="false">ROUND(I62*SUMIF(A:A,A62,D:D),0)</f>
         <v>2432</v>
       </c>
+      <c r="K62" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A62,B:B,B62)/COUNTIFS(B:B,B62,A:A,A62),0)</f>
+        <v>836</v>
+      </c>
+      <c r="L62" s="25" t="n">
+        <f aca="false">K62/SUMIF(A:A,A62,K:K)</f>
+        <v>0.228415300546448</v>
+      </c>
+      <c r="M62" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A62,J:J)*L62,0)</f>
+        <v>2161</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B63" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D63" s="1" t="n">
         <v>465</v>
@@ -9603,16 +10419,28 @@
         <f aca="false">ROUND(I63*SUMIF(A:A,A63,D:D),0)</f>
         <v>290</v>
       </c>
+      <c r="K63" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A63,B:B,B63)/COUNTIFS(B:B,B63,A:A,A63),0)</f>
+        <v>90</v>
+      </c>
+      <c r="L63" s="25" t="n">
+        <f aca="false">K63/SUMIF(A:A,A63,K:K)</f>
+        <v>0.0245901639344262</v>
+      </c>
+      <c r="M63" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A63,J:J)*L63,0)</f>
+        <v>233</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B64" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D64" s="1" t="n">
         <v>427</v>
@@ -9637,13 +10465,25 @@
         <f aca="false">ROUND(I64*SUMIF(A:A,A64,D:D),0)</f>
         <v>266</v>
       </c>
+      <c r="K64" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A64,B:B,B64)/COUNTIFS(B:B,B64,A:A,A64),0)</f>
+        <v>90</v>
+      </c>
+      <c r="L64" s="25" t="n">
+        <f aca="false">K64/SUMIF(A:A,A64,K:K)</f>
+        <v>0.0245901639344262</v>
+      </c>
+      <c r="M64" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A64,J:J)*L64,0)</f>
+        <v>233</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B65" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>87</v>
@@ -9671,10 +10511,22 @@
         <f aca="false">ROUND(I65*SUMIF(A:A,A65,D:D),0)</f>
         <v>255</v>
       </c>
+      <c r="K65" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A65,B:B,B65)/COUNTIFS(B:B,B65,A:A,A65),0)</f>
+        <v>90</v>
+      </c>
+      <c r="L65" s="25" t="n">
+        <f aca="false">K65/SUMIF(A:A,A65,K:K)</f>
+        <v>0.0245901639344262</v>
+      </c>
+      <c r="M65" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A65,J:J)*L65,0)</f>
+        <v>233</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B66" s="27" t="s">
         <v>216</v>
@@ -9705,16 +10557,28 @@
         <f aca="false">ROUND(I66*SUMIF(A:A,A66,D:D),0)</f>
         <v>135</v>
       </c>
+      <c r="K66" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A66,B:B,B66)/COUNTIFS(B:B,B66,A:A,A66),0)</f>
+        <v>41</v>
+      </c>
+      <c r="L66" s="25" t="n">
+        <f aca="false">K66/SUMIF(A:A,A66,K:K)</f>
+        <v>0.0112021857923497</v>
+      </c>
+      <c r="M66" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A66,J:J)*L66,0)</f>
+        <v>106</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B67" s="27" t="s">
         <v>216</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D67" s="1" t="n">
         <v>336</v>
@@ -9739,16 +10603,28 @@
         <f aca="false">ROUND(I67*SUMIF(A:A,A67,D:D),0)</f>
         <v>127</v>
       </c>
+      <c r="K67" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A67,B:B,B67)/COUNTIFS(B:B,B67,A:A,A67),0)</f>
+        <v>41</v>
+      </c>
+      <c r="L67" s="25" t="n">
+        <f aca="false">K67/SUMIF(A:A,A67,K:K)</f>
+        <v>0.0112021857923497</v>
+      </c>
+      <c r="M67" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A67,J:J)*L67,0)</f>
+        <v>106</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B68" s="27" t="s">
         <v>216</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D68" s="1" t="n">
         <v>286</v>
@@ -9773,16 +10649,28 @@
         <f aca="false">ROUND(I68*SUMIF(A:A,A68,D:D),0)</f>
         <v>108</v>
       </c>
+      <c r="K68" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A68,B:B,B68)/COUNTIFS(B:B,B68,A:A,A68),0)</f>
+        <v>41</v>
+      </c>
+      <c r="L68" s="25" t="n">
+        <f aca="false">K68/SUMIF(A:A,A68,K:K)</f>
+        <v>0.0112021857923497</v>
+      </c>
+      <c r="M68" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A68,J:J)*L68,0)</f>
+        <v>106</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B69" s="30" t="s">
         <v>219</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D69" s="1" t="n">
         <v>140</v>
@@ -9807,16 +10695,28 @@
         <f aca="false">ROUND(I69*SUMIF(A:A,A69,D:D),0)</f>
         <v>317</v>
       </c>
+      <c r="K69" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A69,B:B,B69)/COUNTIFS(B:B,B69,A:A,A69),0)</f>
+        <v>317</v>
+      </c>
+      <c r="L69" s="25" t="n">
+        <f aca="false">K69/SUMIF(A:A,A69,K:K)</f>
+        <v>0.0866120218579235</v>
+      </c>
+      <c r="M69" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A69,J:J)*L69,0)</f>
+        <v>820</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B70" s="27" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D70" s="1" t="n">
         <v>94</v>
@@ -9841,16 +10741,28 @@
         <f aca="false">ROUND(I70*SUMIF(A:A,A70,D:D),0)</f>
         <v>374</v>
       </c>
+      <c r="K70" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A70,B:B,B70)/COUNTIFS(B:B,B70,A:A,A70),0)</f>
+        <v>374</v>
+      </c>
+      <c r="L70" s="25" t="n">
+        <f aca="false">K70/SUMIF(A:A,A70,K:K)</f>
+        <v>0.102185792349727</v>
+      </c>
+      <c r="M70" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A70,J:J)*L70,0)</f>
+        <v>967</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B71" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D71" s="1" t="n">
         <v>51</v>
@@ -9875,16 +10787,28 @@
         <f aca="false">ROUND(I71*SUMIF(A:A,A71,D:D),0)</f>
         <v>68</v>
       </c>
+      <c r="K71" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A71,B:B,B71)/COUNTIFS(B:B,B71,A:A,A71),0)</f>
+        <v>68</v>
+      </c>
+      <c r="L71" s="25" t="n">
+        <f aca="false">K71/SUMIF(A:A,A71,K:K)</f>
+        <v>0.0185792349726776</v>
+      </c>
+      <c r="M71" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A71,J:J)*L71,0)</f>
+        <v>176</v>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B72" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D72" s="1" t="n">
         <v>1752</v>
@@ -9909,16 +10833,28 @@
         <f aca="false">ROUND(I72*SUMIF(A:A,A72,D:D),0)</f>
         <v>1708</v>
       </c>
+      <c r="K72" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A72,B:B,B72)/COUNTIFS(B:B,B72,A:A,A72),0)</f>
+        <v>552</v>
+      </c>
+      <c r="L72" s="25" t="n">
+        <f aca="false">K72/SUMIF(A:A,A72,K:K)</f>
+        <v>0.140816326530612</v>
+      </c>
+      <c r="M72" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A72,J:J)*L72,0)</f>
+        <v>1158</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B73" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D73" s="1" t="n">
         <v>1728</v>
@@ -9943,16 +10879,28 @@
         <f aca="false">ROUND(I73*SUMIF(A:A,A73,D:D),0)</f>
         <v>1685</v>
       </c>
+      <c r="K73" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A73,B:B,B73)/COUNTIFS(B:B,B73,A:A,A73),0)</f>
+        <v>552</v>
+      </c>
+      <c r="L73" s="25" t="n">
+        <f aca="false">K73/SUMIF(A:A,A73,K:K)</f>
+        <v>0.140816326530612</v>
+      </c>
+      <c r="M73" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A73,J:J)*L73,0)</f>
+        <v>1158</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B74" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D74" s="1" t="n">
         <v>1618</v>
@@ -9977,16 +10925,28 @@
         <f aca="false">ROUND(I74*SUMIF(A:A,A74,D:D),0)</f>
         <v>1578</v>
       </c>
+      <c r="K74" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A74,B:B,B74)/COUNTIFS(B:B,B74,A:A,A74),0)</f>
+        <v>552</v>
+      </c>
+      <c r="L74" s="25" t="n">
+        <f aca="false">K74/SUMIF(A:A,A74,K:K)</f>
+        <v>0.140816326530612</v>
+      </c>
+      <c r="M74" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A74,J:J)*L74,0)</f>
+        <v>1158</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B75" s="27" t="s">
         <v>216</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D75" s="1" t="n">
         <v>917</v>
@@ -10011,16 +10971,28 @@
         <f aca="false">ROUND(I75*SUMIF(A:A,A75,D:D),0)</f>
         <v>541</v>
       </c>
+      <c r="K75" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A75,B:B,B75)/COUNTIFS(B:B,B75,A:A,A75),0)</f>
+        <v>165</v>
+      </c>
+      <c r="L75" s="25" t="n">
+        <f aca="false">K75/SUMIF(A:A,A75,K:K)</f>
+        <v>0.0420918367346939</v>
+      </c>
+      <c r="M75" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A75,J:J)*L75,0)</f>
+        <v>346</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B76" s="27" t="s">
         <v>216</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="D76" s="1" t="n">
         <v>817</v>
@@ -10045,16 +11017,28 @@
         <f aca="false">ROUND(I76*SUMIF(A:A,A76,D:D),0)</f>
         <v>482</v>
       </c>
+      <c r="K76" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A76,B:B,B76)/COUNTIFS(B:B,B76,A:A,A76),0)</f>
+        <v>165</v>
+      </c>
+      <c r="L76" s="25" t="n">
+        <f aca="false">K76/SUMIF(A:A,A76,K:K)</f>
+        <v>0.0420918367346939</v>
+      </c>
+      <c r="M76" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A76,J:J)*L76,0)</f>
+        <v>346</v>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B77" s="27" t="s">
         <v>216</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D77" s="1" t="n">
         <v>777</v>
@@ -10079,16 +11063,28 @@
         <f aca="false">ROUND(I77*SUMIF(A:A,A77,D:D),0)</f>
         <v>458</v>
       </c>
+      <c r="K77" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A77,B:B,B77)/COUNTIFS(B:B,B77,A:A,A77),0)</f>
+        <v>165</v>
+      </c>
+      <c r="L77" s="25" t="n">
+        <f aca="false">K77/SUMIF(A:A,A77,K:K)</f>
+        <v>0.0420918367346939</v>
+      </c>
+      <c r="M77" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A77,J:J)*L77,0)</f>
+        <v>346</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B78" s="30" t="s">
         <v>219</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D78" s="1" t="n">
         <v>339</v>
@@ -10113,16 +11109,28 @@
         <f aca="false">ROUND(I78*SUMIF(A:A,A78,D:D),0)</f>
         <v>1201</v>
       </c>
+      <c r="K78" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A78,B:B,B78)/COUNTIFS(B:B,B78,A:A,A78),0)</f>
+        <v>1201</v>
+      </c>
+      <c r="L78" s="25" t="n">
+        <f aca="false">K78/SUMIF(A:A,A78,K:K)</f>
+        <v>0.306377551020408</v>
+      </c>
+      <c r="M78" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A78,J:J)*L78,0)</f>
+        <v>2519</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B79" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D79" s="1" t="n">
         <v>272</v>
@@ -10147,16 +11155,28 @@
         <f aca="false">ROUND(I79*SUMIF(A:A,A79,D:D),0)</f>
         <v>568</v>
       </c>
+      <c r="K79" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A79,B:B,B79)/COUNTIFS(B:B,B79,A:A,A79),0)</f>
+        <v>568</v>
+      </c>
+      <c r="L79" s="25" t="n">
+        <f aca="false">K79/SUMIF(A:A,A79,K:K)</f>
+        <v>0.144897959183673</v>
+      </c>
+      <c r="M79" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A79,J:J)*L79,0)</f>
+        <v>1191</v>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B80" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D80" s="1" t="n">
         <v>796</v>
@@ -10181,16 +11201,28 @@
         <f aca="false">ROUND(I80*SUMIF(A:A,A80,D:D),0)</f>
         <v>481</v>
       </c>
+      <c r="K80" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A80,B:B,B80)/COUNTIFS(B:B,B80,A:A,A80),0)</f>
+        <v>234</v>
+      </c>
+      <c r="L80" s="25" t="n">
+        <f aca="false">K80/SUMIF(A:A,A80,K:K)</f>
+        <v>0.122065727699531</v>
+      </c>
+      <c r="M80" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A80,J:J)*L80,0)</f>
+        <v>355</v>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B81" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D81" s="1" t="n">
         <v>751</v>
@@ -10215,16 +11247,28 @@
         <f aca="false">ROUND(I81*SUMIF(A:A,A81,D:D),0)</f>
         <v>454</v>
       </c>
+      <c r="K81" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A81,B:B,B81)/COUNTIFS(B:B,B81,A:A,A81),0)</f>
+        <v>234</v>
+      </c>
+      <c r="L81" s="25" t="n">
+        <f aca="false">K81/SUMIF(A:A,A81,K:K)</f>
+        <v>0.122065727699531</v>
+      </c>
+      <c r="M81" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A81,J:J)*L81,0)</f>
+        <v>355</v>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B82" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D82" s="1" t="n">
         <v>541</v>
@@ -10249,16 +11293,28 @@
         <f aca="false">ROUND(I82*SUMIF(A:A,A82,D:D),0)</f>
         <v>541</v>
       </c>
+      <c r="K82" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A82,B:B,B82)/COUNTIFS(B:B,B82,A:A,A82),0)</f>
+        <v>263</v>
+      </c>
+      <c r="L82" s="25" t="n">
+        <f aca="false">K82/SUMIF(A:A,A82,K:K)</f>
+        <v>0.137193531559729</v>
+      </c>
+      <c r="M82" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A82,J:J)*L82,0)</f>
+        <v>399</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B83" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D83" s="1" t="n">
         <v>510</v>
@@ -10283,16 +11339,28 @@
         <f aca="false">ROUND(I83*SUMIF(A:A,A83,D:D),0)</f>
         <v>510</v>
       </c>
+      <c r="K83" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A83,B:B,B83)/COUNTIFS(B:B,B83,A:A,A83),0)</f>
+        <v>263</v>
+      </c>
+      <c r="L83" s="25" t="n">
+        <f aca="false">K83/SUMIF(A:A,A83,K:K)</f>
+        <v>0.137193531559729</v>
+      </c>
+      <c r="M83" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A83,J:J)*L83,0)</f>
+        <v>399</v>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B84" s="30" t="s">
         <v>219</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D84" s="1" t="n">
         <v>174</v>
@@ -10317,16 +11385,28 @@
         <f aca="false">ROUND(I84*SUMIF(A:A,A84,D:D),0)</f>
         <v>632</v>
       </c>
+      <c r="K84" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A84,B:B,B84)/COUNTIFS(B:B,B84,A:A,A84),0)</f>
+        <v>632</v>
+      </c>
+      <c r="L84" s="25" t="n">
+        <f aca="false">K84/SUMIF(A:A,A84,K:K)</f>
+        <v>0.329681794470527</v>
+      </c>
+      <c r="M84" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A84,J:J)*L84,0)</f>
+        <v>959</v>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B85" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D85" s="1" t="n">
         <v>136</v>
@@ -10351,16 +11431,28 @@
         <f aca="false">ROUND(I85*SUMIF(A:A,A85,D:D),0)</f>
         <v>291</v>
       </c>
+      <c r="K85" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A85,B:B,B85)/COUNTIFS(B:B,B85,A:A,A85),0)</f>
+        <v>291</v>
+      </c>
+      <c r="L85" s="25" t="n">
+        <f aca="false">K85/SUMIF(A:A,A85,K:K)</f>
+        <v>0.151799687010955</v>
+      </c>
+      <c r="M85" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A85,J:J)*L85,0)</f>
+        <v>442</v>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B86" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D86" s="1" t="n">
         <v>938</v>
@@ -10385,16 +11477,28 @@
         <f aca="false">ROUND(I86*SUMIF(A:A,A86,D:D),0)</f>
         <v>885</v>
       </c>
+      <c r="K86" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A86,B:B,B86)/COUNTIFS(B:B,B86,A:A,A86),0)</f>
+        <v>441</v>
+      </c>
+      <c r="L86" s="25" t="n">
+        <f aca="false">K86/SUMIF(A:A,A86,K:K)</f>
+        <v>0.230769230769231</v>
+      </c>
+      <c r="M86" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A86,J:J)*L86,0)</f>
+        <v>705</v>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B87" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D87" s="1" t="n">
         <v>933</v>
@@ -10419,16 +11523,28 @@
         <f aca="false">ROUND(I87*SUMIF(A:A,A87,D:D),0)</f>
         <v>880</v>
       </c>
+      <c r="K87" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A87,B:B,B87)/COUNTIFS(B:B,B87,A:A,A87),0)</f>
+        <v>441</v>
+      </c>
+      <c r="L87" s="25" t="n">
+        <f aca="false">K87/SUMIF(A:A,A87,K:K)</f>
+        <v>0.230769230769231</v>
+      </c>
+      <c r="M87" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A87,J:J)*L87,0)</f>
+        <v>705</v>
+      </c>
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B88" s="27" t="s">
         <v>216</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D88" s="1" t="n">
         <v>486</v>
@@ -10453,16 +11569,28 @@
         <f aca="false">ROUND(I88*SUMIF(A:A,A88,D:D),0)</f>
         <v>277</v>
       </c>
+      <c r="K88" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A88,B:B,B88)/COUNTIFS(B:B,B88,A:A,A88),0)</f>
+        <v>130</v>
+      </c>
+      <c r="L88" s="25" t="n">
+        <f aca="false">K88/SUMIF(A:A,A88,K:K)</f>
+        <v>0.0680272108843538</v>
+      </c>
+      <c r="M88" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A88,J:J)*L88,0)</f>
+        <v>208</v>
+      </c>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B89" s="27" t="s">
         <v>216</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D89" s="1" t="n">
         <v>425</v>
@@ -10487,16 +11615,28 @@
         <f aca="false">ROUND(I89*SUMIF(A:A,A89,D:D),0)</f>
         <v>242</v>
       </c>
+      <c r="K89" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A89,B:B,B89)/COUNTIFS(B:B,B89,A:A,A89),0)</f>
+        <v>130</v>
+      </c>
+      <c r="L89" s="25" t="n">
+        <f aca="false">K89/SUMIF(A:A,A89,K:K)</f>
+        <v>0.0680272108843538</v>
+      </c>
+      <c r="M89" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A89,J:J)*L89,0)</f>
+        <v>208</v>
+      </c>
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B90" s="30" t="s">
         <v>219</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D90" s="1" t="n">
         <v>156</v>
@@ -10521,16 +11661,28 @@
         <f aca="false">ROUND(I90*SUMIF(A:A,A90,D:D),0)</f>
         <v>535</v>
       </c>
+      <c r="K90" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A90,B:B,B90)/COUNTIFS(B:B,B90,A:A,A90),0)</f>
+        <v>535</v>
+      </c>
+      <c r="L90" s="25" t="n">
+        <f aca="false">K90/SUMIF(A:A,A90,K:K)</f>
+        <v>0.279958137100994</v>
+      </c>
+      <c r="M90" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A90,J:J)*L90,0)</f>
+        <v>855</v>
+      </c>
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B91" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D91" s="1" t="n">
         <v>116</v>
@@ -10555,16 +11707,28 @@
         <f aca="false">ROUND(I91*SUMIF(A:A,A91,D:D),0)</f>
         <v>234</v>
       </c>
+      <c r="K91" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A91,B:B,B91)/COUNTIFS(B:B,B91,A:A,A91),0)</f>
+        <v>234</v>
+      </c>
+      <c r="L91" s="25" t="n">
+        <f aca="false">K91/SUMIF(A:A,A91,K:K)</f>
+        <v>0.122448979591837</v>
+      </c>
+      <c r="M91" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A91,J:J)*L91,0)</f>
+        <v>374</v>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B92" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D92" s="1" t="n">
         <v>1210</v>
@@ -10589,16 +11753,28 @@
         <f aca="false">ROUND(I92*SUMIF(A:A,A92,D:D),0)</f>
         <v>1010</v>
       </c>
+      <c r="K92" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A92,B:B,B92)/COUNTIFS(B:B,B92,A:A,A92),0)</f>
+        <v>322</v>
+      </c>
+      <c r="L92" s="25" t="n">
+        <f aca="false">K92/SUMIF(A:A,A92,K:K)</f>
+        <v>0.0888766215843224</v>
+      </c>
+      <c r="M92" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A92,J:J)*L92,0)</f>
+        <v>728</v>
+      </c>
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B93" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D93" s="1" t="n">
         <v>1138</v>
@@ -10623,16 +11799,28 @@
         <f aca="false">ROUND(I93*SUMIF(A:A,A93,D:D),0)</f>
         <v>950</v>
       </c>
+      <c r="K93" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A93,B:B,B93)/COUNTIFS(B:B,B93,A:A,A93),0)</f>
+        <v>322</v>
+      </c>
+      <c r="L93" s="25" t="n">
+        <f aca="false">K93/SUMIF(A:A,A93,K:K)</f>
+        <v>0.0888766215843224</v>
+      </c>
+      <c r="M93" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A93,J:J)*L93,0)</f>
+        <v>728</v>
+      </c>
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B94" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D94" s="1" t="n">
         <v>1124</v>
@@ -10657,16 +11845,28 @@
         <f aca="false">ROUND(I94*SUMIF(A:A,A94,D:D),0)</f>
         <v>938</v>
       </c>
+      <c r="K94" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A94,B:B,B94)/COUNTIFS(B:B,B94,A:A,A94),0)</f>
+        <v>322</v>
+      </c>
+      <c r="L94" s="25" t="n">
+        <f aca="false">K94/SUMIF(A:A,A94,K:K)</f>
+        <v>0.0888766215843224</v>
+      </c>
+      <c r="M94" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A94,J:J)*L94,0)</f>
+        <v>728</v>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B95" s="27" t="s">
         <v>216</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="D95" s="1" t="n">
         <v>1025</v>
@@ -10691,16 +11891,28 @@
         <f aca="false">ROUND(I95*SUMIF(A:A,A95,D:D),0)</f>
         <v>517</v>
       </c>
+      <c r="K95" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A95,B:B,B95)/COUNTIFS(B:B,B95,A:A,A95),0)</f>
+        <v>161</v>
+      </c>
+      <c r="L95" s="25" t="n">
+        <f aca="false">K95/SUMIF(A:A,A95,K:K)</f>
+        <v>0.0444383107921612</v>
+      </c>
+      <c r="M95" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A95,J:J)*L95,0)</f>
+        <v>364</v>
+      </c>
     </row>
     <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B96" s="27" t="s">
         <v>216</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D96" s="1" t="n">
         <v>946</v>
@@ -10725,16 +11937,28 @@
         <f aca="false">ROUND(I96*SUMIF(A:A,A96,D:D),0)</f>
         <v>477</v>
       </c>
+      <c r="K96" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A96,B:B,B96)/COUNTIFS(B:B,B96,A:A,A96),0)</f>
+        <v>161</v>
+      </c>
+      <c r="L96" s="25" t="n">
+        <f aca="false">K96/SUMIF(A:A,A96,K:K)</f>
+        <v>0.0444383107921612</v>
+      </c>
+      <c r="M96" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A96,J:J)*L96,0)</f>
+        <v>364</v>
+      </c>
     </row>
     <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B97" s="27" t="s">
         <v>216</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D97" s="1" t="n">
         <v>907</v>
@@ -10759,16 +11983,28 @@
         <f aca="false">ROUND(I97*SUMIF(A:A,A97,D:D),0)</f>
         <v>458</v>
       </c>
+      <c r="K97" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A97,B:B,B97)/COUNTIFS(B:B,B97,A:A,A97),0)</f>
+        <v>161</v>
+      </c>
+      <c r="L97" s="25" t="n">
+        <f aca="false">K97/SUMIF(A:A,A97,K:K)</f>
+        <v>0.0444383107921612</v>
+      </c>
+      <c r="M97" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A97,J:J)*L97,0)</f>
+        <v>364</v>
+      </c>
     </row>
     <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B98" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D98" s="1" t="n">
         <v>675</v>
@@ -10793,16 +12029,28 @@
         <f aca="false">ROUND(I98*SUMIF(A:A,A98,D:D),0)</f>
         <v>1206</v>
       </c>
+      <c r="K98" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A98,B:B,B98)/COUNTIFS(B:B,B98,A:A,A98),0)</f>
+        <v>278</v>
+      </c>
+      <c r="L98" s="25" t="n">
+        <f aca="false">K98/SUMIF(A:A,A98,K:K)</f>
+        <v>0.0767319900634833</v>
+      </c>
+      <c r="M98" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A98,J:J)*L98,0)</f>
+        <v>629</v>
+      </c>
     </row>
     <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B99" s="30" t="s">
         <v>219</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D99" s="1" t="n">
         <v>442</v>
@@ -10827,16 +12075,28 @@
         <f aca="false">ROUND(I99*SUMIF(A:A,A99,D:D),0)</f>
         <v>1340</v>
       </c>
+      <c r="K99" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A99,B:B,B99)/COUNTIFS(B:B,B99,A:A,A99),0)</f>
+        <v>1340</v>
+      </c>
+      <c r="L99" s="25" t="n">
+        <f aca="false">K99/SUMIF(A:A,A99,K:K)</f>
+        <v>0.369859232680099</v>
+      </c>
+      <c r="M99" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A99,J:J)*L99,0)</f>
+        <v>3030</v>
+      </c>
     </row>
     <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B100" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D100" s="1" t="n">
         <v>402</v>
@@ -10861,16 +12121,28 @@
         <f aca="false">ROUND(I100*SUMIF(A:A,A100,D:D),0)</f>
         <v>718</v>
       </c>
+      <c r="K100" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A100,B:B,B100)/COUNTIFS(B:B,B100,A:A,A100),0)</f>
+        <v>278</v>
+      </c>
+      <c r="L100" s="25" t="n">
+        <f aca="false">K100/SUMIF(A:A,A100,K:K)</f>
+        <v>0.0767319900634833</v>
+      </c>
+      <c r="M100" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A100,J:J)*L100,0)</f>
+        <v>629</v>
+      </c>
     </row>
     <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B101" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D101" s="1" t="n">
         <v>323</v>
@@ -10895,16 +12167,28 @@
         <f aca="false">ROUND(I101*SUMIF(A:A,A101,D:D),0)</f>
         <v>577</v>
       </c>
+      <c r="K101" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A101,B:B,B101)/COUNTIFS(B:B,B101,A:A,A101),0)</f>
+        <v>278</v>
+      </c>
+      <c r="L101" s="25" t="n">
+        <f aca="false">K101/SUMIF(A:A,A101,K:K)</f>
+        <v>0.0767319900634833</v>
+      </c>
+      <c r="M101" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A101,J:J)*L101,0)</f>
+        <v>629</v>
+      </c>
     </row>
     <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B102" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D102" s="1" t="n">
         <v>1455</v>
@@ -10929,16 +12213,28 @@
         <f aca="false">ROUND(I102*SUMIF(A:A,A102,D:D),0)</f>
         <v>1344</v>
       </c>
+      <c r="K102" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A102,B:B,B102)/COUNTIFS(B:B,B102,A:A,A102),0)</f>
+        <v>445</v>
+      </c>
+      <c r="L102" s="25" t="n">
+        <f aca="false">K102/SUMIF(A:A,A102,K:K)</f>
+        <v>0.106714628297362</v>
+      </c>
+      <c r="M102" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A102,J:J)*L102,0)</f>
+        <v>829</v>
+      </c>
     </row>
     <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B103" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D103" s="1" t="n">
         <v>1448</v>
@@ -10963,16 +12259,28 @@
         <f aca="false">ROUND(I103*SUMIF(A:A,A103,D:D),0)</f>
         <v>1337</v>
       </c>
+      <c r="K103" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A103,B:B,B103)/COUNTIFS(B:B,B103,A:A,A103),0)</f>
+        <v>445</v>
+      </c>
+      <c r="L103" s="25" t="n">
+        <f aca="false">K103/SUMIF(A:A,A103,K:K)</f>
+        <v>0.106714628297362</v>
+      </c>
+      <c r="M103" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A103,J:J)*L103,0)</f>
+        <v>829</v>
+      </c>
     </row>
     <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B104" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="D104" s="1" t="n">
         <v>1430</v>
@@ -10997,16 +12305,28 @@
         <f aca="false">ROUND(I104*SUMIF(A:A,A104,D:D),0)</f>
         <v>1321</v>
       </c>
+      <c r="K104" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A104,B:B,B104)/COUNTIFS(B:B,B104,A:A,A104),0)</f>
+        <v>445</v>
+      </c>
+      <c r="L104" s="25" t="n">
+        <f aca="false">K104/SUMIF(A:A,A104,K:K)</f>
+        <v>0.106714628297362</v>
+      </c>
+      <c r="M104" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A104,J:J)*L104,0)</f>
+        <v>829</v>
+      </c>
     </row>
     <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B105" s="27" t="s">
         <v>216</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D105" s="1" t="n">
         <v>920</v>
@@ -11031,16 +12351,28 @@
         <f aca="false">ROUND(I105*SUMIF(A:A,A105,D:D),0)</f>
         <v>514</v>
       </c>
+      <c r="K105" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A105,B:B,B105)/COUNTIFS(B:B,B105,A:A,A105),0)</f>
+        <v>156</v>
+      </c>
+      <c r="L105" s="25" t="n">
+        <f aca="false">K105/SUMIF(A:A,A105,K:K)</f>
+        <v>0.037410071942446</v>
+      </c>
+      <c r="M105" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A105,J:J)*L105,0)</f>
+        <v>291</v>
+      </c>
     </row>
     <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B106" s="27" t="s">
         <v>216</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D106" s="1" t="n">
         <v>835</v>
@@ -11065,16 +12397,28 @@
         <f aca="false">ROUND(I106*SUMIF(A:A,A106,D:D),0)</f>
         <v>466</v>
       </c>
+      <c r="K106" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A106,B:B,B106)/COUNTIFS(B:B,B106,A:A,A106),0)</f>
+        <v>156</v>
+      </c>
+      <c r="L106" s="25" t="n">
+        <f aca="false">K106/SUMIF(A:A,A106,K:K)</f>
+        <v>0.037410071942446</v>
+      </c>
+      <c r="M106" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A106,J:J)*L106,0)</f>
+        <v>291</v>
+      </c>
     </row>
     <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B107" s="27" t="s">
         <v>216</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D107" s="1" t="n">
         <v>759</v>
@@ -11099,16 +12443,28 @@
         <f aca="false">ROUND(I107*SUMIF(A:A,A107,D:D),0)</f>
         <v>424</v>
       </c>
+      <c r="K107" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A107,B:B,B107)/COUNTIFS(B:B,B107,A:A,A107),0)</f>
+        <v>156</v>
+      </c>
+      <c r="L107" s="25" t="n">
+        <f aca="false">K107/SUMIF(A:A,A107,K:K)</f>
+        <v>0.037410071942446</v>
+      </c>
+      <c r="M107" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A107,J:J)*L107,0)</f>
+        <v>291</v>
+      </c>
     </row>
     <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B108" s="30" t="s">
         <v>219</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="D108" s="1" t="n">
         <v>431</v>
@@ -11133,16 +12489,28 @@
         <f aca="false">ROUND(I108*SUMIF(A:A,A108,D:D),0)</f>
         <v>1446</v>
       </c>
+      <c r="K108" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A108,B:B,B108)/COUNTIFS(B:B,B108,A:A,A108),0)</f>
+        <v>1446</v>
+      </c>
+      <c r="L108" s="25" t="n">
+        <f aca="false">K108/SUMIF(A:A,A108,K:K)</f>
+        <v>0.346762589928058</v>
+      </c>
+      <c r="M108" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A108,J:J)*L108,0)</f>
+        <v>2695</v>
+      </c>
     </row>
     <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B109" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D109" s="1" t="n">
         <v>337</v>
@@ -11167,16 +12535,28 @@
         <f aca="false">ROUND(I109*SUMIF(A:A,A109,D:D),0)</f>
         <v>666</v>
       </c>
+      <c r="K109" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A109,B:B,B109)/COUNTIFS(B:B,B109,A:A,A109),0)</f>
+        <v>666</v>
+      </c>
+      <c r="L109" s="25" t="n">
+        <f aca="false">K109/SUMIF(A:A,A109,K:K)</f>
+        <v>0.159712230215827</v>
+      </c>
+      <c r="M109" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A109,J:J)*L109,0)</f>
+        <v>1241</v>
+      </c>
     </row>
     <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B110" s="27" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D110" s="1" t="n">
         <v>158</v>
@@ -11201,16 +12581,28 @@
         <f aca="false">ROUND(I110*SUMIF(A:A,A110,D:D),0)</f>
         <v>255</v>
       </c>
+      <c r="K110" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A110,B:B,B110)/COUNTIFS(B:B,B110,A:A,A110),0)</f>
+        <v>255</v>
+      </c>
+      <c r="L110" s="25" t="n">
+        <f aca="false">K110/SUMIF(A:A,A110,K:K)</f>
+        <v>0.0611510791366907</v>
+      </c>
+      <c r="M110" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A110,J:J)*L110,0)</f>
+        <v>475</v>
+      </c>
     </row>
     <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B111" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D111" s="1" t="n">
         <v>1177</v>
@@ -11235,16 +12627,28 @@
         <f aca="false">ROUND(I111*SUMIF(A:A,A111,D:D),0)</f>
         <v>967</v>
       </c>
+      <c r="K111" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A111,B:B,B111)/COUNTIFS(B:B,B111,A:A,A111),0)</f>
+        <v>453</v>
+      </c>
+      <c r="L111" s="25" t="n">
+        <f aca="false">K111/SUMIF(A:A,A111,K:K)</f>
+        <v>0.154134059203811</v>
+      </c>
+      <c r="M111" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A111,J:J)*L111,0)</f>
+        <v>676</v>
+      </c>
     </row>
     <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B112" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D112" s="1" t="n">
         <v>1027</v>
@@ -11269,16 +12673,28 @@
         <f aca="false">ROUND(I112*SUMIF(A:A,A112,D:D),0)</f>
         <v>844</v>
       </c>
+      <c r="K112" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A112,B:B,B112)/COUNTIFS(B:B,B112,A:A,A112),0)</f>
+        <v>453</v>
+      </c>
+      <c r="L112" s="25" t="n">
+        <f aca="false">K112/SUMIF(A:A,A112,K:K)</f>
+        <v>0.154134059203811</v>
+      </c>
+      <c r="M112" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A112,J:J)*L112,0)</f>
+        <v>676</v>
+      </c>
     </row>
     <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B113" s="27" t="s">
         <v>216</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D113" s="1" t="n">
         <v>750</v>
@@ -11303,16 +12719,28 @@
         <f aca="false">ROUND(I113*SUMIF(A:A,A113,D:D),0)</f>
         <v>373</v>
       </c>
+      <c r="K113" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A113,B:B,B113)/COUNTIFS(B:B,B113,A:A,A113),0)</f>
+        <v>155</v>
+      </c>
+      <c r="L113" s="25" t="n">
+        <f aca="false">K113/SUMIF(A:A,A113,K:K)</f>
+        <v>0.0527390268798911</v>
+      </c>
+      <c r="M113" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A113,J:J)*L113,0)</f>
+        <v>231</v>
+      </c>
     </row>
     <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B114" s="27" t="s">
         <v>216</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D114" s="1" t="n">
         <v>498</v>
@@ -11337,16 +12765,28 @@
         <f aca="false">ROUND(I114*SUMIF(A:A,A114,D:D),0)</f>
         <v>247</v>
       </c>
+      <c r="K114" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A114,B:B,B114)/COUNTIFS(B:B,B114,A:A,A114),0)</f>
+        <v>155</v>
+      </c>
+      <c r="L114" s="25" t="n">
+        <f aca="false">K114/SUMIF(A:A,A114,K:K)</f>
+        <v>0.0527390268798911</v>
+      </c>
+      <c r="M114" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A114,J:J)*L114,0)</f>
+        <v>231</v>
+      </c>
     </row>
     <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B115" s="30" t="s">
         <v>219</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D115" s="1" t="n">
         <v>341</v>
@@ -11371,16 +12811,28 @@
         <f aca="false">ROUND(I115*SUMIF(A:A,A115,D:D),0)</f>
         <v>1018</v>
       </c>
+      <c r="K115" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A115,B:B,B115)/COUNTIFS(B:B,B115,A:A,A115),0)</f>
+        <v>1018</v>
+      </c>
+      <c r="L115" s="25" t="n">
+        <f aca="false">K115/SUMIF(A:A,A115,K:K)</f>
+        <v>0.346376318475672</v>
+      </c>
+      <c r="M115" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A115,J:J)*L115,0)</f>
+        <v>1519</v>
+      </c>
     </row>
     <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B116" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D116" s="1" t="n">
         <v>269</v>
@@ -11405,16 +12857,28 @@
         <f aca="false">ROUND(I116*SUMIF(A:A,A116,D:D),0)</f>
         <v>473</v>
       </c>
+      <c r="K116" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A116,B:B,B116)/COUNTIFS(B:B,B116,A:A,A116),0)</f>
+        <v>473</v>
+      </c>
+      <c r="L116" s="25" t="n">
+        <f aca="false">K116/SUMIF(A:A,A116,K:K)</f>
+        <v>0.160939094930248</v>
+      </c>
+      <c r="M116" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A116,J:J)*L116,0)</f>
+        <v>706</v>
+      </c>
     </row>
     <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B117" s="27" t="s">
         <v>23</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D117" s="1" t="n">
         <v>226</v>
@@ -11439,16 +12903,28 @@
         <f aca="false">ROUND(I117*SUMIF(A:A,A117,D:D),0)</f>
         <v>325</v>
       </c>
+      <c r="K117" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A117,B:B,B117)/COUNTIFS(B:B,B117,A:A,A117),0)</f>
+        <v>116</v>
+      </c>
+      <c r="L117" s="25" t="n">
+        <f aca="false">K117/SUMIF(A:A,A117,K:K)</f>
+        <v>0.0394692072133379</v>
+      </c>
+      <c r="M117" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A117,J:J)*L117,0)</f>
+        <v>173</v>
+      </c>
     </row>
     <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B118" s="27" t="s">
         <v>23</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="D118" s="1" t="n">
         <v>96</v>
@@ -11473,16 +12949,28 @@
         <f aca="false">ROUND(I118*SUMIF(A:A,A118,D:D),0)</f>
         <v>138</v>
       </c>
+      <c r="K118" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A118,B:B,B118)/COUNTIFS(B:B,B118,A:A,A118),0)</f>
+        <v>116</v>
+      </c>
+      <c r="L118" s="25" t="n">
+        <f aca="false">K118/SUMIF(A:A,A118,K:K)</f>
+        <v>0.0394692072133379</v>
+      </c>
+      <c r="M118" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A118,J:J)*L118,0)</f>
+        <v>173</v>
+      </c>
     </row>
     <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B119" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D119" s="1" t="n">
         <v>1658</v>
@@ -11505,18 +12993,30 @@
       </c>
       <c r="J119" s="29" t="n">
         <f aca="false">ROUND(I119*SUMIF(A:A,A119,D:D),0)</f>
-        <v>578</v>
+        <v>357</v>
+      </c>
+      <c r="K119" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A119,B:B,B119)/COUNTIFS(B:B,B119,A:A,A119),0)</f>
+        <v>108</v>
+      </c>
+      <c r="L119" s="25" t="n">
+        <f aca="false">K119/SUMIF(A:A,A119,K:K)</f>
+        <v>0.0884520884520885</v>
+      </c>
+      <c r="M119" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A119,J:J)*L119,0)</f>
+        <v>212</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B120" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C120" s="31" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D120" s="1" t="n">
         <v>1517</v>
@@ -11539,18 +13039,30 @@
       </c>
       <c r="J120" s="29" t="n">
         <f aca="false">ROUND(I120*SUMIF(A:A,A120,D:D),0)</f>
-        <v>529</v>
+        <v>327</v>
+      </c>
+      <c r="K120" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A120,B:B,B120)/COUNTIFS(B:B,B120,A:A,A120),0)</f>
+        <v>108</v>
+      </c>
+      <c r="L120" s="25" t="n">
+        <f aca="false">K120/SUMIF(A:A,A120,K:K)</f>
+        <v>0.0884520884520885</v>
+      </c>
+      <c r="M120" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A120,J:J)*L120,0)</f>
+        <v>212</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B121" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C121" s="32" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="D121" s="1" t="n">
         <v>1347</v>
@@ -11573,18 +13085,30 @@
       </c>
       <c r="J121" s="29" t="n">
         <f aca="false">ROUND(I121*SUMIF(A:A,A121,D:D),0)</f>
-        <v>470</v>
+        <v>290</v>
+      </c>
+      <c r="K121" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A121,B:B,B121)/COUNTIFS(B:B,B121,A:A,A121),0)</f>
+        <v>108</v>
+      </c>
+      <c r="L121" s="25" t="n">
+        <f aca="false">K121/SUMIF(A:A,A121,K:K)</f>
+        <v>0.0884520884520885</v>
+      </c>
+      <c r="M121" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A121,J:J)*L121,0)</f>
+        <v>212</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B122" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="D122" s="1" t="n">
         <v>784</v>
@@ -11607,18 +13131,30 @@
       </c>
       <c r="J122" s="29" t="n">
         <f aca="false">ROUND(I122*SUMIF(A:A,A122,D:D),0)</f>
-        <v>452</v>
+        <v>279</v>
+      </c>
+      <c r="K122" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A122,B:B,B122)/COUNTIFS(B:B,B122,A:A,A122),0)</f>
+        <v>87</v>
+      </c>
+      <c r="L122" s="25" t="n">
+        <f aca="false">K122/SUMIF(A:A,A122,K:K)</f>
+        <v>0.0712530712530713</v>
+      </c>
+      <c r="M122" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A122,J:J)*L122,0)</f>
+        <v>171</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B123" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D123" s="1" t="n">
         <v>755</v>
@@ -11641,15 +13177,27 @@
       </c>
       <c r="J123" s="29" t="n">
         <f aca="false">ROUND(I123*SUMIF(A:A,A123,D:D),0)</f>
-        <v>435</v>
+        <v>269</v>
+      </c>
+      <c r="K123" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A123,B:B,B123)/COUNTIFS(B:B,B123,A:A,A123),0)</f>
+        <v>87</v>
+      </c>
+      <c r="L123" s="25" t="n">
+        <f aca="false">K123/SUMIF(A:A,A123,K:K)</f>
+        <v>0.0712530712530713</v>
+      </c>
+      <c r="M123" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A123,J:J)*L123,0)</f>
+        <v>171</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B124" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>146</v>
@@ -11675,12 +13223,24 @@
       </c>
       <c r="J124" s="29" t="n">
         <f aca="false">ROUND(I124*SUMIF(A:A,A124,D:D),0)</f>
-        <v>384</v>
+        <v>237</v>
+      </c>
+      <c r="K124" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A124,B:B,B124)/COUNTIFS(B:B,B124,A:A,A124),0)</f>
+        <v>87</v>
+      </c>
+      <c r="L124" s="25" t="n">
+        <f aca="false">K124/SUMIF(A:A,A124,K:K)</f>
+        <v>0.0712530712530713</v>
+      </c>
+      <c r="M124" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A124,J:J)*L124,0)</f>
+        <v>171</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B125" s="30" t="s">
         <v>219</v>
@@ -11709,18 +13269,30 @@
       </c>
       <c r="J125" s="29" t="n">
         <f aca="false">ROUND(I125*SUMIF(A:A,A125,D:D),0)</f>
-        <v>775</v>
+        <v>479</v>
+      </c>
+      <c r="K125" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A125,B:B,B125)/COUNTIFS(B:B,B125,A:A,A125),0)</f>
+        <v>479</v>
+      </c>
+      <c r="L125" s="25" t="n">
+        <f aca="false">K125/SUMIF(A:A,A125,K:K)</f>
+        <v>0.392301392301392</v>
+      </c>
+      <c r="M125" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A125,J:J)*L125,0)</f>
+        <v>940</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B126" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D126" s="1" t="n">
         <v>206</v>
@@ -11743,18 +13315,30 @@
       </c>
       <c r="J126" s="29" t="n">
         <f aca="false">ROUND(I126*SUMIF(A:A,A126,D:D),0)</f>
-        <v>254</v>
+        <v>157</v>
+      </c>
+      <c r="K126" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A126,B:B,B126)/COUNTIFS(B:B,B126,A:A,A126),0)</f>
+        <v>157</v>
+      </c>
+      <c r="L126" s="25" t="n">
+        <f aca="false">K126/SUMIF(A:A,A126,K:K)</f>
+        <v>0.128583128583129</v>
+      </c>
+      <c r="M126" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A126,J:J)*L126,0)</f>
+        <v>308</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B127" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D127" s="1" t="n">
         <v>1807</v>
@@ -11779,16 +13363,28 @@
         <f aca="false">ROUND(I127*SUMIF(A:A,A127,D:D),0)</f>
         <v>1124</v>
       </c>
+      <c r="K127" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A127,B:B,B127)/COUNTIFS(B:B,B127,A:A,A127),0)</f>
+        <v>353</v>
+      </c>
+      <c r="L127" s="25" t="n">
+        <f aca="false">K127/SUMIF(A:A,A127,K:K)</f>
+        <v>0.071967380224261</v>
+      </c>
+      <c r="M127" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A127,J:J)*L127,0)</f>
+        <v>674</v>
+      </c>
     </row>
     <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B128" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="D128" s="1" t="n">
         <v>1670</v>
@@ -11813,16 +13409,28 @@
         <f aca="false">ROUND(I128*SUMIF(A:A,A128,D:D),0)</f>
         <v>1039</v>
       </c>
+      <c r="K128" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A128,B:B,B128)/COUNTIFS(B:B,B128,A:A,A128),0)</f>
+        <v>353</v>
+      </c>
+      <c r="L128" s="25" t="n">
+        <f aca="false">K128/SUMIF(A:A,A128,K:K)</f>
+        <v>0.071967380224261</v>
+      </c>
+      <c r="M128" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A128,J:J)*L128,0)</f>
+        <v>674</v>
+      </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B129" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="D129" s="1" t="n">
         <v>1624</v>
@@ -11847,16 +13455,28 @@
         <f aca="false">ROUND(I129*SUMIF(A:A,A129,D:D),0)</f>
         <v>1010</v>
       </c>
+      <c r="K129" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A129,B:B,B129)/COUNTIFS(B:B,B129,A:A,A129),0)</f>
+        <v>353</v>
+      </c>
+      <c r="L129" s="25" t="n">
+        <f aca="false">K129/SUMIF(A:A,A129,K:K)</f>
+        <v>0.071967380224261</v>
+      </c>
+      <c r="M129" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A129,J:J)*L129,0)</f>
+        <v>674</v>
+      </c>
     </row>
     <row r="130" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B130" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D130" s="1" t="n">
         <v>1336</v>
@@ -11881,16 +13501,28 @@
         <f aca="false">ROUND(I130*SUMIF(A:A,A130,D:D),0)</f>
         <v>1374</v>
       </c>
+      <c r="K130" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A130,B:B,B130)/COUNTIFS(B:B,B130,A:A,A130),0)</f>
+        <v>392</v>
+      </c>
+      <c r="L130" s="25" t="n">
+        <f aca="false">K130/SUMIF(A:A,A130,K:K)</f>
+        <v>0.0799184505606524</v>
+      </c>
+      <c r="M130" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A130,J:J)*L130,0)</f>
+        <v>749</v>
+      </c>
     </row>
     <row r="131" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B131" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D131" s="1" t="n">
         <v>1080</v>
@@ -11915,16 +13547,28 @@
         <f aca="false">ROUND(I131*SUMIF(A:A,A131,D:D),0)</f>
         <v>1111</v>
       </c>
+      <c r="K131" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A131,B:B,B131)/COUNTIFS(B:B,B131,A:A,A131),0)</f>
+        <v>392</v>
+      </c>
+      <c r="L131" s="25" t="n">
+        <f aca="false">K131/SUMIF(A:A,A131,K:K)</f>
+        <v>0.0799184505606524</v>
+      </c>
+      <c r="M131" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A131,J:J)*L131,0)</f>
+        <v>749</v>
+      </c>
     </row>
     <row r="132" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B132" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D132" s="1" t="n">
         <v>1010</v>
@@ -11949,16 +13593,28 @@
         <f aca="false">ROUND(I132*SUMIF(A:A,A132,D:D),0)</f>
         <v>1039</v>
       </c>
+      <c r="K132" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A132,B:B,B132)/COUNTIFS(B:B,B132,A:A,A132),0)</f>
+        <v>392</v>
+      </c>
+      <c r="L132" s="25" t="n">
+        <f aca="false">K132/SUMIF(A:A,A132,K:K)</f>
+        <v>0.0799184505606524</v>
+      </c>
+      <c r="M132" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A132,J:J)*L132,0)</f>
+        <v>749</v>
+      </c>
     </row>
     <row r="133" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B133" s="30" t="s">
         <v>219</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="D133" s="1" t="n">
         <v>536</v>
@@ -11983,16 +13639,28 @@
         <f aca="false">ROUND(I133*SUMIF(A:A,A133,D:D),0)</f>
         <v>2003</v>
       </c>
+      <c r="K133" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A133,B:B,B133)/COUNTIFS(B:B,B133,A:A,A133),0)</f>
+        <v>2003</v>
+      </c>
+      <c r="L133" s="25" t="n">
+        <f aca="false">K133/SUMIF(A:A,A133,K:K)</f>
+        <v>0.408358817533129</v>
+      </c>
+      <c r="M133" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A133,J:J)*L133,0)</f>
+        <v>3825</v>
+      </c>
     </row>
     <row r="134" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B134" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D134" s="1" t="n">
         <v>303</v>
@@ -12017,16 +13685,28 @@
         <f aca="false">ROUND(I134*SUMIF(A:A,A134,D:D),0)</f>
         <v>667</v>
       </c>
+      <c r="K134" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A134,B:B,B134)/COUNTIFS(B:B,B134,A:A,A134),0)</f>
+        <v>667</v>
+      </c>
+      <c r="L134" s="25" t="n">
+        <f aca="false">K134/SUMIF(A:A,A134,K:K)</f>
+        <v>0.135983690112131</v>
+      </c>
+      <c r="M134" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A134,J:J)*L134,0)</f>
+        <v>1274</v>
+      </c>
     </row>
     <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B135" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D135" s="1" t="n">
         <v>479</v>
@@ -12051,16 +13731,28 @@
         <f aca="false">ROUND(I135*SUMIF(A:A,A135,D:D),0)</f>
         <v>348</v>
       </c>
+      <c r="K135" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A135,B:B,B135)/COUNTIFS(B:B,B135,A:A,A135),0)</f>
+        <v>348</v>
+      </c>
+      <c r="L135" s="25" t="n">
+        <f aca="false">K135/SUMIF(A:A,A135,K:K)</f>
+        <v>0.324324324324324</v>
+      </c>
+      <c r="M135" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A135,J:J)*L135,0)</f>
+        <v>348</v>
+      </c>
     </row>
     <row r="136" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B136" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D136" s="1" t="n">
         <v>323</v>
@@ -12085,16 +13777,28 @@
         <f aca="false">ROUND(I136*SUMIF(A:A,A136,D:D),0)</f>
         <v>503</v>
       </c>
+      <c r="K136" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A136,B:B,B136)/COUNTIFS(B:B,B136,A:A,A136),0)</f>
+        <v>503</v>
+      </c>
+      <c r="L136" s="25" t="n">
+        <f aca="false">K136/SUMIF(A:A,A136,K:K)</f>
+        <v>0.468779123951538</v>
+      </c>
+      <c r="M136" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A136,J:J)*L136,0)</f>
+        <v>503</v>
+      </c>
     </row>
     <row r="137" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B137" s="27" t="s">
         <v>216</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="D137" s="1" t="n">
         <v>224</v>
@@ -12119,16 +13823,28 @@
         <f aca="false">ROUND(I137*SUMIF(A:A,A137,D:D),0)</f>
         <v>98</v>
       </c>
+      <c r="K137" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A137,B:B,B137)/COUNTIFS(B:B,B137,A:A,A137),0)</f>
+        <v>98</v>
+      </c>
+      <c r="L137" s="25" t="n">
+        <f aca="false">K137/SUMIF(A:A,A137,K:K)</f>
+        <v>0.0913327120223672</v>
+      </c>
+      <c r="M137" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A137,J:J)*L137,0)</f>
+        <v>98</v>
+      </c>
     </row>
     <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B138" s="30" t="s">
         <v>219</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D138" s="1" t="n">
         <v>47</v>
@@ -12153,16 +13869,28 @@
         <f aca="false">ROUND(I138*SUMIF(A:A,A138,D:D),0)</f>
         <v>124</v>
       </c>
+      <c r="K138" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A138,B:B,B138)/COUNTIFS(B:B,B138,A:A,A138),0)</f>
+        <v>124</v>
+      </c>
+      <c r="L138" s="25" t="n">
+        <f aca="false">K138/SUMIF(A:A,A138,K:K)</f>
+        <v>0.115563839701771</v>
+      </c>
+      <c r="M138" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A138,J:J)*L138,0)</f>
+        <v>124</v>
+      </c>
     </row>
     <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B139" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D139" s="1" t="n">
         <v>1774</v>
@@ -12187,16 +13915,28 @@
         <f aca="false">ROUND(I139*SUMIF(A:A,A139,D:D),0)</f>
         <v>1144</v>
       </c>
+      <c r="K139" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A139,B:B,B139)/COUNTIFS(B:B,B139,A:A,A139),0)</f>
+        <v>373</v>
+      </c>
+      <c r="L139" s="25" t="n">
+        <f aca="false">K139/SUMIF(A:A,A139,K:K)</f>
+        <v>0.0777893639207508</v>
+      </c>
+      <c r="M139" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A139,J:J)*L139,0)</f>
+        <v>733</v>
+      </c>
     </row>
     <row r="140" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B140" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D140" s="1" t="n">
         <v>1758</v>
@@ -12221,16 +13961,28 @@
         <f aca="false">ROUND(I140*SUMIF(A:A,A140,D:D),0)</f>
         <v>1133</v>
       </c>
+      <c r="K140" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A140,B:B,B140)/COUNTIFS(B:B,B140,A:A,A140),0)</f>
+        <v>373</v>
+      </c>
+      <c r="L140" s="25" t="n">
+        <f aca="false">K140/SUMIF(A:A,A140,K:K)</f>
+        <v>0.0777893639207508</v>
+      </c>
+      <c r="M140" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A140,J:J)*L140,0)</f>
+        <v>733</v>
+      </c>
     </row>
     <row r="141" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B141" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D141" s="1" t="n">
         <v>1682</v>
@@ -12255,16 +14007,28 @@
         <f aca="false">ROUND(I141*SUMIF(A:A,A141,D:D),0)</f>
         <v>1084</v>
       </c>
+      <c r="K141" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A141,B:B,B141)/COUNTIFS(B:B,B141,A:A,A141),0)</f>
+        <v>373</v>
+      </c>
+      <c r="L141" s="25" t="n">
+        <f aca="false">K141/SUMIF(A:A,A141,K:K)</f>
+        <v>0.0777893639207508</v>
+      </c>
+      <c r="M141" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A141,J:J)*L141,0)</f>
+        <v>733</v>
+      </c>
     </row>
     <row r="142" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B142" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="D142" s="1" t="n">
         <v>1202</v>
@@ -12289,16 +14053,28 @@
         <f aca="false">ROUND(I142*SUMIF(A:A,A142,D:D),0)</f>
         <v>1282</v>
       </c>
+      <c r="K142" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A142,B:B,B142)/COUNTIFS(B:B,B142,A:A,A142),0)</f>
+        <v>397</v>
+      </c>
+      <c r="L142" s="25" t="n">
+        <f aca="false">K142/SUMIF(A:A,A142,K:K)</f>
+        <v>0.0827945776850886</v>
+      </c>
+      <c r="M142" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A142,J:J)*L142,0)</f>
+        <v>780</v>
+      </c>
     </row>
     <row r="143" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B143" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D143" s="1" t="n">
         <v>1078</v>
@@ -12323,16 +14099,28 @@
         <f aca="false">ROUND(I143*SUMIF(A:A,A143,D:D),0)</f>
         <v>1149</v>
       </c>
+      <c r="K143" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A143,B:B,B143)/COUNTIFS(B:B,B143,A:A,A143),0)</f>
+        <v>397</v>
+      </c>
+      <c r="L143" s="25" t="n">
+        <f aca="false">K143/SUMIF(A:A,A143,K:K)</f>
+        <v>0.0827945776850886</v>
+      </c>
+      <c r="M143" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A143,J:J)*L143,0)</f>
+        <v>780</v>
+      </c>
     </row>
     <row r="144" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B144" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="D144" s="1" t="n">
         <v>1069</v>
@@ -12357,16 +14145,28 @@
         <f aca="false">ROUND(I144*SUMIF(A:A,A144,D:D),0)</f>
         <v>1140</v>
       </c>
+      <c r="K144" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A144,B:B,B144)/COUNTIFS(B:B,B144,A:A,A144),0)</f>
+        <v>397</v>
+      </c>
+      <c r="L144" s="25" t="n">
+        <f aca="false">K144/SUMIF(A:A,A144,K:K)</f>
+        <v>0.0827945776850886</v>
+      </c>
+      <c r="M144" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A144,J:J)*L144,0)</f>
+        <v>780</v>
+      </c>
     </row>
     <row r="145" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B145" s="30" t="s">
         <v>219</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="D145" s="1" t="n">
         <v>393</v>
@@ -12391,16 +14191,28 @@
         <f aca="false">ROUND(I145*SUMIF(A:A,A145,D:D),0)</f>
         <v>1522</v>
       </c>
+      <c r="K145" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A145,B:B,B145)/COUNTIFS(B:B,B145,A:A,A145),0)</f>
+        <v>1522</v>
+      </c>
+      <c r="L145" s="25" t="n">
+        <f aca="false">K145/SUMIF(A:A,A145,K:K)</f>
+        <v>0.317413972888425</v>
+      </c>
+      <c r="M145" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A145,J:J)*L145,0)</f>
+        <v>2989</v>
+      </c>
     </row>
     <row r="146" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B146" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="D146" s="1" t="n">
         <v>245</v>
@@ -12425,16 +14237,28 @@
         <f aca="false">ROUND(I146*SUMIF(A:A,A146,D:D),0)</f>
         <v>559</v>
       </c>
+      <c r="K146" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A146,B:B,B146)/COUNTIFS(B:B,B146,A:A,A146),0)</f>
+        <v>559</v>
+      </c>
+      <c r="L146" s="25" t="n">
+        <f aca="false">K146/SUMIF(A:A,A146,K:K)</f>
+        <v>0.116579770594369</v>
+      </c>
+      <c r="M146" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A146,J:J)*L146,0)</f>
+        <v>1098</v>
+      </c>
     </row>
     <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B147" s="27" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D147" s="1" t="n">
         <v>217</v>
@@ -12459,16 +14283,28 @@
         <f aca="false">ROUND(I147*SUMIF(A:A,A147,D:D),0)</f>
         <v>404</v>
       </c>
+      <c r="K147" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A147,B:B,B147)/COUNTIFS(B:B,B147,A:A,A147),0)</f>
+        <v>404</v>
+      </c>
+      <c r="L147" s="25" t="n">
+        <f aca="false">K147/SUMIF(A:A,A147,K:K)</f>
+        <v>0.0842544316996872</v>
+      </c>
+      <c r="M147" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A147,J:J)*L147,0)</f>
+        <v>793</v>
+      </c>
     </row>
     <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B148" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="D148" s="1" t="n">
         <v>1458</v>
@@ -12493,16 +14329,28 @@
         <f aca="false">ROUND(I148*SUMIF(A:A,A148,D:D),0)</f>
         <v>1297</v>
       </c>
+      <c r="K148" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A148,B:B,B148)/COUNTIFS(B:B,B148,A:A,A148),0)</f>
+        <v>426</v>
+      </c>
+      <c r="L148" s="25" t="n">
+        <f aca="false">K148/SUMIF(A:A,A148,K:K)</f>
+        <v>0.123873218959</v>
+      </c>
+      <c r="M148" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A148,J:J)*L148,0)</f>
+        <v>975</v>
+      </c>
     </row>
     <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B149" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D149" s="1" t="n">
         <v>1446</v>
@@ -12527,16 +14375,28 @@
         <f aca="false">ROUND(I149*SUMIF(A:A,A149,D:D),0)</f>
         <v>1286</v>
       </c>
+      <c r="K149" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A149,B:B,B149)/COUNTIFS(B:B,B149,A:A,A149),0)</f>
+        <v>426</v>
+      </c>
+      <c r="L149" s="25" t="n">
+        <f aca="false">K149/SUMIF(A:A,A149,K:K)</f>
+        <v>0.123873218959</v>
+      </c>
+      <c r="M149" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A149,J:J)*L149,0)</f>
+        <v>975</v>
+      </c>
     </row>
     <row r="150" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B150" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="D150" s="1" t="n">
         <v>1409</v>
@@ -12561,16 +14421,28 @@
         <f aca="false">ROUND(I150*SUMIF(A:A,A150,D:D),0)</f>
         <v>1254</v>
       </c>
+      <c r="K150" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A150,B:B,B150)/COUNTIFS(B:B,B150,A:A,A150),0)</f>
+        <v>426</v>
+      </c>
+      <c r="L150" s="25" t="n">
+        <f aca="false">K150/SUMIF(A:A,A150,K:K)</f>
+        <v>0.123873218959</v>
+      </c>
+      <c r="M150" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A150,J:J)*L150,0)</f>
+        <v>975</v>
+      </c>
     </row>
     <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B151" s="27" t="s">
         <v>216</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D151" s="1" t="n">
         <v>849</v>
@@ -12595,16 +14467,28 @@
         <f aca="false">ROUND(I151*SUMIF(A:A,A151,D:D),0)</f>
         <v>457</v>
       </c>
+      <c r="K151" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A151,B:B,B151)/COUNTIFS(B:B,B151,A:A,A151),0)</f>
+        <v>142</v>
+      </c>
+      <c r="L151" s="25" t="n">
+        <f aca="false">K151/SUMIF(A:A,A151,K:K)</f>
+        <v>0.0412910729863332</v>
+      </c>
+      <c r="M151" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A151,J:J)*L151,0)</f>
+        <v>325</v>
+      </c>
     </row>
     <row r="152" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B152" s="27" t="s">
         <v>216</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="D152" s="1" t="n">
         <v>786</v>
@@ -12629,10 +14513,22 @@
         <f aca="false">ROUND(I152*SUMIF(A:A,A152,D:D),0)</f>
         <v>423</v>
       </c>
+      <c r="K152" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A152,B:B,B152)/COUNTIFS(B:B,B152,A:A,A152),0)</f>
+        <v>142</v>
+      </c>
+      <c r="L152" s="25" t="n">
+        <f aca="false">K152/SUMIF(A:A,A152,K:K)</f>
+        <v>0.0412910729863332</v>
+      </c>
+      <c r="M152" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A152,J:J)*L152,0)</f>
+        <v>325</v>
+      </c>
     </row>
     <row r="153" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B153" s="27" t="s">
         <v>216</v>
@@ -12663,16 +14559,28 @@
         <f aca="false">ROUND(I153*SUMIF(A:A,A153,D:D),0)</f>
         <v>399</v>
       </c>
+      <c r="K153" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A153,B:B,B153)/COUNTIFS(B:B,B153,A:A,A153),0)</f>
+        <v>142</v>
+      </c>
+      <c r="L153" s="25" t="n">
+        <f aca="false">K153/SUMIF(A:A,A153,K:K)</f>
+        <v>0.0412910729863332</v>
+      </c>
+      <c r="M153" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A153,J:J)*L153,0)</f>
+        <v>325</v>
+      </c>
     </row>
     <row r="154" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B154" s="30" t="s">
         <v>219</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D154" s="1" t="n">
         <v>379</v>
@@ -12697,16 +14605,28 @@
         <f aca="false">ROUND(I154*SUMIF(A:A,A154,D:D),0)</f>
         <v>1225</v>
       </c>
+      <c r="K154" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A154,B:B,B154)/COUNTIFS(B:B,B154,A:A,A154),0)</f>
+        <v>1225</v>
+      </c>
+      <c r="L154" s="25" t="n">
+        <f aca="false">K154/SUMIF(A:A,A154,K:K)</f>
+        <v>0.356208200058156</v>
+      </c>
+      <c r="M154" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A154,J:J)*L154,0)</f>
+        <v>2805</v>
+      </c>
     </row>
     <row r="155" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B155" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D155" s="1" t="n">
         <v>304</v>
@@ -12731,16 +14651,28 @@
         <f aca="false">ROUND(I155*SUMIF(A:A,A155,D:D),0)</f>
         <v>579</v>
       </c>
+      <c r="K155" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A155,B:B,B155)/COUNTIFS(B:B,B155,A:A,A155),0)</f>
+        <v>170</v>
+      </c>
+      <c r="L155" s="25" t="n">
+        <f aca="false">K155/SUMIF(A:A,A155,K:K)</f>
+        <v>0.0494329747019482</v>
+      </c>
+      <c r="M155" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A155,J:J)*L155,0)</f>
+        <v>389</v>
+      </c>
     </row>
     <row r="156" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B156" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D156" s="1" t="n">
         <v>282</v>
@@ -12765,16 +14697,28 @@
         <f aca="false">ROUND(I156*SUMIF(A:A,A156,D:D),0)</f>
         <v>537</v>
       </c>
+      <c r="K156" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A156,B:B,B156)/COUNTIFS(B:B,B156,A:A,A156),0)</f>
+        <v>170</v>
+      </c>
+      <c r="L156" s="25" t="n">
+        <f aca="false">K156/SUMIF(A:A,A156,K:K)</f>
+        <v>0.0494329747019482</v>
+      </c>
+      <c r="M156" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A156,J:J)*L156,0)</f>
+        <v>389</v>
+      </c>
     </row>
     <row r="157" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B157" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D157" s="1" t="n">
         <v>219</v>
@@ -12799,16 +14743,28 @@
         <f aca="false">ROUND(I157*SUMIF(A:A,A157,D:D),0)</f>
         <v>417</v>
       </c>
+      <c r="K157" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A157,B:B,B157)/COUNTIFS(B:B,B157,A:A,A157),0)</f>
+        <v>170</v>
+      </c>
+      <c r="L157" s="25" t="n">
+        <f aca="false">K157/SUMIF(A:A,A157,K:K)</f>
+        <v>0.0494329747019482</v>
+      </c>
+      <c r="M157" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A157,J:J)*L157,0)</f>
+        <v>389</v>
+      </c>
     </row>
     <row r="158" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="1" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B158" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="D158" s="1" t="n">
         <v>1338</v>
@@ -12833,16 +14789,28 @@
         <f aca="false">ROUND(I158*SUMIF(A:A,A158,D:D),0)</f>
         <v>873</v>
       </c>
+      <c r="K158" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A158,B:B,B158)/COUNTIFS(B:B,B158,A:A,A158),0)</f>
+        <v>280</v>
+      </c>
+      <c r="L158" s="25" t="n">
+        <f aca="false">K158/SUMIF(A:A,A158,K:K)</f>
+        <v>0.0781686208821887</v>
+      </c>
+      <c r="M158" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A158,J:J)*L158,0)</f>
+        <v>576</v>
+      </c>
     </row>
     <row r="159" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="1" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B159" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D159" s="1" t="n">
         <v>1291</v>
@@ -12867,16 +14835,28 @@
         <f aca="false">ROUND(I159*SUMIF(A:A,A159,D:D),0)</f>
         <v>842</v>
       </c>
+      <c r="K159" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A159,B:B,B159)/COUNTIFS(B:B,B159,A:A,A159),0)</f>
+        <v>280</v>
+      </c>
+      <c r="L159" s="25" t="n">
+        <f aca="false">K159/SUMIF(A:A,A159,K:K)</f>
+        <v>0.0781686208821887</v>
+      </c>
+      <c r="M159" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A159,J:J)*L159,0)</f>
+        <v>576</v>
+      </c>
     </row>
     <row r="160" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B160" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="D160" s="1" t="n">
         <v>1236</v>
@@ -12901,16 +14881,28 @@
         <f aca="false">ROUND(I160*SUMIF(A:A,A160,D:D),0)</f>
         <v>807</v>
       </c>
+      <c r="K160" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A160,B:B,B160)/COUNTIFS(B:B,B160,A:A,A160),0)</f>
+        <v>280</v>
+      </c>
+      <c r="L160" s="25" t="n">
+        <f aca="false">K160/SUMIF(A:A,A160,K:K)</f>
+        <v>0.0781686208821887</v>
+      </c>
+      <c r="M160" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A160,J:J)*L160,0)</f>
+        <v>576</v>
+      </c>
     </row>
     <row r="161" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B161" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="D161" s="1" t="n">
         <v>991</v>
@@ -12935,16 +14927,28 @@
         <f aca="false">ROUND(I161*SUMIF(A:A,A161,D:D),0)</f>
         <v>1069</v>
       </c>
+      <c r="K161" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A161,B:B,B161)/COUNTIFS(B:B,B161,A:A,A161),0)</f>
+        <v>352</v>
+      </c>
+      <c r="L161" s="25" t="n">
+        <f aca="false">K161/SUMIF(A:A,A161,K:K)</f>
+        <v>0.0982691233947515</v>
+      </c>
+      <c r="M161" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A161,J:J)*L161,0)</f>
+        <v>725</v>
+      </c>
     </row>
     <row r="162" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B162" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D162" s="1" t="n">
         <v>972</v>
@@ -12969,16 +14973,28 @@
         <f aca="false">ROUND(I162*SUMIF(A:A,A162,D:D),0)</f>
         <v>1049</v>
       </c>
+      <c r="K162" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A162,B:B,B162)/COUNTIFS(B:B,B162,A:A,A162),0)</f>
+        <v>352</v>
+      </c>
+      <c r="L162" s="25" t="n">
+        <f aca="false">K162/SUMIF(A:A,A162,K:K)</f>
+        <v>0.0982691233947515</v>
+      </c>
+      <c r="M162" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A162,J:J)*L162,0)</f>
+        <v>725</v>
+      </c>
     </row>
     <row r="163" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="1" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B163" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D163" s="1" t="n">
         <v>970</v>
@@ -13003,10 +15019,22 @@
         <f aca="false">ROUND(I163*SUMIF(A:A,A163,D:D),0)</f>
         <v>1047</v>
       </c>
+      <c r="K163" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A163,B:B,B163)/COUNTIFS(B:B,B163,A:A,A163),0)</f>
+        <v>352</v>
+      </c>
+      <c r="L163" s="25" t="n">
+        <f aca="false">K163/SUMIF(A:A,A163,K:K)</f>
+        <v>0.0982691233947515</v>
+      </c>
+      <c r="M163" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A163,J:J)*L163,0)</f>
+        <v>725</v>
+      </c>
     </row>
     <row r="164" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="1" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B164" s="30" t="s">
         <v>219</v>
@@ -13037,16 +15065,28 @@
         <f aca="false">ROUND(I164*SUMIF(A:A,A164,D:D),0)</f>
         <v>1027</v>
       </c>
+      <c r="K164" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A164,B:B,B164)/COUNTIFS(B:B,B164,A:A,A164),0)</f>
+        <v>1027</v>
+      </c>
+      <c r="L164" s="25" t="n">
+        <f aca="false">K164/SUMIF(A:A,A164,K:K)</f>
+        <v>0.286711334450028</v>
+      </c>
+      <c r="M164" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A164,J:J)*L164,0)</f>
+        <v>2114</v>
+      </c>
     </row>
     <row r="165" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="1" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B165" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="D165" s="1" t="n">
         <v>159</v>
@@ -13071,16 +15111,28 @@
         <f aca="false">ROUND(I165*SUMIF(A:A,A165,D:D),0)</f>
         <v>367</v>
       </c>
+      <c r="K165" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A165,B:B,B165)/COUNTIFS(B:B,B165,A:A,A165),0)</f>
+        <v>367</v>
+      </c>
+      <c r="L165" s="25" t="n">
+        <f aca="false">K165/SUMIF(A:A,A165,K:K)</f>
+        <v>0.102456728084869</v>
+      </c>
+      <c r="M165" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A165,J:J)*L165,0)</f>
+        <v>755</v>
+      </c>
     </row>
     <row r="166" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="1" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B166" s="27" t="s">
         <v>23</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D166" s="1" t="n">
         <v>155</v>
@@ -13105,16 +15157,28 @@
         <f aca="false">ROUND(I166*SUMIF(A:A,A166,D:D),0)</f>
         <v>292</v>
       </c>
+      <c r="K166" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A166,B:B,B166)/COUNTIFS(B:B,B166,A:A,A166),0)</f>
+        <v>292</v>
+      </c>
+      <c r="L166" s="25" t="n">
+        <f aca="false">K166/SUMIF(A:A,A166,K:K)</f>
+        <v>0.0815187046342825</v>
+      </c>
+      <c r="M166" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A166,J:J)*L166,0)</f>
+        <v>601</v>
+      </c>
     </row>
     <row r="167" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B167" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D167" s="1" t="n">
         <v>967</v>
@@ -13139,16 +15203,28 @@
         <f aca="false">ROUND(I167*SUMIF(A:A,A167,D:D),0)</f>
         <v>579</v>
       </c>
+      <c r="K167" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A167,B:B,B167)/COUNTIFS(B:B,B167,A:A,A167),0)</f>
+        <v>275</v>
+      </c>
+      <c r="L167" s="25" t="n">
+        <f aca="false">K167/SUMIF(A:A,A167,K:K)</f>
+        <v>0.127373784159333</v>
+      </c>
+      <c r="M167" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A167,J:J)*L167,0)</f>
+        <v>407</v>
+      </c>
     </row>
     <row r="168" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B168" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D168" s="1" t="n">
         <v>869</v>
@@ -13173,13 +15249,25 @@
         <f aca="false">ROUND(I168*SUMIF(A:A,A168,D:D),0)</f>
         <v>520</v>
       </c>
+      <c r="K168" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A168,B:B,B168)/COUNTIFS(B:B,B168,A:A,A168),0)</f>
+        <v>275</v>
+      </c>
+      <c r="L168" s="25" t="n">
+        <f aca="false">K168/SUMIF(A:A,A168,K:K)</f>
+        <v>0.127373784159333</v>
+      </c>
+      <c r="M168" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A168,J:J)*L168,0)</f>
+        <v>407</v>
+      </c>
     </row>
     <row r="169" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B169" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>192</v>
@@ -13207,16 +15295,28 @@
         <f aca="false">ROUND(I169*SUMIF(A:A,A169,D:D),0)</f>
         <v>497</v>
       </c>
+      <c r="K169" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A169,B:B,B169)/COUNTIFS(B:B,B169,A:A,A169),0)</f>
+        <v>245</v>
+      </c>
+      <c r="L169" s="25" t="n">
+        <f aca="false">K169/SUMIF(A:A,A169,K:K)</f>
+        <v>0.113478462251042</v>
+      </c>
+      <c r="M169" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A169,J:J)*L169,0)</f>
+        <v>363</v>
+      </c>
     </row>
     <row r="170" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B170" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D170" s="1" t="n">
         <v>489</v>
@@ -13241,16 +15341,28 @@
         <f aca="false">ROUND(I170*SUMIF(A:A,A170,D:D),0)</f>
         <v>484</v>
       </c>
+      <c r="K170" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A170,B:B,B170)/COUNTIFS(B:B,B170,A:A,A170),0)</f>
+        <v>245</v>
+      </c>
+      <c r="L170" s="25" t="n">
+        <f aca="false">K170/SUMIF(A:A,A170,K:K)</f>
+        <v>0.113478462251042</v>
+      </c>
+      <c r="M170" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A170,J:J)*L170,0)</f>
+        <v>363</v>
+      </c>
     </row>
     <row r="171" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B171" s="30" t="s">
         <v>219</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="D171" s="1" t="n">
         <v>222</v>
@@ -13275,10 +15387,22 @@
         <f aca="false">ROUND(I171*SUMIF(A:A,A171,D:D),0)</f>
         <v>799</v>
       </c>
+      <c r="K171" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A171,B:B,B171)/COUNTIFS(B:B,B171,A:A,A171),0)</f>
+        <v>799</v>
+      </c>
+      <c r="L171" s="25" t="n">
+        <f aca="false">K171/SUMIF(A:A,A171,K:K)</f>
+        <v>0.37007874015748</v>
+      </c>
+      <c r="M171" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A171,J:J)*L171,0)</f>
+        <v>1184</v>
+      </c>
     </row>
     <row r="172" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B172" s="27" t="s">
         <v>19</v>
@@ -13309,16 +15433,28 @@
         <f aca="false">ROUND(I172*SUMIF(A:A,A172,D:D),0)</f>
         <v>320</v>
       </c>
+      <c r="K172" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A172,B:B,B172)/COUNTIFS(B:B,B172,A:A,A172),0)</f>
+        <v>320</v>
+      </c>
+      <c r="L172" s="25" t="n">
+        <f aca="false">K172/SUMIF(A:A,A172,K:K)</f>
+        <v>0.148216767021769</v>
+      </c>
+      <c r="M172" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A172,J:J)*L172,0)</f>
+        <v>474</v>
+      </c>
     </row>
     <row r="173" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="1" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B173" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D173" s="1" t="n">
         <v>1998</v>
@@ -13343,13 +15479,25 @@
         <f aca="false">ROUND(I173*SUMIF(A:A,A173,D:D),0)</f>
         <v>1355</v>
       </c>
+      <c r="K173" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A173,B:B,B173)/COUNTIFS(B:B,B173,A:A,A173),0)</f>
+        <v>437</v>
+      </c>
+      <c r="L173" s="25" t="n">
+        <f aca="false">K173/SUMIF(A:A,A173,K:K)</f>
+        <v>0.0969172765579951</v>
+      </c>
+      <c r="M173" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A173,J:J)*L173,0)</f>
+        <v>880</v>
+      </c>
     </row>
     <row r="174" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B174" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>197</v>
@@ -13377,16 +15525,28 @@
         <f aca="false">ROUND(I174*SUMIF(A:A,A174,D:D),0)</f>
         <v>1341</v>
       </c>
+      <c r="K174" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A174,B:B,B174)/COUNTIFS(B:B,B174,A:A,A174),0)</f>
+        <v>437</v>
+      </c>
+      <c r="L174" s="25" t="n">
+        <f aca="false">K174/SUMIF(A:A,A174,K:K)</f>
+        <v>0.0969172765579951</v>
+      </c>
+      <c r="M174" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A174,J:J)*L174,0)</f>
+        <v>880</v>
+      </c>
     </row>
     <row r="175" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="1" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B175" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D175" s="1" t="n">
         <v>1823</v>
@@ -13411,16 +15571,28 @@
         <f aca="false">ROUND(I175*SUMIF(A:A,A175,D:D),0)</f>
         <v>1236</v>
       </c>
+      <c r="K175" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A175,B:B,B175)/COUNTIFS(B:B,B175,A:A,A175),0)</f>
+        <v>437</v>
+      </c>
+      <c r="L175" s="25" t="n">
+        <f aca="false">K175/SUMIF(A:A,A175,K:K)</f>
+        <v>0.0969172765579951</v>
+      </c>
+      <c r="M175" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A175,J:J)*L175,0)</f>
+        <v>880</v>
+      </c>
     </row>
     <row r="176" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="1" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B176" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="D176" s="1" t="n">
         <v>985</v>
@@ -13445,16 +15617,28 @@
         <f aca="false">ROUND(I176*SUMIF(A:A,A176,D:D),0)</f>
         <v>1105</v>
       </c>
+      <c r="K176" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A176,B:B,B176)/COUNTIFS(B:B,B176,A:A,A176),0)</f>
+        <v>325</v>
+      </c>
+      <c r="L176" s="25" t="n">
+        <f aca="false">K176/SUMIF(A:A,A176,K:K)</f>
+        <v>0.0720780660900421</v>
+      </c>
+      <c r="M176" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A176,J:J)*L176,0)</f>
+        <v>655</v>
+      </c>
     </row>
     <row r="177" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="1" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B177" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="D177" s="1" t="n">
         <v>817</v>
@@ -13479,13 +15663,25 @@
         <f aca="false">ROUND(I177*SUMIF(A:A,A177,D:D),0)</f>
         <v>916</v>
       </c>
+      <c r="K177" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A177,B:B,B177)/COUNTIFS(B:B,B177,A:A,A177),0)</f>
+        <v>325</v>
+      </c>
+      <c r="L177" s="25" t="n">
+        <f aca="false">K177/SUMIF(A:A,A177,K:K)</f>
+        <v>0.0720780660900421</v>
+      </c>
+      <c r="M177" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A177,J:J)*L177,0)</f>
+        <v>655</v>
+      </c>
     </row>
     <row r="178" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B178" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>201</v>
@@ -13513,10 +15709,22 @@
         <f aca="false">ROUND(I178*SUMIF(A:A,A178,D:D),0)</f>
         <v>906</v>
       </c>
+      <c r="K178" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A178,B:B,B178)/COUNTIFS(B:B,B178,A:A,A178),0)</f>
+        <v>325</v>
+      </c>
+      <c r="L178" s="25" t="n">
+        <f aca="false">K178/SUMIF(A:A,A178,K:K)</f>
+        <v>0.0720780660900421</v>
+      </c>
+      <c r="M178" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A178,J:J)*L178,0)</f>
+        <v>655</v>
+      </c>
     </row>
     <row r="179" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="1" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B179" s="30" t="s">
         <v>219</v>
@@ -13547,16 +15755,28 @@
         <f aca="false">ROUND(I179*SUMIF(A:A,A179,D:D),0)</f>
         <v>1471</v>
       </c>
+      <c r="K179" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A179,B:B,B179)/COUNTIFS(B:B,B179,A:A,A179),0)</f>
+        <v>1471</v>
+      </c>
+      <c r="L179" s="25" t="n">
+        <f aca="false">K179/SUMIF(A:A,A179,K:K)</f>
+        <v>0.326236416056775</v>
+      </c>
+      <c r="M179" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A179,J:J)*L179,0)</f>
+        <v>2963</v>
+      </c>
     </row>
     <row r="180" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="1" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B180" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D180" s="1" t="n">
         <v>313</v>
@@ -13581,16 +15801,28 @@
         <f aca="false">ROUND(I180*SUMIF(A:A,A180,D:D),0)</f>
         <v>752</v>
       </c>
+      <c r="K180" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A180,B:B,B180)/COUNTIFS(B:B,B180,A:A,A180),0)</f>
+        <v>752</v>
+      </c>
+      <c r="L180" s="25" t="n">
+        <f aca="false">K180/SUMIF(A:A,A180,K:K)</f>
+        <v>0.166777555999113</v>
+      </c>
+      <c r="M180" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A180,J:J)*L180,0)</f>
+        <v>1515</v>
+      </c>
     </row>
     <row r="181" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B181" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D181" s="1" t="n">
         <v>986</v>
@@ -13615,16 +15847,28 @@
         <f aca="false">ROUND(I181*SUMIF(A:A,A181,D:D),0)</f>
         <v>640</v>
       </c>
+      <c r="K181" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A181,B:B,B181)/COUNTIFS(B:B,B181,A:A,A181),0)</f>
+        <v>309</v>
+      </c>
+      <c r="L181" s="25" t="n">
+        <f aca="false">K181/SUMIF(A:A,A181,K:K)</f>
+        <v>0.13570487483531</v>
+      </c>
+      <c r="M181" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A181,J:J)*L181,0)</f>
+        <v>501</v>
+      </c>
     </row>
     <row r="182" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B182" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="D182" s="1" t="n">
         <v>915</v>
@@ -13649,13 +15893,25 @@
         <f aca="false">ROUND(I182*SUMIF(A:A,A182,D:D),0)</f>
         <v>594</v>
       </c>
+      <c r="K182" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A182,B:B,B182)/COUNTIFS(B:B,B182,A:A,A182),0)</f>
+        <v>309</v>
+      </c>
+      <c r="L182" s="25" t="n">
+        <f aca="false">K182/SUMIF(A:A,A182,K:K)</f>
+        <v>0.13570487483531</v>
+      </c>
+      <c r="M182" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A182,J:J)*L182,0)</f>
+        <v>501</v>
+      </c>
     </row>
     <row r="183" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B183" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>206</v>
@@ -13683,13 +15939,25 @@
         <f aca="false">ROUND(I183*SUMIF(A:A,A183,D:D),0)</f>
         <v>858</v>
       </c>
+      <c r="K183" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A183,B:B,B183)/COUNTIFS(B:B,B183,A:A,A183),0)</f>
+        <v>400</v>
+      </c>
+      <c r="L183" s="25" t="n">
+        <f aca="false">K183/SUMIF(A:A,A183,K:K)</f>
+        <v>0.175669740887132</v>
+      </c>
+      <c r="M183" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A183,J:J)*L183,0)</f>
+        <v>648</v>
+      </c>
     </row>
     <row r="184" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B184" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>207</v>
@@ -13717,16 +15985,28 @@
         <f aca="false">ROUND(I184*SUMIF(A:A,A184,D:D),0)</f>
         <v>740</v>
       </c>
+      <c r="K184" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A184,B:B,B184)/COUNTIFS(B:B,B184,A:A,A184),0)</f>
+        <v>400</v>
+      </c>
+      <c r="L184" s="25" t="n">
+        <f aca="false">K184/SUMIF(A:A,A184,K:K)</f>
+        <v>0.175669740887132</v>
+      </c>
+      <c r="M184" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A184,J:J)*L184,0)</f>
+        <v>648</v>
+      </c>
     </row>
     <row r="185" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B185" s="30" t="s">
         <v>219</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D185" s="1" t="n">
         <v>121</v>
@@ -13751,16 +16031,28 @@
         <f aca="false">ROUND(I185*SUMIF(A:A,A185,D:D),0)</f>
         <v>472</v>
       </c>
+      <c r="K185" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A185,B:B,B185)/COUNTIFS(B:B,B185,A:A,A185),0)</f>
+        <v>472</v>
+      </c>
+      <c r="L185" s="25" t="n">
+        <f aca="false">K185/SUMIF(A:A,A185,K:K)</f>
+        <v>0.207290294246816</v>
+      </c>
+      <c r="M185" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A185,J:J)*L185,0)</f>
+        <v>765</v>
+      </c>
     </row>
     <row r="186" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B186" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D186" s="1" t="n">
         <v>108</v>
@@ -13785,16 +16077,28 @@
         <f aca="false">ROUND(I186*SUMIF(A:A,A186,D:D),0)</f>
         <v>248</v>
       </c>
+      <c r="K186" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A186,B:B,B186)/COUNTIFS(B:B,B186,A:A,A186),0)</f>
+        <v>248</v>
+      </c>
+      <c r="L186" s="25" t="n">
+        <f aca="false">K186/SUMIF(A:A,A186,K:K)</f>
+        <v>0.108915239350022</v>
+      </c>
+      <c r="M186" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A186,J:J)*L186,0)</f>
+        <v>402</v>
+      </c>
     </row>
     <row r="187" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B187" s="27" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D187" s="1" t="n">
         <v>74</v>
@@ -13819,620 +16123,21 @@
         <f aca="false">ROUND(I187*SUMIF(A:A,A187,D:D),0)</f>
         <v>139</v>
       </c>
-    </row>
-    <row r="188" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B188" s="27" t="s">
-        <v>238</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="D188" s="1" t="n">
-        <v>870</v>
-      </c>
-      <c r="E188" s="25" t="n">
-        <v>0.386</v>
-      </c>
-      <c r="F188" s="1" t="n">
-        <v>2636</v>
-      </c>
-      <c r="G188" s="1" t="n">
-        <v>9363</v>
-      </c>
-      <c r="H188" s="28" t="n">
-        <f aca="false">ROUND(D188*IF(ISNUMBER(SEARCH("Labour",B188)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B188)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B188)),ISNUMBER(SEARCH("RefUK",B188))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B188)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B188)),ISNUMBER(SEARCH("Lib Dem",B188))),National!$L$8,National!$L$9))))),0)</f>
-        <v>3625</v>
-      </c>
-      <c r="I188" s="25" t="n">
-        <v>0.270649685596478</v>
-      </c>
-      <c r="J188" s="29" t="n">
-        <f aca="false">ROUND(I188*SUMIF(A:A,A188,D:D),0)</f>
-        <v>3198</v>
-      </c>
-    </row>
-    <row r="189" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B189" s="27" t="s">
-        <v>238</v>
-      </c>
-      <c r="C189" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="D189" s="1" t="n">
-        <v>802</v>
-      </c>
-      <c r="E189" s="25" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="F189" s="1" t="n">
-        <v>2636</v>
-      </c>
-      <c r="G189" s="1" t="n">
-        <v>9363</v>
-      </c>
-      <c r="H189" s="28" t="n">
-        <f aca="false">ROUND(D189*IF(ISNUMBER(SEARCH("Labour",B189)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B189)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B189)),ISNUMBER(SEARCH("RefUK",B189))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B189)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B189)),ISNUMBER(SEARCH("Lib Dem",B189))),National!$L$8,National!$L$9))))),0)</f>
-        <v>3342</v>
-      </c>
-      <c r="I189" s="25" t="n">
-        <v>0.249495457296984</v>
-      </c>
-      <c r="J189" s="29" t="n">
-        <f aca="false">ROUND(I189*SUMIF(A:A,A189,D:D),0)</f>
-        <v>2948</v>
-      </c>
-    </row>
-    <row r="190" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B190" s="27" t="s">
-        <v>243</v>
-      </c>
-      <c r="C190" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="D190" s="1" t="n">
-        <v>781</v>
-      </c>
-      <c r="E190" s="25" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="F190" s="1" t="n">
-        <v>2636</v>
-      </c>
-      <c r="G190" s="1" t="n">
-        <v>9363</v>
-      </c>
-      <c r="H190" s="28" t="n">
-        <f aca="false">ROUND(D190*IF(ISNUMBER(SEARCH("Labour",B190)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B190)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B190)),ISNUMBER(SEARCH("RefUK",B190))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B190)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B190)),ISNUMBER(SEARCH("Lib Dem",B190))),National!$L$8,National!$L$9))))),0)</f>
-        <v>309</v>
-      </c>
-      <c r="I190" s="25" t="n">
-        <v>0.0230531892584728</v>
-      </c>
-      <c r="J190" s="29" t="n">
-        <f aca="false">ROUND(I190*SUMIF(A:A,A190,D:D),0)</f>
-        <v>272</v>
-      </c>
-    </row>
-    <row r="191" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B191" s="27" t="s">
-        <v>243</v>
-      </c>
-      <c r="C191" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="D191" s="1" t="n">
-        <v>717</v>
-      </c>
-      <c r="E191" s="25" t="n">
-        <v>0.318</v>
-      </c>
-      <c r="F191" s="1" t="n">
-        <v>2636</v>
-      </c>
-      <c r="G191" s="1" t="n">
-        <v>9363</v>
-      </c>
-      <c r="H191" s="28" t="n">
-        <f aca="false">ROUND(D191*IF(ISNUMBER(SEARCH("Labour",B191)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B191)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B191)),ISNUMBER(SEARCH("RefUK",B191))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B191)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B191)),ISNUMBER(SEARCH("Lib Dem",B191))),National!$L$8,National!$L$9))))),0)</f>
-        <v>283</v>
-      </c>
-      <c r="I191" s="25" t="n">
-        <v>0.0211640674754481</v>
-      </c>
-      <c r="J191" s="29" t="n">
-        <f aca="false">ROUND(I191*SUMIF(A:A,A191,D:D),0)</f>
-        <v>250</v>
-      </c>
-    </row>
-    <row r="192" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B192" s="27" t="s">
-        <v>235</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="D192" s="1" t="n">
-        <v>479</v>
-      </c>
-      <c r="E192" s="25" t="n">
-        <v>0.212</v>
-      </c>
-      <c r="F192" s="1" t="n">
-        <v>2636</v>
-      </c>
-      <c r="G192" s="1" t="n">
-        <v>9363</v>
-      </c>
-      <c r="H192" s="28" t="n">
-        <f aca="false">ROUND(D192*IF(ISNUMBER(SEARCH("Labour",B192)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B192)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B192)),ISNUMBER(SEARCH("RefUK",B192))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B192)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B192)),ISNUMBER(SEARCH("Lib Dem",B192))),National!$L$8,National!$L$9))))),0)</f>
-        <v>313</v>
-      </c>
-      <c r="I192" s="25" t="n">
-        <v>0.0233835585125955</v>
-      </c>
-      <c r="J192" s="29" t="n">
-        <f aca="false">ROUND(I192*SUMIF(A:A,A192,D:D),0)</f>
-        <v>276</v>
-      </c>
-    </row>
-    <row r="193" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B193" s="27" t="s">
-        <v>235</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="D193" s="1" t="n">
-        <v>432</v>
-      </c>
-      <c r="E193" s="25" t="n">
-        <v>0.191</v>
-      </c>
-      <c r="F193" s="1" t="n">
-        <v>2636</v>
-      </c>
-      <c r="G193" s="1" t="n">
-        <v>9363</v>
-      </c>
-      <c r="H193" s="28" t="n">
-        <f aca="false">ROUND(D193*IF(ISNUMBER(SEARCH("Labour",B193)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B193)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B193)),ISNUMBER(SEARCH("RefUK",B193))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B193)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B193)),ISNUMBER(SEARCH("Lib Dem",B193))),National!$L$8,National!$L$9))))),0)</f>
-        <v>282</v>
-      </c>
-      <c r="I193" s="25" t="n">
-        <v>0.0210891383662656</v>
-      </c>
-      <c r="J193" s="29" t="n">
-        <f aca="false">ROUND(I193*SUMIF(A:A,A193,D:D),0)</f>
-        <v>249</v>
-      </c>
-    </row>
-    <row r="194" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B194" s="30" t="s">
-        <v>219</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="D194" s="1" t="n">
-        <v>141</v>
-      </c>
-      <c r="E194" s="25" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="F194" s="1" t="n">
-        <v>2636</v>
-      </c>
-      <c r="G194" s="1" t="n">
-        <v>9363</v>
-      </c>
-      <c r="H194" s="28" t="n">
-        <f aca="false">ROUND(D194*IF(ISNUMBER(SEARCH("Labour",B194)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B194)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B194)),ISNUMBER(SEARCH("RefUK",B194))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B194)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B194)),ISNUMBER(SEARCH("Lib Dem",B194))),National!$L$8,National!$L$9))))),0)</f>
-        <v>335</v>
-      </c>
-      <c r="I194" s="25" t="n">
-        <v>0.0250024313004471</v>
-      </c>
-      <c r="J194" s="29" t="n">
-        <f aca="false">ROUND(I194*SUMIF(A:A,A194,D:D),0)</f>
-        <v>295</v>
-      </c>
-    </row>
-    <row r="195" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B195" s="30" t="s">
-        <v>219</v>
-      </c>
-      <c r="C195" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D195" s="1" t="n">
-        <v>109</v>
-      </c>
-      <c r="E195" s="25" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="F195" s="1" t="n">
-        <v>2636</v>
-      </c>
-      <c r="G195" s="1" t="n">
-        <v>9363</v>
-      </c>
-      <c r="H195" s="28" t="n">
-        <f aca="false">ROUND(D195*IF(ISNUMBER(SEARCH("Labour",B195)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B195)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B195)),ISNUMBER(SEARCH("RefUK",B195))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B195)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B195)),ISNUMBER(SEARCH("Lib Dem",B195))),National!$L$8,National!$L$9))))),0)</f>
-        <v>259</v>
-      </c>
-      <c r="I195" s="25" t="n">
-        <v>0.0193281206507002</v>
-      </c>
-      <c r="J195" s="29" t="n">
-        <f aca="false">ROUND(I195*SUMIF(A:A,A195,D:D),0)</f>
-        <v>228</v>
-      </c>
-    </row>
-    <row r="196" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B196" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="C196" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="D196" s="1" t="n">
-        <v>81</v>
-      </c>
-      <c r="E196" s="25" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="F196" s="1" t="n">
-        <v>2636</v>
-      </c>
-      <c r="G196" s="1" t="n">
-        <v>9363</v>
-      </c>
-      <c r="H196" s="28" t="n">
-        <f aca="false">ROUND(D196*IF(ISNUMBER(SEARCH("Labour",B196)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B196)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B196)),ISNUMBER(SEARCH("RefUK",B196))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B196)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B196)),ISNUMBER(SEARCH("Lib Dem",B196))),National!$L$8,National!$L$9))))),0)</f>
-        <v>113</v>
-      </c>
-      <c r="I196" s="25" t="n">
-        <v>0.00846666878528018</v>
-      </c>
-      <c r="J196" s="29" t="n">
-        <f aca="false">ROUND(I196*SUMIF(A:A,A196,D:D),0)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="197" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B197" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="C197" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="D197" s="1" t="n">
-        <v>80</v>
-      </c>
-      <c r="E197" s="25" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="F197" s="1" t="n">
-        <v>2636</v>
-      </c>
-      <c r="G197" s="1" t="n">
-        <v>9363</v>
-      </c>
-      <c r="H197" s="28" t="n">
-        <f aca="false">ROUND(D197*IF(ISNUMBER(SEARCH("Labour",B197)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B197)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B197)),ISNUMBER(SEARCH("RefUK",B197))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B197)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B197)),ISNUMBER(SEARCH("Lib Dem",B197))),National!$L$8,National!$L$9))))),0)</f>
-        <v>112</v>
-      </c>
-      <c r="I197" s="25" t="n">
-        <v>0.00836214201015326</v>
-      </c>
-      <c r="J197" s="29" t="n">
-        <f aca="false">ROUND(I197*SUMIF(A:A,A197,D:D),0)</f>
-        <v>99</v>
-      </c>
-    </row>
-    <row r="198" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B198" s="27" t="s">
-        <v>389</v>
-      </c>
-      <c r="C198" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="D198" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="E198" s="25" t="n">
-        <v>0.009</v>
-      </c>
-      <c r="F198" s="1" t="n">
-        <v>2636</v>
-      </c>
-      <c r="G198" s="1" t="n">
-        <v>9363</v>
-      </c>
-      <c r="H198" s="28" t="n">
-        <f aca="false">ROUND(D198*IF(ISNUMBER(SEARCH("Labour",B198)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B198)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B198)),ISNUMBER(SEARCH("RefUK",B198))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B198)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B198)),ISNUMBER(SEARCH("Lib Dem",B198))),National!$L$8,National!$L$9))))),0)</f>
-        <v>24</v>
-      </c>
-      <c r="I198" s="25" t="n">
-        <v>0.00179188757360427</v>
-      </c>
-      <c r="J198" s="29" t="n">
-        <f aca="false">ROUND(I198*SUMIF(A:A,A198,D:D),0)</f>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="199" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="B199" s="27" t="s">
-        <v>243</v>
-      </c>
-      <c r="C199" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="D199" s="1" t="n">
-        <v>706</v>
-      </c>
-      <c r="E199" s="25" t="n">
-        <v>0.374</v>
-      </c>
-      <c r="F199" s="1" t="n">
-        <v>2478</v>
-      </c>
-      <c r="G199" s="1" t="n">
-        <v>11085</v>
-      </c>
-      <c r="H199" s="28" t="n">
-        <f aca="false">ROUND(D199*IF(ISNUMBER(SEARCH("Labour",B199)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B199)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B199)),ISNUMBER(SEARCH("RefUK",B199))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B199)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B199)),ISNUMBER(SEARCH("Lib Dem",B199))),National!$L$8,National!$L$9))))),0)</f>
-        <v>279</v>
-      </c>
-      <c r="I199" s="25" t="n">
-        <v>0.0383066437298769</v>
-      </c>
-      <c r="J199" s="29" t="n">
-        <f aca="false">ROUND(I199*SUMIF(A:A,A199,D:D),0)</f>
-        <v>329</v>
-      </c>
-    </row>
-    <row r="200" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="B200" s="27" t="s">
-        <v>238</v>
-      </c>
-      <c r="C200" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="D200" s="1" t="n">
-        <v>506</v>
-      </c>
-      <c r="E200" s="25" t="n">
-        <v>0.268</v>
-      </c>
-      <c r="F200" s="1" t="n">
-        <v>2478</v>
-      </c>
-      <c r="G200" s="1" t="n">
-        <v>11085</v>
-      </c>
-      <c r="H200" s="28" t="n">
-        <f aca="false">ROUND(D200*IF(ISNUMBER(SEARCH("Labour",B200)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B200)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B200)),ISNUMBER(SEARCH("RefUK",B200))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B200)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B200)),ISNUMBER(SEARCH("Lib Dem",B200))),National!$L$8,National!$L$9))))),0)</f>
-        <v>2108</v>
-      </c>
-      <c r="I200" s="25" t="n">
-        <v>0.289353147487454</v>
-      </c>
-      <c r="J200" s="29" t="n">
-        <f aca="false">ROUND(I200*SUMIF(A:A,A200,D:D),0)</f>
-        <v>2481</v>
-      </c>
-    </row>
-    <row r="201" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="B201" s="27" t="s">
-        <v>235</v>
-      </c>
-      <c r="C201" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="D201" s="1" t="n">
-        <v>330</v>
-      </c>
-      <c r="E201" s="25" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="F201" s="1" t="n">
-        <v>2478</v>
-      </c>
-      <c r="G201" s="1" t="n">
-        <v>11085</v>
-      </c>
-      <c r="H201" s="28" t="n">
-        <f aca="false">ROUND(D201*IF(ISNUMBER(SEARCH("Labour",B201)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B201)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B201)),ISNUMBER(SEARCH("RefUK",B201))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B201)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B201)),ISNUMBER(SEARCH("Lib Dem",B201))),National!$L$8,National!$L$9))))),0)</f>
-        <v>216</v>
-      </c>
-      <c r="I201" s="25" t="n">
-        <v>0.029612730144201</v>
-      </c>
-      <c r="J201" s="29" t="n">
-        <f aca="false">ROUND(I201*SUMIF(A:A,A201,D:D),0)</f>
-        <v>254</v>
-      </c>
-    </row>
-    <row r="202" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="B202" s="30" t="s">
-        <v>219</v>
-      </c>
-      <c r="C202" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="D202" s="1" t="n">
-        <v>167</v>
-      </c>
-      <c r="E202" s="25" t="n">
-        <v>0.088</v>
-      </c>
-      <c r="F202" s="1" t="n">
-        <v>2478</v>
-      </c>
-      <c r="G202" s="1" t="n">
-        <v>11085</v>
-      </c>
-      <c r="H202" s="28" t="n">
-        <f aca="false">ROUND(D202*IF(ISNUMBER(SEARCH("Labour",B202)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B202)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B202)),ISNUMBER(SEARCH("RefUK",B202))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B202)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B202)),ISNUMBER(SEARCH("Lib Dem",B202))),National!$L$8,National!$L$9))))),0)</f>
-        <v>397</v>
-      </c>
-      <c r="I202" s="25" t="n">
-        <v>0.054433846065871</v>
-      </c>
-      <c r="J202" s="29" t="n">
-        <f aca="false">ROUND(I202*SUMIF(A:A,A202,D:D),0)</f>
-        <v>467</v>
-      </c>
-    </row>
-    <row r="203" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="B203" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="C203" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="D203" s="1" t="n">
-        <v>99</v>
-      </c>
-      <c r="E203" s="25" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="F203" s="1" t="n">
-        <v>2478</v>
-      </c>
-      <c r="G203" s="1" t="n">
-        <v>11085</v>
-      </c>
-      <c r="H203" s="28" t="n">
-        <f aca="false">ROUND(D203*IF(ISNUMBER(SEARCH("Labour",B203)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B203)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B203)),ISNUMBER(SEARCH("RefUK",B203))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B203)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B203)),ISNUMBER(SEARCH("Lib Dem",B203))),National!$L$8,National!$L$9))))),0)</f>
+      <c r="K187" s="24" t="n">
+        <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A187,B:B,B187)/COUNTIFS(B:B,B187,A:A,A187),0)</f>
         <v>139</v>
       </c>
-      <c r="I203" s="25" t="n">
-        <v>0.0190218243043926</v>
-      </c>
-      <c r="J203" s="29" t="n">
-        <f aca="false">ROUND(I203*SUMIF(A:A,A203,D:D),0)</f>
-        <v>163</v>
-      </c>
-    </row>
-    <row r="204" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="B204" s="27" t="s">
-        <v>291</v>
-      </c>
-      <c r="C204" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="D204" s="1" t="n">
-        <v>69</v>
-      </c>
-      <c r="E204" s="25" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="F204" s="1" t="n">
-        <v>2478</v>
-      </c>
-      <c r="G204" s="1" t="n">
-        <v>11085</v>
-      </c>
-      <c r="H204" s="28" t="n">
-        <f aca="false">ROUND(D204*IF(ISNUMBER(SEARCH("Labour",B204)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B204)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B204)),ISNUMBER(SEARCH("RefUK",B204))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B204)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B204)),ISNUMBER(SEARCH("Lib Dem",B204))),National!$L$8,National!$L$9))))),0)</f>
-        <v>79</v>
-      </c>
-      <c r="I204" s="25" t="n">
-        <v>0.0108225592826476</v>
-      </c>
-      <c r="J204" s="29" t="n">
-        <f aca="false">ROUND(I204*SUMIF(A:A,A204,D:D),0)</f>
-        <v>93</v>
-      </c>
-    </row>
-    <row r="205" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="B205" s="27" t="s">
-        <v>389</v>
-      </c>
-      <c r="C205" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="D205" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="E205" s="25" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="F205" s="1" t="n">
-        <v>2478</v>
-      </c>
-      <c r="G205" s="1" t="n">
-        <v>11085</v>
-      </c>
-      <c r="H205" s="28" t="n">
-        <f aca="false">ROUND(D205*IF(ISNUMBER(SEARCH("Labour",B205)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B205)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B205)),ISNUMBER(SEARCH("RefUK",B205))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B205)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B205)),ISNUMBER(SEARCH("Lib Dem",B205))),National!$L$8,National!$L$9))))),0)</f>
-        <v>14</v>
-      </c>
-      <c r="I205" s="25" t="n">
-        <v>0.00188218422306915</v>
-      </c>
-      <c r="J205" s="29" t="n">
-        <f aca="false">ROUND(I205*SUMIF(A:A,A205,D:D),0)</f>
-        <v>16</v>
+      <c r="L187" s="25" t="n">
+        <f aca="false">K187/SUMIF(A:A,A187,K:K)</f>
+        <v>0.0610452349582784</v>
+      </c>
+      <c r="M187" s="1" t="n">
+        <f aca="false">ROUND(SUMIF(A:A,A187,J:J)*L187,0)</f>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K187"/>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" display="Independent"/>
     <hyperlink ref="B3" r:id="rId2" display="Independent"/>
@@ -14622,24 +16327,6 @@
     <hyperlink ref="B185" r:id="rId186" display="Green"/>
     <hyperlink ref="B186" r:id="rId187" display="Liberal Democrats"/>
     <hyperlink ref="B187" r:id="rId188" display="SDP"/>
-    <hyperlink ref="B188" r:id="rId189" display="Reform"/>
-    <hyperlink ref="B189" r:id="rId190" display="Reform"/>
-    <hyperlink ref="B190" r:id="rId191" display="Labour Co-op"/>
-    <hyperlink ref="B191" r:id="rId192" display="Labour Co-op"/>
-    <hyperlink ref="B192" r:id="rId193" display="Conservative"/>
-    <hyperlink ref="B193" r:id="rId194" display="Conservative"/>
-    <hyperlink ref="B194" r:id="rId195" display="Green"/>
-    <hyperlink ref="B195" r:id="rId196" display="Green"/>
-    <hyperlink ref="B196" r:id="rId197" display="Liberal Democrats"/>
-    <hyperlink ref="B197" r:id="rId198" display="Liberal Democrats"/>
-    <hyperlink ref="B198" r:id="rId199" display="Heritage"/>
-    <hyperlink ref="B199" r:id="rId200" display="Labour Co-op"/>
-    <hyperlink ref="B200" r:id="rId201" display="Reform"/>
-    <hyperlink ref="B201" r:id="rId202" display="Conservative"/>
-    <hyperlink ref="B202" r:id="rId203" display="Green"/>
-    <hyperlink ref="B203" r:id="rId204" display="Liberal Democrats"/>
-    <hyperlink ref="B204" r:id="rId205" display="SDP"/>
-    <hyperlink ref="B205" r:id="rId206" display="Heritage"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -14648,6 +16335,7 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId189"/>
 </worksheet>
 </file>
 
@@ -14787,20 +16475,20 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="19" t="n">
         <v>880</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="20" t="n">
         <f aca="false">C9*100/SUM($C$7:$C$13)</f>
         <v>24.4037714919578</v>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="20" t="n">
         <f aca="false">C9*100/$B$1</f>
         <v>14.3579703051069</v>
       </c>
@@ -14814,20 +16502,20 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="19" t="n">
         <v>685</v>
       </c>
-      <c r="D10" s="21" t="n">
+      <c r="D10" s="20" t="n">
         <f aca="false">C10*100/SUM($C$7:$C$13)</f>
         <v>18.9961175818081</v>
       </c>
-      <c r="E10" s="21" t="n">
+      <c r="E10" s="20" t="n">
         <f aca="false">C10*100/$B$1</f>
         <v>11.176374612498</v>
       </c>
@@ -14840,7 +16528,7 @@
         <v>7.30762955432559</v>
       </c>
     </row>
-    <row r="11" s="18" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
         <v>40</v>
       </c>
@@ -14867,7 +16555,7 @@
         <v>24.8388807309512</v>
       </c>
     </row>
-    <row r="12" s="18" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
         <v>41</v>
       </c>
@@ -15045,20 +16733,20 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="19" t="n">
         <v>489</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="20" t="n">
         <f aca="false">C8*100/SUM($C$7:$C$10)</f>
         <v>45.1940850277264</v>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="E8" s="20" t="n">
         <f aca="false">C8*100/$B$1</f>
         <v>13.8526912181303</v>
       </c>
@@ -15071,7 +16759,7 @@
         <v>9.0575288733929</v>
       </c>
     </row>
-    <row r="9" s="18" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
         <v>45</v>
       </c>
@@ -15116,11 +16804,11 @@
         <f aca="false">C10*100/$B$1</f>
         <v>9.74504249291785</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="19" t="n">
         <f aca="false">C10*IF(ISNUMBER(SEARCH("Labour",B10)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B10)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B10)),ISNUMBER(SEARCH("RefUK",B10))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B10)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B10)),ISNUMBER(SEARCH("Lib Dem",B10))),National!$L$8,National!$L$9)))))</f>
         <v>481.6</v>
       </c>
-      <c r="G10" s="21" t="n">
+      <c r="G10" s="20" t="n">
         <f aca="false">F10*100/$B$1</f>
         <v>13.643059490085</v>
       </c>
@@ -15176,13 +16864,18 @@
       </c>
       <c r="C2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" s="21" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>0.3374</v>
       </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
@@ -15222,20 +16915,20 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="19" t="n">
         <v>1726</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="20" t="n">
         <f aca="false">C7*100/SUM($C$7:$C$14)</f>
         <v>20.0861166065402</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="20" t="n">
         <f aca="false">C7*100/$B$1</f>
         <v>18.8222464558342</v>
       </c>
@@ -15249,20 +16942,20 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="19" t="n">
         <v>1634</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="20" t="n">
         <f aca="false">C8*100/SUM($C$7:$C$14)</f>
         <v>19.0154777144187</v>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="E8" s="20" t="n">
         <f aca="false">C8*100/$B$1</f>
         <v>17.8189749182116</v>
       </c>
@@ -15276,20 +16969,20 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="19" t="n">
         <v>1577</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="20" t="n">
         <f aca="false">C9*100/SUM($C$7:$C$14)</f>
         <v>18.3521470964739</v>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="20" t="n">
         <f aca="false">C9*100/$B$1</f>
         <v>17.1973827699019</v>
       </c>
@@ -15383,7 +17076,7 @@
         <v>6.42437714956799</v>
       </c>
     </row>
-    <row r="13" s="18" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
         <v>53</v>
       </c>
@@ -15488,13 +17181,18 @@
       </c>
       <c r="C2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" s="21" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>0.2175</v>
       </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
@@ -15534,20 +17232,20 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="19" t="n">
         <v>1419</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="20" t="n">
         <f aca="false">C7*100/SUM($C$7:$C$14)</f>
         <v>23.3158067696352</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="20" t="n">
         <f aca="false">C7*100/$B$1</f>
         <v>13.8614828563056</v>
       </c>
@@ -15561,20 +17259,20 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="19" t="n">
         <v>1355</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="20" t="n">
         <f aca="false">C8*100/SUM($C$7:$C$14)</f>
         <v>22.2642129477489</v>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="E8" s="20" t="n">
         <f aca="false">C8*100/$B$1</f>
         <v>13.2362996971769</v>
       </c>
@@ -15588,20 +17286,20 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="19" t="n">
         <v>1339</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="20" t="n">
         <f aca="false">C9*100/SUM($C$7:$C$14)</f>
         <v>22.0013144922774</v>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="20" t="n">
         <f aca="false">C9*100/$B$1</f>
         <v>13.0800039073947</v>
       </c>
@@ -15695,7 +17393,7 @@
         <v>2.61870590091749</v>
       </c>
     </row>
-    <row r="13" s="18" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
         <v>62</v>
       </c>
@@ -15808,13 +17506,42 @@
       <c r="AH2" s="24"/>
       <c r="AI2" s="24"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" s="21" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>0.2235</v>
       </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="1"/>
+      <c r="Z3" s="1"/>
+      <c r="AA3" s="1"/>
+      <c r="AB3" s="1"/>
+      <c r="AC3" s="1"/>
+      <c r="AD3" s="1"/>
+      <c r="AE3" s="1"/>
       <c r="AF3" s="24"/>
       <c r="AG3" s="24"/>
       <c r="AH3" s="24"/>
@@ -15870,20 +17597,20 @@
       <c r="AI6" s="24"/>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="19" t="n">
         <v>1617</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="20" t="n">
         <f aca="false">C7*100/SUM($C$7:$C$14)</f>
         <v>24.181247196052</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="20" t="n">
         <f aca="false">C7*100/$B$1</f>
         <v>14.5872801082544</v>
       </c>
@@ -15901,20 +17628,20 @@
       <c r="AI7" s="24"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="19" t="n">
         <v>1531</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="20" t="n">
         <f aca="false">C8*100/SUM($C$7:$C$14)</f>
         <v>22.8951697323164</v>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="E8" s="20" t="n">
         <f aca="false">C8*100/$B$1</f>
         <v>13.8114569237709</v>
       </c>
@@ -15932,20 +17659,20 @@
       <c r="AI8" s="24"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="19" t="n">
         <v>1491</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="20" t="n">
         <f aca="false">C9*100/SUM($C$7:$C$14)</f>
         <v>22.2969941677882</v>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="20" t="n">
         <f aca="false">C9*100/$B$1</f>
         <v>13.4506089309878</v>
       </c>
@@ -16055,7 +17782,7 @@
       <c r="AH12" s="24"/>
       <c r="AI12" s="24"/>
     </row>
-    <row r="13" s="18" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
         <v>70</v>
       </c>
@@ -16081,6 +17808,30 @@
         <f aca="false">F13*100/$B$1</f>
         <v>7.99165539016689</v>
       </c>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="21"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="21"/>
+      <c r="R13" s="21"/>
+      <c r="S13" s="21"/>
+      <c r="T13" s="21"/>
+      <c r="U13" s="21"/>
+      <c r="V13" s="21"/>
+      <c r="W13" s="21"/>
+      <c r="X13" s="21"/>
+      <c r="Y13" s="21"/>
+      <c r="Z13" s="21"/>
+      <c r="AA13" s="21"/>
+      <c r="AB13" s="21"/>
+      <c r="AC13" s="21"/>
+      <c r="AD13" s="21"/>
+      <c r="AE13" s="21"/>
       <c r="AF13" s="24"/>
       <c r="AG13" s="24"/>
       <c r="AH13" s="24"/>
@@ -16454,60 +18205,60 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="19" t="n">
         <v>1709</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="20" t="n">
         <f aca="false">C9*100/SUM($C$7:$C$14)</f>
         <v>34.5531742822483</v>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="20" t="n">
         <f aca="false">C9*100/$B$1</f>
         <v>22.899638215195</v>
       </c>
-      <c r="F9" s="20" t="n">
+      <c r="F9" s="19" t="n">
         <f aca="false">C9*IF(ISNUMBER(SEARCH("Labour",B9)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B9)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B9)),ISNUMBER(SEARCH("RefUK",B9))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B9)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B9)),ISNUMBER(SEARCH("Lib Dem",B9))),National!$L$8,National!$L$9)))))</f>
         <v>1117.42307692308</v>
       </c>
-      <c r="G9" s="21" t="n">
+      <c r="G9" s="20" t="n">
         <f aca="false">F9*100/$B$1</f>
         <v>14.9728403714736</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="19" t="n">
         <v>1617</v>
       </c>
-      <c r="D10" s="21" t="n">
+      <c r="D10" s="20" t="n">
         <f aca="false">C10*100/SUM($C$7:$C$14)</f>
         <v>32.6930853214719</v>
       </c>
-      <c r="E10" s="21" t="n">
+      <c r="E10" s="20" t="n">
         <f aca="false">C10*100/$B$1</f>
         <v>21.6668899906204</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="19" t="n">
         <f aca="false">C10*IF(ISNUMBER(SEARCH("Labour",B10)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B10)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B10)),ISNUMBER(SEARCH("RefUK",B10))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B10)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B10)),ISNUMBER(SEARCH("Lib Dem",B10))),National!$L$8,National!$L$9)))))</f>
         <v>1057.26923076923</v>
       </c>
-      <c r="G10" s="21" t="n">
+      <c r="G10" s="20" t="n">
         <f aca="false">F10*100/$B$1</f>
         <v>14.1668126861749</v>
       </c>
     </row>
-    <row r="11" s="18" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
         <v>76</v>
       </c>
@@ -16666,13 +18417,18 @@
       </c>
       <c r="C2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" s="21" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>0.3333</v>
       </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
@@ -16873,7 +18629,7 @@
         <v>2.66119093365586</v>
       </c>
     </row>
-    <row r="13" s="18" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
         <v>88</v>
       </c>
@@ -16955,82 +18711,82 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="20" t="n">
+      <c r="C16" s="19" t="n">
         <v>2388</v>
       </c>
-      <c r="D16" s="21" t="n">
+      <c r="D16" s="20" t="n">
         <f aca="false">C16*100/SUM($C$7:$C$18)</f>
         <v>25.2351262813061</v>
       </c>
-      <c r="E16" s="21" t="n">
+      <c r="E16" s="20" t="n">
         <f aca="false">C16*100/$B$1</f>
         <v>23.7635585630411</v>
       </c>
-      <c r="F16" s="20" t="n">
+      <c r="F16" s="19" t="n">
         <f aca="false">C16*IF(ISNUMBER(SEARCH("Labour",B16)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B16)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B16)),ISNUMBER(SEARCH("RefUK",B16))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B16)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B16)),ISNUMBER(SEARCH("Lib Dem",B16))),National!$L$8,National!$L$9)))))</f>
         <v>2729.14285714286</v>
       </c>
-      <c r="G16" s="21" t="n">
+      <c r="G16" s="20" t="n">
         <f aca="false">F16*100/$B$1</f>
         <v>27.1583526434755</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="20" t="n">
+      <c r="C17" s="19" t="n">
         <v>2279</v>
       </c>
-      <c r="D17" s="21" t="n">
+      <c r="D17" s="20" t="n">
         <f aca="false">C17*100/SUM($C$7:$C$18)</f>
         <v>24.083271689739</v>
       </c>
-      <c r="E17" s="21" t="n">
+      <c r="E17" s="20" t="n">
         <f aca="false">C17*100/$B$1</f>
         <v>22.6788735197532</v>
       </c>
-      <c r="F17" s="20" t="n">
+      <c r="F17" s="19" t="n">
         <f aca="false">C17*IF(ISNUMBER(SEARCH("Labour",B17)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B17)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B17)),ISNUMBER(SEARCH("RefUK",B17))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B17)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B17)),ISNUMBER(SEARCH("Lib Dem",B17))),National!$L$8,National!$L$9)))))</f>
         <v>2604.57142857143</v>
       </c>
-      <c r="G17" s="21" t="n">
+      <c r="G17" s="20" t="n">
         <f aca="false">F17*100/$B$1</f>
         <v>25.9187125940037</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="20" t="n">
+      <c r="C18" s="19" t="n">
         <v>2230</v>
       </c>
-      <c r="D18" s="21" t="n">
+      <c r="D18" s="20" t="n">
         <f aca="false">C18*100/SUM($C$7:$C$18)</f>
         <v>23.5654654971996</v>
       </c>
-      <c r="E18" s="21" t="n">
+      <c r="E18" s="20" t="n">
         <f aca="false">C18*100/$B$1</f>
         <v>22.1912628122201</v>
       </c>
-      <c r="F18" s="20" t="n">
+      <c r="F18" s="19" t="n">
         <f aca="false">C18*IF(ISNUMBER(SEARCH("Labour",B18)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B18)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B18)),ISNUMBER(SEARCH("RefUK",B18))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B18)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B18)),ISNUMBER(SEARCH("Lib Dem",B18))),National!$L$8,National!$L$9)))))</f>
         <v>2548.57142857143</v>
       </c>
-      <c r="G18" s="21" t="n">
+      <c r="G18" s="20" t="n">
         <f aca="false">F18*100/$B$1</f>
         <v>25.3614432139659</v>
       </c>

--- a/Data/Stats/2023 results and national trend model.xlsx
+++ b/Data/Stats/2023 results and national trend model.xlsx
@@ -741,19 +741,19 @@
     <t xml:space="preserve">Registered Electors</t>
   </si>
   <si>
-    <t xml:space="preserve">Projected Votes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projected Vote %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projected Votes – # Votes Cast – 2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Average Projection Per Party</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% Projected Vote Share Per Party (Apportioned by Candidate)</t>
+    <t xml:space="preserve">DRAFT – Projected Votes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Councillors – Projected Vote %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Councillors – Projected Vote #</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRAFT – Average Projection Per Party</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projected Vote % Per Party (Apportioned by Candidate)</t>
   </si>
   <si>
     <t xml:space="preserve">Projected Votes Per Party</t>
@@ -765,7 +765,7 @@
     <t xml:space="preserve">Rank by Party</t>
   </si>
   <si>
-    <t xml:space="preserve">% Projected Vote Share Per Party (Unapportioned)</t>
+    <t xml:space="preserve">Projected Vote % Per Party (Unapportioned)</t>
   </si>
   <si>
     <t xml:space="preserve">All Saints</t>
@@ -1458,7 +1458,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1487,6 +1487,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
         <bgColor rgb="FFEEECE1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFFFF"/>
+        <bgColor rgb="FFCCFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -1588,7 +1594,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1697,6 +1703,18 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="170" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1705,7 +1723,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1745,7 +1763,7 @@
     <cellStyle name="Pivot Table Title" xfId="29"/>
     <cellStyle name="Pivot Table Value" xfId="30"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1773,6 +1791,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF0000FF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCCFFFF"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -7576,22 +7602,23 @@
   <dimension ref="A1:P187"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="27.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="5.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="25" width="7.88"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="17.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="26" width="17.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="25" width="16.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="24" width="34.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="24" width="20.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="25" width="27.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="25.64"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16" min="14" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="19.75"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="18" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="27.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="23.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="25" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="19.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="26" width="24.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="27" width="28.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="28" width="27.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="24" width="34.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="27" width="47.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="29" width="23.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="13.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="14.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="38.29"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="17" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7619,19 +7646,19 @@
       <c r="H1" s="26" t="s">
         <v>230</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="I1" s="27" t="s">
         <v>231</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="29" t="s">
         <v>232</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="L1" s="25" t="s">
+      <c r="L1" s="27" t="s">
         <v>234</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="29" t="s">
         <v>235</v>
       </c>
       <c r="N1" s="1" t="s">
@@ -7648,7 +7675,7 @@
       <c r="A2" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="30" t="s">
         <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -7666,15 +7693,15 @@
       <c r="G2" s="1" t="n">
         <v>3495</v>
       </c>
-      <c r="H2" s="28" t="n">
+      <c r="H2" s="31" t="n">
         <f aca="false">ROUND(D2*IF(ISNUMBER(SEARCH("Labour",B2)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B2)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B2)),ISNUMBER(SEARCH("RefUK",B2))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B2)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B2)),ISNUMBER(SEARCH("Lib Dem",B2))),National!$L$8,National!$L$9))))),0)</f>
         <v>337</v>
       </c>
-      <c r="I2" s="25" t="n">
+      <c r="I2" s="27" t="n">
         <f aca="false">H2/SUMIFS(H:H,A:A,A2)</f>
         <v>0.303057553956835</v>
       </c>
-      <c r="J2" s="29" t="n">
+      <c r="J2" s="32" t="n">
         <f aca="false">ROUND(I2*SUMIF(A:A,A2,D:D),0)</f>
         <v>291</v>
       </c>
@@ -7682,11 +7709,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A2,B:B,B2)/COUNTIFS(B:B,B2,A:A,A2),0)</f>
         <v>135</v>
       </c>
-      <c r="L2" s="25" t="n">
+      <c r="L2" s="27" t="n">
         <f aca="false">K2/SUMIF(A:A,A2,K:K)</f>
         <v>0.195369030390738</v>
       </c>
-      <c r="M2" s="1" t="n">
+      <c r="M2" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A2,J:J)*L2,0)</f>
         <v>188</v>
       </c>
@@ -7707,7 +7734,7 @@
       <c r="A3" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="30" t="s">
         <v>23</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -7725,15 +7752,15 @@
       <c r="G3" s="1" t="n">
         <v>3495</v>
       </c>
-      <c r="H3" s="28" t="n">
+      <c r="H3" s="31" t="n">
         <f aca="false">ROUND(D3*IF(ISNUMBER(SEARCH("Labour",B3)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B3)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B3)),ISNUMBER(SEARCH("RefUK",B3))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B3)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B3)),ISNUMBER(SEARCH("Lib Dem",B3))),National!$L$8,National!$L$9))))),0)</f>
         <v>288</v>
       </c>
-      <c r="I3" s="25" t="n">
+      <c r="I3" s="27" t="n">
         <f aca="false">H3/SUMIFS(H:H,A:A,A3)</f>
         <v>0.258992805755396</v>
       </c>
-      <c r="J3" s="29" t="n">
+      <c r="J3" s="32" t="n">
         <f aca="false">ROUND(I3*SUMIF(A:A,A3,D:D),0)</f>
         <v>249</v>
       </c>
@@ -7741,11 +7768,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A3,B:B,B3)/COUNTIFS(B:B,B3,A:A,A3),0)</f>
         <v>135</v>
       </c>
-      <c r="L3" s="25" t="n">
+      <c r="L3" s="27" t="n">
         <f aca="false">K3/SUMIF(A:A,A3,K:K)</f>
         <v>0.195369030390738</v>
       </c>
-      <c r="M3" s="1" t="n">
+      <c r="M3" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A3,J:J)*L3,0)</f>
         <v>188</v>
       </c>
@@ -7766,7 +7793,7 @@
       <c r="A4" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -7784,15 +7811,15 @@
       <c r="G4" s="1" t="n">
         <v>3495</v>
       </c>
-      <c r="H4" s="28" t="n">
+      <c r="H4" s="31" t="n">
         <f aca="false">ROUND(D4*IF(ISNUMBER(SEARCH("Labour",B4)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B4)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B4)),ISNUMBER(SEARCH("RefUK",B4))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B4)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B4)),ISNUMBER(SEARCH("Lib Dem",B4))),National!$L$8,National!$L$9))))),0)</f>
         <v>124</v>
       </c>
-      <c r="I4" s="25" t="n">
+      <c r="I4" s="27" t="n">
         <f aca="false">H4/SUMIFS(H:H,A:A,A4)</f>
         <v>0.111510791366906</v>
       </c>
-      <c r="J4" s="29" t="n">
+      <c r="J4" s="32" t="n">
         <f aca="false">ROUND(I4*SUMIF(A:A,A4,D:D),0)</f>
         <v>107</v>
       </c>
@@ -7800,11 +7827,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A4,B:B,B4)/COUNTIFS(B:B,B4,A:A,A4),0)</f>
         <v>107</v>
       </c>
-      <c r="L4" s="25" t="n">
+      <c r="L4" s="27" t="n">
         <f aca="false">K4/SUMIF(A:A,A4,K:K)</f>
         <v>0.154848046309696</v>
       </c>
-      <c r="M4" s="1" t="n">
+      <c r="M4" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A4,J:J)*L4,0)</f>
         <v>149</v>
       </c>
@@ -7825,7 +7852,7 @@
       <c r="A5" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="30" t="s">
         <v>216</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -7843,15 +7870,15 @@
       <c r="G5" s="1" t="n">
         <v>3495</v>
       </c>
-      <c r="H5" s="28" t="n">
+      <c r="H5" s="31" t="n">
         <f aca="false">ROUND(D5*IF(ISNUMBER(SEARCH("Labour",B5)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B5)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B5)),ISNUMBER(SEARCH("RefUK",B5))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B5)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B5)),ISNUMBER(SEARCH("Lib Dem",B5))),National!$L$8,National!$L$9))))),0)</f>
         <v>47</v>
       </c>
-      <c r="I5" s="25" t="n">
+      <c r="I5" s="27" t="n">
         <f aca="false">H5/SUMIFS(H:H,A:A,A5)</f>
         <v>0.0422661870503597</v>
       </c>
-      <c r="J5" s="29" t="n">
+      <c r="J5" s="32" t="n">
         <f aca="false">ROUND(I5*SUMIF(A:A,A5,D:D),0)</f>
         <v>41</v>
       </c>
@@ -7859,11 +7886,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A5,B:B,B5)/COUNTIFS(B:B,B5,A:A,A5),0)</f>
         <v>41</v>
       </c>
-      <c r="L5" s="25" t="n">
+      <c r="L5" s="27" t="n">
         <f aca="false">K5/SUMIF(A:A,A5,K:K)</f>
         <v>0.0593342981186686</v>
       </c>
-      <c r="M5" s="1" t="n">
+      <c r="M5" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A5,J:J)*L5,0)</f>
         <v>57</v>
       </c>
@@ -7884,7 +7911,7 @@
       <c r="A6" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="30" t="s">
         <v>244</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -7902,15 +7929,15 @@
       <c r="G6" s="1" t="n">
         <v>3495</v>
       </c>
-      <c r="H6" s="28" t="n">
+      <c r="H6" s="31" t="n">
         <f aca="false">ROUND(D6*IF(ISNUMBER(SEARCH("Labour",B6)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B6)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B6)),ISNUMBER(SEARCH("RefUK",B6))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B6)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B6)),ISNUMBER(SEARCH("Lib Dem",B6))),National!$L$8,National!$L$9))))),0)</f>
         <v>204</v>
       </c>
-      <c r="I6" s="25" t="n">
+      <c r="I6" s="27" t="n">
         <f aca="false">H6/SUMIFS(H:H,A:A,A6)</f>
         <v>0.183453237410072</v>
       </c>
-      <c r="J6" s="29" t="n">
+      <c r="J6" s="32" t="n">
         <f aca="false">ROUND(I6*SUMIF(A:A,A6,D:D),0)</f>
         <v>176</v>
       </c>
@@ -7918,11 +7945,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A6,B:B,B6)/COUNTIFS(B:B,B6,A:A,A6),0)</f>
         <v>176</v>
       </c>
-      <c r="L6" s="25" t="n">
+      <c r="L6" s="27" t="n">
         <f aca="false">K6/SUMIF(A:A,A6,K:K)</f>
         <v>0.254703328509407</v>
       </c>
-      <c r="M6" s="1" t="n">
+      <c r="M6" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A6,J:J)*L6,0)</f>
         <v>245</v>
       </c>
@@ -7943,7 +7970,7 @@
       <c r="A7" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="33" t="s">
         <v>219</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -7961,15 +7988,15 @@
       <c r="G7" s="1" t="n">
         <v>3495</v>
       </c>
-      <c r="H7" s="28" t="n">
+      <c r="H7" s="31" t="n">
         <f aca="false">ROUND(D7*IF(ISNUMBER(SEARCH("Labour",B7)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B7)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B7)),ISNUMBER(SEARCH("RefUK",B7))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B7)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B7)),ISNUMBER(SEARCH("Lib Dem",B7))),National!$L$8,National!$L$9))))),0)</f>
         <v>81</v>
       </c>
-      <c r="I7" s="25" t="n">
+      <c r="I7" s="27" t="n">
         <f aca="false">H7/SUMIFS(H:H,A:A,A7)</f>
         <v>0.072841726618705</v>
       </c>
-      <c r="J7" s="29" t="n">
+      <c r="J7" s="32" t="n">
         <f aca="false">ROUND(I7*SUMIF(A:A,A7,D:D),0)</f>
         <v>70</v>
       </c>
@@ -7977,11 +8004,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A7,B:B,B7)/COUNTIFS(B:B,B7,A:A,A7),0)</f>
         <v>70</v>
       </c>
-      <c r="L7" s="25" t="n">
+      <c r="L7" s="27" t="n">
         <f aca="false">K7/SUMIF(A:A,A7,K:K)</f>
         <v>0.101302460202605</v>
       </c>
-      <c r="M7" s="1" t="n">
+      <c r="M7" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A7,J:J)*L7,0)</f>
         <v>97</v>
       </c>
@@ -8002,7 +8029,7 @@
       <c r="A8" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -8020,15 +8047,15 @@
       <c r="G8" s="1" t="n">
         <v>3495</v>
       </c>
-      <c r="H8" s="28" t="n">
+      <c r="H8" s="31" t="n">
         <f aca="false">ROUND(D8*IF(ISNUMBER(SEARCH("Labour",B8)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B8)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B8)),ISNUMBER(SEARCH("RefUK",B8))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B8)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B8)),ISNUMBER(SEARCH("Lib Dem",B8))),National!$L$8,National!$L$9))))),0)</f>
         <v>31</v>
       </c>
-      <c r="I8" s="25" t="n">
+      <c r="I8" s="27" t="n">
         <f aca="false">H8/SUMIFS(H:H,A:A,A8)</f>
         <v>0.0278776978417266</v>
       </c>
-      <c r="J8" s="29" t="n">
+      <c r="J8" s="32" t="n">
         <f aca="false">ROUND(I8*SUMIF(A:A,A8,D:D),0)</f>
         <v>27</v>
       </c>
@@ -8036,11 +8063,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A8,B:B,B8)/COUNTIFS(B:B,B8,A:A,A8),0)</f>
         <v>27</v>
       </c>
-      <c r="L8" s="25" t="n">
+      <c r="L8" s="27" t="n">
         <f aca="false">K8/SUMIF(A:A,A8,K:K)</f>
         <v>0.0390738060781476</v>
       </c>
-      <c r="M8" s="1" t="n">
+      <c r="M8" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A8,J:J)*L8,0)</f>
         <v>38</v>
       </c>
@@ -8061,7 +8088,7 @@
       <c r="A9" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="30" t="s">
         <v>249</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -8079,15 +8106,15 @@
       <c r="G9" s="1" t="n">
         <v>10525</v>
       </c>
-      <c r="H9" s="28" t="n">
+      <c r="H9" s="31" t="n">
         <f aca="false">ROUND(D9*IF(ISNUMBER(SEARCH("Labour",B9)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B9)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B9)),ISNUMBER(SEARCH("RefUK",B9))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B9)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B9)),ISNUMBER(SEARCH("Lib Dem",B9))),National!$L$8,National!$L$9))))),0)</f>
         <v>551</v>
       </c>
-      <c r="I9" s="25" t="n">
+      <c r="I9" s="27" t="n">
         <f aca="false">H9/SUMIFS(H:H,A:A,A9)</f>
         <v>0.149160801299404</v>
       </c>
-      <c r="J9" s="29" t="n">
+      <c r="J9" s="32" t="n">
         <f aca="false">ROUND(I9*SUMIF(A:A,A9,D:D),0)</f>
         <v>881</v>
       </c>
@@ -8095,11 +8122,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A9,B:B,B9)/COUNTIFS(B:B,B9,A:A,A9),0)</f>
         <v>263</v>
       </c>
-      <c r="L9" s="25" t="n">
+      <c r="L9" s="27" t="n">
         <f aca="false">K9/SUMIF(A:A,A9,K:K)</f>
         <v>0.0806748466257669</v>
       </c>
-      <c r="M9" s="1" t="n">
+      <c r="M9" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A9,J:J)*L9,0)</f>
         <v>477</v>
       </c>
@@ -8120,7 +8147,7 @@
       <c r="A10" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="30" t="s">
         <v>249</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -8138,15 +8165,15 @@
       <c r="G10" s="1" t="n">
         <v>10525</v>
       </c>
-      <c r="H10" s="28" t="n">
+      <c r="H10" s="31" t="n">
         <f aca="false">ROUND(D10*IF(ISNUMBER(SEARCH("Labour",B10)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B10)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B10)),ISNUMBER(SEARCH("RefUK",B10))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B10)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B10)),ISNUMBER(SEARCH("Lib Dem",B10))),National!$L$8,National!$L$9))))),0)</f>
         <v>479</v>
       </c>
-      <c r="I10" s="25" t="n">
+      <c r="I10" s="27" t="n">
         <f aca="false">H10/SUMIFS(H:H,A:A,A10)</f>
         <v>0.129669734704927</v>
       </c>
-      <c r="J10" s="29" t="n">
+      <c r="J10" s="32" t="n">
         <f aca="false">ROUND(I10*SUMIF(A:A,A10,D:D),0)</f>
         <v>766</v>
       </c>
@@ -8154,11 +8181,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A10,B:B,B10)/COUNTIFS(B:B,B10,A:A,A10),0)</f>
         <v>263</v>
       </c>
-      <c r="L10" s="25" t="n">
+      <c r="L10" s="27" t="n">
         <f aca="false">K10/SUMIF(A:A,A10,K:K)</f>
         <v>0.0806748466257669</v>
       </c>
-      <c r="M10" s="1" t="n">
+      <c r="M10" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A10,J:J)*L10,0)</f>
         <v>477</v>
       </c>
@@ -8179,7 +8206,7 @@
       <c r="A11" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="30" t="s">
         <v>249</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -8197,15 +8224,15 @@
       <c r="G11" s="1" t="n">
         <v>10525</v>
       </c>
-      <c r="H11" s="28" t="n">
+      <c r="H11" s="31" t="n">
         <f aca="false">ROUND(D11*IF(ISNUMBER(SEARCH("Labour",B11)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B11)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B11)),ISNUMBER(SEARCH("RefUK",B11))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B11)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B11)),ISNUMBER(SEARCH("Lib Dem",B11))),National!$L$8,National!$L$9))))),0)</f>
         <v>449</v>
       </c>
-      <c r="I11" s="25" t="n">
+      <c r="I11" s="27" t="n">
         <f aca="false">H11/SUMIFS(H:H,A:A,A11)</f>
         <v>0.121548456957228</v>
       </c>
-      <c r="J11" s="29" t="n">
+      <c r="J11" s="32" t="n">
         <f aca="false">ROUND(I11*SUMIF(A:A,A11,D:D),0)</f>
         <v>718</v>
       </c>
@@ -8213,11 +8240,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A11,B:B,B11)/COUNTIFS(B:B,B11,A:A,A11),0)</f>
         <v>263</v>
       </c>
-      <c r="L11" s="25" t="n">
+      <c r="L11" s="27" t="n">
         <f aca="false">K11/SUMIF(A:A,A11,K:K)</f>
         <v>0.0806748466257669</v>
       </c>
-      <c r="M11" s="1" t="n">
+      <c r="M11" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A11,J:J)*L11,0)</f>
         <v>477</v>
       </c>
@@ -8238,7 +8265,7 @@
       <c r="A12" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -8256,15 +8283,15 @@
       <c r="G12" s="1" t="n">
         <v>10525</v>
       </c>
-      <c r="H12" s="28" t="n">
+      <c r="H12" s="31" t="n">
         <f aca="false">ROUND(D12*IF(ISNUMBER(SEARCH("Labour",B12)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B12)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B12)),ISNUMBER(SEARCH("RefUK",B12))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B12)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B12)),ISNUMBER(SEARCH("Lib Dem",B12))),National!$L$8,National!$L$9))))),0)</f>
         <v>361</v>
       </c>
-      <c r="I12" s="25" t="n">
+      <c r="I12" s="27" t="n">
         <f aca="false">H12/SUMIFS(H:H,A:A,A12)</f>
         <v>0.0977260422306443</v>
       </c>
-      <c r="J12" s="29" t="n">
+      <c r="J12" s="32" t="n">
         <f aca="false">ROUND(I12*SUMIF(A:A,A12,D:D),0)</f>
         <v>577</v>
       </c>
@@ -8272,11 +8299,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A12,B:B,B12)/COUNTIFS(B:B,B12,A:A,A12),0)</f>
         <v>178</v>
       </c>
-      <c r="L12" s="25" t="n">
+      <c r="L12" s="27" t="n">
         <f aca="false">K12/SUMIF(A:A,A12,K:K)</f>
         <v>0.054601226993865</v>
       </c>
-      <c r="M12" s="1" t="n">
+      <c r="M12" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A12,J:J)*L12,0)</f>
         <v>323</v>
       </c>
@@ -8297,7 +8324,7 @@
       <c r="A13" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -8315,15 +8342,15 @@
       <c r="G13" s="1" t="n">
         <v>10525</v>
       </c>
-      <c r="H13" s="28" t="n">
+      <c r="H13" s="31" t="n">
         <f aca="false">ROUND(D13*IF(ISNUMBER(SEARCH("Labour",B13)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B13)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B13)),ISNUMBER(SEARCH("RefUK",B13))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B13)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B13)),ISNUMBER(SEARCH("Lib Dem",B13))),National!$L$8,National!$L$9))))),0)</f>
         <v>338</v>
       </c>
-      <c r="I13" s="25" t="n">
+      <c r="I13" s="27" t="n">
         <f aca="false">H13/SUMIFS(H:H,A:A,A13)</f>
         <v>0.0914997292907417</v>
       </c>
-      <c r="J13" s="29" t="n">
+      <c r="J13" s="32" t="n">
         <f aca="false">ROUND(I13*SUMIF(A:A,A13,D:D),0)</f>
         <v>541</v>
       </c>
@@ -8331,11 +8358,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A13,B:B,B13)/COUNTIFS(B:B,B13,A:A,A13),0)</f>
         <v>178</v>
       </c>
-      <c r="L13" s="25" t="n">
+      <c r="L13" s="27" t="n">
         <f aca="false">K13/SUMIF(A:A,A13,K:K)</f>
         <v>0.054601226993865</v>
       </c>
-      <c r="M13" s="1" t="n">
+      <c r="M13" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A13,J:J)*L13,0)</f>
         <v>323</v>
       </c>
@@ -8356,7 +8383,7 @@
       <c r="A14" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -8374,15 +8401,15 @@
       <c r="G14" s="1" t="n">
         <v>10525</v>
       </c>
-      <c r="H14" s="28" t="n">
+      <c r="H14" s="31" t="n">
         <f aca="false">ROUND(D14*IF(ISNUMBER(SEARCH("Labour",B14)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B14)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B14)),ISNUMBER(SEARCH("RefUK",B14))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B14)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B14)),ISNUMBER(SEARCH("Lib Dem",B14))),National!$L$8,National!$L$9))))),0)</f>
         <v>305</v>
       </c>
-      <c r="I14" s="25" t="n">
+      <c r="I14" s="27" t="n">
         <f aca="false">H14/SUMIFS(H:H,A:A,A14)</f>
         <v>0.0825663237682729</v>
       </c>
-      <c r="J14" s="29" t="n">
+      <c r="J14" s="32" t="n">
         <f aca="false">ROUND(I14*SUMIF(A:A,A14,D:D),0)</f>
         <v>488</v>
       </c>
@@ -8390,11 +8417,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A14,B:B,B14)/COUNTIFS(B:B,B14,A:A,A14),0)</f>
         <v>178</v>
       </c>
-      <c r="L14" s="25" t="n">
+      <c r="L14" s="27" t="n">
         <f aca="false">K14/SUMIF(A:A,A14,K:K)</f>
         <v>0.054601226993865</v>
       </c>
-      <c r="M14" s="1" t="n">
+      <c r="M14" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A14,J:J)*L14,0)</f>
         <v>323</v>
       </c>
@@ -8415,7 +8442,7 @@
       <c r="A15" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B15" s="30" t="s">
+      <c r="B15" s="33" t="s">
         <v>219</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -8433,15 +8460,15 @@
       <c r="G15" s="1" t="n">
         <v>10525</v>
       </c>
-      <c r="H15" s="28" t="n">
+      <c r="H15" s="31" t="n">
         <f aca="false">ROUND(D15*IF(ISNUMBER(SEARCH("Labour",B15)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B15)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B15)),ISNUMBER(SEARCH("RefUK",B15))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B15)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B15)),ISNUMBER(SEARCH("Lib Dem",B15))),National!$L$8,National!$L$9))))),0)</f>
         <v>798</v>
       </c>
-      <c r="I15" s="25" t="n">
+      <c r="I15" s="27" t="n">
         <f aca="false">H15/SUMIFS(H:H,A:A,A15)</f>
         <v>0.216025988088793</v>
       </c>
-      <c r="J15" s="29" t="n">
+      <c r="J15" s="32" t="n">
         <f aca="false">ROUND(I15*SUMIF(A:A,A15,D:D),0)</f>
         <v>1276</v>
       </c>
@@ -8449,11 +8476,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A15,B:B,B15)/COUNTIFS(B:B,B15,A:A,A15),0)</f>
         <v>1276</v>
       </c>
-      <c r="L15" s="25" t="n">
+      <c r="L15" s="27" t="n">
         <f aca="false">K15/SUMIF(A:A,A15,K:K)</f>
         <v>0.391411042944785</v>
       </c>
-      <c r="M15" s="1" t="n">
+      <c r="M15" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A15,J:J)*L15,0)</f>
         <v>2312</v>
       </c>
@@ -8474,7 +8501,7 @@
       <c r="A16" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -8492,15 +8519,15 @@
       <c r="G16" s="1" t="n">
         <v>10525</v>
       </c>
-      <c r="H16" s="28" t="n">
+      <c r="H16" s="31" t="n">
         <f aca="false">ROUND(D16*IF(ISNUMBER(SEARCH("Labour",B16)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B16)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B16)),ISNUMBER(SEARCH("RefUK",B16))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B16)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B16)),ISNUMBER(SEARCH("Lib Dem",B16))),National!$L$8,National!$L$9))))),0)</f>
         <v>413</v>
       </c>
-      <c r="I16" s="25" t="n">
+      <c r="I16" s="27" t="n">
         <f aca="false">H16/SUMIFS(H:H,A:A,A16)</f>
         <v>0.111802923659989</v>
       </c>
-      <c r="J16" s="29" t="n">
+      <c r="J16" s="32" t="n">
         <f aca="false">ROUND(I16*SUMIF(A:A,A16,D:D),0)</f>
         <v>661</v>
       </c>
@@ -8508,11 +8535,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A16,B:B,B16)/COUNTIFS(B:B,B16,A:A,A16),0)</f>
         <v>661</v>
       </c>
-      <c r="L16" s="25" t="n">
+      <c r="L16" s="27" t="n">
         <f aca="false">K16/SUMIF(A:A,A16,K:K)</f>
         <v>0.202760736196319</v>
       </c>
-      <c r="M16" s="1" t="n">
+      <c r="M16" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A16,J:J)*L16,0)</f>
         <v>1198</v>
       </c>
@@ -8533,7 +8560,7 @@
       <c r="A17" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -8551,15 +8578,15 @@
       <c r="G17" s="1" t="n">
         <v>6129</v>
       </c>
-      <c r="H17" s="28" t="n">
+      <c r="H17" s="31" t="n">
         <f aca="false">ROUND(D17*IF(ISNUMBER(SEARCH("Labour",B17)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B17)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B17)),ISNUMBER(SEARCH("RefUK",B17))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B17)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B17)),ISNUMBER(SEARCH("Lib Dem",B17))),National!$L$8,National!$L$9))))),0)</f>
         <v>575</v>
       </c>
-      <c r="I17" s="25" t="n">
+      <c r="I17" s="27" t="n">
         <f aca="false">H17/SUMIFS(H:H,A:A,A17)</f>
         <v>0.137955854126679</v>
       </c>
-      <c r="J17" s="29" t="n">
+      <c r="J17" s="32" t="n">
         <f aca="false">ROUND(I17*SUMIF(A:A,A17,D:D),0)</f>
         <v>497</v>
       </c>
@@ -8567,11 +8594,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A17,B:B,B17)/COUNTIFS(B:B,B17,A:A,A17),0)</f>
         <v>221</v>
       </c>
-      <c r="L17" s="25" t="n">
+      <c r="L17" s="27" t="n">
         <f aca="false">K17/SUMIF(A:A,A17,K:K)</f>
         <v>0.119588744588745</v>
       </c>
-      <c r="M17" s="1" t="n">
+      <c r="M17" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A17,J:J)*L17,0)</f>
         <v>431</v>
       </c>
@@ -8592,7 +8619,7 @@
       <c r="A18" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B18" s="27" t="s">
+      <c r="B18" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -8610,15 +8637,15 @@
       <c r="G18" s="1" t="n">
         <v>6129</v>
       </c>
-      <c r="H18" s="28" t="n">
+      <c r="H18" s="31" t="n">
         <f aca="false">ROUND(D18*IF(ISNUMBER(SEARCH("Labour",B18)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B18)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B18)),ISNUMBER(SEARCH("RefUK",B18))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B18)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B18)),ISNUMBER(SEARCH("Lib Dem",B18))),National!$L$8,National!$L$9))))),0)</f>
         <v>448</v>
       </c>
-      <c r="I18" s="25" t="n">
+      <c r="I18" s="27" t="n">
         <f aca="false">H18/SUMIFS(H:H,A:A,A18)</f>
         <v>0.107485604606526</v>
       </c>
-      <c r="J18" s="29" t="n">
+      <c r="J18" s="32" t="n">
         <f aca="false">ROUND(I18*SUMIF(A:A,A18,D:D),0)</f>
         <v>388</v>
       </c>
@@ -8626,11 +8653,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A18,B:B,B18)/COUNTIFS(B:B,B18,A:A,A18),0)</f>
         <v>221</v>
       </c>
-      <c r="L18" s="25" t="n">
+      <c r="L18" s="27" t="n">
         <f aca="false">K18/SUMIF(A:A,A18,K:K)</f>
         <v>0.119588744588745</v>
       </c>
-      <c r="M18" s="1" t="n">
+      <c r="M18" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A18,J:J)*L18,0)</f>
         <v>431</v>
       </c>
@@ -8651,7 +8678,7 @@
       <c r="A19" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B19" s="30" t="s">
+      <c r="B19" s="33" t="s">
         <v>219</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -8669,15 +8696,15 @@
       <c r="G19" s="1" t="n">
         <v>6129</v>
       </c>
-      <c r="H19" s="28" t="n">
+      <c r="H19" s="31" t="n">
         <f aca="false">ROUND(D19*IF(ISNUMBER(SEARCH("Labour",B19)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B19)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B19)),ISNUMBER(SEARCH("RefUK",B19))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B19)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B19)),ISNUMBER(SEARCH("Lib Dem",B19))),National!$L$8,National!$L$9))))),0)</f>
         <v>1522</v>
       </c>
-      <c r="I19" s="25" t="n">
+      <c r="I19" s="27" t="n">
         <f aca="false">H19/SUMIFS(H:H,A:A,A19)</f>
         <v>0.365163147792706</v>
       </c>
-      <c r="J19" s="29" t="n">
+      <c r="J19" s="32" t="n">
         <f aca="false">ROUND(I19*SUMIF(A:A,A19,D:D),0)</f>
         <v>1317</v>
       </c>
@@ -8685,11 +8712,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A19,B:B,B19)/COUNTIFS(B:B,B19,A:A,A19),0)</f>
         <v>587</v>
       </c>
-      <c r="L19" s="25" t="n">
+      <c r="L19" s="27" t="n">
         <f aca="false">K19/SUMIF(A:A,A19,K:K)</f>
         <v>0.317640692640693</v>
       </c>
-      <c r="M19" s="1" t="n">
+      <c r="M19" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A19,J:J)*L19,0)</f>
         <v>1145</v>
       </c>
@@ -8710,7 +8737,7 @@
       <c r="A20" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B20" s="30" t="s">
+      <c r="B20" s="33" t="s">
         <v>219</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -8728,15 +8755,15 @@
       <c r="G20" s="1" t="n">
         <v>6129</v>
       </c>
-      <c r="H20" s="28" t="n">
+      <c r="H20" s="31" t="n">
         <f aca="false">ROUND(D20*IF(ISNUMBER(SEARCH("Labour",B20)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B20)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B20)),ISNUMBER(SEARCH("RefUK",B20))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B20)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B20)),ISNUMBER(SEARCH("Lib Dem",B20))),National!$L$8,National!$L$9))))),0)</f>
         <v>1192</v>
       </c>
-      <c r="I20" s="25" t="n">
+      <c r="I20" s="27" t="n">
         <f aca="false">H20/SUMIFS(H:H,A:A,A20)</f>
         <v>0.285988483685221</v>
       </c>
-      <c r="J20" s="29" t="n">
+      <c r="J20" s="32" t="n">
         <f aca="false">ROUND(I20*SUMIF(A:A,A20,D:D),0)</f>
         <v>1031</v>
       </c>
@@ -8744,11 +8771,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A20,B:B,B20)/COUNTIFS(B:B,B20,A:A,A20),0)</f>
         <v>587</v>
       </c>
-      <c r="L20" s="25" t="n">
+      <c r="L20" s="27" t="n">
         <f aca="false">K20/SUMIF(A:A,A20,K:K)</f>
         <v>0.317640692640693</v>
       </c>
-      <c r="M20" s="1" t="n">
+      <c r="M20" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A20,J:J)*L20,0)</f>
         <v>1145</v>
       </c>
@@ -8769,7 +8796,7 @@
       <c r="A21" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="30" t="s">
         <v>216</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -8787,15 +8814,15 @@
       <c r="G21" s="1" t="n">
         <v>6129</v>
       </c>
-      <c r="H21" s="28" t="n">
+      <c r="H21" s="31" t="n">
         <f aca="false">ROUND(D21*IF(ISNUMBER(SEARCH("Labour",B21)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B21)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B21)),ISNUMBER(SEARCH("RefUK",B21))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B21)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B21)),ISNUMBER(SEARCH("Lib Dem",B21))),National!$L$8,National!$L$9))))),0)</f>
         <v>164</v>
       </c>
-      <c r="I21" s="25" t="n">
+      <c r="I21" s="27" t="n">
         <f aca="false">H21/SUMIFS(H:H,A:A,A21)</f>
         <v>0.0393474088291747</v>
       </c>
-      <c r="J21" s="29" t="n">
+      <c r="J21" s="32" t="n">
         <f aca="false">ROUND(I21*SUMIF(A:A,A21,D:D),0)</f>
         <v>142</v>
       </c>
@@ -8803,11 +8830,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A21,B:B,B21)/COUNTIFS(B:B,B21,A:A,A21),0)</f>
         <v>70</v>
       </c>
-      <c r="L21" s="25" t="n">
+      <c r="L21" s="27" t="n">
         <f aca="false">K21/SUMIF(A:A,A21,K:K)</f>
         <v>0.0378787878787879</v>
       </c>
-      <c r="M21" s="1" t="n">
+      <c r="M21" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A21,J:J)*L21,0)</f>
         <v>137</v>
       </c>
@@ -8828,7 +8855,7 @@
       <c r="A22" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="30" t="s">
         <v>216</v>
       </c>
       <c r="C22" s="1" t="s">
@@ -8846,15 +8873,15 @@
       <c r="G22" s="1" t="n">
         <v>6129</v>
       </c>
-      <c r="H22" s="28" t="n">
+      <c r="H22" s="31" t="n">
         <f aca="false">ROUND(D22*IF(ISNUMBER(SEARCH("Labour",B22)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B22)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B22)),ISNUMBER(SEARCH("RefUK",B22))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B22)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B22)),ISNUMBER(SEARCH("Lib Dem",B22))),National!$L$8,National!$L$9))))),0)</f>
         <v>161</v>
       </c>
-      <c r="I22" s="25" t="n">
+      <c r="I22" s="27" t="n">
         <f aca="false">H22/SUMIFS(H:H,A:A,A22)</f>
         <v>0.0386276391554702</v>
       </c>
-      <c r="J22" s="29" t="n">
+      <c r="J22" s="32" t="n">
         <f aca="false">ROUND(I22*SUMIF(A:A,A22,D:D),0)</f>
         <v>139</v>
       </c>
@@ -8862,11 +8889,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A22,B:B,B22)/COUNTIFS(B:B,B22,A:A,A22),0)</f>
         <v>70</v>
       </c>
-      <c r="L22" s="25" t="n">
+      <c r="L22" s="27" t="n">
         <f aca="false">K22/SUMIF(A:A,A22,K:K)</f>
         <v>0.0378787878787879</v>
       </c>
-      <c r="M22" s="1" t="n">
+      <c r="M22" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A22,J:J)*L22,0)</f>
         <v>137</v>
       </c>
@@ -8887,7 +8914,7 @@
       <c r="A23" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C23" s="1" t="s">
@@ -8905,15 +8932,15 @@
       <c r="G23" s="1" t="n">
         <v>6129</v>
       </c>
-      <c r="H23" s="28" t="n">
+      <c r="H23" s="31" t="n">
         <f aca="false">ROUND(D23*IF(ISNUMBER(SEARCH("Labour",B23)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B23)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B23)),ISNUMBER(SEARCH("RefUK",B23))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B23)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B23)),ISNUMBER(SEARCH("Lib Dem",B23))),National!$L$8,National!$L$9))))),0)</f>
         <v>106</v>
       </c>
-      <c r="I23" s="25" t="n">
+      <c r="I23" s="27" t="n">
         <f aca="false">H23/SUMIFS(H:H,A:A,A23)</f>
         <v>0.0254318618042227</v>
       </c>
-      <c r="J23" s="29" t="n">
+      <c r="J23" s="32" t="n">
         <f aca="false">ROUND(I23*SUMIF(A:A,A23,D:D),0)</f>
         <v>92</v>
       </c>
@@ -8921,11 +8948,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A23,B:B,B23)/COUNTIFS(B:B,B23,A:A,A23),0)</f>
         <v>92</v>
       </c>
-      <c r="L23" s="25" t="n">
+      <c r="L23" s="27" t="n">
         <f aca="false">K23/SUMIF(A:A,A23,K:K)</f>
         <v>0.0497835497835498</v>
       </c>
-      <c r="M23" s="1" t="n">
+      <c r="M23" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A23,J:J)*L23,0)</f>
         <v>180</v>
       </c>
@@ -8946,7 +8973,7 @@
       <c r="A24" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C24" s="1" t="s">
@@ -8964,15 +8991,15 @@
       <c r="G24" s="1" t="n">
         <v>3530</v>
       </c>
-      <c r="H24" s="28" t="n">
+      <c r="H24" s="31" t="n">
         <f aca="false">ROUND(D24*IF(ISNUMBER(SEARCH("Labour",B24)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B24)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B24)),ISNUMBER(SEARCH("RefUK",B24))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B24)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B24)),ISNUMBER(SEARCH("Lib Dem",B24))),National!$L$8,National!$L$9))))),0)</f>
         <v>320</v>
       </c>
-      <c r="I24" s="25" t="n">
+      <c r="I24" s="27" t="n">
         <f aca="false">H24/SUMIFS(H:H,A:A,A24)</f>
         <v>0.328542094455852</v>
       </c>
-      <c r="J24" s="29" t="n">
+      <c r="J24" s="32" t="n">
         <f aca="false">ROUND(I24*SUMIF(A:A,A24,D:D),0)</f>
         <v>355</v>
       </c>
@@ -8980,11 +9007,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A24,B:B,B24)/COUNTIFS(B:B,B24,A:A,A24),0)</f>
         <v>355</v>
       </c>
-      <c r="L24" s="25" t="n">
+      <c r="L24" s="27" t="n">
         <f aca="false">K24/SUMIF(A:A,A24,K:K)</f>
         <v>0.328399629972248</v>
       </c>
-      <c r="M24" s="1" t="n">
+      <c r="M24" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A24,J:J)*L24,0)</f>
         <v>355</v>
       </c>
@@ -9005,7 +9032,7 @@
       <c r="A25" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B25" s="27" t="s">
+      <c r="B25" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -9023,15 +9050,15 @@
       <c r="G25" s="1" t="n">
         <v>3530</v>
       </c>
-      <c r="H25" s="28" t="n">
+      <c r="H25" s="31" t="n">
         <f aca="false">ROUND(D25*IF(ISNUMBER(SEARCH("Labour",B25)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B25)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B25)),ISNUMBER(SEARCH("RefUK",B25))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B25)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B25)),ISNUMBER(SEARCH("Lib Dem",B25))),National!$L$8,National!$L$9))))),0)</f>
         <v>482</v>
       </c>
-      <c r="I25" s="25" t="n">
+      <c r="I25" s="27" t="n">
         <f aca="false">H25/SUMIFS(H:H,A:A,A25)</f>
         <v>0.494866529774127</v>
       </c>
-      <c r="J25" s="29" t="n">
+      <c r="J25" s="32" t="n">
         <f aca="false">ROUND(I25*SUMIF(A:A,A25,D:D),0)</f>
         <v>535</v>
       </c>
@@ -9039,11 +9066,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A25,B:B,B25)/COUNTIFS(B:B,B25,A:A,A25),0)</f>
         <v>535</v>
       </c>
-      <c r="L25" s="25" t="n">
+      <c r="L25" s="27" t="n">
         <f aca="false">K25/SUMIF(A:A,A25,K:K)</f>
         <v>0.494912118408881</v>
       </c>
-      <c r="M25" s="1" t="n">
+      <c r="M25" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A25,J:J)*L25,0)</f>
         <v>535</v>
       </c>
@@ -9064,7 +9091,7 @@
       <c r="A26" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B26" s="27" t="s">
+      <c r="B26" s="30" t="s">
         <v>216</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -9082,15 +9109,15 @@
       <c r="G26" s="1" t="n">
         <v>3530</v>
       </c>
-      <c r="H26" s="28" t="n">
+      <c r="H26" s="31" t="n">
         <f aca="false">ROUND(D26*IF(ISNUMBER(SEARCH("Labour",B26)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B26)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B26)),ISNUMBER(SEARCH("RefUK",B26))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B26)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B26)),ISNUMBER(SEARCH("Lib Dem",B26))),National!$L$8,National!$L$9))))),0)</f>
         <v>84</v>
       </c>
-      <c r="I26" s="25" t="n">
+      <c r="I26" s="27" t="n">
         <f aca="false">H26/SUMIFS(H:H,A:A,A26)</f>
         <v>0.0862422997946612</v>
       </c>
-      <c r="J26" s="29" t="n">
+      <c r="J26" s="32" t="n">
         <f aca="false">ROUND(I26*SUMIF(A:A,A26,D:D),0)</f>
         <v>93</v>
       </c>
@@ -9098,11 +9125,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A26,B:B,B26)/COUNTIFS(B:B,B26,A:A,A26),0)</f>
         <v>93</v>
       </c>
-      <c r="L26" s="25" t="n">
+      <c r="L26" s="27" t="n">
         <f aca="false">K26/SUMIF(A:A,A26,K:K)</f>
         <v>0.0860314523589269</v>
       </c>
-      <c r="M26" s="1" t="n">
+      <c r="M26" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A26,J:J)*L26,0)</f>
         <v>93</v>
       </c>
@@ -9123,7 +9150,7 @@
       <c r="A27" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B27" s="30" t="s">
+      <c r="B27" s="33" t="s">
         <v>219</v>
       </c>
       <c r="C27" s="1" t="s">
@@ -9141,15 +9168,15 @@
       <c r="G27" s="1" t="n">
         <v>3530</v>
       </c>
-      <c r="H27" s="28" t="n">
+      <c r="H27" s="31" t="n">
         <f aca="false">ROUND(D27*IF(ISNUMBER(SEARCH("Labour",B27)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B27)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B27)),ISNUMBER(SEARCH("RefUK",B27))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B27)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B27)),ISNUMBER(SEARCH("Lib Dem",B27))),National!$L$8,National!$L$9))))),0)</f>
         <v>88</v>
       </c>
-      <c r="I27" s="25" t="n">
+      <c r="I27" s="27" t="n">
         <f aca="false">H27/SUMIFS(H:H,A:A,A27)</f>
         <v>0.0903490759753594</v>
       </c>
-      <c r="J27" s="29" t="n">
+      <c r="J27" s="32" t="n">
         <f aca="false">ROUND(I27*SUMIF(A:A,A27,D:D),0)</f>
         <v>98</v>
       </c>
@@ -9157,11 +9184,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A27,B:B,B27)/COUNTIFS(B:B,B27,A:A,A27),0)</f>
         <v>98</v>
       </c>
-      <c r="L27" s="25" t="n">
+      <c r="L27" s="27" t="n">
         <f aca="false">K27/SUMIF(A:A,A27,K:K)</f>
         <v>0.0906567992599445</v>
       </c>
-      <c r="M27" s="1" t="n">
+      <c r="M27" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A27,J:J)*L27,0)</f>
         <v>98</v>
       </c>
@@ -9182,7 +9209,7 @@
       <c r="A28" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B28" s="27" t="s">
+      <c r="B28" s="30" t="s">
         <v>249</v>
       </c>
       <c r="C28" s="1" t="s">
@@ -9200,15 +9227,15 @@
       <c r="G28" s="1" t="n">
         <v>9170</v>
       </c>
-      <c r="H28" s="28" t="n">
+      <c r="H28" s="31" t="n">
         <f aca="false">ROUND(D28*IF(ISNUMBER(SEARCH("Labour",B28)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B28)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B28)),ISNUMBER(SEARCH("RefUK",B28))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B28)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B28)),ISNUMBER(SEARCH("Lib Dem",B28))),National!$L$8,National!$L$9))))),0)</f>
         <v>682</v>
       </c>
-      <c r="I28" s="25" t="n">
+      <c r="I28" s="27" t="n">
         <f aca="false">H28/SUMIFS(H:H,A:A,A28)</f>
         <v>0.125482980680773</v>
       </c>
-      <c r="J28" s="29" t="n">
+      <c r="J28" s="32" t="n">
         <f aca="false">ROUND(I28*SUMIF(A:A,A28,D:D),0)</f>
         <v>1078</v>
       </c>
@@ -9216,11 +9243,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A28,B:B,B28)/COUNTIFS(B:B,B28,A:A,A28),0)</f>
         <v>343</v>
       </c>
-      <c r="L28" s="25" t="n">
+      <c r="L28" s="27" t="n">
         <f aca="false">K28/SUMIF(A:A,A28,K:K)</f>
         <v>0.0753349439929717</v>
       </c>
-      <c r="M28" s="1" t="n">
+      <c r="M28" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A28,J:J)*L28,0)</f>
         <v>647</v>
       </c>
@@ -9241,7 +9268,7 @@
       <c r="A29" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B29" s="27" t="s">
+      <c r="B29" s="30" t="s">
         <v>249</v>
       </c>
       <c r="C29" s="1" t="s">
@@ -9259,15 +9286,15 @@
       <c r="G29" s="1" t="n">
         <v>9170</v>
       </c>
-      <c r="H29" s="28" t="n">
+      <c r="H29" s="31" t="n">
         <f aca="false">ROUND(D29*IF(ISNUMBER(SEARCH("Labour",B29)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B29)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B29)),ISNUMBER(SEARCH("RefUK",B29))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B29)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B29)),ISNUMBER(SEARCH("Lib Dem",B29))),National!$L$8,National!$L$9))))),0)</f>
         <v>646</v>
       </c>
-      <c r="I29" s="25" t="n">
+      <c r="I29" s="27" t="n">
         <f aca="false">H29/SUMIFS(H:H,A:A,A29)</f>
         <v>0.118859245630175</v>
       </c>
-      <c r="J29" s="29" t="n">
+      <c r="J29" s="32" t="n">
         <f aca="false">ROUND(I29*SUMIF(A:A,A29,D:D),0)</f>
         <v>1021</v>
       </c>
@@ -9275,11 +9302,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A29,B:B,B29)/COUNTIFS(B:B,B29,A:A,A29),0)</f>
         <v>343</v>
       </c>
-      <c r="L29" s="25" t="n">
+      <c r="L29" s="27" t="n">
         <f aca="false">K29/SUMIF(A:A,A29,K:K)</f>
         <v>0.0753349439929717</v>
       </c>
-      <c r="M29" s="1" t="n">
+      <c r="M29" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A29,J:J)*L29,0)</f>
         <v>647</v>
       </c>
@@ -9300,7 +9327,7 @@
       <c r="A30" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B30" s="27" t="s">
+      <c r="B30" s="30" t="s">
         <v>249</v>
       </c>
       <c r="C30" s="1" t="s">
@@ -9318,15 +9345,15 @@
       <c r="G30" s="1" t="n">
         <v>9170</v>
       </c>
-      <c r="H30" s="28" t="n">
+      <c r="H30" s="31" t="n">
         <f aca="false">ROUND(D30*IF(ISNUMBER(SEARCH("Labour",B30)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B30)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B30)),ISNUMBER(SEARCH("RefUK",B30))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B30)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B30)),ISNUMBER(SEARCH("Lib Dem",B30))),National!$L$8,National!$L$9))))),0)</f>
         <v>623</v>
       </c>
-      <c r="I30" s="25" t="n">
+      <c r="I30" s="27" t="n">
         <f aca="false">H30/SUMIFS(H:H,A:A,A30)</f>
         <v>0.114627414903404</v>
       </c>
-      <c r="J30" s="29" t="n">
+      <c r="J30" s="32" t="n">
         <f aca="false">ROUND(I30*SUMIF(A:A,A30,D:D),0)</f>
         <v>985</v>
       </c>
@@ -9334,11 +9361,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A30,B:B,B30)/COUNTIFS(B:B,B30,A:A,A30),0)</f>
         <v>343</v>
       </c>
-      <c r="L30" s="25" t="n">
+      <c r="L30" s="27" t="n">
         <f aca="false">K30/SUMIF(A:A,A30,K:K)</f>
         <v>0.0753349439929717</v>
       </c>
-      <c r="M30" s="1" t="n">
+      <c r="M30" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A30,J:J)*L30,0)</f>
         <v>647</v>
       </c>
@@ -9359,7 +9386,7 @@
       <c r="A31" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B31" s="27" t="s">
+      <c r="B31" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C31" s="1" t="s">
@@ -9377,15 +9404,15 @@
       <c r="G31" s="1" t="n">
         <v>9170</v>
       </c>
-      <c r="H31" s="28" t="n">
+      <c r="H31" s="31" t="n">
         <f aca="false">ROUND(D31*IF(ISNUMBER(SEARCH("Labour",B31)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B31)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B31)),ISNUMBER(SEARCH("RefUK",B31))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B31)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B31)),ISNUMBER(SEARCH("Lib Dem",B31))),National!$L$8,National!$L$9))))),0)</f>
         <v>672</v>
       </c>
-      <c r="I31" s="25" t="n">
+      <c r="I31" s="27" t="n">
         <f aca="false">H31/SUMIFS(H:H,A:A,A31)</f>
         <v>0.123643054277829</v>
       </c>
-      <c r="J31" s="29" t="n">
+      <c r="J31" s="32" t="n">
         <f aca="false">ROUND(I31*SUMIF(A:A,A31,D:D),0)</f>
         <v>1062</v>
       </c>
@@ -9393,11 +9420,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A31,B:B,B31)/COUNTIFS(B:B,B31,A:A,A31),0)</f>
         <v>331</v>
       </c>
-      <c r="L31" s="25" t="n">
+      <c r="L31" s="27" t="n">
         <f aca="false">K31/SUMIF(A:A,A31,K:K)</f>
         <v>0.0726993191302438</v>
       </c>
-      <c r="M31" s="1" t="n">
+      <c r="M31" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A31,J:J)*L31,0)</f>
         <v>625</v>
       </c>
@@ -9418,7 +9445,7 @@
       <c r="A32" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C32" s="1" t="s">
@@ -9436,15 +9463,15 @@
       <c r="G32" s="1" t="n">
         <v>9170</v>
       </c>
-      <c r="H32" s="28" t="n">
+      <c r="H32" s="31" t="n">
         <f aca="false">ROUND(D32*IF(ISNUMBER(SEARCH("Labour",B32)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B32)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B32)),ISNUMBER(SEARCH("RefUK",B32))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B32)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B32)),ISNUMBER(SEARCH("Lib Dem",B32))),National!$L$8,National!$L$9))))),0)</f>
         <v>622</v>
       </c>
-      <c r="I32" s="25" t="n">
+      <c r="I32" s="27" t="n">
         <f aca="false">H32/SUMIFS(H:H,A:A,A32)</f>
         <v>0.114443422263109</v>
       </c>
-      <c r="J32" s="29" t="n">
+      <c r="J32" s="32" t="n">
         <f aca="false">ROUND(I32*SUMIF(A:A,A32,D:D),0)</f>
         <v>983</v>
       </c>
@@ -9452,11 +9479,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A32,B:B,B32)/COUNTIFS(B:B,B32,A:A,A32),0)</f>
         <v>331</v>
       </c>
-      <c r="L32" s="25" t="n">
+      <c r="L32" s="27" t="n">
         <f aca="false">K32/SUMIF(A:A,A32,K:K)</f>
         <v>0.0726993191302438</v>
       </c>
-      <c r="M32" s="1" t="n">
+      <c r="M32" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A32,J:J)*L32,0)</f>
         <v>625</v>
       </c>
@@ -9477,7 +9504,7 @@
       <c r="A33" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B33" s="27" t="s">
+      <c r="B33" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C33" s="1" t="s">
@@ -9495,15 +9522,15 @@
       <c r="G33" s="1" t="n">
         <v>9170</v>
       </c>
-      <c r="H33" s="28" t="n">
+      <c r="H33" s="31" t="n">
         <f aca="false">ROUND(D33*IF(ISNUMBER(SEARCH("Labour",B33)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B33)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B33)),ISNUMBER(SEARCH("RefUK",B33))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B33)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B33)),ISNUMBER(SEARCH("Lib Dem",B33))),National!$L$8,National!$L$9))))),0)</f>
         <v>589</v>
       </c>
-      <c r="I33" s="25" t="n">
+      <c r="I33" s="27" t="n">
         <f aca="false">H33/SUMIFS(H:H,A:A,A33)</f>
         <v>0.108371665133395</v>
       </c>
-      <c r="J33" s="29" t="n">
+      <c r="J33" s="32" t="n">
         <f aca="false">ROUND(I33*SUMIF(A:A,A33,D:D),0)</f>
         <v>931</v>
       </c>
@@ -9511,11 +9538,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A33,B:B,B33)/COUNTIFS(B:B,B33,A:A,A33),0)</f>
         <v>331</v>
       </c>
-      <c r="L33" s="25" t="n">
+      <c r="L33" s="27" t="n">
         <f aca="false">K33/SUMIF(A:A,A33,K:K)</f>
         <v>0.0726993191302438</v>
       </c>
-      <c r="M33" s="1" t="n">
+      <c r="M33" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A33,J:J)*L33,0)</f>
         <v>625</v>
       </c>
@@ -9536,7 +9563,7 @@
       <c r="A34" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B34" s="30" t="s">
+      <c r="B34" s="33" t="s">
         <v>219</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -9554,15 +9581,15 @@
       <c r="G34" s="1" t="n">
         <v>9170</v>
       </c>
-      <c r="H34" s="28" t="n">
+      <c r="H34" s="31" t="n">
         <f aca="false">ROUND(D34*IF(ISNUMBER(SEARCH("Labour",B34)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B34)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B34)),ISNUMBER(SEARCH("RefUK",B34))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B34)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B34)),ISNUMBER(SEARCH("Lib Dem",B34))),National!$L$8,National!$L$9))))),0)</f>
         <v>1252</v>
       </c>
-      <c r="I34" s="25" t="n">
+      <c r="I34" s="27" t="n">
         <f aca="false">H34/SUMIFS(H:H,A:A,A34)</f>
         <v>0.230358785648574</v>
       </c>
-      <c r="J34" s="29" t="n">
+      <c r="J34" s="32" t="n">
         <f aca="false">ROUND(I34*SUMIF(A:A,A34,D:D),0)</f>
         <v>1979</v>
       </c>
@@ -9570,11 +9597,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A34,B:B,B34)/COUNTIFS(B:B,B34,A:A,A34),0)</f>
         <v>1979</v>
       </c>
-      <c r="L34" s="25" t="n">
+      <c r="L34" s="27" t="n">
         <f aca="false">K34/SUMIF(A:A,A34,K:K)</f>
         <v>0.434658466944872</v>
       </c>
-      <c r="M34" s="1" t="n">
+      <c r="M34" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A34,J:J)*L34,0)</f>
         <v>3734</v>
       </c>
@@ -9595,7 +9622,7 @@
       <c r="A35" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B35" s="27" t="s">
+      <c r="B35" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C35" s="1" t="s">
@@ -9613,15 +9640,15 @@
       <c r="G35" s="1" t="n">
         <v>9170</v>
       </c>
-      <c r="H35" s="28" t="n">
+      <c r="H35" s="31" t="n">
         <f aca="false">ROUND(D35*IF(ISNUMBER(SEARCH("Labour",B35)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B35)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B35)),ISNUMBER(SEARCH("RefUK",B35))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B35)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B35)),ISNUMBER(SEARCH("Lib Dem",B35))),National!$L$8,National!$L$9))))),0)</f>
         <v>349</v>
       </c>
-      <c r="I35" s="25" t="n">
+      <c r="I35" s="27" t="n">
         <f aca="false">H35/SUMIFS(H:H,A:A,A35)</f>
         <v>0.0642134314627415</v>
       </c>
-      <c r="J35" s="29" t="n">
+      <c r="J35" s="32" t="n">
         <f aca="false">ROUND(I35*SUMIF(A:A,A35,D:D),0)</f>
         <v>552</v>
       </c>
@@ -9629,11 +9656,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A35,B:B,B35)/COUNTIFS(B:B,B35,A:A,A35),0)</f>
         <v>552</v>
       </c>
-      <c r="L35" s="25" t="n">
+      <c r="L35" s="27" t="n">
         <f aca="false">K35/SUMIF(A:A,A35,K:K)</f>
         <v>0.121238743685482</v>
       </c>
-      <c r="M35" s="1" t="n">
+      <c r="M35" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A35,J:J)*L35,0)</f>
         <v>1042</v>
       </c>
@@ -9654,7 +9681,7 @@
       <c r="A36" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B36" s="27" t="s">
+      <c r="B36" s="30" t="s">
         <v>249</v>
       </c>
       <c r="C36" s="1" t="s">
@@ -9672,15 +9699,15 @@
       <c r="G36" s="1" t="n">
         <v>10237</v>
       </c>
-      <c r="H36" s="28" t="n">
+      <c r="H36" s="31" t="n">
         <f aca="false">ROUND(D36*IF(ISNUMBER(SEARCH("Labour",B36)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B36)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B36)),ISNUMBER(SEARCH("RefUK",B36))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B36)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B36)),ISNUMBER(SEARCH("Lib Dem",B36))),National!$L$8,National!$L$9))))),0)</f>
         <v>561</v>
       </c>
-      <c r="I36" s="25" t="n">
+      <c r="I36" s="27" t="n">
         <f aca="false">H36/SUMIFS(H:H,A:A,A36)</f>
         <v>0.151950162513543</v>
       </c>
-      <c r="J36" s="29" t="n">
+      <c r="J36" s="32" t="n">
         <f aca="false">ROUND(I36*SUMIF(A:A,A36,D:D),0)</f>
         <v>925</v>
       </c>
@@ -9688,11 +9715,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A36,B:B,B36)/COUNTIFS(B:B,B36,A:A,A36),0)</f>
         <v>298</v>
       </c>
-      <c r="L36" s="25" t="n">
+      <c r="L36" s="27" t="n">
         <f aca="false">K36/SUMIF(A:A,A36,K:K)</f>
         <v>0.0900846432889964</v>
       </c>
-      <c r="M36" s="1" t="n">
+      <c r="M36" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A36,J:J)*L36,0)</f>
         <v>548</v>
       </c>
@@ -9713,7 +9740,7 @@
       <c r="A37" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B37" s="27" t="s">
+      <c r="B37" s="30" t="s">
         <v>249</v>
       </c>
       <c r="C37" s="1" t="s">
@@ -9731,15 +9758,15 @@
       <c r="G37" s="1" t="n">
         <v>10237</v>
       </c>
-      <c r="H37" s="28" t="n">
+      <c r="H37" s="31" t="n">
         <f aca="false">ROUND(D37*IF(ISNUMBER(SEARCH("Labour",B37)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B37)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B37)),ISNUMBER(SEARCH("RefUK",B37))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B37)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B37)),ISNUMBER(SEARCH("Lib Dem",B37))),National!$L$8,National!$L$9))))),0)</f>
         <v>536</v>
       </c>
-      <c r="I37" s="25" t="n">
+      <c r="I37" s="27" t="n">
         <f aca="false">H37/SUMIFS(H:H,A:A,A37)</f>
         <v>0.145178764897075</v>
       </c>
-      <c r="J37" s="29" t="n">
+      <c r="J37" s="32" t="n">
         <f aca="false">ROUND(I37*SUMIF(A:A,A37,D:D),0)</f>
         <v>884</v>
       </c>
@@ -9747,11 +9774,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A37,B:B,B37)/COUNTIFS(B:B,B37,A:A,A37),0)</f>
         <v>298</v>
       </c>
-      <c r="L37" s="25" t="n">
+      <c r="L37" s="27" t="n">
         <f aca="false">K37/SUMIF(A:A,A37,K:K)</f>
         <v>0.0900846432889964</v>
       </c>
-      <c r="M37" s="1" t="n">
+      <c r="M37" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A37,J:J)*L37,0)</f>
         <v>548</v>
       </c>
@@ -9772,7 +9799,7 @@
       <c r="A38" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B38" s="27" t="s">
+      <c r="B38" s="30" t="s">
         <v>249</v>
       </c>
       <c r="C38" s="1" t="s">
@@ -9790,15 +9817,15 @@
       <c r="G38" s="1" t="n">
         <v>10237</v>
       </c>
-      <c r="H38" s="28" t="n">
+      <c r="H38" s="31" t="n">
         <f aca="false">ROUND(D38*IF(ISNUMBER(SEARCH("Labour",B38)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B38)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B38)),ISNUMBER(SEARCH("RefUK",B38))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B38)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B38)),ISNUMBER(SEARCH("Lib Dem",B38))),National!$L$8,National!$L$9))))),0)</f>
         <v>529</v>
       </c>
-      <c r="I38" s="25" t="n">
+      <c r="I38" s="27" t="n">
         <f aca="false">H38/SUMIFS(H:H,A:A,A38)</f>
         <v>0.143282773564464</v>
       </c>
-      <c r="J38" s="29" t="n">
+      <c r="J38" s="32" t="n">
         <f aca="false">ROUND(I38*SUMIF(A:A,A38,D:D),0)</f>
         <v>872</v>
       </c>
@@ -9806,11 +9833,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A38,B:B,B38)/COUNTIFS(B:B,B38,A:A,A38),0)</f>
         <v>298</v>
       </c>
-      <c r="L38" s="25" t="n">
+      <c r="L38" s="27" t="n">
         <f aca="false">K38/SUMIF(A:A,A38,K:K)</f>
         <v>0.0900846432889964</v>
       </c>
-      <c r="M38" s="1" t="n">
+      <c r="M38" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A38,J:J)*L38,0)</f>
         <v>548</v>
       </c>
@@ -9831,7 +9858,7 @@
       <c r="A39" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B39" s="27" t="s">
+      <c r="B39" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C39" s="1" t="s">
@@ -9849,15 +9876,15 @@
       <c r="G39" s="1" t="n">
         <v>10237</v>
       </c>
-      <c r="H39" s="28" t="n">
+      <c r="H39" s="31" t="n">
         <f aca="false">ROUND(D39*IF(ISNUMBER(SEARCH("Labour",B39)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B39)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B39)),ISNUMBER(SEARCH("RefUK",B39))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B39)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B39)),ISNUMBER(SEARCH("Lib Dem",B39))),National!$L$8,National!$L$9))))),0)</f>
         <v>347</v>
       </c>
-      <c r="I39" s="25" t="n">
+      <c r="I39" s="27" t="n">
         <f aca="false">H39/SUMIFS(H:H,A:A,A39)</f>
         <v>0.0939869989165764</v>
       </c>
-      <c r="J39" s="29" t="n">
+      <c r="J39" s="32" t="n">
         <f aca="false">ROUND(I39*SUMIF(A:A,A39,D:D),0)</f>
         <v>572</v>
       </c>
@@ -9865,11 +9892,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A39,B:B,B39)/COUNTIFS(B:B,B39,A:A,A39),0)</f>
         <v>165</v>
       </c>
-      <c r="L39" s="25" t="n">
+      <c r="L39" s="27" t="n">
         <f aca="false">K39/SUMIF(A:A,A39,K:K)</f>
         <v>0.0498790810157195</v>
       </c>
-      <c r="M39" s="1" t="n">
+      <c r="M39" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A39,J:J)*L39,0)</f>
         <v>304</v>
       </c>
@@ -9890,7 +9917,7 @@
       <c r="A40" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B40" s="27" t="s">
+      <c r="B40" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C40" s="1" t="s">
@@ -9908,15 +9935,15 @@
       <c r="G40" s="1" t="n">
         <v>10237</v>
       </c>
-      <c r="H40" s="28" t="n">
+      <c r="H40" s="31" t="n">
         <f aca="false">ROUND(D40*IF(ISNUMBER(SEARCH("Labour",B40)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B40)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B40)),ISNUMBER(SEARCH("RefUK",B40))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B40)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B40)),ISNUMBER(SEARCH("Lib Dem",B40))),National!$L$8,National!$L$9))))),0)</f>
         <v>287</v>
       </c>
-      <c r="I40" s="25" t="n">
+      <c r="I40" s="27" t="n">
         <f aca="false">H40/SUMIFS(H:H,A:A,A40)</f>
         <v>0.0777356446370531</v>
       </c>
-      <c r="J40" s="29" t="n">
+      <c r="J40" s="32" t="n">
         <f aca="false">ROUND(I40*SUMIF(A:A,A40,D:D),0)</f>
         <v>473</v>
       </c>
@@ -9924,11 +9951,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A40,B:B,B40)/COUNTIFS(B:B,B40,A:A,A40),0)</f>
         <v>165</v>
       </c>
-      <c r="L40" s="25" t="n">
+      <c r="L40" s="27" t="n">
         <f aca="false">K40/SUMIF(A:A,A40,K:K)</f>
         <v>0.0498790810157195</v>
       </c>
-      <c r="M40" s="1" t="n">
+      <c r="M40" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A40,J:J)*L40,0)</f>
         <v>304</v>
       </c>
@@ -9949,7 +9976,7 @@
       <c r="A41" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B41" s="27" t="s">
+      <c r="B41" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C41" s="1" t="s">
@@ -9967,15 +9994,15 @@
       <c r="G41" s="1" t="n">
         <v>10237</v>
       </c>
-      <c r="H41" s="28" t="n">
+      <c r="H41" s="31" t="n">
         <f aca="false">ROUND(D41*IF(ISNUMBER(SEARCH("Labour",B41)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B41)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B41)),ISNUMBER(SEARCH("RefUK",B41))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B41)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B41)),ISNUMBER(SEARCH("Lib Dem",B41))),National!$L$8,National!$L$9))))),0)</f>
         <v>268</v>
       </c>
-      <c r="I41" s="25" t="n">
+      <c r="I41" s="27" t="n">
         <f aca="false">H41/SUMIFS(H:H,A:A,A41)</f>
         <v>0.0725893824485374</v>
       </c>
-      <c r="J41" s="29" t="n">
+      <c r="J41" s="32" t="n">
         <f aca="false">ROUND(I41*SUMIF(A:A,A41,D:D),0)</f>
         <v>442</v>
       </c>
@@ -9983,11 +10010,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A41,B:B,B41)/COUNTIFS(B:B,B41,A:A,A41),0)</f>
         <v>165</v>
       </c>
-      <c r="L41" s="25" t="n">
+      <c r="L41" s="27" t="n">
         <f aca="false">K41/SUMIF(A:A,A41,K:K)</f>
         <v>0.0498790810157195</v>
       </c>
-      <c r="M41" s="1" t="n">
+      <c r="M41" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A41,J:J)*L41,0)</f>
         <v>304</v>
       </c>
@@ -10008,7 +10035,7 @@
       <c r="A42" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B42" s="30" t="s">
+      <c r="B42" s="33" t="s">
         <v>219</v>
       </c>
       <c r="C42" s="1" t="s">
@@ -10026,15 +10053,15 @@
       <c r="G42" s="1" t="n">
         <v>10237</v>
       </c>
-      <c r="H42" s="28" t="n">
+      <c r="H42" s="31" t="n">
         <f aca="false">ROUND(D42*IF(ISNUMBER(SEARCH("Labour",B42)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B42)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B42)),ISNUMBER(SEARCH("RefUK",B42))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B42)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B42)),ISNUMBER(SEARCH("Lib Dem",B42))),National!$L$8,National!$L$9))))),0)</f>
         <v>808</v>
       </c>
-      <c r="I42" s="25" t="n">
+      <c r="I42" s="27" t="n">
         <f aca="false">H42/SUMIFS(H:H,A:A,A42)</f>
         <v>0.218851570964247</v>
       </c>
-      <c r="J42" s="29" t="n">
+      <c r="J42" s="32" t="n">
         <f aca="false">ROUND(I42*SUMIF(A:A,A42,D:D),0)</f>
         <v>1332</v>
       </c>
@@ -10042,11 +10069,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A42,B:B,B42)/COUNTIFS(B:B,B42,A:A,A42),0)</f>
         <v>1332</v>
       </c>
-      <c r="L42" s="25" t="n">
+      <c r="L42" s="27" t="n">
         <f aca="false">K42/SUMIF(A:A,A42,K:K)</f>
         <v>0.402660217654172</v>
       </c>
-      <c r="M42" s="1" t="n">
+      <c r="M42" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A42,J:J)*L42,0)</f>
         <v>2451</v>
       </c>
@@ -10067,7 +10094,7 @@
       <c r="A43" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B43" s="27" t="s">
+      <c r="B43" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C43" s="1" t="s">
@@ -10085,15 +10112,15 @@
       <c r="G43" s="1" t="n">
         <v>10237</v>
       </c>
-      <c r="H43" s="28" t="n">
+      <c r="H43" s="31" t="n">
         <f aca="false">ROUND(D43*IF(ISNUMBER(SEARCH("Labour",B43)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B43)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B43)),ISNUMBER(SEARCH("RefUK",B43))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B43)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B43)),ISNUMBER(SEARCH("Lib Dem",B43))),National!$L$8,National!$L$9))))),0)</f>
         <v>356</v>
       </c>
-      <c r="I43" s="25" t="n">
+      <c r="I43" s="27" t="n">
         <f aca="false">H43/SUMIFS(H:H,A:A,A43)</f>
         <v>0.0964247020585049</v>
       </c>
-      <c r="J43" s="29" t="n">
+      <c r="J43" s="32" t="n">
         <f aca="false">ROUND(I43*SUMIF(A:A,A43,D:D),0)</f>
         <v>587</v>
       </c>
@@ -10101,11 +10128,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A43,B:B,B43)/COUNTIFS(B:B,B43,A:A,A43),0)</f>
         <v>587</v>
       </c>
-      <c r="L43" s="25" t="n">
+      <c r="L43" s="27" t="n">
         <f aca="false">K43/SUMIF(A:A,A43,K:K)</f>
         <v>0.177448609431681</v>
       </c>
-      <c r="M43" s="1" t="n">
+      <c r="M43" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A43,J:J)*L43,0)</f>
         <v>1080</v>
       </c>
@@ -10126,7 +10153,7 @@
       <c r="A44" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B44" s="27" t="s">
+      <c r="B44" s="30" t="s">
         <v>249</v>
       </c>
       <c r="C44" s="1" t="s">
@@ -10144,15 +10171,15 @@
       <c r="G44" s="1" t="n">
         <v>11085</v>
       </c>
-      <c r="H44" s="28" t="n">
+      <c r="H44" s="31" t="n">
         <f aca="false">ROUND(D44*IF(ISNUMBER(SEARCH("Labour",B44)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B44)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B44)),ISNUMBER(SEARCH("RefUK",B44))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B44)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B44)),ISNUMBER(SEARCH("Lib Dem",B44))),National!$L$8,National!$L$9))))),0)</f>
         <v>639</v>
       </c>
-      <c r="I44" s="25" t="n">
+      <c r="I44" s="27" t="n">
         <f aca="false">H44/SUMIFS(H:H,A:A,A44)</f>
         <v>0.157583230579531</v>
       </c>
-      <c r="J44" s="29" t="n">
+      <c r="J44" s="32" t="n">
         <f aca="false">ROUND(I44*SUMIF(A:A,A44,D:D),0)</f>
         <v>1054</v>
       </c>
@@ -10160,11 +10187,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A44,B:B,B44)/COUNTIFS(B:B,B44,A:A,A44),0)</f>
         <v>336</v>
       </c>
-      <c r="L44" s="25" t="n">
+      <c r="L44" s="27" t="n">
         <f aca="false">K44/SUMIF(A:A,A44,K:K)</f>
         <v>0.0908353609083536</v>
       </c>
-      <c r="M44" s="1" t="n">
+      <c r="M44" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A44,J:J)*L44,0)</f>
         <v>607</v>
       </c>
@@ -10185,7 +10212,7 @@
       <c r="A45" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B45" s="27" t="s">
+      <c r="B45" s="30" t="s">
         <v>249</v>
       </c>
       <c r="C45" s="1" t="s">
@@ -10203,15 +10230,15 @@
       <c r="G45" s="1" t="n">
         <v>11085</v>
       </c>
-      <c r="H45" s="28" t="n">
+      <c r="H45" s="31" t="n">
         <f aca="false">ROUND(D45*IF(ISNUMBER(SEARCH("Labour",B45)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B45)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B45)),ISNUMBER(SEARCH("RefUK",B45))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B45)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B45)),ISNUMBER(SEARCH("Lib Dem",B45))),National!$L$8,National!$L$9))))),0)</f>
         <v>605</v>
       </c>
-      <c r="I45" s="25" t="n">
+      <c r="I45" s="27" t="n">
         <f aca="false">H45/SUMIFS(H:H,A:A,A45)</f>
         <v>0.149198520345253</v>
       </c>
-      <c r="J45" s="29" t="n">
+      <c r="J45" s="32" t="n">
         <f aca="false">ROUND(I45*SUMIF(A:A,A45,D:D),0)</f>
         <v>998</v>
       </c>
@@ -10219,11 +10246,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A45,B:B,B45)/COUNTIFS(B:B,B45,A:A,A45),0)</f>
         <v>336</v>
       </c>
-      <c r="L45" s="25" t="n">
+      <c r="L45" s="27" t="n">
         <f aca="false">K45/SUMIF(A:A,A45,K:K)</f>
         <v>0.0908353609083536</v>
       </c>
-      <c r="M45" s="1" t="n">
+      <c r="M45" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A45,J:J)*L45,0)</f>
         <v>607</v>
       </c>
@@ -10244,7 +10271,7 @@
       <c r="A46" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B46" s="27" t="s">
+      <c r="B46" s="30" t="s">
         <v>249</v>
       </c>
       <c r="C46" s="1" t="s">
@@ -10262,15 +10289,15 @@
       <c r="G46" s="1" t="n">
         <v>11085</v>
       </c>
-      <c r="H46" s="28" t="n">
+      <c r="H46" s="31" t="n">
         <f aca="false">ROUND(D46*IF(ISNUMBER(SEARCH("Labour",B46)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B46)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B46)),ISNUMBER(SEARCH("RefUK",B46))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B46)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B46)),ISNUMBER(SEARCH("Lib Dem",B46))),National!$L$8,National!$L$9))))),0)</f>
         <v>589</v>
       </c>
-      <c r="I46" s="25" t="n">
+      <c r="I46" s="27" t="n">
         <f aca="false">H46/SUMIFS(H:H,A:A,A46)</f>
         <v>0.145252774352651</v>
       </c>
-      <c r="J46" s="29" t="n">
+      <c r="J46" s="32" t="n">
         <f aca="false">ROUND(I46*SUMIF(A:A,A46,D:D),0)</f>
         <v>971</v>
       </c>
@@ -10278,11 +10305,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A46,B:B,B46)/COUNTIFS(B:B,B46,A:A,A46),0)</f>
         <v>336</v>
       </c>
-      <c r="L46" s="25" t="n">
+      <c r="L46" s="27" t="n">
         <f aca="false">K46/SUMIF(A:A,A46,K:K)</f>
         <v>0.0908353609083536</v>
       </c>
-      <c r="M46" s="1" t="n">
+      <c r="M46" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A46,J:J)*L46,0)</f>
         <v>607</v>
       </c>
@@ -10303,7 +10330,7 @@
       <c r="A47" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B47" s="27" t="s">
+      <c r="B47" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C47" s="1" t="s">
@@ -10321,15 +10348,15 @@
       <c r="G47" s="1" t="n">
         <v>11085</v>
       </c>
-      <c r="H47" s="28" t="n">
+      <c r="H47" s="31" t="n">
         <f aca="false">ROUND(D47*IF(ISNUMBER(SEARCH("Labour",B47)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B47)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B47)),ISNUMBER(SEARCH("RefUK",B47))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B47)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B47)),ISNUMBER(SEARCH("Lib Dem",B47))),National!$L$8,National!$L$9))))),0)</f>
         <v>333</v>
       </c>
-      <c r="I47" s="25" t="n">
+      <c r="I47" s="27" t="n">
         <f aca="false">H47/SUMIFS(H:H,A:A,A47)</f>
         <v>0.0821208384710234</v>
       </c>
-      <c r="J47" s="29" t="n">
+      <c r="J47" s="32" t="n">
         <f aca="false">ROUND(I47*SUMIF(A:A,A47,D:D),0)</f>
         <v>549</v>
       </c>
@@ -10337,11 +10364,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A47,B:B,B47)/COUNTIFS(B:B,B47,A:A,A47),0)</f>
         <v>162</v>
       </c>
-      <c r="L47" s="25" t="n">
+      <c r="L47" s="27" t="n">
         <f aca="false">K47/SUMIF(A:A,A47,K:K)</f>
         <v>0.0437956204379562</v>
       </c>
-      <c r="M47" s="1" t="n">
+      <c r="M47" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A47,J:J)*L47,0)</f>
         <v>293</v>
       </c>
@@ -10362,7 +10389,7 @@
       <c r="A48" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B48" s="27" t="s">
+      <c r="B48" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C48" s="1" t="s">
@@ -10380,15 +10407,15 @@
       <c r="G48" s="1" t="n">
         <v>11085</v>
       </c>
-      <c r="H48" s="28" t="n">
+      <c r="H48" s="31" t="n">
         <f aca="false">ROUND(D48*IF(ISNUMBER(SEARCH("Labour",B48)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B48)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B48)),ISNUMBER(SEARCH("RefUK",B48))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B48)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B48)),ISNUMBER(SEARCH("Lib Dem",B48))),National!$L$8,National!$L$9))))),0)</f>
         <v>308</v>
       </c>
-      <c r="I48" s="25" t="n">
+      <c r="I48" s="27" t="n">
         <f aca="false">H48/SUMIFS(H:H,A:A,A48)</f>
         <v>0.0759556103575832</v>
       </c>
-      <c r="J48" s="29" t="n">
+      <c r="J48" s="32" t="n">
         <f aca="false">ROUND(I48*SUMIF(A:A,A48,D:D),0)</f>
         <v>508</v>
       </c>
@@ -10396,11 +10423,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A48,B:B,B48)/COUNTIFS(B:B,B48,A:A,A48),0)</f>
         <v>162</v>
       </c>
-      <c r="L48" s="25" t="n">
+      <c r="L48" s="27" t="n">
         <f aca="false">K48/SUMIF(A:A,A48,K:K)</f>
         <v>0.0437956204379562</v>
       </c>
-      <c r="M48" s="1" t="n">
+      <c r="M48" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A48,J:J)*L48,0)</f>
         <v>293</v>
       </c>
@@ -10421,7 +10448,7 @@
       <c r="A49" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B49" s="30" t="s">
+      <c r="B49" s="33" t="s">
         <v>219</v>
       </c>
       <c r="C49" s="1" t="s">
@@ -10439,15 +10466,15 @@
       <c r="G49" s="1" t="n">
         <v>11085</v>
       </c>
-      <c r="H49" s="28" t="n">
+      <c r="H49" s="31" t="n">
         <f aca="false">ROUND(D49*IF(ISNUMBER(SEARCH("Labour",B49)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B49)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B49)),ISNUMBER(SEARCH("RefUK",B49))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B49)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B49)),ISNUMBER(SEARCH("Lib Dem",B49))),National!$L$8,National!$L$9))))),0)</f>
         <v>886</v>
       </c>
-      <c r="I49" s="25" t="n">
+      <c r="I49" s="27" t="n">
         <f aca="false">H49/SUMIFS(H:H,A:A,A49)</f>
         <v>0.218495684340321</v>
       </c>
-      <c r="J49" s="29" t="n">
+      <c r="J49" s="32" t="n">
         <f aca="false">ROUND(I49*SUMIF(A:A,A49,D:D),0)</f>
         <v>1461</v>
       </c>
@@ -10455,11 +10482,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A49,B:B,B49)/COUNTIFS(B:B,B49,A:A,A49),0)</f>
         <v>1461</v>
       </c>
-      <c r="L49" s="25" t="n">
+      <c r="L49" s="27" t="n">
         <f aca="false">K49/SUMIF(A:A,A49,K:K)</f>
         <v>0.394971613949716</v>
       </c>
-      <c r="M49" s="1" t="n">
+      <c r="M49" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A49,J:J)*L49,0)</f>
         <v>2641</v>
       </c>
@@ -10480,7 +10507,7 @@
       <c r="A50" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B50" s="27" t="s">
+      <c r="B50" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C50" s="1" t="s">
@@ -10498,15 +10525,15 @@
       <c r="G50" s="1" t="n">
         <v>11085</v>
       </c>
-      <c r="H50" s="28" t="n">
+      <c r="H50" s="31" t="n">
         <f aca="false">ROUND(D50*IF(ISNUMBER(SEARCH("Labour",B50)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B50)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B50)),ISNUMBER(SEARCH("RefUK",B50))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B50)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B50)),ISNUMBER(SEARCH("Lib Dem",B50))),National!$L$8,National!$L$9))))),0)</f>
         <v>244</v>
       </c>
-      <c r="I50" s="25" t="n">
+      <c r="I50" s="27" t="n">
         <f aca="false">H50/SUMIFS(H:H,A:A,A50)</f>
         <v>0.0601726263871763</v>
       </c>
-      <c r="J50" s="29" t="n">
+      <c r="J50" s="32" t="n">
         <f aca="false">ROUND(I50*SUMIF(A:A,A50,D:D),0)</f>
         <v>402</v>
       </c>
@@ -10514,11 +10541,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A50,B:B,B50)/COUNTIFS(B:B,B50,A:A,A50),0)</f>
         <v>162</v>
       </c>
-      <c r="L50" s="25" t="n">
+      <c r="L50" s="27" t="n">
         <f aca="false">K50/SUMIF(A:A,A50,K:K)</f>
         <v>0.0437956204379562</v>
       </c>
-      <c r="M50" s="1" t="n">
+      <c r="M50" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A50,J:J)*L50,0)</f>
         <v>293</v>
       </c>
@@ -10539,7 +10566,7 @@
       <c r="A51" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B51" s="27" t="s">
+      <c r="B51" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C51" s="1" t="s">
@@ -10557,15 +10584,15 @@
       <c r="G51" s="1" t="n">
         <v>11085</v>
       </c>
-      <c r="H51" s="28" t="n">
+      <c r="H51" s="31" t="n">
         <f aca="false">ROUND(D51*IF(ISNUMBER(SEARCH("Labour",B51)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B51)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B51)),ISNUMBER(SEARCH("RefUK",B51))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B51)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B51)),ISNUMBER(SEARCH("Lib Dem",B51))),National!$L$8,National!$L$9))))),0)</f>
         <v>451</v>
       </c>
-      <c r="I51" s="25" t="n">
+      <c r="I51" s="27" t="n">
         <f aca="false">H51/SUMIFS(H:H,A:A,A51)</f>
         <v>0.111220715166461</v>
       </c>
-      <c r="J51" s="29" t="n">
+      <c r="J51" s="32" t="n">
         <f aca="false">ROUND(I51*SUMIF(A:A,A51,D:D),0)</f>
         <v>744</v>
       </c>
@@ -10573,11 +10600,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A51,B:B,B51)/COUNTIFS(B:B,B51,A:A,A51),0)</f>
         <v>744</v>
       </c>
-      <c r="L51" s="25" t="n">
+      <c r="L51" s="27" t="n">
         <f aca="false">K51/SUMIF(A:A,A51,K:K)</f>
         <v>0.201135442011354</v>
       </c>
-      <c r="M51" s="1" t="n">
+      <c r="M51" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A51,J:J)*L51,0)</f>
         <v>1345</v>
       </c>
@@ -10598,7 +10625,7 @@
       <c r="A52" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B52" s="27" t="s">
+      <c r="B52" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C52" s="1" t="s">
@@ -10616,15 +10643,15 @@
       <c r="G52" s="1" t="n">
         <v>7463</v>
       </c>
-      <c r="H52" s="28" t="n">
+      <c r="H52" s="31" t="n">
         <f aca="false">ROUND(D52*IF(ISNUMBER(SEARCH("Labour",B52)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B52)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B52)),ISNUMBER(SEARCH("RefUK",B52))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B52)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B52)),ISNUMBER(SEARCH("Lib Dem",B52))),National!$L$8,National!$L$9))))),0)</f>
         <v>1117</v>
       </c>
-      <c r="I52" s="25" t="n">
+      <c r="I52" s="27" t="n">
         <f aca="false">H52/SUMIFS(H:H,A:A,A52)</f>
         <v>0.311402286032897</v>
       </c>
-      <c r="J52" s="29" t="n">
+      <c r="J52" s="32" t="n">
         <f aca="false">ROUND(I52*SUMIF(A:A,A52,D:D),0)</f>
         <v>1540</v>
       </c>
@@ -10632,11 +10659,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A52,B:B,B52)/COUNTIFS(B:B,B52,A:A,A52),0)</f>
         <v>749</v>
       </c>
-      <c r="L52" s="25" t="n">
+      <c r="L52" s="27" t="n">
         <f aca="false">K52/SUMIF(A:A,A52,K:K)</f>
         <v>0.237100348211459</v>
       </c>
-      <c r="M52" s="1" t="n">
+      <c r="M52" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A52,J:J)*L52,0)</f>
         <v>1172</v>
       </c>
@@ -10657,7 +10684,7 @@
       <c r="A53" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B53" s="27" t="s">
+      <c r="B53" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C53" s="1" t="s">
@@ -10675,15 +10702,15 @@
       <c r="G53" s="1" t="n">
         <v>7463</v>
       </c>
-      <c r="H53" s="28" t="n">
+      <c r="H53" s="31" t="n">
         <f aca="false">ROUND(D53*IF(ISNUMBER(SEARCH("Labour",B53)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B53)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B53)),ISNUMBER(SEARCH("RefUK",B53))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B53)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B53)),ISNUMBER(SEARCH("Lib Dem",B53))),National!$L$8,National!$L$9))))),0)</f>
         <v>1057</v>
       </c>
-      <c r="I53" s="25" t="n">
+      <c r="I53" s="27" t="n">
         <f aca="false">H53/SUMIFS(H:H,A:A,A53)</f>
         <v>0.294675216057987</v>
       </c>
-      <c r="J53" s="29" t="n">
+      <c r="J53" s="32" t="n">
         <f aca="false">ROUND(I53*SUMIF(A:A,A53,D:D),0)</f>
         <v>1457</v>
       </c>
@@ -10691,11 +10718,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A53,B:B,B53)/COUNTIFS(B:B,B53,A:A,A53),0)</f>
         <v>749</v>
       </c>
-      <c r="L53" s="25" t="n">
+      <c r="L53" s="27" t="n">
         <f aca="false">K53/SUMIF(A:A,A53,K:K)</f>
         <v>0.237100348211459</v>
       </c>
-      <c r="M53" s="1" t="n">
+      <c r="M53" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A53,J:J)*L53,0)</f>
         <v>1172</v>
       </c>
@@ -10716,7 +10743,7 @@
       <c r="A54" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B54" s="27" t="s">
+      <c r="B54" s="30" t="s">
         <v>216</v>
       </c>
       <c r="C54" s="1" t="s">
@@ -10734,15 +10761,15 @@
       <c r="G54" s="1" t="n">
         <v>7463</v>
       </c>
-      <c r="H54" s="28" t="n">
+      <c r="H54" s="31" t="n">
         <f aca="false">ROUND(D54*IF(ISNUMBER(SEARCH("Labour",B54)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B54)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B54)),ISNUMBER(SEARCH("RefUK",B54))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B54)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B54)),ISNUMBER(SEARCH("Lib Dem",B54))),National!$L$8,National!$L$9))))),0)</f>
         <v>238</v>
       </c>
-      <c r="I54" s="25" t="n">
+      <c r="I54" s="27" t="n">
         <f aca="false">H54/SUMIFS(H:H,A:A,A54)</f>
         <v>0.0663507109004739</v>
       </c>
-      <c r="J54" s="29" t="n">
+      <c r="J54" s="32" t="n">
         <f aca="false">ROUND(I54*SUMIF(A:A,A54,D:D),0)</f>
         <v>328</v>
       </c>
@@ -10750,11 +10777,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A54,B:B,B54)/COUNTIFS(B:B,B54,A:A,A54),0)</f>
         <v>143</v>
       </c>
-      <c r="L54" s="25" t="n">
+      <c r="L54" s="27" t="n">
         <f aca="false">K54/SUMIF(A:A,A54,K:K)</f>
         <v>0.0452674897119342</v>
       </c>
-      <c r="M54" s="1" t="n">
+      <c r="M54" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A54,J:J)*L54,0)</f>
         <v>224</v>
       </c>
@@ -10775,7 +10802,7 @@
       <c r="A55" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B55" s="27" t="s">
+      <c r="B55" s="30" t="s">
         <v>216</v>
       </c>
       <c r="C55" s="1" t="s">
@@ -10793,15 +10820,15 @@
       <c r="G55" s="1" t="n">
         <v>7463</v>
       </c>
-      <c r="H55" s="28" t="n">
+      <c r="H55" s="31" t="n">
         <f aca="false">ROUND(D55*IF(ISNUMBER(SEARCH("Labour",B55)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B55)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B55)),ISNUMBER(SEARCH("RefUK",B55))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B55)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B55)),ISNUMBER(SEARCH("Lib Dem",B55))),National!$L$8,National!$L$9))))),0)</f>
         <v>178</v>
       </c>
-      <c r="I55" s="25" t="n">
+      <c r="I55" s="27" t="n">
         <f aca="false">H55/SUMIFS(H:H,A:A,A55)</f>
         <v>0.0496236409255645</v>
       </c>
-      <c r="J55" s="29" t="n">
+      <c r="J55" s="32" t="n">
         <f aca="false">ROUND(I55*SUMIF(A:A,A55,D:D),0)</f>
         <v>245</v>
       </c>
@@ -10809,11 +10836,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A55,B:B,B55)/COUNTIFS(B:B,B55,A:A,A55),0)</f>
         <v>143</v>
       </c>
-      <c r="L55" s="25" t="n">
+      <c r="L55" s="27" t="n">
         <f aca="false">K55/SUMIF(A:A,A55,K:K)</f>
         <v>0.0452674897119342</v>
       </c>
-      <c r="M55" s="1" t="n">
+      <c r="M55" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A55,J:J)*L55,0)</f>
         <v>224</v>
       </c>
@@ -10834,7 +10861,7 @@
       <c r="A56" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B56" s="30" t="s">
+      <c r="B56" s="33" t="s">
         <v>219</v>
       </c>
       <c r="C56" s="1" t="s">
@@ -10852,15 +10879,15 @@
       <c r="G56" s="1" t="n">
         <v>7463</v>
       </c>
-      <c r="H56" s="28" t="n">
+      <c r="H56" s="31" t="n">
         <f aca="false">ROUND(D56*IF(ISNUMBER(SEARCH("Labour",B56)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B56)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B56)),ISNUMBER(SEARCH("RefUK",B56))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B56)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B56)),ISNUMBER(SEARCH("Lib Dem",B56))),National!$L$8,National!$L$9))))),0)</f>
         <v>563</v>
       </c>
-      <c r="I56" s="25" t="n">
+      <c r="I56" s="27" t="n">
         <f aca="false">H56/SUMIFS(H:H,A:A,A56)</f>
         <v>0.156955673264567</v>
       </c>
-      <c r="J56" s="29" t="n">
+      <c r="J56" s="32" t="n">
         <f aca="false">ROUND(I56*SUMIF(A:A,A56,D:D),0)</f>
         <v>776</v>
       </c>
@@ -10868,11 +10895,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A56,B:B,B56)/COUNTIFS(B:B,B56,A:A,A56),0)</f>
         <v>776</v>
       </c>
-      <c r="L56" s="25" t="n">
+      <c r="L56" s="27" t="n">
         <f aca="false">K56/SUMIF(A:A,A56,K:K)</f>
         <v>0.245647356758468</v>
       </c>
-      <c r="M56" s="1" t="n">
+      <c r="M56" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A56,J:J)*L56,0)</f>
         <v>1215</v>
       </c>
@@ -10893,7 +10920,7 @@
       <c r="A57" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B57" s="27" t="s">
+      <c r="B57" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C57" s="1" t="s">
@@ -10911,15 +10938,15 @@
       <c r="G57" s="1" t="n">
         <v>7463</v>
       </c>
-      <c r="H57" s="28" t="n">
+      <c r="H57" s="31" t="n">
         <f aca="false">ROUND(D57*IF(ISNUMBER(SEARCH("Labour",B57)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B57)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B57)),ISNUMBER(SEARCH("RefUK",B57))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B57)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B57)),ISNUMBER(SEARCH("Lib Dem",B57))),National!$L$8,National!$L$9))))),0)</f>
         <v>311</v>
       </c>
-      <c r="I57" s="25" t="n">
+      <c r="I57" s="27" t="n">
         <f aca="false">H57/SUMIFS(H:H,A:A,A57)</f>
         <v>0.086701979369947</v>
       </c>
-      <c r="J57" s="29" t="n">
+      <c r="J57" s="32" t="n">
         <f aca="false">ROUND(I57*SUMIF(A:A,A57,D:D),0)</f>
         <v>429</v>
       </c>
@@ -10927,11 +10954,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A57,B:B,B57)/COUNTIFS(B:B,B57,A:A,A57),0)</f>
         <v>429</v>
       </c>
-      <c r="L57" s="25" t="n">
+      <c r="L57" s="27" t="n">
         <f aca="false">K57/SUMIF(A:A,A57,K:K)</f>
         <v>0.135802469135802</v>
       </c>
-      <c r="M57" s="1" t="n">
+      <c r="M57" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A57,J:J)*L57,0)</f>
         <v>672</v>
       </c>
@@ -10952,7 +10979,7 @@
       <c r="A58" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B58" s="27" t="s">
+      <c r="B58" s="30" t="s">
         <v>297</v>
       </c>
       <c r="C58" s="1" t="s">
@@ -10970,15 +10997,15 @@
       <c r="G58" s="1" t="n">
         <v>7463</v>
       </c>
-      <c r="H58" s="28" t="n">
+      <c r="H58" s="31" t="n">
         <f aca="false">ROUND(D58*IF(ISNUMBER(SEARCH("Labour",B58)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B58)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B58)),ISNUMBER(SEARCH("RefUK",B58))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B58)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B58)),ISNUMBER(SEARCH("Lib Dem",B58))),National!$L$8,National!$L$9))))),0)</f>
         <v>66</v>
       </c>
-      <c r="I58" s="25" t="n">
+      <c r="I58" s="27" t="n">
         <f aca="false">H58/SUMIFS(H:H,A:A,A58)</f>
         <v>0.0183997769724003</v>
       </c>
-      <c r="J58" s="29" t="n">
+      <c r="J58" s="32" t="n">
         <f aca="false">ROUND(I58*SUMIF(A:A,A58,D:D),0)</f>
         <v>91</v>
       </c>
@@ -10986,11 +11013,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A58,B:B,B58)/COUNTIFS(B:B,B58,A:A,A58),0)</f>
         <v>91</v>
       </c>
-      <c r="L58" s="25" t="n">
+      <c r="L58" s="27" t="n">
         <f aca="false">K58/SUMIF(A:A,A58,K:K)</f>
         <v>0.0288065843621399</v>
       </c>
-      <c r="M58" s="1" t="n">
+      <c r="M58" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A58,J:J)*L58,0)</f>
         <v>142</v>
       </c>
@@ -11011,7 +11038,7 @@
       <c r="A59" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B59" s="27" t="s">
+      <c r="B59" s="30" t="s">
         <v>299</v>
       </c>
       <c r="C59" s="1" t="s">
@@ -11029,15 +11056,15 @@
       <c r="G59" s="1" t="n">
         <v>7463</v>
       </c>
-      <c r="H59" s="28" t="n">
+      <c r="H59" s="31" t="n">
         <f aca="false">ROUND(D59*IF(ISNUMBER(SEARCH("Labour",B59)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B59)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B59)),ISNUMBER(SEARCH("RefUK",B59))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B59)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B59)),ISNUMBER(SEARCH("Lib Dem",B59))),National!$L$8,National!$L$9))))),0)</f>
         <v>57</v>
       </c>
-      <c r="I59" s="25" t="n">
+      <c r="I59" s="27" t="n">
         <f aca="false">H59/SUMIFS(H:H,A:A,A59)</f>
         <v>0.0158907164761639</v>
       </c>
-      <c r="J59" s="29" t="n">
+      <c r="J59" s="32" t="n">
         <f aca="false">ROUND(I59*SUMIF(A:A,A59,D:D),0)</f>
         <v>79</v>
       </c>
@@ -11045,11 +11072,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A59,B:B,B59)/COUNTIFS(B:B,B59,A:A,A59),0)</f>
         <v>79</v>
       </c>
-      <c r="L59" s="25" t="n">
+      <c r="L59" s="27" t="n">
         <f aca="false">K59/SUMIF(A:A,A59,K:K)</f>
         <v>0.0250079138968028</v>
       </c>
-      <c r="M59" s="1" t="n">
+      <c r="M59" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A59,J:J)*L59,0)</f>
         <v>124</v>
       </c>
@@ -11070,7 +11097,7 @@
       <c r="A60" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B60" s="27" t="s">
+      <c r="B60" s="30" t="s">
         <v>23</v>
       </c>
       <c r="C60" s="1" t="s">
@@ -11088,15 +11115,15 @@
       <c r="G60" s="1" t="n">
         <v>10049</v>
       </c>
-      <c r="H60" s="28" t="n">
+      <c r="H60" s="31" t="n">
         <f aca="false">ROUND(D60*IF(ISNUMBER(SEARCH("Labour",B60)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B60)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B60)),ISNUMBER(SEARCH("RefUK",B60))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B60)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B60)),ISNUMBER(SEARCH("Lib Dem",B60))),National!$L$8,National!$L$9))))),0)</f>
         <v>2729</v>
       </c>
-      <c r="I60" s="25" t="n">
+      <c r="I60" s="27" t="n">
         <f aca="false">H60/SUMIFS(H:H,A:A,A60)</f>
         <v>0.275184027427649</v>
       </c>
-      <c r="J60" s="29" t="n">
+      <c r="J60" s="32" t="n">
         <f aca="false">ROUND(I60*SUMIF(A:A,A60,D:D),0)</f>
         <v>2604</v>
       </c>
@@ -11104,11 +11131,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A60,B:B,B60)/COUNTIFS(B:B,B60,A:A,A60),0)</f>
         <v>836</v>
       </c>
-      <c r="L60" s="25" t="n">
+      <c r="L60" s="27" t="n">
         <f aca="false">K60/SUMIF(A:A,A60,K:K)</f>
         <v>0.228352909041246</v>
       </c>
-      <c r="M60" s="1" t="n">
+      <c r="M60" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A60,J:J)*L60,0)</f>
         <v>2161</v>
       </c>
@@ -11129,7 +11156,7 @@
       <c r="A61" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B61" s="27" t="s">
+      <c r="B61" s="30" t="s">
         <v>23</v>
       </c>
       <c r="C61" s="1" t="s">
@@ -11147,15 +11174,15 @@
       <c r="G61" s="1" t="n">
         <v>10049</v>
       </c>
-      <c r="H61" s="28" t="n">
+      <c r="H61" s="31" t="n">
         <f aca="false">ROUND(D61*IF(ISNUMBER(SEARCH("Labour",B61)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B61)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B61)),ISNUMBER(SEARCH("RefUK",B61))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B61)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B61)),ISNUMBER(SEARCH("Lib Dem",B61))),National!$L$8,National!$L$9))))),0)</f>
         <v>2605</v>
       </c>
-      <c r="I61" s="25" t="n">
+      <c r="I61" s="27" t="n">
         <f aca="false">H61/SUMIFS(H:H,A:A,A61)</f>
         <v>0.26268024604215</v>
       </c>
-      <c r="J61" s="29" t="n">
+      <c r="J61" s="32" t="n">
         <f aca="false">ROUND(I61*SUMIF(A:A,A61,D:D),0)</f>
         <v>2486</v>
       </c>
@@ -11163,11 +11190,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A61,B:B,B61)/COUNTIFS(B:B,B61,A:A,A61),0)</f>
         <v>836</v>
       </c>
-      <c r="L61" s="25" t="n">
+      <c r="L61" s="27" t="n">
         <f aca="false">K61/SUMIF(A:A,A61,K:K)</f>
         <v>0.228352909041246</v>
       </c>
-      <c r="M61" s="1" t="n">
+      <c r="M61" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A61,J:J)*L61,0)</f>
         <v>2161</v>
       </c>
@@ -11188,7 +11215,7 @@
       <c r="A62" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B62" s="27" t="s">
+      <c r="B62" s="30" t="s">
         <v>23</v>
       </c>
       <c r="C62" s="1" t="s">
@@ -11206,15 +11233,15 @@
       <c r="G62" s="1" t="n">
         <v>10049</v>
       </c>
-      <c r="H62" s="28" t="n">
+      <c r="H62" s="31" t="n">
         <f aca="false">ROUND(D62*IF(ISNUMBER(SEARCH("Labour",B62)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B62)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B62)),ISNUMBER(SEARCH("RefUK",B62))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B62)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B62)),ISNUMBER(SEARCH("Lib Dem",B62))),National!$L$8,National!$L$9))))),0)</f>
         <v>2549</v>
       </c>
-      <c r="I62" s="25" t="n">
+      <c r="I62" s="27" t="n">
         <f aca="false">H62/SUMIFS(H:H,A:A,A62)</f>
         <v>0.257033377029344</v>
       </c>
-      <c r="J62" s="29" t="n">
+      <c r="J62" s="32" t="n">
         <f aca="false">ROUND(I62*SUMIF(A:A,A62,D:D),0)</f>
         <v>2432</v>
       </c>
@@ -11222,11 +11249,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A62,B:B,B62)/COUNTIFS(B:B,B62,A:A,A62),0)</f>
         <v>836</v>
       </c>
-      <c r="L62" s="25" t="n">
+      <c r="L62" s="27" t="n">
         <f aca="false">K62/SUMIF(A:A,A62,K:K)</f>
         <v>0.228352909041246</v>
       </c>
-      <c r="M62" s="1" t="n">
+      <c r="M62" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A62,J:J)*L62,0)</f>
         <v>2161</v>
       </c>
@@ -11247,7 +11274,7 @@
       <c r="A63" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B63" s="27" t="s">
+      <c r="B63" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C63" s="1" t="s">
@@ -11265,15 +11292,15 @@
       <c r="G63" s="1" t="n">
         <v>10049</v>
       </c>
-      <c r="H63" s="28" t="n">
+      <c r="H63" s="31" t="n">
         <f aca="false">ROUND(D63*IF(ISNUMBER(SEARCH("Labour",B63)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B63)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B63)),ISNUMBER(SEARCH("RefUK",B63))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B63)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B63)),ISNUMBER(SEARCH("Lib Dem",B63))),National!$L$8,National!$L$9))))),0)</f>
         <v>304</v>
       </c>
-      <c r="I63" s="25" t="n">
+      <c r="I63" s="27" t="n">
         <f aca="false">H63/SUMIFS(H:H,A:A,A63)</f>
         <v>0.0306544317838056</v>
       </c>
-      <c r="J63" s="29" t="n">
+      <c r="J63" s="32" t="n">
         <f aca="false">ROUND(I63*SUMIF(A:A,A63,D:D),0)</f>
         <v>290</v>
       </c>
@@ -11281,11 +11308,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A63,B:B,B63)/COUNTIFS(B:B,B63,A:A,A63),0)</f>
         <v>90</v>
       </c>
-      <c r="L63" s="25" t="n">
+      <c r="L63" s="27" t="n">
         <f aca="false">K63/SUMIF(A:A,A63,K:K)</f>
         <v>0.0245834471455886</v>
       </c>
-      <c r="M63" s="1" t="n">
+      <c r="M63" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A63,J:J)*L63,0)</f>
         <v>233</v>
       </c>
@@ -11306,7 +11333,7 @@
       <c r="A64" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B64" s="27" t="s">
+      <c r="B64" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C64" s="1" t="s">
@@ -11324,15 +11351,15 @@
       <c r="G64" s="1" t="n">
         <v>10049</v>
       </c>
-      <c r="H64" s="28" t="n">
+      <c r="H64" s="31" t="n">
         <f aca="false">ROUND(D64*IF(ISNUMBER(SEARCH("Labour",B64)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B64)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B64)),ISNUMBER(SEARCH("RefUK",B64))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B64)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B64)),ISNUMBER(SEARCH("Lib Dem",B64))),National!$L$8,National!$L$9))))),0)</f>
         <v>279</v>
       </c>
-      <c r="I64" s="25" t="n">
+      <c r="I64" s="27" t="n">
         <f aca="false">H64/SUMIFS(H:H,A:A,A64)</f>
         <v>0.0281335081173742</v>
       </c>
-      <c r="J64" s="29" t="n">
+      <c r="J64" s="32" t="n">
         <f aca="false">ROUND(I64*SUMIF(A:A,A64,D:D),0)</f>
         <v>266</v>
       </c>
@@ -11340,11 +11367,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A64,B:B,B64)/COUNTIFS(B:B,B64,A:A,A64),0)</f>
         <v>90</v>
       </c>
-      <c r="L64" s="25" t="n">
+      <c r="L64" s="27" t="n">
         <f aca="false">K64/SUMIF(A:A,A64,K:K)</f>
         <v>0.0245834471455886</v>
       </c>
-      <c r="M64" s="1" t="n">
+      <c r="M64" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A64,J:J)*L64,0)</f>
         <v>233</v>
       </c>
@@ -11365,7 +11392,7 @@
       <c r="A65" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B65" s="27" t="s">
+      <c r="B65" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C65" s="1" t="s">
@@ -11383,15 +11410,15 @@
       <c r="G65" s="1" t="n">
         <v>10049</v>
       </c>
-      <c r="H65" s="28" t="n">
+      <c r="H65" s="31" t="n">
         <f aca="false">ROUND(D65*IF(ISNUMBER(SEARCH("Labour",B65)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B65)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B65)),ISNUMBER(SEARCH("RefUK",B65))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B65)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B65)),ISNUMBER(SEARCH("Lib Dem",B65))),National!$L$8,National!$L$9))))),0)</f>
         <v>267</v>
       </c>
-      <c r="I65" s="25" t="n">
+      <c r="I65" s="27" t="n">
         <f aca="false">H65/SUMIFS(H:H,A:A,A65)</f>
         <v>0.0269234647574871</v>
       </c>
-      <c r="J65" s="29" t="n">
+      <c r="J65" s="32" t="n">
         <f aca="false">ROUND(I65*SUMIF(A:A,A65,D:D),0)</f>
         <v>255</v>
       </c>
@@ -11399,11 +11426,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A65,B:B,B65)/COUNTIFS(B:B,B65,A:A,A65),0)</f>
         <v>90</v>
       </c>
-      <c r="L65" s="25" t="n">
+      <c r="L65" s="27" t="n">
         <f aca="false">K65/SUMIF(A:A,A65,K:K)</f>
         <v>0.0245834471455886</v>
       </c>
-      <c r="M65" s="1" t="n">
+      <c r="M65" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A65,J:J)*L65,0)</f>
         <v>233</v>
       </c>
@@ -11424,7 +11451,7 @@
       <c r="A66" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B66" s="27" t="s">
+      <c r="B66" s="30" t="s">
         <v>216</v>
       </c>
       <c r="C66" s="1" t="s">
@@ -11442,15 +11469,15 @@
       <c r="G66" s="1" t="n">
         <v>10049</v>
       </c>
-      <c r="H66" s="28" t="n">
+      <c r="H66" s="31" t="n">
         <f aca="false">ROUND(D66*IF(ISNUMBER(SEARCH("Labour",B66)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B66)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B66)),ISNUMBER(SEARCH("RefUK",B66))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B66)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B66)),ISNUMBER(SEARCH("Lib Dem",B66))),National!$L$8,National!$L$9))))),0)</f>
         <v>142</v>
       </c>
-      <c r="I66" s="25" t="n">
+      <c r="I66" s="27" t="n">
         <f aca="false">H66/SUMIFS(H:H,A:A,A66)</f>
         <v>0.0143188464253302</v>
       </c>
-      <c r="J66" s="29" t="n">
+      <c r="J66" s="32" t="n">
         <f aca="false">ROUND(I66*SUMIF(A:A,A66,D:D),0)</f>
         <v>135</v>
       </c>
@@ -11458,11 +11485,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A66,B:B,B66)/COUNTIFS(B:B,B66,A:A,A66),0)</f>
         <v>41</v>
       </c>
-      <c r="L66" s="25" t="n">
+      <c r="L66" s="27" t="n">
         <f aca="false">K66/SUMIF(A:A,A66,K:K)</f>
         <v>0.0111991259218793</v>
       </c>
-      <c r="M66" s="1" t="n">
+      <c r="M66" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A66,J:J)*L66,0)</f>
         <v>106</v>
       </c>
@@ -11483,7 +11510,7 @@
       <c r="A67" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B67" s="27" t="s">
+      <c r="B67" s="30" t="s">
         <v>216</v>
       </c>
       <c r="C67" s="1" t="s">
@@ -11501,15 +11528,15 @@
       <c r="G67" s="1" t="n">
         <v>10049</v>
       </c>
-      <c r="H67" s="28" t="n">
+      <c r="H67" s="31" t="n">
         <f aca="false">ROUND(D67*IF(ISNUMBER(SEARCH("Labour",B67)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B67)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B67)),ISNUMBER(SEARCH("RefUK",B67))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B67)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B67)),ISNUMBER(SEARCH("Lib Dem",B67))),National!$L$8,National!$L$9))))),0)</f>
         <v>133</v>
       </c>
-      <c r="I67" s="25" t="n">
+      <c r="I67" s="27" t="n">
         <f aca="false">H67/SUMIFS(H:H,A:A,A67)</f>
         <v>0.0134113139054149</v>
       </c>
-      <c r="J67" s="29" t="n">
+      <c r="J67" s="32" t="n">
         <f aca="false">ROUND(I67*SUMIF(A:A,A67,D:D),0)</f>
         <v>127</v>
       </c>
@@ -11517,11 +11544,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A67,B:B,B67)/COUNTIFS(B:B,B67,A:A,A67),0)</f>
         <v>41</v>
       </c>
-      <c r="L67" s="25" t="n">
+      <c r="L67" s="27" t="n">
         <f aca="false">K67/SUMIF(A:A,A67,K:K)</f>
         <v>0.0111991259218793</v>
       </c>
-      <c r="M67" s="1" t="n">
+      <c r="M67" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A67,J:J)*L67,0)</f>
         <v>106</v>
       </c>
@@ -11542,7 +11569,7 @@
       <c r="A68" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B68" s="27" t="s">
+      <c r="B68" s="30" t="s">
         <v>216</v>
       </c>
       <c r="C68" s="1" t="s">
@@ -11560,15 +11587,15 @@
       <c r="G68" s="1" t="n">
         <v>10049</v>
       </c>
-      <c r="H68" s="28" t="n">
+      <c r="H68" s="31" t="n">
         <f aca="false">ROUND(D68*IF(ISNUMBER(SEARCH("Labour",B68)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B68)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B68)),ISNUMBER(SEARCH("RefUK",B68))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B68)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B68)),ISNUMBER(SEARCH("Lib Dem",B68))),National!$L$8,National!$L$9))))),0)</f>
         <v>113</v>
       </c>
-      <c r="I68" s="25" t="n">
+      <c r="I68" s="27" t="n">
         <f aca="false">H68/SUMIFS(H:H,A:A,A68)</f>
         <v>0.0113945749722698</v>
       </c>
-      <c r="J68" s="29" t="n">
+      <c r="J68" s="32" t="n">
         <f aca="false">ROUND(I68*SUMIF(A:A,A68,D:D),0)</f>
         <v>108</v>
       </c>
@@ -11576,11 +11603,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A68,B:B,B68)/COUNTIFS(B:B,B68,A:A,A68),0)</f>
         <v>41</v>
       </c>
-      <c r="L68" s="25" t="n">
+      <c r="L68" s="27" t="n">
         <f aca="false">K68/SUMIF(A:A,A68,K:K)</f>
         <v>0.0111991259218793</v>
       </c>
-      <c r="M68" s="1" t="n">
+      <c r="M68" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A68,J:J)*L68,0)</f>
         <v>106</v>
       </c>
@@ -11601,7 +11628,7 @@
       <c r="A69" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B69" s="30" t="s">
+      <c r="B69" s="33" t="s">
         <v>219</v>
       </c>
       <c r="C69" s="1" t="s">
@@ -11619,15 +11646,15 @@
       <c r="G69" s="1" t="n">
         <v>10049</v>
       </c>
-      <c r="H69" s="28" t="n">
+      <c r="H69" s="31" t="n">
         <f aca="false">ROUND(D69*IF(ISNUMBER(SEARCH("Labour",B69)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B69)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B69)),ISNUMBER(SEARCH("RefUK",B69))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B69)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B69)),ISNUMBER(SEARCH("Lib Dem",B69))),National!$L$8,National!$L$9))))),0)</f>
         <v>333</v>
       </c>
-      <c r="I69" s="25" t="n">
+      <c r="I69" s="27" t="n">
         <f aca="false">H69/SUMIFS(H:H,A:A,A69)</f>
         <v>0.033578703236866</v>
       </c>
-      <c r="J69" s="29" t="n">
+      <c r="J69" s="32" t="n">
         <f aca="false">ROUND(I69*SUMIF(A:A,A69,D:D),0)</f>
         <v>318</v>
       </c>
@@ -11635,11 +11662,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A69,B:B,B69)/COUNTIFS(B:B,B69,A:A,A69),0)</f>
         <v>318</v>
       </c>
-      <c r="L69" s="25" t="n">
+      <c r="L69" s="27" t="n">
         <f aca="false">K69/SUMIF(A:A,A69,K:K)</f>
         <v>0.0868615132477465</v>
       </c>
-      <c r="M69" s="1" t="n">
+      <c r="M69" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A69,J:J)*L69,0)</f>
         <v>822</v>
       </c>
@@ -11660,7 +11687,7 @@
       <c r="A70" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B70" s="27" t="s">
+      <c r="B70" s="30" t="s">
         <v>244</v>
       </c>
       <c r="C70" s="1" t="s">
@@ -11678,15 +11705,15 @@
       <c r="G70" s="1" t="n">
         <v>10049</v>
       </c>
-      <c r="H70" s="28" t="n">
+      <c r="H70" s="31" t="n">
         <f aca="false">ROUND(D70*IF(ISNUMBER(SEARCH("Labour",B70)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B70)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B70)),ISNUMBER(SEARCH("RefUK",B70))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B70)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B70)),ISNUMBER(SEARCH("Lib Dem",B70))),National!$L$8,National!$L$9))))),0)</f>
         <v>392</v>
       </c>
-      <c r="I70" s="25" t="n">
+      <c r="I70" s="27" t="n">
         <f aca="false">H70/SUMIFS(H:H,A:A,A70)</f>
         <v>0.0395280830896441</v>
       </c>
-      <c r="J70" s="29" t="n">
+      <c r="J70" s="32" t="n">
         <f aca="false">ROUND(I70*SUMIF(A:A,A70,D:D),0)</f>
         <v>374</v>
       </c>
@@ -11694,11 +11721,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A70,B:B,B70)/COUNTIFS(B:B,B70,A:A,A70),0)</f>
         <v>374</v>
       </c>
-      <c r="L70" s="25" t="n">
+      <c r="L70" s="27" t="n">
         <f aca="false">K70/SUMIF(A:A,A70,K:K)</f>
         <v>0.102157880360557</v>
       </c>
-      <c r="M70" s="1" t="n">
+      <c r="M70" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A70,J:J)*L70,0)</f>
         <v>967</v>
       </c>
@@ -11719,7 +11746,7 @@
       <c r="A71" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B71" s="27" t="s">
+      <c r="B71" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C71" s="1" t="s">
@@ -11737,15 +11764,15 @@
       <c r="G71" s="1" t="n">
         <v>10049</v>
       </c>
-      <c r="H71" s="28" t="n">
+      <c r="H71" s="31" t="n">
         <f aca="false">ROUND(D71*IF(ISNUMBER(SEARCH("Labour",B71)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B71)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B71)),ISNUMBER(SEARCH("RefUK",B71))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B71)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B71)),ISNUMBER(SEARCH("Lib Dem",B71))),National!$L$8,National!$L$9))))),0)</f>
         <v>71</v>
       </c>
-      <c r="I71" s="25" t="n">
+      <c r="I71" s="27" t="n">
         <f aca="false">H71/SUMIFS(H:H,A:A,A71)</f>
         <v>0.00715942321266512</v>
       </c>
-      <c r="J71" s="29" t="n">
+      <c r="J71" s="32" t="n">
         <f aca="false">ROUND(I71*SUMIF(A:A,A71,D:D),0)</f>
         <v>68</v>
       </c>
@@ -11753,11 +11780,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A71,B:B,B71)/COUNTIFS(B:B,B71,A:A,A71),0)</f>
         <v>68</v>
       </c>
-      <c r="L71" s="25" t="n">
+      <c r="L71" s="27" t="n">
         <f aca="false">K71/SUMIF(A:A,A71,K:K)</f>
         <v>0.0185741600655559</v>
       </c>
-      <c r="M71" s="1" t="n">
+      <c r="M71" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A71,J:J)*L71,0)</f>
         <v>176</v>
       </c>
@@ -11778,7 +11805,7 @@
       <c r="A72" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B72" s="27" t="s">
+      <c r="B72" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C72" s="1" t="s">
@@ -11796,15 +11823,15 @@
       <c r="G72" s="1" t="n">
         <v>10857</v>
       </c>
-      <c r="H72" s="28" t="n">
+      <c r="H72" s="31" t="n">
         <f aca="false">ROUND(D72*IF(ISNUMBER(SEARCH("Labour",B72)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B72)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B72)),ISNUMBER(SEARCH("RefUK",B72))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B72)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B72)),ISNUMBER(SEARCH("Lib Dem",B72))),National!$L$8,National!$L$9))))),0)</f>
         <v>1146</v>
       </c>
-      <c r="I72" s="25" t="n">
+      <c r="I72" s="27" t="n">
         <f aca="false">H72/SUMIFS(H:H,A:A,A72)</f>
         <v>0.207872301832033</v>
       </c>
-      <c r="J72" s="29" t="n">
+      <c r="J72" s="32" t="n">
         <f aca="false">ROUND(I72*SUMIF(A:A,A72,D:D),0)</f>
         <v>1709</v>
       </c>
@@ -11812,11 +11839,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A72,B:B,B72)/COUNTIFS(B:B,B72,A:A,A72),0)</f>
         <v>552</v>
       </c>
-      <c r="L72" s="25" t="n">
+      <c r="L72" s="27" t="n">
         <f aca="false">K72/SUMIF(A:A,A72,K:K)</f>
         <v>0.14085225822914</v>
       </c>
-      <c r="M72" s="1" t="n">
+      <c r="M72" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A72,J:J)*L72,0)</f>
         <v>1158</v>
       </c>
@@ -11837,7 +11864,7 @@
       <c r="A73" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B73" s="27" t="s">
+      <c r="B73" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C73" s="1" t="s">
@@ -11855,15 +11882,15 @@
       <c r="G73" s="1" t="n">
         <v>10857</v>
       </c>
-      <c r="H73" s="28" t="n">
+      <c r="H73" s="31" t="n">
         <f aca="false">ROUND(D73*IF(ISNUMBER(SEARCH("Labour",B73)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B73)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B73)),ISNUMBER(SEARCH("RefUK",B73))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B73)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B73)),ISNUMBER(SEARCH("Lib Dem",B73))),National!$L$8,National!$L$9))))),0)</f>
         <v>1130</v>
       </c>
-      <c r="I73" s="25" t="n">
+      <c r="I73" s="27" t="n">
         <f aca="false">H73/SUMIFS(H:H,A:A,A73)</f>
         <v>0.204970070741883</v>
       </c>
-      <c r="J73" s="29" t="n">
+      <c r="J73" s="32" t="n">
         <f aca="false">ROUND(I73*SUMIF(A:A,A73,D:D),0)</f>
         <v>1685</v>
       </c>
@@ -11871,11 +11898,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A73,B:B,B73)/COUNTIFS(B:B,B73,A:A,A73),0)</f>
         <v>552</v>
       </c>
-      <c r="L73" s="25" t="n">
+      <c r="L73" s="27" t="n">
         <f aca="false">K73/SUMIF(A:A,A73,K:K)</f>
         <v>0.14085225822914</v>
       </c>
-      <c r="M73" s="1" t="n">
+      <c r="M73" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A73,J:J)*L73,0)</f>
         <v>1158</v>
       </c>
@@ -11896,7 +11923,7 @@
       <c r="A74" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B74" s="27" t="s">
+      <c r="B74" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C74" s="1" t="s">
@@ -11914,15 +11941,15 @@
       <c r="G74" s="1" t="n">
         <v>10857</v>
       </c>
-      <c r="H74" s="28" t="n">
+      <c r="H74" s="31" t="n">
         <f aca="false">ROUND(D74*IF(ISNUMBER(SEARCH("Labour",B74)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B74)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B74)),ISNUMBER(SEARCH("RefUK",B74))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B74)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B74)),ISNUMBER(SEARCH("Lib Dem",B74))),National!$L$8,National!$L$9))))),0)</f>
         <v>1058</v>
       </c>
-      <c r="I74" s="25" t="n">
+      <c r="I74" s="27" t="n">
         <f aca="false">H74/SUMIFS(H:H,A:A,A74)</f>
         <v>0.191910030836205</v>
       </c>
-      <c r="J74" s="29" t="n">
+      <c r="J74" s="32" t="n">
         <f aca="false">ROUND(I74*SUMIF(A:A,A74,D:D),0)</f>
         <v>1578</v>
       </c>
@@ -11930,11 +11957,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A74,B:B,B74)/COUNTIFS(B:B,B74,A:A,A74),0)</f>
         <v>552</v>
       </c>
-      <c r="L74" s="25" t="n">
+      <c r="L74" s="27" t="n">
         <f aca="false">K74/SUMIF(A:A,A74,K:K)</f>
         <v>0.14085225822914</v>
       </c>
-      <c r="M74" s="1" t="n">
+      <c r="M74" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A74,J:J)*L74,0)</f>
         <v>1158</v>
       </c>
@@ -11955,7 +11982,7 @@
       <c r="A75" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B75" s="27" t="s">
+      <c r="B75" s="30" t="s">
         <v>216</v>
       </c>
       <c r="C75" s="1" t="s">
@@ -11973,15 +12000,15 @@
       <c r="G75" s="1" t="n">
         <v>10857</v>
       </c>
-      <c r="H75" s="28" t="n">
+      <c r="H75" s="31" t="n">
         <f aca="false">ROUND(D75*IF(ISNUMBER(SEARCH("Labour",B75)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B75)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B75)),ISNUMBER(SEARCH("RefUK",B75))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B75)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B75)),ISNUMBER(SEARCH("Lib Dem",B75))),National!$L$8,National!$L$9))))),0)</f>
         <v>363</v>
       </c>
-      <c r="I75" s="25" t="n">
+      <c r="I75" s="27" t="n">
         <f aca="false">H75/SUMIFS(H:H,A:A,A75)</f>
         <v>0.0658443678577907</v>
       </c>
-      <c r="J75" s="29" t="n">
+      <c r="J75" s="32" t="n">
         <f aca="false">ROUND(I75*SUMIF(A:A,A75,D:D),0)</f>
         <v>541</v>
       </c>
@@ -11989,11 +12016,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A75,B:B,B75)/COUNTIFS(B:B,B75,A:A,A75),0)</f>
         <v>165</v>
       </c>
-      <c r="L75" s="25" t="n">
+      <c r="L75" s="27" t="n">
         <f aca="false">K75/SUMIF(A:A,A75,K:K)</f>
         <v>0.0421025771880582</v>
       </c>
-      <c r="M75" s="1" t="n">
+      <c r="M75" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A75,J:J)*L75,0)</f>
         <v>346</v>
       </c>
@@ -12014,7 +12041,7 @@
       <c r="A76" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B76" s="27" t="s">
+      <c r="B76" s="30" t="s">
         <v>216</v>
       </c>
       <c r="C76" s="1" t="s">
@@ -12032,15 +12059,15 @@
       <c r="G76" s="1" t="n">
         <v>10857</v>
       </c>
-      <c r="H76" s="28" t="n">
+      <c r="H76" s="31" t="n">
         <f aca="false">ROUND(D76*IF(ISNUMBER(SEARCH("Labour",B76)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B76)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B76)),ISNUMBER(SEARCH("RefUK",B76))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B76)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B76)),ISNUMBER(SEARCH("Lib Dem",B76))),National!$L$8,National!$L$9))))),0)</f>
         <v>323</v>
       </c>
-      <c r="I76" s="25" t="n">
+      <c r="I76" s="27" t="n">
         <f aca="false">H76/SUMIFS(H:H,A:A,A76)</f>
         <v>0.0585887901324143</v>
       </c>
-      <c r="J76" s="29" t="n">
+      <c r="J76" s="32" t="n">
         <f aca="false">ROUND(I76*SUMIF(A:A,A76,D:D),0)</f>
         <v>482</v>
       </c>
@@ -12048,11 +12075,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A76,B:B,B76)/COUNTIFS(B:B,B76,A:A,A76),0)</f>
         <v>165</v>
       </c>
-      <c r="L76" s="25" t="n">
+      <c r="L76" s="27" t="n">
         <f aca="false">K76/SUMIF(A:A,A76,K:K)</f>
         <v>0.0421025771880582</v>
       </c>
-      <c r="M76" s="1" t="n">
+      <c r="M76" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A76,J:J)*L76,0)</f>
         <v>346</v>
       </c>
@@ -12073,7 +12100,7 @@
       <c r="A77" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B77" s="27" t="s">
+      <c r="B77" s="30" t="s">
         <v>216</v>
       </c>
       <c r="C77" s="1" t="s">
@@ -12091,15 +12118,15 @@
       <c r="G77" s="1" t="n">
         <v>10857</v>
       </c>
-      <c r="H77" s="28" t="n">
+      <c r="H77" s="31" t="n">
         <f aca="false">ROUND(D77*IF(ISNUMBER(SEARCH("Labour",B77)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B77)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B77)),ISNUMBER(SEARCH("RefUK",B77))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B77)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B77)),ISNUMBER(SEARCH("Lib Dem",B77))),National!$L$8,National!$L$9))))),0)</f>
         <v>307</v>
       </c>
-      <c r="I77" s="25" t="n">
+      <c r="I77" s="27" t="n">
         <f aca="false">H77/SUMIFS(H:H,A:A,A77)</f>
         <v>0.0556865590422637</v>
       </c>
-      <c r="J77" s="29" t="n">
+      <c r="J77" s="32" t="n">
         <f aca="false">ROUND(I77*SUMIF(A:A,A77,D:D),0)</f>
         <v>458</v>
       </c>
@@ -12107,11 +12134,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A77,B:B,B77)/COUNTIFS(B:B,B77,A:A,A77),0)</f>
         <v>165</v>
       </c>
-      <c r="L77" s="25" t="n">
+      <c r="L77" s="27" t="n">
         <f aca="false">K77/SUMIF(A:A,A77,K:K)</f>
         <v>0.0421025771880582</v>
       </c>
-      <c r="M77" s="1" t="n">
+      <c r="M77" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A77,J:J)*L77,0)</f>
         <v>346</v>
       </c>
@@ -12132,7 +12159,7 @@
       <c r="A78" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B78" s="30" t="s">
+      <c r="B78" s="33" t="s">
         <v>219</v>
       </c>
       <c r="C78" s="1" t="s">
@@ -12150,15 +12177,15 @@
       <c r="G78" s="1" t="n">
         <v>10857</v>
       </c>
-      <c r="H78" s="28" t="n">
+      <c r="H78" s="31" t="n">
         <f aca="false">ROUND(D78*IF(ISNUMBER(SEARCH("Labour",B78)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B78)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B78)),ISNUMBER(SEARCH("RefUK",B78))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B78)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B78)),ISNUMBER(SEARCH("Lib Dem",B78))),National!$L$8,National!$L$9))))),0)</f>
         <v>805</v>
       </c>
-      <c r="I78" s="25" t="n">
+      <c r="I78" s="27" t="n">
         <f aca="false">H78/SUMIFS(H:H,A:A,A78)</f>
         <v>0.1460185017232</v>
       </c>
-      <c r="J78" s="29" t="n">
+      <c r="J78" s="32" t="n">
         <f aca="false">ROUND(I78*SUMIF(A:A,A78,D:D),0)</f>
         <v>1200</v>
       </c>
@@ -12166,11 +12193,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A78,B:B,B78)/COUNTIFS(B:B,B78,A:A,A78),0)</f>
         <v>1200</v>
       </c>
-      <c r="L78" s="25" t="n">
+      <c r="L78" s="27" t="n">
         <f aca="false">K78/SUMIF(A:A,A78,K:K)</f>
         <v>0.306200561367696</v>
       </c>
-      <c r="M78" s="1" t="n">
+      <c r="M78" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A78,J:J)*L78,0)</f>
         <v>2517</v>
       </c>
@@ -12191,7 +12218,7 @@
       <c r="A79" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B79" s="27" t="s">
+      <c r="B79" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C79" s="1" t="s">
@@ -12209,15 +12236,15 @@
       <c r="G79" s="1" t="n">
         <v>10857</v>
       </c>
-      <c r="H79" s="28" t="n">
+      <c r="H79" s="31" t="n">
         <f aca="false">ROUND(D79*IF(ISNUMBER(SEARCH("Labour",B79)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B79)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B79)),ISNUMBER(SEARCH("RefUK",B79))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B79)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B79)),ISNUMBER(SEARCH("Lib Dem",B79))),National!$L$8,National!$L$9))))),0)</f>
         <v>381</v>
       </c>
-      <c r="I79" s="25" t="n">
+      <c r="I79" s="27" t="n">
         <f aca="false">H79/SUMIFS(H:H,A:A,A79)</f>
         <v>0.0691093778342101</v>
       </c>
-      <c r="J79" s="29" t="n">
+      <c r="J79" s="32" t="n">
         <f aca="false">ROUND(I79*SUMIF(A:A,A79,D:D),0)</f>
         <v>568</v>
       </c>
@@ -12225,11 +12252,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A79,B:B,B79)/COUNTIFS(B:B,B79,A:A,A79),0)</f>
         <v>568</v>
       </c>
-      <c r="L79" s="25" t="n">
+      <c r="L79" s="27" t="n">
         <f aca="false">K79/SUMIF(A:A,A79,K:K)</f>
         <v>0.144934932380709</v>
       </c>
-      <c r="M79" s="1" t="n">
+      <c r="M79" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A79,J:J)*L79,0)</f>
         <v>1192</v>
       </c>
@@ -12250,7 +12277,7 @@
       <c r="A80" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B80" s="27" t="s">
+      <c r="B80" s="30" t="s">
         <v>249</v>
       </c>
       <c r="C80" s="1" t="s">
@@ -12268,15 +12295,15 @@
       <c r="G80" s="1" t="n">
         <v>6871</v>
       </c>
-      <c r="H80" s="28" t="n">
+      <c r="H80" s="31" t="n">
         <f aca="false">ROUND(D80*IF(ISNUMBER(SEARCH("Labour",B80)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B80)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B80)),ISNUMBER(SEARCH("RefUK",B80))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B80)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B80)),ISNUMBER(SEARCH("Lib Dem",B80))),National!$L$8,National!$L$9))))),0)</f>
         <v>315</v>
       </c>
-      <c r="I80" s="25" t="n">
+      <c r="I80" s="27" t="n">
         <f aca="false">H80/SUMIFS(H:H,A:A,A80)</f>
         <v>0.165615141955836</v>
       </c>
-      <c r="J80" s="29" t="n">
+      <c r="J80" s="32" t="n">
         <f aca="false">ROUND(I80*SUMIF(A:A,A80,D:D),0)</f>
         <v>482</v>
       </c>
@@ -12284,11 +12311,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A80,B:B,B80)/COUNTIFS(B:B,B80,A:A,A80),0)</f>
         <v>234</v>
       </c>
-      <c r="L80" s="25" t="n">
+      <c r="L80" s="27" t="n">
         <f aca="false">K80/SUMIF(A:A,A80,K:K)</f>
         <v>0.122193211488251</v>
       </c>
-      <c r="M80" s="1" t="n">
+      <c r="M80" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A80,J:J)*L80,0)</f>
         <v>355</v>
       </c>
@@ -12309,7 +12336,7 @@
       <c r="A81" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B81" s="27" t="s">
+      <c r="B81" s="30" t="s">
         <v>249</v>
       </c>
       <c r="C81" s="1" t="s">
@@ -12327,15 +12354,15 @@
       <c r="G81" s="1" t="n">
         <v>6871</v>
       </c>
-      <c r="H81" s="28" t="n">
+      <c r="H81" s="31" t="n">
         <f aca="false">ROUND(D81*IF(ISNUMBER(SEARCH("Labour",B81)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B81)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B81)),ISNUMBER(SEARCH("RefUK",B81))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B81)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B81)),ISNUMBER(SEARCH("Lib Dem",B81))),National!$L$8,National!$L$9))))),0)</f>
         <v>297</v>
       </c>
-      <c r="I81" s="25" t="n">
+      <c r="I81" s="27" t="n">
         <f aca="false">H81/SUMIFS(H:H,A:A,A81)</f>
         <v>0.15615141955836</v>
       </c>
-      <c r="J81" s="29" t="n">
+      <c r="J81" s="32" t="n">
         <f aca="false">ROUND(I81*SUMIF(A:A,A81,D:D),0)</f>
         <v>454</v>
       </c>
@@ -12343,11 +12370,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A81,B:B,B81)/COUNTIFS(B:B,B81,A:A,A81),0)</f>
         <v>234</v>
       </c>
-      <c r="L81" s="25" t="n">
+      <c r="L81" s="27" t="n">
         <f aca="false">K81/SUMIF(A:A,A81,K:K)</f>
         <v>0.122193211488251</v>
       </c>
-      <c r="M81" s="1" t="n">
+      <c r="M81" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A81,J:J)*L81,0)</f>
         <v>355</v>
       </c>
@@ -12368,7 +12395,7 @@
       <c r="A82" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B82" s="27" t="s">
+      <c r="B82" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C82" s="1" t="s">
@@ -12386,15 +12413,15 @@
       <c r="G82" s="1" t="n">
         <v>6871</v>
       </c>
-      <c r="H82" s="28" t="n">
+      <c r="H82" s="31" t="n">
         <f aca="false">ROUND(D82*IF(ISNUMBER(SEARCH("Labour",B82)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B82)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B82)),ISNUMBER(SEARCH("RefUK",B82))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B82)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B82)),ISNUMBER(SEARCH("Lib Dem",B82))),National!$L$8,National!$L$9))))),0)</f>
         <v>354</v>
       </c>
-      <c r="I82" s="25" t="n">
+      <c r="I82" s="27" t="n">
         <f aca="false">H82/SUMIFS(H:H,A:A,A82)</f>
         <v>0.186119873817035</v>
       </c>
-      <c r="J82" s="29" t="n">
+      <c r="J82" s="32" t="n">
         <f aca="false">ROUND(I82*SUMIF(A:A,A82,D:D),0)</f>
         <v>541</v>
       </c>
@@ -12402,11 +12429,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A82,B:B,B82)/COUNTIFS(B:B,B82,A:A,A82),0)</f>
         <v>263</v>
       </c>
-      <c r="L82" s="25" t="n">
+      <c r="L82" s="27" t="n">
         <f aca="false">K82/SUMIF(A:A,A82,K:K)</f>
         <v>0.13733681462141</v>
       </c>
-      <c r="M82" s="1" t="n">
+      <c r="M82" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A82,J:J)*L82,0)</f>
         <v>399</v>
       </c>
@@ -12427,7 +12454,7 @@
       <c r="A83" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B83" s="27" t="s">
+      <c r="B83" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C83" s="1" t="s">
@@ -12445,15 +12472,15 @@
       <c r="G83" s="1" t="n">
         <v>6871</v>
       </c>
-      <c r="H83" s="28" t="n">
+      <c r="H83" s="31" t="n">
         <f aca="false">ROUND(D83*IF(ISNUMBER(SEARCH("Labour",B83)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B83)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B83)),ISNUMBER(SEARCH("RefUK",B83))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B83)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B83)),ISNUMBER(SEARCH("Lib Dem",B83))),National!$L$8,National!$L$9))))),0)</f>
         <v>333</v>
       </c>
-      <c r="I83" s="25" t="n">
+      <c r="I83" s="27" t="n">
         <f aca="false">H83/SUMIFS(H:H,A:A,A83)</f>
         <v>0.175078864353312</v>
       </c>
-      <c r="J83" s="29" t="n">
+      <c r="J83" s="32" t="n">
         <f aca="false">ROUND(I83*SUMIF(A:A,A83,D:D),0)</f>
         <v>509</v>
       </c>
@@ -12461,11 +12488,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A83,B:B,B83)/COUNTIFS(B:B,B83,A:A,A83),0)</f>
         <v>263</v>
       </c>
-      <c r="L83" s="25" t="n">
+      <c r="L83" s="27" t="n">
         <f aca="false">K83/SUMIF(A:A,A83,K:K)</f>
         <v>0.13733681462141</v>
       </c>
-      <c r="M83" s="1" t="n">
+      <c r="M83" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A83,J:J)*L83,0)</f>
         <v>399</v>
       </c>
@@ -12486,7 +12513,7 @@
       <c r="A84" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B84" s="30" t="s">
+      <c r="B84" s="33" t="s">
         <v>219</v>
       </c>
       <c r="C84" s="1" t="s">
@@ -12504,15 +12531,15 @@
       <c r="G84" s="1" t="n">
         <v>6871</v>
       </c>
-      <c r="H84" s="28" t="n">
+      <c r="H84" s="31" t="n">
         <f aca="false">ROUND(D84*IF(ISNUMBER(SEARCH("Labour",B84)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B84)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B84)),ISNUMBER(SEARCH("RefUK",B84))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B84)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B84)),ISNUMBER(SEARCH("Lib Dem",B84))),National!$L$8,National!$L$9))))),0)</f>
         <v>413</v>
       </c>
-      <c r="I84" s="25" t="n">
+      <c r="I84" s="27" t="n">
         <f aca="false">H84/SUMIFS(H:H,A:A,A84)</f>
         <v>0.217139852786541</v>
       </c>
-      <c r="J84" s="29" t="n">
+      <c r="J84" s="32" t="n">
         <f aca="false">ROUND(I84*SUMIF(A:A,A84,D:D),0)</f>
         <v>631</v>
       </c>
@@ -12520,11 +12547,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A84,B:B,B84)/COUNTIFS(B:B,B84,A:A,A84),0)</f>
         <v>631</v>
       </c>
-      <c r="L84" s="25" t="n">
+      <c r="L84" s="27" t="n">
         <f aca="false">K84/SUMIF(A:A,A84,K:K)</f>
         <v>0.329503916449086</v>
       </c>
-      <c r="M84" s="1" t="n">
+      <c r="M84" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A84,J:J)*L84,0)</f>
         <v>958</v>
       </c>
@@ -12545,7 +12572,7 @@
       <c r="A85" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B85" s="27" t="s">
+      <c r="B85" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C85" s="1" t="s">
@@ -12563,15 +12590,15 @@
       <c r="G85" s="1" t="n">
         <v>6871</v>
       </c>
-      <c r="H85" s="28" t="n">
+      <c r="H85" s="31" t="n">
         <f aca="false">ROUND(D85*IF(ISNUMBER(SEARCH("Labour",B85)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B85)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B85)),ISNUMBER(SEARCH("RefUK",B85))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B85)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B85)),ISNUMBER(SEARCH("Lib Dem",B85))),National!$L$8,National!$L$9))))),0)</f>
         <v>190</v>
       </c>
-      <c r="I85" s="25" t="n">
+      <c r="I85" s="27" t="n">
         <f aca="false">H85/SUMIFS(H:H,A:A,A85)</f>
         <v>0.0998948475289169</v>
       </c>
-      <c r="J85" s="29" t="n">
+      <c r="J85" s="32" t="n">
         <f aca="false">ROUND(I85*SUMIF(A:A,A85,D:D),0)</f>
         <v>290</v>
       </c>
@@ -12579,11 +12606,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A85,B:B,B85)/COUNTIFS(B:B,B85,A:A,A85),0)</f>
         <v>290</v>
       </c>
-      <c r="L85" s="25" t="n">
+      <c r="L85" s="27" t="n">
         <f aca="false">K85/SUMIF(A:A,A85,K:K)</f>
         <v>0.151436031331593</v>
       </c>
-      <c r="M85" s="1" t="n">
+      <c r="M85" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A85,J:J)*L85,0)</f>
         <v>440</v>
       </c>
@@ -12604,7 +12631,7 @@
       <c r="A86" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B86" s="27" t="s">
+      <c r="B86" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C86" s="1" t="s">
@@ -12622,15 +12649,15 @@
       <c r="G86" s="1" t="n">
         <v>6645</v>
       </c>
-      <c r="H86" s="28" t="n">
+      <c r="H86" s="31" t="n">
         <f aca="false">ROUND(D86*IF(ISNUMBER(SEARCH("Labour",B86)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B86)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B86)),ISNUMBER(SEARCH("RefUK",B86))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B86)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B86)),ISNUMBER(SEARCH("Lib Dem",B86))),National!$L$8,National!$L$9))))),0)</f>
         <v>613</v>
       </c>
-      <c r="I86" s="25" t="n">
+      <c r="I86" s="27" t="n">
         <f aca="false">H86/SUMIFS(H:H,A:A,A86)</f>
         <v>0.289697542533081</v>
       </c>
-      <c r="J86" s="29" t="n">
+      <c r="J86" s="32" t="n">
         <f aca="false">ROUND(I86*SUMIF(A:A,A86,D:D),0)</f>
         <v>885</v>
       </c>
@@ -12638,11 +12665,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A86,B:B,B86)/COUNTIFS(B:B,B86,A:A,A86),0)</f>
         <v>441</v>
       </c>
-      <c r="L86" s="25" t="n">
+      <c r="L86" s="27" t="n">
         <f aca="false">K86/SUMIF(A:A,A86,K:K)</f>
         <v>0.230769230769231</v>
       </c>
-      <c r="M86" s="1" t="n">
+      <c r="M86" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A86,J:J)*L86,0)</f>
         <v>705</v>
       </c>
@@ -12663,7 +12690,7 @@
       <c r="A87" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B87" s="27" t="s">
+      <c r="B87" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C87" s="1" t="s">
@@ -12681,15 +12708,15 @@
       <c r="G87" s="1" t="n">
         <v>6645</v>
       </c>
-      <c r="H87" s="28" t="n">
+      <c r="H87" s="31" t="n">
         <f aca="false">ROUND(D87*IF(ISNUMBER(SEARCH("Labour",B87)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B87)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B87)),ISNUMBER(SEARCH("RefUK",B87))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B87)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B87)),ISNUMBER(SEARCH("Lib Dem",B87))),National!$L$8,National!$L$9))))),0)</f>
         <v>610</v>
       </c>
-      <c r="I87" s="25" t="n">
+      <c r="I87" s="27" t="n">
         <f aca="false">H87/SUMIFS(H:H,A:A,A87)</f>
         <v>0.2882797731569</v>
       </c>
-      <c r="J87" s="29" t="n">
+      <c r="J87" s="32" t="n">
         <f aca="false">ROUND(I87*SUMIF(A:A,A87,D:D),0)</f>
         <v>880</v>
       </c>
@@ -12697,11 +12724,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A87,B:B,B87)/COUNTIFS(B:B,B87,A:A,A87),0)</f>
         <v>441</v>
       </c>
-      <c r="L87" s="25" t="n">
+      <c r="L87" s="27" t="n">
         <f aca="false">K87/SUMIF(A:A,A87,K:K)</f>
         <v>0.230769230769231</v>
       </c>
-      <c r="M87" s="1" t="n">
+      <c r="M87" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A87,J:J)*L87,0)</f>
         <v>705</v>
       </c>
@@ -12722,7 +12749,7 @@
       <c r="A88" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B88" s="27" t="s">
+      <c r="B88" s="30" t="s">
         <v>216</v>
       </c>
       <c r="C88" s="1" t="s">
@@ -12740,15 +12767,15 @@
       <c r="G88" s="1" t="n">
         <v>6645</v>
       </c>
-      <c r="H88" s="28" t="n">
+      <c r="H88" s="31" t="n">
         <f aca="false">ROUND(D88*IF(ISNUMBER(SEARCH("Labour",B88)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B88)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B88)),ISNUMBER(SEARCH("RefUK",B88))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B88)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B88)),ISNUMBER(SEARCH("Lib Dem",B88))),National!$L$8,National!$L$9))))),0)</f>
         <v>192</v>
       </c>
-      <c r="I88" s="25" t="n">
+      <c r="I88" s="27" t="n">
         <f aca="false">H88/SUMIFS(H:H,A:A,A88)</f>
         <v>0.0907372400756144</v>
       </c>
-      <c r="J88" s="29" t="n">
+      <c r="J88" s="32" t="n">
         <f aca="false">ROUND(I88*SUMIF(A:A,A88,D:D),0)</f>
         <v>277</v>
       </c>
@@ -12756,11 +12783,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A88,B:B,B88)/COUNTIFS(B:B,B88,A:A,A88),0)</f>
         <v>130</v>
       </c>
-      <c r="L88" s="25" t="n">
+      <c r="L88" s="27" t="n">
         <f aca="false">K88/SUMIF(A:A,A88,K:K)</f>
         <v>0.0680272108843538</v>
       </c>
-      <c r="M88" s="1" t="n">
+      <c r="M88" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A88,J:J)*L88,0)</f>
         <v>208</v>
       </c>
@@ -12781,7 +12808,7 @@
       <c r="A89" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B89" s="27" t="s">
+      <c r="B89" s="30" t="s">
         <v>216</v>
       </c>
       <c r="C89" s="1" t="s">
@@ -12799,15 +12826,15 @@
       <c r="G89" s="1" t="n">
         <v>6645</v>
       </c>
-      <c r="H89" s="28" t="n">
+      <c r="H89" s="31" t="n">
         <f aca="false">ROUND(D89*IF(ISNUMBER(SEARCH("Labour",B89)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B89)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B89)),ISNUMBER(SEARCH("RefUK",B89))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B89)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B89)),ISNUMBER(SEARCH("Lib Dem",B89))),National!$L$8,National!$L$9))))),0)</f>
         <v>168</v>
       </c>
-      <c r="I89" s="25" t="n">
+      <c r="I89" s="27" t="n">
         <f aca="false">H89/SUMIFS(H:H,A:A,A89)</f>
         <v>0.0793950850661626</v>
       </c>
-      <c r="J89" s="29" t="n">
+      <c r="J89" s="32" t="n">
         <f aca="false">ROUND(I89*SUMIF(A:A,A89,D:D),0)</f>
         <v>242</v>
       </c>
@@ -12815,11 +12842,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A89,B:B,B89)/COUNTIFS(B:B,B89,A:A,A89),0)</f>
         <v>130</v>
       </c>
-      <c r="L89" s="25" t="n">
+      <c r="L89" s="27" t="n">
         <f aca="false">K89/SUMIF(A:A,A89,K:K)</f>
         <v>0.0680272108843538</v>
       </c>
-      <c r="M89" s="1" t="n">
+      <c r="M89" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A89,J:J)*L89,0)</f>
         <v>208</v>
       </c>
@@ -12840,7 +12867,7 @@
       <c r="A90" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B90" s="30" t="s">
+      <c r="B90" s="33" t="s">
         <v>219</v>
       </c>
       <c r="C90" s="1" t="s">
@@ -12858,15 +12885,15 @@
       <c r="G90" s="1" t="n">
         <v>6645</v>
       </c>
-      <c r="H90" s="28" t="n">
+      <c r="H90" s="31" t="n">
         <f aca="false">ROUND(D90*IF(ISNUMBER(SEARCH("Labour",B90)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B90)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B90)),ISNUMBER(SEARCH("RefUK",B90))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B90)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B90)),ISNUMBER(SEARCH("Lib Dem",B90))),National!$L$8,National!$L$9))))),0)</f>
         <v>371</v>
       </c>
-      <c r="I90" s="25" t="n">
+      <c r="I90" s="27" t="n">
         <f aca="false">H90/SUMIFS(H:H,A:A,A90)</f>
         <v>0.175330812854442</v>
       </c>
-      <c r="J90" s="29" t="n">
+      <c r="J90" s="32" t="n">
         <f aca="false">ROUND(I90*SUMIF(A:A,A90,D:D),0)</f>
         <v>535</v>
       </c>
@@ -12874,11 +12901,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A90,B:B,B90)/COUNTIFS(B:B,B90,A:A,A90),0)</f>
         <v>535</v>
       </c>
-      <c r="L90" s="25" t="n">
+      <c r="L90" s="27" t="n">
         <f aca="false">K90/SUMIF(A:A,A90,K:K)</f>
         <v>0.279958137100994</v>
       </c>
-      <c r="M90" s="1" t="n">
+      <c r="M90" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A90,J:J)*L90,0)</f>
         <v>855</v>
       </c>
@@ -12899,7 +12926,7 @@
       <c r="A91" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B91" s="27" t="s">
+      <c r="B91" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C91" s="1" t="s">
@@ -12917,15 +12944,15 @@
       <c r="G91" s="1" t="n">
         <v>6645</v>
       </c>
-      <c r="H91" s="28" t="n">
+      <c r="H91" s="31" t="n">
         <f aca="false">ROUND(D91*IF(ISNUMBER(SEARCH("Labour",B91)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B91)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B91)),ISNUMBER(SEARCH("RefUK",B91))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B91)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B91)),ISNUMBER(SEARCH("Lib Dem",B91))),National!$L$8,National!$L$9))))),0)</f>
         <v>162</v>
       </c>
-      <c r="I91" s="25" t="n">
+      <c r="I91" s="27" t="n">
         <f aca="false">H91/SUMIFS(H:H,A:A,A91)</f>
         <v>0.0765595463137996</v>
       </c>
-      <c r="J91" s="29" t="n">
+      <c r="J91" s="32" t="n">
         <f aca="false">ROUND(I91*SUMIF(A:A,A91,D:D),0)</f>
         <v>234</v>
       </c>
@@ -12933,11 +12960,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A91,B:B,B91)/COUNTIFS(B:B,B91,A:A,A91),0)</f>
         <v>234</v>
       </c>
-      <c r="L91" s="25" t="n">
+      <c r="L91" s="27" t="n">
         <f aca="false">K91/SUMIF(A:A,A91,K:K)</f>
         <v>0.122448979591837</v>
       </c>
-      <c r="M91" s="1" t="n">
+      <c r="M91" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A91,J:J)*L91,0)</f>
         <v>374</v>
       </c>
@@ -12958,7 +12985,7 @@
       <c r="A92" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B92" s="27" t="s">
+      <c r="B92" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C92" s="1" t="s">
@@ -12976,15 +13003,15 @@
       <c r="G92" s="1" t="n">
         <v>10341</v>
       </c>
-      <c r="H92" s="28" t="n">
+      <c r="H92" s="31" t="n">
         <f aca="false">ROUND(D92*IF(ISNUMBER(SEARCH("Labour",B92)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B92)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B92)),ISNUMBER(SEARCH("RefUK",B92))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B92)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B92)),ISNUMBER(SEARCH("Lib Dem",B92))),National!$L$8,National!$L$9))))),0)</f>
         <v>791</v>
       </c>
-      <c r="I92" s="25" t="n">
+      <c r="I92" s="27" t="n">
         <f aca="false">H92/SUMIFS(H:H,A:A,A92)</f>
         <v>0.123247117482082</v>
       </c>
-      <c r="J92" s="29" t="n">
+      <c r="J92" s="32" t="n">
         <f aca="false">ROUND(I92*SUMIF(A:A,A92,D:D),0)</f>
         <v>1010</v>
       </c>
@@ -12992,11 +13019,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A92,B:B,B92)/COUNTIFS(B:B,B92,A:A,A92),0)</f>
         <v>322</v>
       </c>
-      <c r="L92" s="25" t="n">
+      <c r="L92" s="27" t="n">
         <f aca="false">K92/SUMIF(A:A,A92,K:K)</f>
         <v>0.0888766215843224</v>
       </c>
-      <c r="M92" s="1" t="n">
+      <c r="M92" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A92,J:J)*L92,0)</f>
         <v>728</v>
       </c>
@@ -13017,7 +13044,7 @@
       <c r="A93" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B93" s="27" t="s">
+      <c r="B93" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C93" s="1" t="s">
@@ -13035,15 +13062,15 @@
       <c r="G93" s="1" t="n">
         <v>10341</v>
       </c>
-      <c r="H93" s="28" t="n">
+      <c r="H93" s="31" t="n">
         <f aca="false">ROUND(D93*IF(ISNUMBER(SEARCH("Labour",B93)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B93)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B93)),ISNUMBER(SEARCH("RefUK",B93))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B93)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B93)),ISNUMBER(SEARCH("Lib Dem",B93))),National!$L$8,National!$L$9))))),0)</f>
         <v>744</v>
       </c>
-      <c r="I93" s="25" t="n">
+      <c r="I93" s="27" t="n">
         <f aca="false">H93/SUMIFS(H:H,A:A,A93)</f>
         <v>0.115923963851667</v>
       </c>
-      <c r="J93" s="29" t="n">
+      <c r="J93" s="32" t="n">
         <f aca="false">ROUND(I93*SUMIF(A:A,A93,D:D),0)</f>
         <v>950</v>
       </c>
@@ -13051,11 +13078,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A93,B:B,B93)/COUNTIFS(B:B,B93,A:A,A93),0)</f>
         <v>322</v>
       </c>
-      <c r="L93" s="25" t="n">
+      <c r="L93" s="27" t="n">
         <f aca="false">K93/SUMIF(A:A,A93,K:K)</f>
         <v>0.0888766215843224</v>
       </c>
-      <c r="M93" s="1" t="n">
+      <c r="M93" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A93,J:J)*L93,0)</f>
         <v>728</v>
       </c>
@@ -13076,7 +13103,7 @@
       <c r="A94" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B94" s="27" t="s">
+      <c r="B94" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C94" s="1" t="s">
@@ -13094,15 +13121,15 @@
       <c r="G94" s="1" t="n">
         <v>10341</v>
       </c>
-      <c r="H94" s="28" t="n">
+      <c r="H94" s="31" t="n">
         <f aca="false">ROUND(D94*IF(ISNUMBER(SEARCH("Labour",B94)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B94)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B94)),ISNUMBER(SEARCH("RefUK",B94))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B94)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B94)),ISNUMBER(SEARCH("Lib Dem",B94))),National!$L$8,National!$L$9))))),0)</f>
         <v>735</v>
       </c>
-      <c r="I94" s="25" t="n">
+      <c r="I94" s="27" t="n">
         <f aca="false">H94/SUMIFS(H:H,A:A,A94)</f>
         <v>0.114521657837333</v>
       </c>
-      <c r="J94" s="29" t="n">
+      <c r="J94" s="32" t="n">
         <f aca="false">ROUND(I94*SUMIF(A:A,A94,D:D),0)</f>
         <v>938</v>
       </c>
@@ -13110,11 +13137,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A94,B:B,B94)/COUNTIFS(B:B,B94,A:A,A94),0)</f>
         <v>322</v>
       </c>
-      <c r="L94" s="25" t="n">
+      <c r="L94" s="27" t="n">
         <f aca="false">K94/SUMIF(A:A,A94,K:K)</f>
         <v>0.0888766215843224</v>
       </c>
-      <c r="M94" s="1" t="n">
+      <c r="M94" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A94,J:J)*L94,0)</f>
         <v>728</v>
       </c>
@@ -13135,7 +13162,7 @@
       <c r="A95" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B95" s="27" t="s">
+      <c r="B95" s="30" t="s">
         <v>216</v>
       </c>
       <c r="C95" s="1" t="s">
@@ -13153,15 +13180,15 @@
       <c r="G95" s="1" t="n">
         <v>10341</v>
       </c>
-      <c r="H95" s="28" t="n">
+      <c r="H95" s="31" t="n">
         <f aca="false">ROUND(D95*IF(ISNUMBER(SEARCH("Labour",B95)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B95)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B95)),ISNUMBER(SEARCH("RefUK",B95))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B95)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B95)),ISNUMBER(SEARCH("Lib Dem",B95))),National!$L$8,National!$L$9))))),0)</f>
         <v>405</v>
       </c>
-      <c r="I95" s="25" t="n">
+      <c r="I95" s="27" t="n">
         <f aca="false">H95/SUMIFS(H:H,A:A,A95)</f>
         <v>0.0631037706450608</v>
       </c>
-      <c r="J95" s="29" t="n">
+      <c r="J95" s="32" t="n">
         <f aca="false">ROUND(I95*SUMIF(A:A,A95,D:D),0)</f>
         <v>517</v>
       </c>
@@ -13169,11 +13196,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A95,B:B,B95)/COUNTIFS(B:B,B95,A:A,A95),0)</f>
         <v>161</v>
       </c>
-      <c r="L95" s="25" t="n">
+      <c r="L95" s="27" t="n">
         <f aca="false">K95/SUMIF(A:A,A95,K:K)</f>
         <v>0.0444383107921612</v>
       </c>
-      <c r="M95" s="1" t="n">
+      <c r="M95" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A95,J:J)*L95,0)</f>
         <v>364</v>
       </c>
@@ -13194,7 +13221,7 @@
       <c r="A96" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B96" s="27" t="s">
+      <c r="B96" s="30" t="s">
         <v>216</v>
       </c>
       <c r="C96" s="1" t="s">
@@ -13212,15 +13239,15 @@
       <c r="G96" s="1" t="n">
         <v>10341</v>
       </c>
-      <c r="H96" s="28" t="n">
+      <c r="H96" s="31" t="n">
         <f aca="false">ROUND(D96*IF(ISNUMBER(SEARCH("Labour",B96)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B96)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B96)),ISNUMBER(SEARCH("RefUK",B96))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B96)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B96)),ISNUMBER(SEARCH("Lib Dem",B96))),National!$L$8,National!$L$9))))),0)</f>
         <v>374</v>
       </c>
-      <c r="I96" s="25" t="n">
+      <c r="I96" s="27" t="n">
         <f aca="false">H96/SUMIFS(H:H,A:A,A96)</f>
         <v>0.0582736054845746</v>
       </c>
-      <c r="J96" s="29" t="n">
+      <c r="J96" s="32" t="n">
         <f aca="false">ROUND(I96*SUMIF(A:A,A96,D:D),0)</f>
         <v>477</v>
       </c>
@@ -13228,11 +13255,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A96,B:B,B96)/COUNTIFS(B:B,B96,A:A,A96),0)</f>
         <v>161</v>
       </c>
-      <c r="L96" s="25" t="n">
+      <c r="L96" s="27" t="n">
         <f aca="false">K96/SUMIF(A:A,A96,K:K)</f>
         <v>0.0444383107921612</v>
       </c>
-      <c r="M96" s="1" t="n">
+      <c r="M96" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A96,J:J)*L96,0)</f>
         <v>364</v>
       </c>
@@ -13253,7 +13280,7 @@
       <c r="A97" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B97" s="27" t="s">
+      <c r="B97" s="30" t="s">
         <v>216</v>
       </c>
       <c r="C97" s="1" t="s">
@@ -13271,15 +13298,15 @@
       <c r="G97" s="1" t="n">
         <v>10341</v>
       </c>
-      <c r="H97" s="28" t="n">
+      <c r="H97" s="31" t="n">
         <f aca="false">ROUND(D97*IF(ISNUMBER(SEARCH("Labour",B97)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B97)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B97)),ISNUMBER(SEARCH("RefUK",B97))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B97)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B97)),ISNUMBER(SEARCH("Lib Dem",B97))),National!$L$8,National!$L$9))))),0)</f>
         <v>359</v>
       </c>
-      <c r="I97" s="25" t="n">
+      <c r="I97" s="27" t="n">
         <f aca="false">H97/SUMIFS(H:H,A:A,A97)</f>
         <v>0.0559364287940168</v>
       </c>
-      <c r="J97" s="29" t="n">
+      <c r="J97" s="32" t="n">
         <f aca="false">ROUND(I97*SUMIF(A:A,A97,D:D),0)</f>
         <v>458</v>
       </c>
@@ -13287,11 +13314,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A97,B:B,B97)/COUNTIFS(B:B,B97,A:A,A97),0)</f>
         <v>161</v>
       </c>
-      <c r="L97" s="25" t="n">
+      <c r="L97" s="27" t="n">
         <f aca="false">K97/SUMIF(A:A,A97,K:K)</f>
         <v>0.0444383107921612</v>
       </c>
-      <c r="M97" s="1" t="n">
+      <c r="M97" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A97,J:J)*L97,0)</f>
         <v>364</v>
       </c>
@@ -13312,7 +13339,7 @@
       <c r="A98" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B98" s="27" t="s">
+      <c r="B98" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C98" s="1" t="s">
@@ -13330,15 +13357,15 @@
       <c r="G98" s="1" t="n">
         <v>10341</v>
       </c>
-      <c r="H98" s="28" t="n">
+      <c r="H98" s="31" t="n">
         <f aca="false">ROUND(D98*IF(ISNUMBER(SEARCH("Labour",B98)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B98)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B98)),ISNUMBER(SEARCH("RefUK",B98))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B98)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B98)),ISNUMBER(SEARCH("Lib Dem",B98))),National!$L$8,National!$L$9))))),0)</f>
         <v>945</v>
       </c>
-      <c r="I98" s="25" t="n">
+      <c r="I98" s="27" t="n">
         <f aca="false">H98/SUMIFS(H:H,A:A,A98)</f>
         <v>0.147242131505142</v>
       </c>
-      <c r="J98" s="29" t="n">
+      <c r="J98" s="32" t="n">
         <f aca="false">ROUND(I98*SUMIF(A:A,A98,D:D),0)</f>
         <v>1206</v>
       </c>
@@ -13346,11 +13373,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A98,B:B,B98)/COUNTIFS(B:B,B98,A:A,A98),0)</f>
         <v>278</v>
       </c>
-      <c r="L98" s="25" t="n">
+      <c r="L98" s="27" t="n">
         <f aca="false">K98/SUMIF(A:A,A98,K:K)</f>
         <v>0.0767319900634833</v>
       </c>
-      <c r="M98" s="1" t="n">
+      <c r="M98" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A98,J:J)*L98,0)</f>
         <v>629</v>
       </c>
@@ -13371,7 +13398,7 @@
       <c r="A99" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B99" s="30" t="s">
+      <c r="B99" s="33" t="s">
         <v>219</v>
       </c>
       <c r="C99" s="1" t="s">
@@ -13389,15 +13416,15 @@
       <c r="G99" s="1" t="n">
         <v>10341</v>
       </c>
-      <c r="H99" s="28" t="n">
+      <c r="H99" s="31" t="n">
         <f aca="false">ROUND(D99*IF(ISNUMBER(SEARCH("Labour",B99)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B99)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B99)),ISNUMBER(SEARCH("RefUK",B99))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B99)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B99)),ISNUMBER(SEARCH("Lib Dem",B99))),National!$L$8,National!$L$9))))),0)</f>
         <v>1050</v>
       </c>
-      <c r="I99" s="25" t="n">
+      <c r="I99" s="27" t="n">
         <f aca="false">H99/SUMIFS(H:H,A:A,A99)</f>
         <v>0.163602368339046</v>
       </c>
-      <c r="J99" s="29" t="n">
+      <c r="J99" s="32" t="n">
         <f aca="false">ROUND(I99*SUMIF(A:A,A99,D:D),0)</f>
         <v>1340</v>
       </c>
@@ -13405,11 +13432,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A99,B:B,B99)/COUNTIFS(B:B,B99,A:A,A99),0)</f>
         <v>1340</v>
       </c>
-      <c r="L99" s="25" t="n">
+      <c r="L99" s="27" t="n">
         <f aca="false">K99/SUMIF(A:A,A99,K:K)</f>
         <v>0.369859232680099</v>
       </c>
-      <c r="M99" s="1" t="n">
+      <c r="M99" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A99,J:J)*L99,0)</f>
         <v>3030</v>
       </c>
@@ -13430,7 +13457,7 @@
       <c r="A100" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B100" s="27" t="s">
+      <c r="B100" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C100" s="1" t="s">
@@ -13448,15 +13475,15 @@
       <c r="G100" s="1" t="n">
         <v>10341</v>
       </c>
-      <c r="H100" s="28" t="n">
+      <c r="H100" s="31" t="n">
         <f aca="false">ROUND(D100*IF(ISNUMBER(SEARCH("Labour",B100)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B100)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B100)),ISNUMBER(SEARCH("RefUK",B100))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B100)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B100)),ISNUMBER(SEARCH("Lib Dem",B100))),National!$L$8,National!$L$9))))),0)</f>
         <v>563</v>
       </c>
-      <c r="I100" s="25" t="n">
+      <c r="I100" s="27" t="n">
         <f aca="false">H100/SUMIFS(H:H,A:A,A100)</f>
         <v>0.087722031785603</v>
       </c>
-      <c r="J100" s="29" t="n">
+      <c r="J100" s="32" t="n">
         <f aca="false">ROUND(I100*SUMIF(A:A,A100,D:D),0)</f>
         <v>719</v>
       </c>
@@ -13464,11 +13491,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A100,B:B,B100)/COUNTIFS(B:B,B100,A:A,A100),0)</f>
         <v>278</v>
       </c>
-      <c r="L100" s="25" t="n">
+      <c r="L100" s="27" t="n">
         <f aca="false">K100/SUMIF(A:A,A100,K:K)</f>
         <v>0.0767319900634833</v>
       </c>
-      <c r="M100" s="1" t="n">
+      <c r="M100" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A100,J:J)*L100,0)</f>
         <v>629</v>
       </c>
@@ -13489,7 +13516,7 @@
       <c r="A101" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B101" s="27" t="s">
+      <c r="B101" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C101" s="1" t="s">
@@ -13507,15 +13534,15 @@
       <c r="G101" s="1" t="n">
         <v>10341</v>
       </c>
-      <c r="H101" s="28" t="n">
+      <c r="H101" s="31" t="n">
         <f aca="false">ROUND(D101*IF(ISNUMBER(SEARCH("Labour",B101)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B101)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B101)),ISNUMBER(SEARCH("RefUK",B101))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B101)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B101)),ISNUMBER(SEARCH("Lib Dem",B101))),National!$L$8,National!$L$9))))),0)</f>
         <v>452</v>
       </c>
-      <c r="I101" s="25" t="n">
+      <c r="I101" s="27" t="n">
         <f aca="false">H101/SUMIFS(H:H,A:A,A101)</f>
         <v>0.0704269242754752</v>
       </c>
-      <c r="J101" s="29" t="n">
+      <c r="J101" s="32" t="n">
         <f aca="false">ROUND(I101*SUMIF(A:A,A101,D:D),0)</f>
         <v>577</v>
       </c>
@@ -13523,11 +13550,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A101,B:B,B101)/COUNTIFS(B:B,B101,A:A,A101),0)</f>
         <v>278</v>
       </c>
-      <c r="L101" s="25" t="n">
+      <c r="L101" s="27" t="n">
         <f aca="false">K101/SUMIF(A:A,A101,K:K)</f>
         <v>0.0767319900634833</v>
       </c>
-      <c r="M101" s="1" t="n">
+      <c r="M101" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A101,J:J)*L101,0)</f>
         <v>629</v>
       </c>
@@ -13548,7 +13575,7 @@
       <c r="A102" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B102" s="27" t="s">
+      <c r="B102" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C102" s="1" t="s">
@@ -13566,15 +13593,15 @@
       <c r="G102" s="1" t="n">
         <v>10466</v>
       </c>
-      <c r="H102" s="28" t="n">
+      <c r="H102" s="31" t="n">
         <f aca="false">ROUND(D102*IF(ISNUMBER(SEARCH("Labour",B102)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B102)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B102)),ISNUMBER(SEARCH("RefUK",B102))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B102)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B102)),ISNUMBER(SEARCH("Lib Dem",B102))),National!$L$8,National!$L$9))))),0)</f>
         <v>951</v>
       </c>
-      <c r="I102" s="25" t="n">
+      <c r="I102" s="27" t="n">
         <f aca="false">H102/SUMIFS(H:H,A:A,A102)</f>
         <v>0.172783430232558</v>
       </c>
-      <c r="J102" s="29" t="n">
+      <c r="J102" s="32" t="n">
         <f aca="false">ROUND(I102*SUMIF(A:A,A102,D:D),0)</f>
         <v>1343</v>
       </c>
@@ -13582,11 +13609,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A102,B:B,B102)/COUNTIFS(B:B,B102,A:A,A102),0)</f>
         <v>444</v>
       </c>
-      <c r="L102" s="25" t="n">
+      <c r="L102" s="27" t="n">
         <f aca="false">K102/SUMIF(A:A,A102,K:K)</f>
         <v>0.106500359798513</v>
       </c>
-      <c r="M102" s="1" t="n">
+      <c r="M102" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A102,J:J)*L102,0)</f>
         <v>828</v>
       </c>
@@ -13607,7 +13634,7 @@
       <c r="A103" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B103" s="27" t="s">
+      <c r="B103" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C103" s="1" t="s">
@@ -13625,15 +13652,15 @@
       <c r="G103" s="1" t="n">
         <v>10466</v>
       </c>
-      <c r="H103" s="28" t="n">
+      <c r="H103" s="31" t="n">
         <f aca="false">ROUND(D103*IF(ISNUMBER(SEARCH("Labour",B103)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B103)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B103)),ISNUMBER(SEARCH("RefUK",B103))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B103)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B103)),ISNUMBER(SEARCH("Lib Dem",B103))),National!$L$8,National!$L$9))))),0)</f>
         <v>947</v>
       </c>
-      <c r="I103" s="25" t="n">
+      <c r="I103" s="27" t="n">
         <f aca="false">H103/SUMIFS(H:H,A:A,A103)</f>
         <v>0.172056686046512</v>
       </c>
-      <c r="J103" s="29" t="n">
+      <c r="J103" s="32" t="n">
         <f aca="false">ROUND(I103*SUMIF(A:A,A103,D:D),0)</f>
         <v>1337</v>
       </c>
@@ -13641,11 +13668,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A103,B:B,B103)/COUNTIFS(B:B,B103,A:A,A103),0)</f>
         <v>444</v>
       </c>
-      <c r="L103" s="25" t="n">
+      <c r="L103" s="27" t="n">
         <f aca="false">K103/SUMIF(A:A,A103,K:K)</f>
         <v>0.106500359798513</v>
       </c>
-      <c r="M103" s="1" t="n">
+      <c r="M103" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A103,J:J)*L103,0)</f>
         <v>828</v>
       </c>
@@ -13666,7 +13693,7 @@
       <c r="A104" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B104" s="27" t="s">
+      <c r="B104" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C104" s="1" t="s">
@@ -13684,15 +13711,15 @@
       <c r="G104" s="1" t="n">
         <v>10466</v>
       </c>
-      <c r="H104" s="28" t="n">
+      <c r="H104" s="31" t="n">
         <f aca="false">ROUND(D104*IF(ISNUMBER(SEARCH("Labour",B104)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B104)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B104)),ISNUMBER(SEARCH("RefUK",B104))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B104)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B104)),ISNUMBER(SEARCH("Lib Dem",B104))),National!$L$8,National!$L$9))))),0)</f>
         <v>935</v>
       </c>
-      <c r="I104" s="25" t="n">
+      <c r="I104" s="27" t="n">
         <f aca="false">H104/SUMIFS(H:H,A:A,A104)</f>
         <v>0.169876453488372</v>
       </c>
-      <c r="J104" s="29" t="n">
+      <c r="J104" s="32" t="n">
         <f aca="false">ROUND(I104*SUMIF(A:A,A104,D:D),0)</f>
         <v>1320</v>
       </c>
@@ -13700,11 +13727,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A104,B:B,B104)/COUNTIFS(B:B,B104,A:A,A104),0)</f>
         <v>444</v>
       </c>
-      <c r="L104" s="25" t="n">
+      <c r="L104" s="27" t="n">
         <f aca="false">K104/SUMIF(A:A,A104,K:K)</f>
         <v>0.106500359798513</v>
       </c>
-      <c r="M104" s="1" t="n">
+      <c r="M104" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A104,J:J)*L104,0)</f>
         <v>828</v>
       </c>
@@ -13725,7 +13752,7 @@
       <c r="A105" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B105" s="27" t="s">
+      <c r="B105" s="30" t="s">
         <v>216</v>
       </c>
       <c r="C105" s="1" t="s">
@@ -13743,15 +13770,15 @@
       <c r="G105" s="1" t="n">
         <v>10466</v>
       </c>
-      <c r="H105" s="28" t="n">
+      <c r="H105" s="31" t="n">
         <f aca="false">ROUND(D105*IF(ISNUMBER(SEARCH("Labour",B105)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B105)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B105)),ISNUMBER(SEARCH("RefUK",B105))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B105)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B105)),ISNUMBER(SEARCH("Lib Dem",B105))),National!$L$8,National!$L$9))))),0)</f>
         <v>364</v>
       </c>
-      <c r="I105" s="25" t="n">
+      <c r="I105" s="27" t="n">
         <f aca="false">H105/SUMIFS(H:H,A:A,A105)</f>
         <v>0.0661337209302326</v>
       </c>
-      <c r="J105" s="29" t="n">
+      <c r="J105" s="32" t="n">
         <f aca="false">ROUND(I105*SUMIF(A:A,A105,D:D),0)</f>
         <v>514</v>
       </c>
@@ -13759,11 +13786,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A105,B:B,B105)/COUNTIFS(B:B,B105,A:A,A105),0)</f>
         <v>156</v>
       </c>
-      <c r="L105" s="25" t="n">
+      <c r="L105" s="27" t="n">
         <f aca="false">K105/SUMIF(A:A,A105,K:K)</f>
         <v>0.0374190453346126</v>
       </c>
-      <c r="M105" s="1" t="n">
+      <c r="M105" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A105,J:J)*L105,0)</f>
         <v>291</v>
       </c>
@@ -13784,7 +13811,7 @@
       <c r="A106" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B106" s="27" t="s">
+      <c r="B106" s="30" t="s">
         <v>216</v>
       </c>
       <c r="C106" s="1" t="s">
@@ -13802,15 +13829,15 @@
       <c r="G106" s="1" t="n">
         <v>10466</v>
       </c>
-      <c r="H106" s="28" t="n">
+      <c r="H106" s="31" t="n">
         <f aca="false">ROUND(D106*IF(ISNUMBER(SEARCH("Labour",B106)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B106)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B106)),ISNUMBER(SEARCH("RefUK",B106))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B106)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B106)),ISNUMBER(SEARCH("Lib Dem",B106))),National!$L$8,National!$L$9))))),0)</f>
         <v>330</v>
       </c>
-      <c r="I106" s="25" t="n">
+      <c r="I106" s="27" t="n">
         <f aca="false">H106/SUMIFS(H:H,A:A,A106)</f>
         <v>0.0599563953488372</v>
       </c>
-      <c r="J106" s="29" t="n">
+      <c r="J106" s="32" t="n">
         <f aca="false">ROUND(I106*SUMIF(A:A,A106,D:D),0)</f>
         <v>466</v>
       </c>
@@ -13818,11 +13845,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A106,B:B,B106)/COUNTIFS(B:B,B106,A:A,A106),0)</f>
         <v>156</v>
       </c>
-      <c r="L106" s="25" t="n">
+      <c r="L106" s="27" t="n">
         <f aca="false">K106/SUMIF(A:A,A106,K:K)</f>
         <v>0.0374190453346126</v>
       </c>
-      <c r="M106" s="1" t="n">
+      <c r="M106" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A106,J:J)*L106,0)</f>
         <v>291</v>
       </c>
@@ -13843,7 +13870,7 @@
       <c r="A107" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B107" s="27" t="s">
+      <c r="B107" s="30" t="s">
         <v>216</v>
       </c>
       <c r="C107" s="1" t="s">
@@ -13861,15 +13888,15 @@
       <c r="G107" s="1" t="n">
         <v>10466</v>
       </c>
-      <c r="H107" s="28" t="n">
+      <c r="H107" s="31" t="n">
         <f aca="false">ROUND(D107*IF(ISNUMBER(SEARCH("Labour",B107)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B107)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B107)),ISNUMBER(SEARCH("RefUK",B107))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B107)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B107)),ISNUMBER(SEARCH("Lib Dem",B107))),National!$L$8,National!$L$9))))),0)</f>
         <v>300</v>
       </c>
-      <c r="I107" s="25" t="n">
+      <c r="I107" s="27" t="n">
         <f aca="false">H107/SUMIFS(H:H,A:A,A107)</f>
         <v>0.0545058139534884</v>
       </c>
-      <c r="J107" s="29" t="n">
+      <c r="J107" s="32" t="n">
         <f aca="false">ROUND(I107*SUMIF(A:A,A107,D:D),0)</f>
         <v>424</v>
       </c>
@@ -13877,11 +13904,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A107,B:B,B107)/COUNTIFS(B:B,B107,A:A,A107),0)</f>
         <v>156</v>
       </c>
-      <c r="L107" s="25" t="n">
+      <c r="L107" s="27" t="n">
         <f aca="false">K107/SUMIF(A:A,A107,K:K)</f>
         <v>0.0374190453346126</v>
       </c>
-      <c r="M107" s="1" t="n">
+      <c r="M107" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A107,J:J)*L107,0)</f>
         <v>291</v>
       </c>
@@ -13902,7 +13929,7 @@
       <c r="A108" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B108" s="30" t="s">
+      <c r="B108" s="33" t="s">
         <v>219</v>
       </c>
       <c r="C108" s="1" t="s">
@@ -13920,15 +13947,15 @@
       <c r="G108" s="1" t="n">
         <v>10466</v>
       </c>
-      <c r="H108" s="28" t="n">
+      <c r="H108" s="31" t="n">
         <f aca="false">ROUND(D108*IF(ISNUMBER(SEARCH("Labour",B108)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B108)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B108)),ISNUMBER(SEARCH("RefUK",B108))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B108)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B108)),ISNUMBER(SEARCH("Lib Dem",B108))),National!$L$8,National!$L$9))))),0)</f>
         <v>1024</v>
       </c>
-      <c r="I108" s="25" t="n">
+      <c r="I108" s="27" t="n">
         <f aca="false">H108/SUMIFS(H:H,A:A,A108)</f>
         <v>0.186046511627907</v>
       </c>
-      <c r="J108" s="29" t="n">
+      <c r="J108" s="32" t="n">
         <f aca="false">ROUND(I108*SUMIF(A:A,A108,D:D),0)</f>
         <v>1446</v>
       </c>
@@ -13936,11 +13963,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A108,B:B,B108)/COUNTIFS(B:B,B108,A:A,A108),0)</f>
         <v>1446</v>
       </c>
-      <c r="L108" s="25" t="n">
+      <c r="L108" s="27" t="n">
         <f aca="false">K108/SUMIF(A:A,A108,K:K)</f>
         <v>0.346845766370832</v>
       </c>
-      <c r="M108" s="1" t="n">
+      <c r="M108" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A108,J:J)*L108,0)</f>
         <v>2696</v>
       </c>
@@ -13961,7 +13988,7 @@
       <c r="A109" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B109" s="27" t="s">
+      <c r="B109" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C109" s="1" t="s">
@@ -13979,15 +14006,15 @@
       <c r="G109" s="1" t="n">
         <v>10466</v>
       </c>
-      <c r="H109" s="28" t="n">
+      <c r="H109" s="31" t="n">
         <f aca="false">ROUND(D109*IF(ISNUMBER(SEARCH("Labour",B109)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B109)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B109)),ISNUMBER(SEARCH("RefUK",B109))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B109)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B109)),ISNUMBER(SEARCH("Lib Dem",B109))),National!$L$8,National!$L$9))))),0)</f>
         <v>472</v>
       </c>
-      <c r="I109" s="25" t="n">
+      <c r="I109" s="27" t="n">
         <f aca="false">H109/SUMIFS(H:H,A:A,A109)</f>
         <v>0.0857558139534884</v>
       </c>
-      <c r="J109" s="29" t="n">
+      <c r="J109" s="32" t="n">
         <f aca="false">ROUND(I109*SUMIF(A:A,A109,D:D),0)</f>
         <v>667</v>
       </c>
@@ -13995,11 +14022,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A109,B:B,B109)/COUNTIFS(B:B,B109,A:A,A109),0)</f>
         <v>667</v>
       </c>
-      <c r="L109" s="25" t="n">
+      <c r="L109" s="27" t="n">
         <f aca="false">K109/SUMIF(A:A,A109,K:K)</f>
         <v>0.159990405372991</v>
       </c>
-      <c r="M109" s="1" t="n">
+      <c r="M109" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A109,J:J)*L109,0)</f>
         <v>1244</v>
       </c>
@@ -14020,7 +14047,7 @@
       <c r="A110" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B110" s="27" t="s">
+      <c r="B110" s="30" t="s">
         <v>299</v>
       </c>
       <c r="C110" s="1" t="s">
@@ -14038,15 +14065,15 @@
       <c r="G110" s="1" t="n">
         <v>10466</v>
       </c>
-      <c r="H110" s="28" t="n">
+      <c r="H110" s="31" t="n">
         <f aca="false">ROUND(D110*IF(ISNUMBER(SEARCH("Labour",B110)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B110)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B110)),ISNUMBER(SEARCH("RefUK",B110))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B110)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B110)),ISNUMBER(SEARCH("Lib Dem",B110))),National!$L$8,National!$L$9))))),0)</f>
         <v>181</v>
       </c>
-      <c r="I110" s="25" t="n">
+      <c r="I110" s="27" t="n">
         <f aca="false">H110/SUMIFS(H:H,A:A,A110)</f>
         <v>0.0328851744186047</v>
       </c>
-      <c r="J110" s="29" t="n">
+      <c r="J110" s="32" t="n">
         <f aca="false">ROUND(I110*SUMIF(A:A,A110,D:D),0)</f>
         <v>256</v>
       </c>
@@ -14054,11 +14081,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A110,B:B,B110)/COUNTIFS(B:B,B110,A:A,A110),0)</f>
         <v>256</v>
       </c>
-      <c r="L110" s="25" t="n">
+      <c r="L110" s="27" t="n">
         <f aca="false">K110/SUMIF(A:A,A110,K:K)</f>
         <v>0.0614056128568002</v>
       </c>
-      <c r="M110" s="1" t="n">
+      <c r="M110" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A110,J:J)*L110,0)</f>
         <v>477</v>
       </c>
@@ -14079,7 +14106,7 @@
       <c r="A111" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B111" s="27" t="s">
+      <c r="B111" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C111" s="1" t="s">
@@ -14097,15 +14124,15 @@
       <c r="G111" s="1" t="n">
         <v>7309</v>
       </c>
-      <c r="H111" s="28" t="n">
+      <c r="H111" s="31" t="n">
         <f aca="false">ROUND(D111*IF(ISNUMBER(SEARCH("Labour",B111)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B111)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B111)),ISNUMBER(SEARCH("RefUK",B111))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B111)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B111)),ISNUMBER(SEARCH("Lib Dem",B111))),National!$L$8,National!$L$9))))),0)</f>
         <v>770</v>
       </c>
-      <c r="I111" s="25" t="n">
+      <c r="I111" s="27" t="n">
         <f aca="false">H111/SUMIFS(H:H,A:A,A111)</f>
         <v>0.220567172729877</v>
       </c>
-      <c r="J111" s="29" t="n">
+      <c r="J111" s="32" t="n">
         <f aca="false">ROUND(I111*SUMIF(A:A,A111,D:D),0)</f>
         <v>967</v>
       </c>
@@ -14113,11 +14140,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A111,B:B,B111)/COUNTIFS(B:B,B111,A:A,A111),0)</f>
         <v>453</v>
       </c>
-      <c r="L111" s="25" t="n">
+      <c r="L111" s="27" t="n">
         <f aca="false">K111/SUMIF(A:A,A111,K:K)</f>
         <v>0.154186521443159</v>
       </c>
-      <c r="M111" s="1" t="n">
+      <c r="M111" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A111,J:J)*L111,0)</f>
         <v>676</v>
       </c>
@@ -14138,7 +14165,7 @@
       <c r="A112" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B112" s="27" t="s">
+      <c r="B112" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C112" s="1" t="s">
@@ -14156,15 +14183,15 @@
       <c r="G112" s="1" t="n">
         <v>7309</v>
       </c>
-      <c r="H112" s="28" t="n">
+      <c r="H112" s="31" t="n">
         <f aca="false">ROUND(D112*IF(ISNUMBER(SEARCH("Labour",B112)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B112)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B112)),ISNUMBER(SEARCH("RefUK",B112))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B112)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B112)),ISNUMBER(SEARCH("Lib Dem",B112))),National!$L$8,National!$L$9))))),0)</f>
         <v>672</v>
       </c>
-      <c r="I112" s="25" t="n">
+      <c r="I112" s="27" t="n">
         <f aca="false">H112/SUMIFS(H:H,A:A,A112)</f>
         <v>0.192494987109711</v>
       </c>
-      <c r="J112" s="29" t="n">
+      <c r="J112" s="32" t="n">
         <f aca="false">ROUND(I112*SUMIF(A:A,A112,D:D),0)</f>
         <v>844</v>
       </c>
@@ -14172,11 +14199,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A112,B:B,B112)/COUNTIFS(B:B,B112,A:A,A112),0)</f>
         <v>453</v>
       </c>
-      <c r="L112" s="25" t="n">
+      <c r="L112" s="27" t="n">
         <f aca="false">K112/SUMIF(A:A,A112,K:K)</f>
         <v>0.154186521443159</v>
       </c>
-      <c r="M112" s="1" t="n">
+      <c r="M112" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A112,J:J)*L112,0)</f>
         <v>676</v>
       </c>
@@ -14197,7 +14224,7 @@
       <c r="A113" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B113" s="27" t="s">
+      <c r="B113" s="30" t="s">
         <v>216</v>
       </c>
       <c r="C113" s="1" t="s">
@@ -14215,15 +14242,15 @@
       <c r="G113" s="1" t="n">
         <v>7309</v>
       </c>
-      <c r="H113" s="28" t="n">
+      <c r="H113" s="31" t="n">
         <f aca="false">ROUND(D113*IF(ISNUMBER(SEARCH("Labour",B113)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B113)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B113)),ISNUMBER(SEARCH("RefUK",B113))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B113)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B113)),ISNUMBER(SEARCH("Lib Dem",B113))),National!$L$8,National!$L$9))))),0)</f>
         <v>297</v>
       </c>
-      <c r="I113" s="25" t="n">
+      <c r="I113" s="27" t="n">
         <f aca="false">H113/SUMIFS(H:H,A:A,A113)</f>
         <v>0.0850759094815239</v>
       </c>
-      <c r="J113" s="29" t="n">
+      <c r="J113" s="32" t="n">
         <f aca="false">ROUND(I113*SUMIF(A:A,A113,D:D),0)</f>
         <v>373</v>
       </c>
@@ -14231,11 +14258,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A113,B:B,B113)/COUNTIFS(B:B,B113,A:A,A113),0)</f>
         <v>155</v>
       </c>
-      <c r="L113" s="25" t="n">
+      <c r="L113" s="27" t="n">
         <f aca="false">K113/SUMIF(A:A,A113,K:K)</f>
         <v>0.0527569775357386</v>
       </c>
-      <c r="M113" s="1" t="n">
+      <c r="M113" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A113,J:J)*L113,0)</f>
         <v>231</v>
       </c>
@@ -14256,7 +14283,7 @@
       <c r="A114" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B114" s="27" t="s">
+      <c r="B114" s="30" t="s">
         <v>216</v>
       </c>
       <c r="C114" s="1" t="s">
@@ -14274,15 +14301,15 @@
       <c r="G114" s="1" t="n">
         <v>7309</v>
       </c>
-      <c r="H114" s="28" t="n">
+      <c r="H114" s="31" t="n">
         <f aca="false">ROUND(D114*IF(ISNUMBER(SEARCH("Labour",B114)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B114)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B114)),ISNUMBER(SEARCH("RefUK",B114))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B114)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B114)),ISNUMBER(SEARCH("Lib Dem",B114))),National!$L$8,National!$L$9))))),0)</f>
         <v>197</v>
       </c>
-      <c r="I114" s="25" t="n">
+      <c r="I114" s="27" t="n">
         <f aca="false">H114/SUMIFS(H:H,A:A,A114)</f>
         <v>0.0564308221140075</v>
       </c>
-      <c r="J114" s="29" t="n">
+      <c r="J114" s="32" t="n">
         <f aca="false">ROUND(I114*SUMIF(A:A,A114,D:D),0)</f>
         <v>247</v>
       </c>
@@ -14290,11 +14317,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A114,B:B,B114)/COUNTIFS(B:B,B114,A:A,A114),0)</f>
         <v>155</v>
       </c>
-      <c r="L114" s="25" t="n">
+      <c r="L114" s="27" t="n">
         <f aca="false">K114/SUMIF(A:A,A114,K:K)</f>
         <v>0.0527569775357386</v>
       </c>
-      <c r="M114" s="1" t="n">
+      <c r="M114" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A114,J:J)*L114,0)</f>
         <v>231</v>
       </c>
@@ -14315,7 +14342,7 @@
       <c r="A115" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B115" s="30" t="s">
+      <c r="B115" s="33" t="s">
         <v>219</v>
       </c>
       <c r="C115" s="1" t="s">
@@ -14333,15 +14360,15 @@
       <c r="G115" s="1" t="n">
         <v>7309</v>
       </c>
-      <c r="H115" s="28" t="n">
+      <c r="H115" s="31" t="n">
         <f aca="false">ROUND(D115*IF(ISNUMBER(SEARCH("Labour",B115)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B115)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B115)),ISNUMBER(SEARCH("RefUK",B115))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B115)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B115)),ISNUMBER(SEARCH("Lib Dem",B115))),National!$L$8,National!$L$9))))),0)</f>
         <v>810</v>
       </c>
-      <c r="I115" s="25" t="n">
+      <c r="I115" s="27" t="n">
         <f aca="false">H115/SUMIFS(H:H,A:A,A115)</f>
         <v>0.232025207676883</v>
       </c>
-      <c r="J115" s="29" t="n">
+      <c r="J115" s="32" t="n">
         <f aca="false">ROUND(I115*SUMIF(A:A,A115,D:D),0)</f>
         <v>1017</v>
       </c>
@@ -14349,11 +14376,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A115,B:B,B115)/COUNTIFS(B:B,B115,A:A,A115),0)</f>
         <v>1017</v>
       </c>
-      <c r="L115" s="25" t="n">
+      <c r="L115" s="27" t="n">
         <f aca="false">K115/SUMIF(A:A,A115,K:K)</f>
         <v>0.346153846153846</v>
       </c>
-      <c r="M115" s="1" t="n">
+      <c r="M115" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A115,J:J)*L115,0)</f>
         <v>1517</v>
       </c>
@@ -14374,7 +14401,7 @@
       <c r="A116" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B116" s="27" t="s">
+      <c r="B116" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C116" s="1" t="s">
@@ -14392,15 +14419,15 @@
       <c r="G116" s="1" t="n">
         <v>7309</v>
       </c>
-      <c r="H116" s="28" t="n">
+      <c r="H116" s="31" t="n">
         <f aca="false">ROUND(D116*IF(ISNUMBER(SEARCH("Labour",B116)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B116)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B116)),ISNUMBER(SEARCH("RefUK",B116))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B116)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B116)),ISNUMBER(SEARCH("Lib Dem",B116))),National!$L$8,National!$L$9))))),0)</f>
         <v>377</v>
       </c>
-      <c r="I116" s="25" t="n">
+      <c r="I116" s="27" t="n">
         <f aca="false">H116/SUMIFS(H:H,A:A,A116)</f>
         <v>0.107991979375537</v>
       </c>
-      <c r="J116" s="29" t="n">
+      <c r="J116" s="32" t="n">
         <f aca="false">ROUND(I116*SUMIF(A:A,A116,D:D),0)</f>
         <v>473</v>
       </c>
@@ -14408,11 +14435,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A116,B:B,B116)/COUNTIFS(B:B,B116,A:A,A116),0)</f>
         <v>473</v>
       </c>
-      <c r="L116" s="25" t="n">
+      <c r="L116" s="27" t="n">
         <f aca="false">K116/SUMIF(A:A,A116,K:K)</f>
         <v>0.160993873383254</v>
       </c>
-      <c r="M116" s="1" t="n">
+      <c r="M116" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A116,J:J)*L116,0)</f>
         <v>706</v>
       </c>
@@ -14433,7 +14460,7 @@
       <c r="A117" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B117" s="27" t="s">
+      <c r="B117" s="30" t="s">
         <v>23</v>
       </c>
       <c r="C117" s="1" t="s">
@@ -14451,15 +14478,15 @@
       <c r="G117" s="1" t="n">
         <v>7309</v>
       </c>
-      <c r="H117" s="28" t="n">
+      <c r="H117" s="31" t="n">
         <f aca="false">ROUND(D117*IF(ISNUMBER(SEARCH("Labour",B117)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B117)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B117)),ISNUMBER(SEARCH("RefUK",B117))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B117)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B117)),ISNUMBER(SEARCH("Lib Dem",B117))),National!$L$8,National!$L$9))))),0)</f>
         <v>258</v>
       </c>
-      <c r="I117" s="25" t="n">
+      <c r="I117" s="27" t="n">
         <f aca="false">H117/SUMIFS(H:H,A:A,A117)</f>
         <v>0.0739043254081925</v>
       </c>
-      <c r="J117" s="29" t="n">
+      <c r="J117" s="32" t="n">
         <f aca="false">ROUND(I117*SUMIF(A:A,A117,D:D),0)</f>
         <v>324</v>
       </c>
@@ -14467,11 +14494,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A117,B:B,B117)/COUNTIFS(B:B,B117,A:A,A117),0)</f>
         <v>116</v>
       </c>
-      <c r="L117" s="25" t="n">
+      <c r="L117" s="27" t="n">
         <f aca="false">K117/SUMIF(A:A,A117,K:K)</f>
         <v>0.0394826412525528</v>
       </c>
-      <c r="M117" s="1" t="n">
+      <c r="M117" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A117,J:J)*L117,0)</f>
         <v>173</v>
       </c>
@@ -14492,7 +14519,7 @@
       <c r="A118" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B118" s="27" t="s">
+      <c r="B118" s="30" t="s">
         <v>23</v>
       </c>
       <c r="C118" s="1" t="s">
@@ -14510,15 +14537,15 @@
       <c r="G118" s="1" t="n">
         <v>7309</v>
       </c>
-      <c r="H118" s="28" t="n">
+      <c r="H118" s="31" t="n">
         <f aca="false">ROUND(D118*IF(ISNUMBER(SEARCH("Labour",B118)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B118)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B118)),ISNUMBER(SEARCH("RefUK",B118))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B118)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B118)),ISNUMBER(SEARCH("Lib Dem",B118))),National!$L$8,National!$L$9))))),0)</f>
         <v>110</v>
       </c>
-      <c r="I118" s="25" t="n">
+      <c r="I118" s="27" t="n">
         <f aca="false">H118/SUMIFS(H:H,A:A,A118)</f>
         <v>0.0315095961042681</v>
       </c>
-      <c r="J118" s="29" t="n">
+      <c r="J118" s="32" t="n">
         <f aca="false">ROUND(I118*SUMIF(A:A,A118,D:D),0)</f>
         <v>138</v>
       </c>
@@ -14526,11 +14553,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A118,B:B,B118)/COUNTIFS(B:B,B118,A:A,A118),0)</f>
         <v>116</v>
       </c>
-      <c r="L118" s="25" t="n">
+      <c r="L118" s="27" t="n">
         <f aca="false">K118/SUMIF(A:A,A118,K:K)</f>
         <v>0.0394826412525528</v>
       </c>
-      <c r="M118" s="1" t="n">
+      <c r="M118" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A118,J:J)*L118,0)</f>
         <v>173</v>
       </c>
@@ -14551,7 +14578,7 @@
       <c r="A119" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B119" s="27" t="s">
+      <c r="B119" s="30" t="s">
         <v>249</v>
       </c>
       <c r="C119" s="1" t="s">
@@ -14569,15 +14596,15 @@
       <c r="G119" s="1" t="n">
         <v>9363</v>
       </c>
-      <c r="H119" s="28" t="n">
+      <c r="H119" s="31" t="n">
         <f aca="false">ROUND(D119*IF(ISNUMBER(SEARCH("Labour",B119)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B119)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B119)),ISNUMBER(SEARCH("RefUK",B119))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B119)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B119)),ISNUMBER(SEARCH("Lib Dem",B119))),National!$L$8,National!$L$9))))),0)</f>
         <v>655</v>
       </c>
-      <c r="I119" s="25" t="n">
+      <c r="I119" s="27" t="n">
         <f aca="false">H119/SUMIFS(H:H,A:A,A119)</f>
         <v>0.148965203547874</v>
       </c>
-      <c r="J119" s="29" t="n">
+      <c r="J119" s="32" t="n">
         <f aca="false">ROUND(I119*SUMIF(A:A,A119,D:D),0)</f>
         <v>1088</v>
       </c>
@@ -14585,11 +14612,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A119,B:B,B119)/COUNTIFS(B:B,B119,A:A,A119),0)</f>
         <v>330</v>
       </c>
-      <c r="L119" s="25" t="n">
+      <c r="L119" s="27" t="n">
         <f aca="false">K119/SUMIF(A:A,A119,K:K)</f>
         <v>0.0885668276972625</v>
       </c>
-      <c r="M119" s="1" t="n">
+      <c r="M119" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A119,J:J)*L119,0)</f>
         <v>647</v>
       </c>
@@ -14610,10 +14637,10 @@
       <c r="A120" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B120" s="27" t="s">
+      <c r="B120" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="C120" s="31" t="s">
+      <c r="C120" s="34" t="s">
         <v>367</v>
       </c>
       <c r="D120" s="1" t="n">
@@ -14628,15 +14655,15 @@
       <c r="G120" s="1" t="n">
         <v>9363</v>
       </c>
-      <c r="H120" s="28" t="n">
+      <c r="H120" s="31" t="n">
         <f aca="false">ROUND(D120*IF(ISNUMBER(SEARCH("Labour",B120)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B120)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B120)),ISNUMBER(SEARCH("RefUK",B120))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B120)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B120)),ISNUMBER(SEARCH("Lib Dem",B120))),National!$L$8,National!$L$9))))),0)</f>
         <v>600</v>
       </c>
-      <c r="I120" s="25" t="n">
+      <c r="I120" s="27" t="n">
         <f aca="false">H120/SUMIFS(H:H,A:A,A120)</f>
         <v>0.136456675005686</v>
       </c>
-      <c r="J120" s="29" t="n">
+      <c r="J120" s="32" t="n">
         <f aca="false">ROUND(I120*SUMIF(A:A,A120,D:D),0)</f>
         <v>996</v>
       </c>
@@ -14644,11 +14671,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A120,B:B,B120)/COUNTIFS(B:B,B120,A:A,A120),0)</f>
         <v>330</v>
       </c>
-      <c r="L120" s="25" t="n">
+      <c r="L120" s="27" t="n">
         <f aca="false">K120/SUMIF(A:A,A120,K:K)</f>
         <v>0.0885668276972625</v>
       </c>
-      <c r="M120" s="1" t="n">
+      <c r="M120" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A120,J:J)*L120,0)</f>
         <v>647</v>
       </c>
@@ -14669,10 +14696,10 @@
       <c r="A121" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B121" s="27" t="s">
+      <c r="B121" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="C121" s="32" t="s">
+      <c r="C121" s="35" t="s">
         <v>368</v>
       </c>
       <c r="D121" s="1" t="n">
@@ -14687,15 +14714,15 @@
       <c r="G121" s="1" t="n">
         <v>9363</v>
       </c>
-      <c r="H121" s="28" t="n">
+      <c r="H121" s="31" t="n">
         <f aca="false">ROUND(D121*IF(ISNUMBER(SEARCH("Labour",B121)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B121)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B121)),ISNUMBER(SEARCH("RefUK",B121))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B121)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B121)),ISNUMBER(SEARCH("Lib Dem",B121))),National!$L$8,National!$L$9))))),0)</f>
         <v>533</v>
       </c>
-      <c r="I121" s="25" t="n">
+      <c r="I121" s="27" t="n">
         <f aca="false">H121/SUMIFS(H:H,A:A,A121)</f>
         <v>0.121219012963384</v>
       </c>
-      <c r="J121" s="29" t="n">
+      <c r="J121" s="32" t="n">
         <f aca="false">ROUND(I121*SUMIF(A:A,A121,D:D),0)</f>
         <v>885</v>
       </c>
@@ -14703,11 +14730,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A121,B:B,B121)/COUNTIFS(B:B,B121,A:A,A121),0)</f>
         <v>330</v>
       </c>
-      <c r="L121" s="25" t="n">
+      <c r="L121" s="27" t="n">
         <f aca="false">K121/SUMIF(A:A,A121,K:K)</f>
         <v>0.0885668276972625</v>
       </c>
-      <c r="M121" s="1" t="n">
+      <c r="M121" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A121,J:J)*L121,0)</f>
         <v>647</v>
       </c>
@@ -14728,7 +14755,7 @@
       <c r="A122" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B122" s="27" t="s">
+      <c r="B122" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C122" s="1" t="s">
@@ -14746,15 +14773,15 @@
       <c r="G122" s="1" t="n">
         <v>9363</v>
       </c>
-      <c r="H122" s="28" t="n">
+      <c r="H122" s="31" t="n">
         <f aca="false">ROUND(D122*IF(ISNUMBER(SEARCH("Labour",B122)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B122)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B122)),ISNUMBER(SEARCH("RefUK",B122))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B122)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B122)),ISNUMBER(SEARCH("Lib Dem",B122))),National!$L$8,National!$L$9))))),0)</f>
         <v>513</v>
       </c>
-      <c r="I122" s="25" t="n">
+      <c r="I122" s="27" t="n">
         <f aca="false">H122/SUMIFS(H:H,A:A,A122)</f>
         <v>0.116670457129861</v>
       </c>
-      <c r="J122" s="29" t="n">
+      <c r="J122" s="32" t="n">
         <f aca="false">ROUND(I122*SUMIF(A:A,A122,D:D),0)</f>
         <v>852</v>
       </c>
@@ -14762,11 +14789,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A122,B:B,B122)/COUNTIFS(B:B,B122,A:A,A122),0)</f>
         <v>266</v>
       </c>
-      <c r="L122" s="25" t="n">
+      <c r="L122" s="27" t="n">
         <f aca="false">K122/SUMIF(A:A,A122,K:K)</f>
         <v>0.0713902308105207</v>
       </c>
-      <c r="M122" s="1" t="n">
+      <c r="M122" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A122,J:J)*L122,0)</f>
         <v>521</v>
       </c>
@@ -14787,7 +14814,7 @@
       <c r="A123" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B123" s="27" t="s">
+      <c r="B123" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C123" s="1" t="s">
@@ -14805,15 +14832,15 @@
       <c r="G123" s="1" t="n">
         <v>9363</v>
       </c>
-      <c r="H123" s="28" t="n">
+      <c r="H123" s="31" t="n">
         <f aca="false">ROUND(D123*IF(ISNUMBER(SEARCH("Labour",B123)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B123)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B123)),ISNUMBER(SEARCH("RefUK",B123))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B123)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B123)),ISNUMBER(SEARCH("Lib Dem",B123))),National!$L$8,National!$L$9))))),0)</f>
         <v>494</v>
       </c>
-      <c r="I123" s="25" t="n">
+      <c r="I123" s="27" t="n">
         <f aca="false">H123/SUMIFS(H:H,A:A,A123)</f>
         <v>0.112349329088015</v>
       </c>
-      <c r="J123" s="29" t="n">
+      <c r="J123" s="32" t="n">
         <f aca="false">ROUND(I123*SUMIF(A:A,A123,D:D),0)</f>
         <v>820</v>
       </c>
@@ -14821,11 +14848,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A123,B:B,B123)/COUNTIFS(B:B,B123,A:A,A123),0)</f>
         <v>266</v>
       </c>
-      <c r="L123" s="25" t="n">
+      <c r="L123" s="27" t="n">
         <f aca="false">K123/SUMIF(A:A,A123,K:K)</f>
         <v>0.0713902308105207</v>
       </c>
-      <c r="M123" s="1" t="n">
+      <c r="M123" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A123,J:J)*L123,0)</f>
         <v>521</v>
       </c>
@@ -14846,7 +14873,7 @@
       <c r="A124" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B124" s="27" t="s">
+      <c r="B124" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C124" s="1" t="s">
@@ -14864,15 +14891,15 @@
       <c r="G124" s="1" t="n">
         <v>9363</v>
       </c>
-      <c r="H124" s="28" t="n">
+      <c r="H124" s="31" t="n">
         <f aca="false">ROUND(D124*IF(ISNUMBER(SEARCH("Labour",B124)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B124)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B124)),ISNUMBER(SEARCH("RefUK",B124))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B124)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B124)),ISNUMBER(SEARCH("Lib Dem",B124))),National!$L$8,National!$L$9))))),0)</f>
         <v>435</v>
       </c>
-      <c r="I124" s="25" t="n">
+      <c r="I124" s="27" t="n">
         <f aca="false">H124/SUMIFS(H:H,A:A,A124)</f>
         <v>0.0989310893791221</v>
       </c>
-      <c r="J124" s="29" t="n">
+      <c r="J124" s="32" t="n">
         <f aca="false">ROUND(I124*SUMIF(A:A,A124,D:D),0)</f>
         <v>722</v>
       </c>
@@ -14880,11 +14907,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A124,B:B,B124)/COUNTIFS(B:B,B124,A:A,A124),0)</f>
         <v>266</v>
       </c>
-      <c r="L124" s="25" t="n">
+      <c r="L124" s="27" t="n">
         <f aca="false">K124/SUMIF(A:A,A124,K:K)</f>
         <v>0.0713902308105207</v>
       </c>
-      <c r="M124" s="1" t="n">
+      <c r="M124" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A124,J:J)*L124,0)</f>
         <v>521</v>
       </c>
@@ -14905,7 +14932,7 @@
       <c r="A125" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B125" s="30" t="s">
+      <c r="B125" s="33" t="s">
         <v>219</v>
       </c>
       <c r="C125" s="1" t="s">
@@ -14923,15 +14950,15 @@
       <c r="G125" s="1" t="n">
         <v>9363</v>
       </c>
-      <c r="H125" s="28" t="n">
+      <c r="H125" s="31" t="n">
         <f aca="false">ROUND(D125*IF(ISNUMBER(SEARCH("Labour",B125)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B125)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B125)),ISNUMBER(SEARCH("RefUK",B125))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B125)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B125)),ISNUMBER(SEARCH("Lib Dem",B125))),National!$L$8,National!$L$9))))),0)</f>
         <v>879</v>
       </c>
-      <c r="I125" s="25" t="n">
+      <c r="I125" s="27" t="n">
         <f aca="false">H125/SUMIFS(H:H,A:A,A125)</f>
         <v>0.19990902888333</v>
       </c>
-      <c r="J125" s="29" t="n">
+      <c r="J125" s="32" t="n">
         <f aca="false">ROUND(I125*SUMIF(A:A,A125,D:D),0)</f>
         <v>1460</v>
       </c>
@@ -14939,11 +14966,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A125,B:B,B125)/COUNTIFS(B:B,B125,A:A,A125),0)</f>
         <v>1460</v>
       </c>
-      <c r="L125" s="25" t="n">
+      <c r="L125" s="27" t="n">
         <f aca="false">K125/SUMIF(A:A,A125,K:K)</f>
         <v>0.391841116478798</v>
       </c>
-      <c r="M125" s="1" t="n">
+      <c r="M125" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A125,J:J)*L125,0)</f>
         <v>2861</v>
       </c>
@@ -14964,7 +14991,7 @@
       <c r="A126" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B126" s="27" t="s">
+      <c r="B126" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C126" s="1" t="s">
@@ -14982,15 +15009,15 @@
       <c r="G126" s="1" t="n">
         <v>9363</v>
       </c>
-      <c r="H126" s="28" t="n">
+      <c r="H126" s="31" t="n">
         <f aca="false">ROUND(D126*IF(ISNUMBER(SEARCH("Labour",B126)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B126)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B126)),ISNUMBER(SEARCH("RefUK",B126))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B126)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B126)),ISNUMBER(SEARCH("Lib Dem",B126))),National!$L$8,National!$L$9))))),0)</f>
         <v>288</v>
       </c>
-      <c r="I126" s="25" t="n">
+      <c r="I126" s="27" t="n">
         <f aca="false">H126/SUMIFS(H:H,A:A,A126)</f>
         <v>0.0654992040027291</v>
       </c>
-      <c r="J126" s="29" t="n">
+      <c r="J126" s="32" t="n">
         <f aca="false">ROUND(I126*SUMIF(A:A,A126,D:D),0)</f>
         <v>478</v>
       </c>
@@ -14998,11 +15025,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A126,B:B,B126)/COUNTIFS(B:B,B126,A:A,A126),0)</f>
         <v>478</v>
       </c>
-      <c r="L126" s="25" t="n">
+      <c r="L126" s="27" t="n">
         <f aca="false">K126/SUMIF(A:A,A126,K:K)</f>
         <v>0.128287707997853</v>
       </c>
-      <c r="M126" s="1" t="n">
+      <c r="M126" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A126,J:J)*L126,0)</f>
         <v>937</v>
       </c>
@@ -15023,7 +15050,7 @@
       <c r="A127" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="B127" s="27" t="s">
+      <c r="B127" s="30" t="s">
         <v>249</v>
       </c>
       <c r="C127" s="1" t="s">
@@ -15041,15 +15068,15 @@
       <c r="G127" s="1" t="n">
         <v>8651</v>
       </c>
-      <c r="H127" s="28" t="n">
+      <c r="H127" s="31" t="n">
         <f aca="false">ROUND(D127*IF(ISNUMBER(SEARCH("Labour",B127)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B127)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B127)),ISNUMBER(SEARCH("RefUK",B127))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B127)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B127)),ISNUMBER(SEARCH("Lib Dem",B127))),National!$L$8,National!$L$9))))),0)</f>
         <v>714</v>
       </c>
-      <c r="I127" s="25" t="n">
+      <c r="I127" s="27" t="n">
         <f aca="false">H127/SUMIFS(H:H,A:A,A127)</f>
         <v>0.119939526289266</v>
       </c>
-      <c r="J127" s="29" t="n">
+      <c r="J127" s="32" t="n">
         <f aca="false">ROUND(I127*SUMIF(A:A,A127,D:D),0)</f>
         <v>1123</v>
       </c>
@@ -15057,11 +15084,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A127,B:B,B127)/COUNTIFS(B:B,B127,A:A,A127),0)</f>
         <v>352</v>
       </c>
-      <c r="L127" s="25" t="n">
+      <c r="L127" s="27" t="n">
         <f aca="false">K127/SUMIF(A:A,A127,K:K)</f>
         <v>0.0718074255405957</v>
       </c>
-      <c r="M127" s="1" t="n">
+      <c r="M127" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A127,J:J)*L127,0)</f>
         <v>672</v>
       </c>
@@ -15082,7 +15109,7 @@
       <c r="A128" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="B128" s="27" t="s">
+      <c r="B128" s="30" t="s">
         <v>249</v>
       </c>
       <c r="C128" s="1" t="s">
@@ -15100,15 +15127,15 @@
       <c r="G128" s="1" t="n">
         <v>8651</v>
       </c>
-      <c r="H128" s="28" t="n">
+      <c r="H128" s="31" t="n">
         <f aca="false">ROUND(D128*IF(ISNUMBER(SEARCH("Labour",B128)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B128)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B128)),ISNUMBER(SEARCH("RefUK",B128))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B128)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B128)),ISNUMBER(SEARCH("Lib Dem",B128))),National!$L$8,National!$L$9))))),0)</f>
         <v>660</v>
       </c>
-      <c r="I128" s="25" t="n">
+      <c r="I128" s="27" t="n">
         <f aca="false">H128/SUMIFS(H:H,A:A,A128)</f>
         <v>0.110868469679153</v>
       </c>
-      <c r="J128" s="29" t="n">
+      <c r="J128" s="32" t="n">
         <f aca="false">ROUND(I128*SUMIF(A:A,A128,D:D),0)</f>
         <v>1038</v>
       </c>
@@ -15116,11 +15143,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A128,B:B,B128)/COUNTIFS(B:B,B128,A:A,A128),0)</f>
         <v>352</v>
       </c>
-      <c r="L128" s="25" t="n">
+      <c r="L128" s="27" t="n">
         <f aca="false">K128/SUMIF(A:A,A128,K:K)</f>
         <v>0.0718074255405957</v>
       </c>
-      <c r="M128" s="1" t="n">
+      <c r="M128" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A128,J:J)*L128,0)</f>
         <v>672</v>
       </c>
@@ -15141,7 +15168,7 @@
       <c r="A129" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="B129" s="27" t="s">
+      <c r="B129" s="30" t="s">
         <v>249</v>
       </c>
       <c r="C129" s="1" t="s">
@@ -15159,15 +15186,15 @@
       <c r="G129" s="1" t="n">
         <v>8651</v>
       </c>
-      <c r="H129" s="28" t="n">
+      <c r="H129" s="31" t="n">
         <f aca="false">ROUND(D129*IF(ISNUMBER(SEARCH("Labour",B129)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B129)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B129)),ISNUMBER(SEARCH("RefUK",B129))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B129)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B129)),ISNUMBER(SEARCH("Lib Dem",B129))),National!$L$8,National!$L$9))))),0)</f>
         <v>642</v>
       </c>
-      <c r="I129" s="25" t="n">
+      <c r="I129" s="27" t="n">
         <f aca="false">H129/SUMIFS(H:H,A:A,A129)</f>
         <v>0.107844784142449</v>
       </c>
-      <c r="J129" s="29" t="n">
+      <c r="J129" s="32" t="n">
         <f aca="false">ROUND(I129*SUMIF(A:A,A129,D:D),0)</f>
         <v>1010</v>
       </c>
@@ -15175,11 +15202,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A129,B:B,B129)/COUNTIFS(B:B,B129,A:A,A129),0)</f>
         <v>352</v>
       </c>
-      <c r="L129" s="25" t="n">
+      <c r="L129" s="27" t="n">
         <f aca="false">K129/SUMIF(A:A,A129,K:K)</f>
         <v>0.0718074255405957</v>
       </c>
-      <c r="M129" s="1" t="n">
+      <c r="M129" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A129,J:J)*L129,0)</f>
         <v>672</v>
       </c>
@@ -15200,7 +15227,7 @@
       <c r="A130" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="B130" s="27" t="s">
+      <c r="B130" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C130" s="1" t="s">
@@ -15218,15 +15245,15 @@
       <c r="G130" s="1" t="n">
         <v>8651</v>
       </c>
-      <c r="H130" s="28" t="n">
+      <c r="H130" s="31" t="n">
         <f aca="false">ROUND(D130*IF(ISNUMBER(SEARCH("Labour",B130)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B130)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B130)),ISNUMBER(SEARCH("RefUK",B130))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B130)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B130)),ISNUMBER(SEARCH("Lib Dem",B130))),National!$L$8,National!$L$9))))),0)</f>
         <v>874</v>
       </c>
-      <c r="I130" s="25" t="n">
+      <c r="I130" s="27" t="n">
         <f aca="false">H130/SUMIFS(H:H,A:A,A130)</f>
         <v>0.14681673105997</v>
       </c>
-      <c r="J130" s="29" t="n">
+      <c r="J130" s="32" t="n">
         <f aca="false">ROUND(I130*SUMIF(A:A,A130,D:D),0)</f>
         <v>1375</v>
       </c>
@@ -15234,11 +15261,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A130,B:B,B130)/COUNTIFS(B:B,B130,A:A,A130),0)</f>
         <v>392</v>
       </c>
-      <c r="L130" s="25" t="n">
+      <c r="L130" s="27" t="n">
         <f aca="false">K130/SUMIF(A:A,A130,K:K)</f>
         <v>0.0799673602611179</v>
       </c>
-      <c r="M130" s="1" t="n">
+      <c r="M130" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A130,J:J)*L130,0)</f>
         <v>749</v>
       </c>
@@ -15259,7 +15286,7 @@
       <c r="A131" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="B131" s="27" t="s">
+      <c r="B131" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C131" s="1" t="s">
@@ -15277,15 +15304,15 @@
       <c r="G131" s="1" t="n">
         <v>8651</v>
       </c>
-      <c r="H131" s="28" t="n">
+      <c r="H131" s="31" t="n">
         <f aca="false">ROUND(D131*IF(ISNUMBER(SEARCH("Labour",B131)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B131)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B131)),ISNUMBER(SEARCH("RefUK",B131))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B131)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B131)),ISNUMBER(SEARCH("Lib Dem",B131))),National!$L$8,National!$L$9))))),0)</f>
         <v>706</v>
       </c>
-      <c r="I131" s="25" t="n">
+      <c r="I131" s="27" t="n">
         <f aca="false">H131/SUMIFS(H:H,A:A,A131)</f>
         <v>0.118595666050731</v>
       </c>
-      <c r="J131" s="29" t="n">
+      <c r="J131" s="32" t="n">
         <f aca="false">ROUND(I131*SUMIF(A:A,A131,D:D),0)</f>
         <v>1111</v>
       </c>
@@ -15293,11 +15320,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A131,B:B,B131)/COUNTIFS(B:B,B131,A:A,A131),0)</f>
         <v>392</v>
       </c>
-      <c r="L131" s="25" t="n">
+      <c r="L131" s="27" t="n">
         <f aca="false">K131/SUMIF(A:A,A131,K:K)</f>
         <v>0.0799673602611179</v>
       </c>
-      <c r="M131" s="1" t="n">
+      <c r="M131" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A131,J:J)*L131,0)</f>
         <v>749</v>
       </c>
@@ -15318,7 +15345,7 @@
       <c r="A132" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="B132" s="27" t="s">
+      <c r="B132" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C132" s="1" t="s">
@@ -15336,15 +15363,15 @@
       <c r="G132" s="1" t="n">
         <v>8651</v>
       </c>
-      <c r="H132" s="28" t="n">
+      <c r="H132" s="31" t="n">
         <f aca="false">ROUND(D132*IF(ISNUMBER(SEARCH("Labour",B132)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B132)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B132)),ISNUMBER(SEARCH("RefUK",B132))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B132)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B132)),ISNUMBER(SEARCH("Lib Dem",B132))),National!$L$8,National!$L$9))))),0)</f>
         <v>660</v>
       </c>
-      <c r="I132" s="25" t="n">
+      <c r="I132" s="27" t="n">
         <f aca="false">H132/SUMIFS(H:H,A:A,A132)</f>
         <v>0.110868469679153</v>
       </c>
-      <c r="J132" s="29" t="n">
+      <c r="J132" s="32" t="n">
         <f aca="false">ROUND(I132*SUMIF(A:A,A132,D:D),0)</f>
         <v>1038</v>
       </c>
@@ -15352,11 +15379,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A132,B:B,B132)/COUNTIFS(B:B,B132,A:A,A132),0)</f>
         <v>392</v>
       </c>
-      <c r="L132" s="25" t="n">
+      <c r="L132" s="27" t="n">
         <f aca="false">K132/SUMIF(A:A,A132,K:K)</f>
         <v>0.0799673602611179</v>
       </c>
-      <c r="M132" s="1" t="n">
+      <c r="M132" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A132,J:J)*L132,0)</f>
         <v>749</v>
       </c>
@@ -15377,7 +15404,7 @@
       <c r="A133" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="B133" s="30" t="s">
+      <c r="B133" s="33" t="s">
         <v>219</v>
       </c>
       <c r="C133" s="1" t="s">
@@ -15395,15 +15422,15 @@
       <c r="G133" s="1" t="n">
         <v>8651</v>
       </c>
-      <c r="H133" s="28" t="n">
+      <c r="H133" s="31" t="n">
         <f aca="false">ROUND(D133*IF(ISNUMBER(SEARCH("Labour",B133)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B133)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B133)),ISNUMBER(SEARCH("RefUK",B133))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B133)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B133)),ISNUMBER(SEARCH("Lib Dem",B133))),National!$L$8,National!$L$9))))),0)</f>
         <v>1273</v>
       </c>
-      <c r="I133" s="25" t="n">
+      <c r="I133" s="27" t="n">
         <f aca="false">H133/SUMIFS(H:H,A:A,A133)</f>
         <v>0.213841760456912</v>
       </c>
-      <c r="J133" s="29" t="n">
+      <c r="J133" s="32" t="n">
         <f aca="false">ROUND(I133*SUMIF(A:A,A133,D:D),0)</f>
         <v>2003</v>
       </c>
@@ -15411,11 +15438,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A133,B:B,B133)/COUNTIFS(B:B,B133,A:A,A133),0)</f>
         <v>2003</v>
       </c>
-      <c r="L133" s="25" t="n">
+      <c r="L133" s="27" t="n">
         <f aca="false">K133/SUMIF(A:A,A133,K:K)</f>
         <v>0.408608731130151</v>
       </c>
-      <c r="M133" s="1" t="n">
+      <c r="M133" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A133,J:J)*L133,0)</f>
         <v>3827</v>
       </c>
@@ -15436,7 +15463,7 @@
       <c r="A134" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="B134" s="27" t="s">
+      <c r="B134" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C134" s="1" t="s">
@@ -15454,15 +15481,15 @@
       <c r="G134" s="1" t="n">
         <v>8651</v>
       </c>
-      <c r="H134" s="28" t="n">
+      <c r="H134" s="31" t="n">
         <f aca="false">ROUND(D134*IF(ISNUMBER(SEARCH("Labour",B134)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B134)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B134)),ISNUMBER(SEARCH("RefUK",B134))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B134)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B134)),ISNUMBER(SEARCH("Lib Dem",B134))),National!$L$8,National!$L$9))))),0)</f>
         <v>424</v>
       </c>
-      <c r="I134" s="25" t="n">
+      <c r="I134" s="27" t="n">
         <f aca="false">H134/SUMIFS(H:H,A:A,A134)</f>
         <v>0.0712245926423652</v>
       </c>
-      <c r="J134" s="29" t="n">
+      <c r="J134" s="32" t="n">
         <f aca="false">ROUND(I134*SUMIF(A:A,A134,D:D),0)</f>
         <v>667</v>
       </c>
@@ -15470,11 +15497,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A134,B:B,B134)/COUNTIFS(B:B,B134,A:A,A134),0)</f>
         <v>667</v>
       </c>
-      <c r="L134" s="25" t="n">
+      <c r="L134" s="27" t="n">
         <f aca="false">K134/SUMIF(A:A,A134,K:K)</f>
         <v>0.136066911464708</v>
       </c>
-      <c r="M134" s="1" t="n">
+      <c r="M134" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A134,J:J)*L134,0)</f>
         <v>1274</v>
       </c>
@@ -15495,7 +15522,7 @@
       <c r="A135" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B135" s="27" t="s">
+      <c r="B135" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C135" s="1" t="s">
@@ -15513,15 +15540,15 @@
       <c r="G135" s="1" t="n">
         <v>3284</v>
       </c>
-      <c r="H135" s="28" t="n">
+      <c r="H135" s="31" t="n">
         <f aca="false">ROUND(D135*IF(ISNUMBER(SEARCH("Labour",B135)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B135)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B135)),ISNUMBER(SEARCH("RefUK",B135))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B135)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B135)),ISNUMBER(SEARCH("Lib Dem",B135))),National!$L$8,National!$L$9))))),0)</f>
         <v>313</v>
       </c>
-      <c r="I135" s="25" t="n">
+      <c r="I135" s="27" t="n">
         <f aca="false">H135/SUMIFS(H:H,A:A,A135)</f>
         <v>0.324016563146998</v>
       </c>
-      <c r="J135" s="29" t="n">
+      <c r="J135" s="32" t="n">
         <f aca="false">ROUND(I135*SUMIF(A:A,A135,D:D),0)</f>
         <v>348</v>
       </c>
@@ -15529,11 +15556,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A135,B:B,B135)/COUNTIFS(B:B,B135,A:A,A135),0)</f>
         <v>348</v>
       </c>
-      <c r="L135" s="25" t="n">
+      <c r="L135" s="27" t="n">
         <f aca="false">K135/SUMIF(A:A,A135,K:K)</f>
         <v>0.324324324324324</v>
       </c>
-      <c r="M135" s="1" t="n">
+      <c r="M135" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A135,J:J)*L135,0)</f>
         <v>348</v>
       </c>
@@ -15554,7 +15581,7 @@
       <c r="A136" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B136" s="27" t="s">
+      <c r="B136" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C136" s="1" t="s">
@@ -15572,15 +15599,15 @@
       <c r="G136" s="1" t="n">
         <v>3284</v>
       </c>
-      <c r="H136" s="28" t="n">
+      <c r="H136" s="31" t="n">
         <f aca="false">ROUND(D136*IF(ISNUMBER(SEARCH("Labour",B136)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B136)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B136)),ISNUMBER(SEARCH("RefUK",B136))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B136)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B136)),ISNUMBER(SEARCH("Lib Dem",B136))),National!$L$8,National!$L$9))))),0)</f>
         <v>452</v>
       </c>
-      <c r="I136" s="25" t="n">
+      <c r="I136" s="27" t="n">
         <f aca="false">H136/SUMIFS(H:H,A:A,A136)</f>
         <v>0.467908902691511</v>
       </c>
-      <c r="J136" s="29" t="n">
+      <c r="J136" s="32" t="n">
         <f aca="false">ROUND(I136*SUMIF(A:A,A136,D:D),0)</f>
         <v>502</v>
       </c>
@@ -15588,11 +15615,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A136,B:B,B136)/COUNTIFS(B:B,B136,A:A,A136),0)</f>
         <v>502</v>
       </c>
-      <c r="L136" s="25" t="n">
+      <c r="L136" s="27" t="n">
         <f aca="false">K136/SUMIF(A:A,A136,K:K)</f>
         <v>0.46784715750233</v>
       </c>
-      <c r="M136" s="1" t="n">
+      <c r="M136" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A136,J:J)*L136,0)</f>
         <v>502</v>
       </c>
@@ -15613,7 +15640,7 @@
       <c r="A137" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B137" s="27" t="s">
+      <c r="B137" s="30" t="s">
         <v>216</v>
       </c>
       <c r="C137" s="1" t="s">
@@ -15631,15 +15658,15 @@
       <c r="G137" s="1" t="n">
         <v>3284</v>
       </c>
-      <c r="H137" s="28" t="n">
+      <c r="H137" s="31" t="n">
         <f aca="false">ROUND(D137*IF(ISNUMBER(SEARCH("Labour",B137)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B137)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B137)),ISNUMBER(SEARCH("RefUK",B137))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B137)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B137)),ISNUMBER(SEARCH("Lib Dem",B137))),National!$L$8,National!$L$9))))),0)</f>
         <v>89</v>
       </c>
-      <c r="I137" s="25" t="n">
+      <c r="I137" s="27" t="n">
         <f aca="false">H137/SUMIFS(H:H,A:A,A137)</f>
         <v>0.0921325051759834</v>
       </c>
-      <c r="J137" s="29" t="n">
+      <c r="J137" s="32" t="n">
         <f aca="false">ROUND(I137*SUMIF(A:A,A137,D:D),0)</f>
         <v>99</v>
       </c>
@@ -15647,11 +15674,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A137,B:B,B137)/COUNTIFS(B:B,B137,A:A,A137),0)</f>
         <v>99</v>
       </c>
-      <c r="L137" s="25" t="n">
+      <c r="L137" s="27" t="n">
         <f aca="false">K137/SUMIF(A:A,A137,K:K)</f>
         <v>0.092264678471575</v>
       </c>
-      <c r="M137" s="1" t="n">
+      <c r="M137" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A137,J:J)*L137,0)</f>
         <v>99</v>
       </c>
@@ -15672,7 +15699,7 @@
       <c r="A138" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B138" s="30" t="s">
+      <c r="B138" s="33" t="s">
         <v>219</v>
       </c>
       <c r="C138" s="1" t="s">
@@ -15690,15 +15717,15 @@
       <c r="G138" s="1" t="n">
         <v>3284</v>
       </c>
-      <c r="H138" s="28" t="n">
+      <c r="H138" s="31" t="n">
         <f aca="false">ROUND(D138*IF(ISNUMBER(SEARCH("Labour",B138)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B138)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B138)),ISNUMBER(SEARCH("RefUK",B138))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B138)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B138)),ISNUMBER(SEARCH("Lib Dem",B138))),National!$L$8,National!$L$9))))),0)</f>
         <v>112</v>
       </c>
-      <c r="I138" s="25" t="n">
+      <c r="I138" s="27" t="n">
         <f aca="false">H138/SUMIFS(H:H,A:A,A138)</f>
         <v>0.115942028985507</v>
       </c>
-      <c r="J138" s="29" t="n">
+      <c r="J138" s="32" t="n">
         <f aca="false">ROUND(I138*SUMIF(A:A,A138,D:D),0)</f>
         <v>124</v>
       </c>
@@ -15706,11 +15733,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A138,B:B,B138)/COUNTIFS(B:B,B138,A:A,A138),0)</f>
         <v>124</v>
       </c>
-      <c r="L138" s="25" t="n">
+      <c r="L138" s="27" t="n">
         <f aca="false">K138/SUMIF(A:A,A138,K:K)</f>
         <v>0.115563839701771</v>
       </c>
-      <c r="M138" s="1" t="n">
+      <c r="M138" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A138,J:J)*L138,0)</f>
         <v>124</v>
       </c>
@@ -15731,7 +15758,7 @@
       <c r="A139" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B139" s="27" t="s">
+      <c r="B139" s="30" t="s">
         <v>249</v>
       </c>
       <c r="C139" s="1" t="s">
@@ -15749,15 +15776,15 @@
       <c r="G139" s="1" t="n">
         <v>10418</v>
       </c>
-      <c r="H139" s="28" t="n">
+      <c r="H139" s="31" t="n">
         <f aca="false">ROUND(D139*IF(ISNUMBER(SEARCH("Labour",B139)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B139)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B139)),ISNUMBER(SEARCH("RefUK",B139))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B139)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B139)),ISNUMBER(SEARCH("Lib Dem",B139))),National!$L$8,National!$L$9))))),0)</f>
         <v>701</v>
       </c>
-      <c r="I139" s="25" t="n">
+      <c r="I139" s="27" t="n">
         <f aca="false">H139/SUMIFS(H:H,A:A,A139)</f>
         <v>0.121385281385281</v>
       </c>
-      <c r="J139" s="29" t="n">
+      <c r="J139" s="32" t="n">
         <f aca="false">ROUND(I139*SUMIF(A:A,A139,D:D),0)</f>
         <v>1143</v>
       </c>
@@ -15765,11 +15792,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A139,B:B,B139)/COUNTIFS(B:B,B139,A:A,A139),0)</f>
         <v>373</v>
       </c>
-      <c r="L139" s="25" t="n">
+      <c r="L139" s="27" t="n">
         <f aca="false">K139/SUMIF(A:A,A139,K:K)</f>
         <v>0.0777893639207508</v>
       </c>
-      <c r="M139" s="1" t="n">
+      <c r="M139" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A139,J:J)*L139,0)</f>
         <v>733</v>
       </c>
@@ -15790,7 +15817,7 @@
       <c r="A140" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B140" s="27" t="s">
+      <c r="B140" s="30" t="s">
         <v>249</v>
       </c>
       <c r="C140" s="1" t="s">
@@ -15808,15 +15835,15 @@
       <c r="G140" s="1" t="n">
         <v>10418</v>
       </c>
-      <c r="H140" s="28" t="n">
+      <c r="H140" s="31" t="n">
         <f aca="false">ROUND(D140*IF(ISNUMBER(SEARCH("Labour",B140)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B140)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B140)),ISNUMBER(SEARCH("RefUK",B140))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B140)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B140)),ISNUMBER(SEARCH("Lib Dem",B140))),National!$L$8,National!$L$9))))),0)</f>
         <v>695</v>
       </c>
-      <c r="I140" s="25" t="n">
+      <c r="I140" s="27" t="n">
         <f aca="false">H140/SUMIFS(H:H,A:A,A140)</f>
         <v>0.12034632034632</v>
       </c>
-      <c r="J140" s="29" t="n">
+      <c r="J140" s="32" t="n">
         <f aca="false">ROUND(I140*SUMIF(A:A,A140,D:D),0)</f>
         <v>1133</v>
       </c>
@@ -15824,11 +15851,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A140,B:B,B140)/COUNTIFS(B:B,B140,A:A,A140),0)</f>
         <v>373</v>
       </c>
-      <c r="L140" s="25" t="n">
+      <c r="L140" s="27" t="n">
         <f aca="false">K140/SUMIF(A:A,A140,K:K)</f>
         <v>0.0777893639207508</v>
       </c>
-      <c r="M140" s="1" t="n">
+      <c r="M140" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A140,J:J)*L140,0)</f>
         <v>733</v>
       </c>
@@ -15849,7 +15876,7 @@
       <c r="A141" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B141" s="27" t="s">
+      <c r="B141" s="30" t="s">
         <v>249</v>
       </c>
       <c r="C141" s="1" t="s">
@@ -15867,15 +15894,15 @@
       <c r="G141" s="1" t="n">
         <v>10418</v>
       </c>
-      <c r="H141" s="28" t="n">
+      <c r="H141" s="31" t="n">
         <f aca="false">ROUND(D141*IF(ISNUMBER(SEARCH("Labour",B141)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B141)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B141)),ISNUMBER(SEARCH("RefUK",B141))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B141)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B141)),ISNUMBER(SEARCH("Lib Dem",B141))),National!$L$8,National!$L$9))))),0)</f>
         <v>665</v>
       </c>
-      <c r="I141" s="25" t="n">
+      <c r="I141" s="27" t="n">
         <f aca="false">H141/SUMIFS(H:H,A:A,A141)</f>
         <v>0.115151515151515</v>
       </c>
-      <c r="J141" s="29" t="n">
+      <c r="J141" s="32" t="n">
         <f aca="false">ROUND(I141*SUMIF(A:A,A141,D:D),0)</f>
         <v>1084</v>
       </c>
@@ -15883,11 +15910,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A141,B:B,B141)/COUNTIFS(B:B,B141,A:A,A141),0)</f>
         <v>373</v>
       </c>
-      <c r="L141" s="25" t="n">
+      <c r="L141" s="27" t="n">
         <f aca="false">K141/SUMIF(A:A,A141,K:K)</f>
         <v>0.0777893639207508</v>
       </c>
-      <c r="M141" s="1" t="n">
+      <c r="M141" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A141,J:J)*L141,0)</f>
         <v>733</v>
       </c>
@@ -15908,7 +15935,7 @@
       <c r="A142" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B142" s="27" t="s">
+      <c r="B142" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C142" s="1" t="s">
@@ -15926,15 +15953,15 @@
       <c r="G142" s="1" t="n">
         <v>10418</v>
       </c>
-      <c r="H142" s="28" t="n">
+      <c r="H142" s="31" t="n">
         <f aca="false">ROUND(D142*IF(ISNUMBER(SEARCH("Labour",B142)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B142)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B142)),ISNUMBER(SEARCH("RefUK",B142))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B142)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B142)),ISNUMBER(SEARCH("Lib Dem",B142))),National!$L$8,National!$L$9))))),0)</f>
         <v>786</v>
       </c>
-      <c r="I142" s="25" t="n">
+      <c r="I142" s="27" t="n">
         <f aca="false">H142/SUMIFS(H:H,A:A,A142)</f>
         <v>0.136103896103896</v>
       </c>
-      <c r="J142" s="29" t="n">
+      <c r="J142" s="32" t="n">
         <f aca="false">ROUND(I142*SUMIF(A:A,A142,D:D),0)</f>
         <v>1282</v>
       </c>
@@ -15942,11 +15969,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A142,B:B,B142)/COUNTIFS(B:B,B142,A:A,A142),0)</f>
         <v>397</v>
       </c>
-      <c r="L142" s="25" t="n">
+      <c r="L142" s="27" t="n">
         <f aca="false">K142/SUMIF(A:A,A142,K:K)</f>
         <v>0.0827945776850886</v>
       </c>
-      <c r="M142" s="1" t="n">
+      <c r="M142" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A142,J:J)*L142,0)</f>
         <v>780</v>
       </c>
@@ -15967,7 +15994,7 @@
       <c r="A143" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B143" s="27" t="s">
+      <c r="B143" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C143" s="1" t="s">
@@ -15985,15 +16012,15 @@
       <c r="G143" s="1" t="n">
         <v>10418</v>
       </c>
-      <c r="H143" s="28" t="n">
+      <c r="H143" s="31" t="n">
         <f aca="false">ROUND(D143*IF(ISNUMBER(SEARCH("Labour",B143)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B143)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B143)),ISNUMBER(SEARCH("RefUK",B143))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B143)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B143)),ISNUMBER(SEARCH("Lib Dem",B143))),National!$L$8,National!$L$9))))),0)</f>
         <v>705</v>
       </c>
-      <c r="I143" s="25" t="n">
+      <c r="I143" s="27" t="n">
         <f aca="false">H143/SUMIFS(H:H,A:A,A143)</f>
         <v>0.122077922077922</v>
       </c>
-      <c r="J143" s="29" t="n">
+      <c r="J143" s="32" t="n">
         <f aca="false">ROUND(I143*SUMIF(A:A,A143,D:D),0)</f>
         <v>1150</v>
       </c>
@@ -16001,11 +16028,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A143,B:B,B143)/COUNTIFS(B:B,B143,A:A,A143),0)</f>
         <v>397</v>
       </c>
-      <c r="L143" s="25" t="n">
+      <c r="L143" s="27" t="n">
         <f aca="false">K143/SUMIF(A:A,A143,K:K)</f>
         <v>0.0827945776850886</v>
       </c>
-      <c r="M143" s="1" t="n">
+      <c r="M143" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A143,J:J)*L143,0)</f>
         <v>780</v>
       </c>
@@ -16026,7 +16053,7 @@
       <c r="A144" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B144" s="27" t="s">
+      <c r="B144" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C144" s="1" t="s">
@@ -16044,15 +16071,15 @@
       <c r="G144" s="1" t="n">
         <v>10418</v>
       </c>
-      <c r="H144" s="28" t="n">
+      <c r="H144" s="31" t="n">
         <f aca="false">ROUND(D144*IF(ISNUMBER(SEARCH("Labour",B144)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B144)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B144)),ISNUMBER(SEARCH("RefUK",B144))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B144)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B144)),ISNUMBER(SEARCH("Lib Dem",B144))),National!$L$8,National!$L$9))))),0)</f>
         <v>699</v>
       </c>
-      <c r="I144" s="25" t="n">
+      <c r="I144" s="27" t="n">
         <f aca="false">H144/SUMIFS(H:H,A:A,A144)</f>
         <v>0.121038961038961</v>
       </c>
-      <c r="J144" s="29" t="n">
+      <c r="J144" s="32" t="n">
         <f aca="false">ROUND(I144*SUMIF(A:A,A144,D:D),0)</f>
         <v>1140</v>
       </c>
@@ -16060,11 +16087,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A144,B:B,B144)/COUNTIFS(B:B,B144,A:A,A144),0)</f>
         <v>397</v>
       </c>
-      <c r="L144" s="25" t="n">
+      <c r="L144" s="27" t="n">
         <f aca="false">K144/SUMIF(A:A,A144,K:K)</f>
         <v>0.0827945776850886</v>
       </c>
-      <c r="M144" s="1" t="n">
+      <c r="M144" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A144,J:J)*L144,0)</f>
         <v>780</v>
       </c>
@@ -16085,7 +16112,7 @@
       <c r="A145" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B145" s="30" t="s">
+      <c r="B145" s="33" t="s">
         <v>219</v>
       </c>
       <c r="C145" s="1" t="s">
@@ -16103,15 +16130,15 @@
       <c r="G145" s="1" t="n">
         <v>10418</v>
       </c>
-      <c r="H145" s="28" t="n">
+      <c r="H145" s="31" t="n">
         <f aca="false">ROUND(D145*IF(ISNUMBER(SEARCH("Labour",B145)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B145)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B145)),ISNUMBER(SEARCH("RefUK",B145))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B145)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B145)),ISNUMBER(SEARCH("Lib Dem",B145))),National!$L$8,National!$L$9))))),0)</f>
         <v>933</v>
       </c>
-      <c r="I145" s="25" t="n">
+      <c r="I145" s="27" t="n">
         <f aca="false">H145/SUMIFS(H:H,A:A,A145)</f>
         <v>0.161558441558442</v>
       </c>
-      <c r="J145" s="29" t="n">
+      <c r="J145" s="32" t="n">
         <f aca="false">ROUND(I145*SUMIF(A:A,A145,D:D),0)</f>
         <v>1522</v>
       </c>
@@ -16119,11 +16146,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A145,B:B,B145)/COUNTIFS(B:B,B145,A:A,A145),0)</f>
         <v>1522</v>
       </c>
-      <c r="L145" s="25" t="n">
+      <c r="L145" s="27" t="n">
         <f aca="false">K145/SUMIF(A:A,A145,K:K)</f>
         <v>0.317413972888425</v>
       </c>
-      <c r="M145" s="1" t="n">
+      <c r="M145" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A145,J:J)*L145,0)</f>
         <v>2989</v>
       </c>
@@ -16144,7 +16171,7 @@
       <c r="A146" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B146" s="27" t="s">
+      <c r="B146" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C146" s="1" t="s">
@@ -16162,15 +16189,15 @@
       <c r="G146" s="1" t="n">
         <v>10418</v>
       </c>
-      <c r="H146" s="28" t="n">
+      <c r="H146" s="31" t="n">
         <f aca="false">ROUND(D146*IF(ISNUMBER(SEARCH("Labour",B146)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B146)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B146)),ISNUMBER(SEARCH("RefUK",B146))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B146)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B146)),ISNUMBER(SEARCH("Lib Dem",B146))),National!$L$8,National!$L$9))))),0)</f>
         <v>343</v>
       </c>
-      <c r="I146" s="25" t="n">
+      <c r="I146" s="27" t="n">
         <f aca="false">H146/SUMIFS(H:H,A:A,A146)</f>
         <v>0.0593939393939394</v>
       </c>
-      <c r="J146" s="29" t="n">
+      <c r="J146" s="32" t="n">
         <f aca="false">ROUND(I146*SUMIF(A:A,A146,D:D),0)</f>
         <v>559</v>
       </c>
@@ -16178,11 +16205,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A146,B:B,B146)/COUNTIFS(B:B,B146,A:A,A146),0)</f>
         <v>559</v>
       </c>
-      <c r="L146" s="25" t="n">
+      <c r="L146" s="27" t="n">
         <f aca="false">K146/SUMIF(A:A,A146,K:K)</f>
         <v>0.116579770594369</v>
       </c>
-      <c r="M146" s="1" t="n">
+      <c r="M146" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A146,J:J)*L146,0)</f>
         <v>1098</v>
       </c>
@@ -16203,7 +16230,7 @@
       <c r="A147" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B147" s="27" t="s">
+      <c r="B147" s="30" t="s">
         <v>395</v>
       </c>
       <c r="C147" s="1" t="s">
@@ -16221,15 +16248,15 @@
       <c r="G147" s="1" t="n">
         <v>10418</v>
       </c>
-      <c r="H147" s="28" t="n">
+      <c r="H147" s="31" t="n">
         <f aca="false">ROUND(D147*IF(ISNUMBER(SEARCH("Labour",B147)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B147)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B147)),ISNUMBER(SEARCH("RefUK",B147))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B147)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B147)),ISNUMBER(SEARCH("Lib Dem",B147))),National!$L$8,National!$L$9))))),0)</f>
         <v>248</v>
       </c>
-      <c r="I147" s="25" t="n">
+      <c r="I147" s="27" t="n">
         <f aca="false">H147/SUMIFS(H:H,A:A,A147)</f>
         <v>0.0429437229437229</v>
       </c>
-      <c r="J147" s="29" t="n">
+      <c r="J147" s="32" t="n">
         <f aca="false">ROUND(I147*SUMIF(A:A,A147,D:D),0)</f>
         <v>404</v>
       </c>
@@ -16237,11 +16264,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A147,B:B,B147)/COUNTIFS(B:B,B147,A:A,A147),0)</f>
         <v>404</v>
       </c>
-      <c r="L147" s="25" t="n">
+      <c r="L147" s="27" t="n">
         <f aca="false">K147/SUMIF(A:A,A147,K:K)</f>
         <v>0.0842544316996872</v>
       </c>
-      <c r="M147" s="1" t="n">
+      <c r="M147" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A147,J:J)*L147,0)</f>
         <v>793</v>
       </c>
@@ -16262,7 +16289,7 @@
       <c r="A148" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B148" s="27" t="s">
+      <c r="B148" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C148" s="1" t="s">
@@ -16280,15 +16307,15 @@
       <c r="G148" s="1" t="n">
         <v>10218</v>
       </c>
-      <c r="H148" s="28" t="n">
+      <c r="H148" s="31" t="n">
         <f aca="false">ROUND(D148*IF(ISNUMBER(SEARCH("Labour",B148)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B148)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B148)),ISNUMBER(SEARCH("RefUK",B148))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B148)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B148)),ISNUMBER(SEARCH("Lib Dem",B148))),National!$L$8,National!$L$9))))),0)</f>
         <v>953</v>
       </c>
-      <c r="I148" s="25" t="n">
+      <c r="I148" s="27" t="n">
         <f aca="false">H148/SUMIFS(H:H,A:A,A148)</f>
         <v>0.164679453948505</v>
       </c>
-      <c r="J148" s="29" t="n">
+      <c r="J148" s="32" t="n">
         <f aca="false">ROUND(I148*SUMIF(A:A,A148,D:D),0)</f>
         <v>1297</v>
       </c>
@@ -16296,11 +16323,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A148,B:B,B148)/COUNTIFS(B:B,B148,A:A,A148),0)</f>
         <v>426</v>
       </c>
-      <c r="L148" s="25" t="n">
+      <c r="L148" s="27" t="n">
         <f aca="false">K148/SUMIF(A:A,A148,K:K)</f>
         <v>0.123765252760023</v>
       </c>
-      <c r="M148" s="1" t="n">
+      <c r="M148" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A148,J:J)*L148,0)</f>
         <v>975</v>
       </c>
@@ -16321,7 +16348,7 @@
       <c r="A149" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B149" s="27" t="s">
+      <c r="B149" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C149" s="1" t="s">
@@ -16339,15 +16366,15 @@
       <c r="G149" s="1" t="n">
         <v>10218</v>
       </c>
-      <c r="H149" s="28" t="n">
+      <c r="H149" s="31" t="n">
         <f aca="false">ROUND(D149*IF(ISNUMBER(SEARCH("Labour",B149)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B149)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B149)),ISNUMBER(SEARCH("RefUK",B149))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B149)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B149)),ISNUMBER(SEARCH("Lib Dem",B149))),National!$L$8,National!$L$9))))),0)</f>
         <v>945</v>
       </c>
-      <c r="I149" s="25" t="n">
+      <c r="I149" s="27" t="n">
         <f aca="false">H149/SUMIFS(H:H,A:A,A149)</f>
         <v>0.163297045101089</v>
       </c>
-      <c r="J149" s="29" t="n">
+      <c r="J149" s="32" t="n">
         <f aca="false">ROUND(I149*SUMIF(A:A,A149,D:D),0)</f>
         <v>1286</v>
       </c>
@@ -16355,11 +16382,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A149,B:B,B149)/COUNTIFS(B:B,B149,A:A,A149),0)</f>
         <v>426</v>
       </c>
-      <c r="L149" s="25" t="n">
+      <c r="L149" s="27" t="n">
         <f aca="false">K149/SUMIF(A:A,A149,K:K)</f>
         <v>0.123765252760023</v>
       </c>
-      <c r="M149" s="1" t="n">
+      <c r="M149" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A149,J:J)*L149,0)</f>
         <v>975</v>
       </c>
@@ -16380,7 +16407,7 @@
       <c r="A150" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B150" s="27" t="s">
+      <c r="B150" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C150" s="1" t="s">
@@ -16398,15 +16425,15 @@
       <c r="G150" s="1" t="n">
         <v>10218</v>
       </c>
-      <c r="H150" s="28" t="n">
+      <c r="H150" s="31" t="n">
         <f aca="false">ROUND(D150*IF(ISNUMBER(SEARCH("Labour",B150)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B150)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B150)),ISNUMBER(SEARCH("RefUK",B150))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B150)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B150)),ISNUMBER(SEARCH("Lib Dem",B150))),National!$L$8,National!$L$9))))),0)</f>
         <v>921</v>
       </c>
-      <c r="I150" s="25" t="n">
+      <c r="I150" s="27" t="n">
         <f aca="false">H150/SUMIFS(H:H,A:A,A150)</f>
         <v>0.159149818558839</v>
       </c>
-      <c r="J150" s="29" t="n">
+      <c r="J150" s="32" t="n">
         <f aca="false">ROUND(I150*SUMIF(A:A,A150,D:D),0)</f>
         <v>1253</v>
       </c>
@@ -16414,11 +16441,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A150,B:B,B150)/COUNTIFS(B:B,B150,A:A,A150),0)</f>
         <v>426</v>
       </c>
-      <c r="L150" s="25" t="n">
+      <c r="L150" s="27" t="n">
         <f aca="false">K150/SUMIF(A:A,A150,K:K)</f>
         <v>0.123765252760023</v>
       </c>
-      <c r="M150" s="1" t="n">
+      <c r="M150" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A150,J:J)*L150,0)</f>
         <v>975</v>
       </c>
@@ -16439,7 +16466,7 @@
       <c r="A151" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B151" s="27" t="s">
+      <c r="B151" s="30" t="s">
         <v>216</v>
       </c>
       <c r="C151" s="1" t="s">
@@ -16457,15 +16484,15 @@
       <c r="G151" s="1" t="n">
         <v>10218</v>
       </c>
-      <c r="H151" s="28" t="n">
+      <c r="H151" s="31" t="n">
         <f aca="false">ROUND(D151*IF(ISNUMBER(SEARCH("Labour",B151)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B151)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B151)),ISNUMBER(SEARCH("RefUK",B151))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B151)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B151)),ISNUMBER(SEARCH("Lib Dem",B151))),National!$L$8,National!$L$9))))),0)</f>
         <v>336</v>
       </c>
-      <c r="I151" s="25" t="n">
+      <c r="I151" s="27" t="n">
         <f aca="false">H151/SUMIFS(H:H,A:A,A151)</f>
         <v>0.0580611715914982</v>
       </c>
-      <c r="J151" s="29" t="n">
+      <c r="J151" s="32" t="n">
         <f aca="false">ROUND(I151*SUMIF(A:A,A151,D:D),0)</f>
         <v>457</v>
       </c>
@@ -16473,11 +16500,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A151,B:B,B151)/COUNTIFS(B:B,B151,A:A,A151),0)</f>
         <v>142</v>
       </c>
-      <c r="L151" s="25" t="n">
+      <c r="L151" s="27" t="n">
         <f aca="false">K151/SUMIF(A:A,A151,K:K)</f>
         <v>0.0412550842533411</v>
       </c>
-      <c r="M151" s="1" t="n">
+      <c r="M151" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A151,J:J)*L151,0)</f>
         <v>325</v>
       </c>
@@ -16498,7 +16525,7 @@
       <c r="A152" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B152" s="27" t="s">
+      <c r="B152" s="30" t="s">
         <v>216</v>
       </c>
       <c r="C152" s="1" t="s">
@@ -16516,15 +16543,15 @@
       <c r="G152" s="1" t="n">
         <v>10218</v>
       </c>
-      <c r="H152" s="28" t="n">
+      <c r="H152" s="31" t="n">
         <f aca="false">ROUND(D152*IF(ISNUMBER(SEARCH("Labour",B152)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B152)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B152)),ISNUMBER(SEARCH("RefUK",B152))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B152)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B152)),ISNUMBER(SEARCH("Lib Dem",B152))),National!$L$8,National!$L$9))))),0)</f>
         <v>311</v>
       </c>
-      <c r="I152" s="25" t="n">
+      <c r="I152" s="27" t="n">
         <f aca="false">H152/SUMIFS(H:H,A:A,A152)</f>
         <v>0.0537411439433212</v>
       </c>
-      <c r="J152" s="29" t="n">
+      <c r="J152" s="32" t="n">
         <f aca="false">ROUND(I152*SUMIF(A:A,A152,D:D),0)</f>
         <v>423</v>
       </c>
@@ -16532,11 +16559,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A152,B:B,B152)/COUNTIFS(B:B,B152,A:A,A152),0)</f>
         <v>142</v>
       </c>
-      <c r="L152" s="25" t="n">
+      <c r="L152" s="27" t="n">
         <f aca="false">K152/SUMIF(A:A,A152,K:K)</f>
         <v>0.0412550842533411</v>
       </c>
-      <c r="M152" s="1" t="n">
+      <c r="M152" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A152,J:J)*L152,0)</f>
         <v>325</v>
       </c>
@@ -16557,7 +16584,7 @@
       <c r="A153" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B153" s="27" t="s">
+      <c r="B153" s="30" t="s">
         <v>216</v>
       </c>
       <c r="C153" s="1" t="s">
@@ -16575,15 +16602,15 @@
       <c r="G153" s="1" t="n">
         <v>10218</v>
       </c>
-      <c r="H153" s="28" t="n">
+      <c r="H153" s="31" t="n">
         <f aca="false">ROUND(D153*IF(ISNUMBER(SEARCH("Labour",B153)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B153)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B153)),ISNUMBER(SEARCH("RefUK",B153))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B153)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B153)),ISNUMBER(SEARCH("Lib Dem",B153))),National!$L$8,National!$L$9))))),0)</f>
         <v>293</v>
       </c>
-      <c r="I153" s="25" t="n">
+      <c r="I153" s="27" t="n">
         <f aca="false">H153/SUMIFS(H:H,A:A,A153)</f>
         <v>0.0506307240366338</v>
       </c>
-      <c r="J153" s="29" t="n">
+      <c r="J153" s="32" t="n">
         <f aca="false">ROUND(I153*SUMIF(A:A,A153,D:D),0)</f>
         <v>399</v>
       </c>
@@ -16591,11 +16618,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A153,B:B,B153)/COUNTIFS(B:B,B153,A:A,A153),0)</f>
         <v>142</v>
       </c>
-      <c r="L153" s="25" t="n">
+      <c r="L153" s="27" t="n">
         <f aca="false">K153/SUMIF(A:A,A153,K:K)</f>
         <v>0.0412550842533411</v>
       </c>
-      <c r="M153" s="1" t="n">
+      <c r="M153" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A153,J:J)*L153,0)</f>
         <v>325</v>
       </c>
@@ -16616,7 +16643,7 @@
       <c r="A154" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B154" s="30" t="s">
+      <c r="B154" s="33" t="s">
         <v>219</v>
       </c>
       <c r="C154" s="1" t="s">
@@ -16634,15 +16661,15 @@
       <c r="G154" s="1" t="n">
         <v>10218</v>
       </c>
-      <c r="H154" s="28" t="n">
+      <c r="H154" s="31" t="n">
         <f aca="false">ROUND(D154*IF(ISNUMBER(SEARCH("Labour",B154)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B154)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B154)),ISNUMBER(SEARCH("RefUK",B154))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B154)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B154)),ISNUMBER(SEARCH("Lib Dem",B154))),National!$L$8,National!$L$9))))),0)</f>
         <v>900</v>
       </c>
-      <c r="I154" s="25" t="n">
+      <c r="I154" s="27" t="n">
         <f aca="false">H154/SUMIFS(H:H,A:A,A154)</f>
         <v>0.15552099533437</v>
       </c>
-      <c r="J154" s="29" t="n">
+      <c r="J154" s="32" t="n">
         <f aca="false">ROUND(I154*SUMIF(A:A,A154,D:D),0)</f>
         <v>1225</v>
       </c>
@@ -16650,11 +16677,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A154,B:B,B154)/COUNTIFS(B:B,B154,A:A,A154),0)</f>
         <v>1225</v>
       </c>
-      <c r="L154" s="25" t="n">
+      <c r="L154" s="27" t="n">
         <f aca="false">K154/SUMIF(A:A,A154,K:K)</f>
         <v>0.355897733875654</v>
       </c>
-      <c r="M154" s="1" t="n">
+      <c r="M154" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A154,J:J)*L154,0)</f>
         <v>2803</v>
       </c>
@@ -16675,7 +16702,7 @@
       <c r="A155" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B155" s="27" t="s">
+      <c r="B155" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C155" s="1" t="s">
@@ -16693,15 +16720,15 @@
       <c r="G155" s="1" t="n">
         <v>10218</v>
       </c>
-      <c r="H155" s="28" t="n">
+      <c r="H155" s="31" t="n">
         <f aca="false">ROUND(D155*IF(ISNUMBER(SEARCH("Labour",B155)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B155)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B155)),ISNUMBER(SEARCH("RefUK",B155))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B155)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B155)),ISNUMBER(SEARCH("Lib Dem",B155))),National!$L$8,National!$L$9))))),0)</f>
         <v>426</v>
       </c>
-      <c r="I155" s="25" t="n">
+      <c r="I155" s="27" t="n">
         <f aca="false">H155/SUMIFS(H:H,A:A,A155)</f>
         <v>0.0736132711249352</v>
       </c>
-      <c r="J155" s="29" t="n">
+      <c r="J155" s="32" t="n">
         <f aca="false">ROUND(I155*SUMIF(A:A,A155,D:D),0)</f>
         <v>580</v>
       </c>
@@ -16709,11 +16736,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A155,B:B,B155)/COUNTIFS(B:B,B155,A:A,A155),0)</f>
         <v>171</v>
       </c>
-      <c r="L155" s="25" t="n">
+      <c r="L155" s="27" t="n">
         <f aca="false">K155/SUMIF(A:A,A155,K:K)</f>
         <v>0.0496804183614178</v>
       </c>
-      <c r="M155" s="1" t="n">
+      <c r="M155" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A155,J:J)*L155,0)</f>
         <v>391</v>
       </c>
@@ -16734,7 +16761,7 @@
       <c r="A156" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B156" s="27" t="s">
+      <c r="B156" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C156" s="1" t="s">
@@ -16752,15 +16779,15 @@
       <c r="G156" s="1" t="n">
         <v>10218</v>
       </c>
-      <c r="H156" s="28" t="n">
+      <c r="H156" s="31" t="n">
         <f aca="false">ROUND(D156*IF(ISNUMBER(SEARCH("Labour",B156)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B156)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B156)),ISNUMBER(SEARCH("RefUK",B156))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B156)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B156)),ISNUMBER(SEARCH("Lib Dem",B156))),National!$L$8,National!$L$9))))),0)</f>
         <v>395</v>
       </c>
-      <c r="I156" s="25" t="n">
+      <c r="I156" s="27" t="n">
         <f aca="false">H156/SUMIFS(H:H,A:A,A156)</f>
         <v>0.0682564368411958</v>
       </c>
-      <c r="J156" s="29" t="n">
+      <c r="J156" s="32" t="n">
         <f aca="false">ROUND(I156*SUMIF(A:A,A156,D:D),0)</f>
         <v>537</v>
       </c>
@@ -16768,11 +16795,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A156,B:B,B156)/COUNTIFS(B:B,B156,A:A,A156),0)</f>
         <v>171</v>
       </c>
-      <c r="L156" s="25" t="n">
+      <c r="L156" s="27" t="n">
         <f aca="false">K156/SUMIF(A:A,A156,K:K)</f>
         <v>0.0496804183614178</v>
       </c>
-      <c r="M156" s="1" t="n">
+      <c r="M156" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A156,J:J)*L156,0)</f>
         <v>391</v>
       </c>
@@ -16793,7 +16820,7 @@
       <c r="A157" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B157" s="27" t="s">
+      <c r="B157" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C157" s="1" t="s">
@@ -16811,15 +16838,15 @@
       <c r="G157" s="1" t="n">
         <v>10218</v>
       </c>
-      <c r="H157" s="28" t="n">
+      <c r="H157" s="31" t="n">
         <f aca="false">ROUND(D157*IF(ISNUMBER(SEARCH("Labour",B157)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B157)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B157)),ISNUMBER(SEARCH("RefUK",B157))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B157)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B157)),ISNUMBER(SEARCH("Lib Dem",B157))),National!$L$8,National!$L$9))))),0)</f>
         <v>307</v>
       </c>
-      <c r="I157" s="25" t="n">
+      <c r="I157" s="27" t="n">
         <f aca="false">H157/SUMIFS(H:H,A:A,A157)</f>
         <v>0.0530499395196129</v>
       </c>
-      <c r="J157" s="29" t="n">
+      <c r="J157" s="32" t="n">
         <f aca="false">ROUND(I157*SUMIF(A:A,A157,D:D),0)</f>
         <v>418</v>
       </c>
@@ -16827,11 +16854,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A157,B:B,B157)/COUNTIFS(B:B,B157,A:A,A157),0)</f>
         <v>171</v>
       </c>
-      <c r="L157" s="25" t="n">
+      <c r="L157" s="27" t="n">
         <f aca="false">K157/SUMIF(A:A,A157,K:K)</f>
         <v>0.0496804183614178</v>
       </c>
-      <c r="M157" s="1" t="n">
+      <c r="M157" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A157,J:J)*L157,0)</f>
         <v>391</v>
       </c>
@@ -16852,7 +16879,7 @@
       <c r="A158" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B158" s="27" t="s">
+      <c r="B158" s="30" t="s">
         <v>249</v>
       </c>
       <c r="C158" s="1" t="s">
@@ -16870,15 +16897,15 @@
       <c r="G158" s="1" t="n">
         <v>10150</v>
       </c>
-      <c r="H158" s="28" t="n">
+      <c r="H158" s="31" t="n">
         <f aca="false">ROUND(D158*IF(ISNUMBER(SEARCH("Labour",B158)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B158)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B158)),ISNUMBER(SEARCH("RefUK",B158))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B158)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B158)),ISNUMBER(SEARCH("Lib Dem",B158))),National!$L$8,National!$L$9))))),0)</f>
         <v>529</v>
       </c>
-      <c r="I158" s="25" t="n">
+      <c r="I158" s="27" t="n">
         <f aca="false">H158/SUMIFS(H:H,A:A,A158)</f>
         <v>0.118397493285586</v>
       </c>
-      <c r="J158" s="29" t="n">
+      <c r="J158" s="32" t="n">
         <f aca="false">ROUND(I158*SUMIF(A:A,A158,D:D),0)</f>
         <v>873</v>
       </c>
@@ -16886,11 +16913,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A158,B:B,B158)/COUNTIFS(B:B,B158,A:A,A158),0)</f>
         <v>280</v>
       </c>
-      <c r="L158" s="25" t="n">
+      <c r="L158" s="27" t="n">
         <f aca="false">K158/SUMIF(A:A,A158,K:K)</f>
         <v>0.0781468043538934</v>
       </c>
-      <c r="M158" s="1" t="n">
+      <c r="M158" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A158,J:J)*L158,0)</f>
         <v>576</v>
       </c>
@@ -16911,7 +16938,7 @@
       <c r="A159" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B159" s="27" t="s">
+      <c r="B159" s="30" t="s">
         <v>249</v>
       </c>
       <c r="C159" s="1" t="s">
@@ -16929,15 +16956,15 @@
       <c r="G159" s="1" t="n">
         <v>10150</v>
       </c>
-      <c r="H159" s="28" t="n">
+      <c r="H159" s="31" t="n">
         <f aca="false">ROUND(D159*IF(ISNUMBER(SEARCH("Labour",B159)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B159)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B159)),ISNUMBER(SEARCH("RefUK",B159))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B159)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B159)),ISNUMBER(SEARCH("Lib Dem",B159))),National!$L$8,National!$L$9))))),0)</f>
         <v>510</v>
       </c>
-      <c r="I159" s="25" t="n">
+      <c r="I159" s="27" t="n">
         <f aca="false">H159/SUMIFS(H:H,A:A,A159)</f>
         <v>0.11414503133393</v>
       </c>
-      <c r="J159" s="29" t="n">
+      <c r="J159" s="32" t="n">
         <f aca="false">ROUND(I159*SUMIF(A:A,A159,D:D),0)</f>
         <v>842</v>
       </c>
@@ -16945,11 +16972,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A159,B:B,B159)/COUNTIFS(B:B,B159,A:A,A159),0)</f>
         <v>280</v>
       </c>
-      <c r="L159" s="25" t="n">
+      <c r="L159" s="27" t="n">
         <f aca="false">K159/SUMIF(A:A,A159,K:K)</f>
         <v>0.0781468043538934</v>
       </c>
-      <c r="M159" s="1" t="n">
+      <c r="M159" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A159,J:J)*L159,0)</f>
         <v>576</v>
       </c>
@@ -16970,7 +16997,7 @@
       <c r="A160" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B160" s="27" t="s">
+      <c r="B160" s="30" t="s">
         <v>249</v>
       </c>
       <c r="C160" s="1" t="s">
@@ -16988,15 +17015,15 @@
       <c r="G160" s="1" t="n">
         <v>10150</v>
       </c>
-      <c r="H160" s="28" t="n">
+      <c r="H160" s="31" t="n">
         <f aca="false">ROUND(D160*IF(ISNUMBER(SEARCH("Labour",B160)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B160)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B160)),ISNUMBER(SEARCH("RefUK",B160))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B160)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B160)),ISNUMBER(SEARCH("Lib Dem",B160))),National!$L$8,National!$L$9))))),0)</f>
         <v>489</v>
       </c>
-      <c r="I160" s="25" t="n">
+      <c r="I160" s="27" t="n">
         <f aca="false">H160/SUMIFS(H:H,A:A,A160)</f>
         <v>0.109444941808415</v>
       </c>
-      <c r="J160" s="29" t="n">
+      <c r="J160" s="32" t="n">
         <f aca="false">ROUND(I160*SUMIF(A:A,A160,D:D),0)</f>
         <v>807</v>
       </c>
@@ -17004,11 +17031,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A160,B:B,B160)/COUNTIFS(B:B,B160,A:A,A160),0)</f>
         <v>280</v>
       </c>
-      <c r="L160" s="25" t="n">
+      <c r="L160" s="27" t="n">
         <f aca="false">K160/SUMIF(A:A,A160,K:K)</f>
         <v>0.0781468043538934</v>
       </c>
-      <c r="M160" s="1" t="n">
+      <c r="M160" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A160,J:J)*L160,0)</f>
         <v>576</v>
       </c>
@@ -17029,7 +17056,7 @@
       <c r="A161" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B161" s="27" t="s">
+      <c r="B161" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C161" s="1" t="s">
@@ -17047,15 +17074,15 @@
       <c r="G161" s="1" t="n">
         <v>10150</v>
       </c>
-      <c r="H161" s="28" t="n">
+      <c r="H161" s="31" t="n">
         <f aca="false">ROUND(D161*IF(ISNUMBER(SEARCH("Labour",B161)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B161)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B161)),ISNUMBER(SEARCH("RefUK",B161))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B161)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B161)),ISNUMBER(SEARCH("Lib Dem",B161))),National!$L$8,National!$L$9))))),0)</f>
         <v>648</v>
       </c>
-      <c r="I161" s="25" t="n">
+      <c r="I161" s="27" t="n">
         <f aca="false">H161/SUMIFS(H:H,A:A,A161)</f>
         <v>0.14503133393017</v>
       </c>
-      <c r="J161" s="29" t="n">
+      <c r="J161" s="32" t="n">
         <f aca="false">ROUND(I161*SUMIF(A:A,A161,D:D),0)</f>
         <v>1069</v>
       </c>
@@ -17063,11 +17090,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A161,B:B,B161)/COUNTIFS(B:B,B161,A:A,A161),0)</f>
         <v>352</v>
       </c>
-      <c r="L161" s="25" t="n">
+      <c r="L161" s="27" t="n">
         <f aca="false">K161/SUMIF(A:A,A161,K:K)</f>
         <v>0.0982416969020374</v>
       </c>
-      <c r="M161" s="1" t="n">
+      <c r="M161" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A161,J:J)*L161,0)</f>
         <v>724</v>
       </c>
@@ -17088,7 +17115,7 @@
       <c r="A162" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B162" s="27" t="s">
+      <c r="B162" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C162" s="1" t="s">
@@ -17106,15 +17133,15 @@
       <c r="G162" s="1" t="n">
         <v>10150</v>
       </c>
-      <c r="H162" s="28" t="n">
+      <c r="H162" s="31" t="n">
         <f aca="false">ROUND(D162*IF(ISNUMBER(SEARCH("Labour",B162)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B162)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B162)),ISNUMBER(SEARCH("RefUK",B162))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B162)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B162)),ISNUMBER(SEARCH("Lib Dem",B162))),National!$L$8,National!$L$9))))),0)</f>
         <v>636</v>
       </c>
-      <c r="I162" s="25" t="n">
+      <c r="I162" s="27" t="n">
         <f aca="false">H162/SUMIFS(H:H,A:A,A162)</f>
         <v>0.142345568487019</v>
       </c>
-      <c r="J162" s="29" t="n">
+      <c r="J162" s="32" t="n">
         <f aca="false">ROUND(I162*SUMIF(A:A,A162,D:D),0)</f>
         <v>1050</v>
       </c>
@@ -17122,11 +17149,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A162,B:B,B162)/COUNTIFS(B:B,B162,A:A,A162),0)</f>
         <v>352</v>
       </c>
-      <c r="L162" s="25" t="n">
+      <c r="L162" s="27" t="n">
         <f aca="false">K162/SUMIF(A:A,A162,K:K)</f>
         <v>0.0982416969020374</v>
       </c>
-      <c r="M162" s="1" t="n">
+      <c r="M162" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A162,J:J)*L162,0)</f>
         <v>724</v>
       </c>
@@ -17147,7 +17174,7 @@
       <c r="A163" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B163" s="27" t="s">
+      <c r="B163" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C163" s="1" t="s">
@@ -17165,15 +17192,15 @@
       <c r="G163" s="1" t="n">
         <v>10150</v>
       </c>
-      <c r="H163" s="28" t="n">
+      <c r="H163" s="31" t="n">
         <f aca="false">ROUND(D163*IF(ISNUMBER(SEARCH("Labour",B163)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B163)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B163)),ISNUMBER(SEARCH("RefUK",B163))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B163)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B163)),ISNUMBER(SEARCH("Lib Dem",B163))),National!$L$8,National!$L$9))))),0)</f>
         <v>634</v>
       </c>
-      <c r="I163" s="25" t="n">
+      <c r="I163" s="27" t="n">
         <f aca="false">H163/SUMIFS(H:H,A:A,A163)</f>
         <v>0.14189794091316</v>
       </c>
-      <c r="J163" s="29" t="n">
+      <c r="J163" s="32" t="n">
         <f aca="false">ROUND(I163*SUMIF(A:A,A163,D:D),0)</f>
         <v>1046</v>
       </c>
@@ -17181,11 +17208,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A163,B:B,B163)/COUNTIFS(B:B,B163,A:A,A163),0)</f>
         <v>352</v>
       </c>
-      <c r="L163" s="25" t="n">
+      <c r="L163" s="27" t="n">
         <f aca="false">K163/SUMIF(A:A,A163,K:K)</f>
         <v>0.0982416969020374</v>
       </c>
-      <c r="M163" s="1" t="n">
+      <c r="M163" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A163,J:J)*L163,0)</f>
         <v>724</v>
       </c>
@@ -17206,7 +17233,7 @@
       <c r="A164" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B164" s="30" t="s">
+      <c r="B164" s="33" t="s">
         <v>219</v>
       </c>
       <c r="C164" s="1" t="s">
@@ -17224,15 +17251,15 @@
       <c r="G164" s="1" t="n">
         <v>10150</v>
       </c>
-      <c r="H164" s="28" t="n">
+      <c r="H164" s="31" t="n">
         <f aca="false">ROUND(D164*IF(ISNUMBER(SEARCH("Labour",B164)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B164)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B164)),ISNUMBER(SEARCH("RefUK",B164))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B164)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B164)),ISNUMBER(SEARCH("Lib Dem",B164))),National!$L$8,National!$L$9))))),0)</f>
         <v>622</v>
       </c>
-      <c r="I164" s="25" t="n">
+      <c r="I164" s="27" t="n">
         <f aca="false">H164/SUMIFS(H:H,A:A,A164)</f>
         <v>0.139212175470009</v>
       </c>
-      <c r="J164" s="29" t="n">
+      <c r="J164" s="32" t="n">
         <f aca="false">ROUND(I164*SUMIF(A:A,A164,D:D),0)</f>
         <v>1027</v>
       </c>
@@ -17240,11 +17267,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A164,B:B,B164)/COUNTIFS(B:B,B164,A:A,A164),0)</f>
         <v>1027</v>
       </c>
-      <c r="L164" s="25" t="n">
+      <c r="L164" s="27" t="n">
         <f aca="false">K164/SUMIF(A:A,A164,K:K)</f>
         <v>0.286631314540888</v>
       </c>
-      <c r="M164" s="1" t="n">
+      <c r="M164" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A164,J:J)*L164,0)</f>
         <v>2114</v>
       </c>
@@ -17265,7 +17292,7 @@
       <c r="A165" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B165" s="27" t="s">
+      <c r="B165" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C165" s="1" t="s">
@@ -17283,15 +17310,15 @@
       <c r="G165" s="1" t="n">
         <v>10150</v>
       </c>
-      <c r="H165" s="28" t="n">
+      <c r="H165" s="31" t="n">
         <f aca="false">ROUND(D165*IF(ISNUMBER(SEARCH("Labour",B165)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B165)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B165)),ISNUMBER(SEARCH("RefUK",B165))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B165)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B165)),ISNUMBER(SEARCH("Lib Dem",B165))),National!$L$8,National!$L$9))))),0)</f>
         <v>223</v>
       </c>
-      <c r="I165" s="25" t="n">
+      <c r="I165" s="27" t="n">
         <f aca="false">H165/SUMIFS(H:H,A:A,A165)</f>
         <v>0.0499104744852283</v>
       </c>
-      <c r="J165" s="29" t="n">
+      <c r="J165" s="32" t="n">
         <f aca="false">ROUND(I165*SUMIF(A:A,A165,D:D),0)</f>
         <v>368</v>
       </c>
@@ -17299,11 +17326,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A165,B:B,B165)/COUNTIFS(B:B,B165,A:A,A165),0)</f>
         <v>368</v>
       </c>
-      <c r="L165" s="25" t="n">
+      <c r="L165" s="27" t="n">
         <f aca="false">K165/SUMIF(A:A,A165,K:K)</f>
         <v>0.102707228579403</v>
       </c>
-      <c r="M165" s="1" t="n">
+      <c r="M165" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A165,J:J)*L165,0)</f>
         <v>757</v>
       </c>
@@ -17324,7 +17351,7 @@
       <c r="A166" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B166" s="27" t="s">
+      <c r="B166" s="30" t="s">
         <v>23</v>
       </c>
       <c r="C166" s="1" t="s">
@@ -17342,15 +17369,15 @@
       <c r="G166" s="1" t="n">
         <v>10150</v>
       </c>
-      <c r="H166" s="28" t="n">
+      <c r="H166" s="31" t="n">
         <f aca="false">ROUND(D166*IF(ISNUMBER(SEARCH("Labour",B166)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B166)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B166)),ISNUMBER(SEARCH("RefUK",B166))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B166)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B166)),ISNUMBER(SEARCH("Lib Dem",B166))),National!$L$8,National!$L$9))))),0)</f>
         <v>177</v>
       </c>
-      <c r="I166" s="25" t="n">
+      <c r="I166" s="27" t="n">
         <f aca="false">H166/SUMIFS(H:H,A:A,A166)</f>
         <v>0.0396150402864817</v>
       </c>
-      <c r="J166" s="29" t="n">
+      <c r="J166" s="32" t="n">
         <f aca="false">ROUND(I166*SUMIF(A:A,A166,D:D),0)</f>
         <v>292</v>
       </c>
@@ -17358,11 +17385,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A166,B:B,B166)/COUNTIFS(B:B,B166,A:A,A166),0)</f>
         <v>292</v>
       </c>
-      <c r="L166" s="25" t="n">
+      <c r="L166" s="27" t="n">
         <f aca="false">K166/SUMIF(A:A,A166,K:K)</f>
         <v>0.0814959531119174</v>
       </c>
-      <c r="M166" s="1" t="n">
+      <c r="M166" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A166,J:J)*L166,0)</f>
         <v>601</v>
       </c>
@@ -17383,7 +17410,7 @@
       <c r="A167" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B167" s="27" t="s">
+      <c r="B167" s="30" t="s">
         <v>249</v>
       </c>
       <c r="C167" s="1" t="s">
@@ -17401,15 +17428,15 @@
       <c r="G167" s="1" t="n">
         <v>7120</v>
       </c>
-      <c r="H167" s="28" t="n">
+      <c r="H167" s="31" t="n">
         <f aca="false">ROUND(D167*IF(ISNUMBER(SEARCH("Labour",B167)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B167)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B167)),ISNUMBER(SEARCH("RefUK",B167))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B167)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B167)),ISNUMBER(SEARCH("Lib Dem",B167))),National!$L$8,National!$L$9))))),0)</f>
         <v>382</v>
       </c>
-      <c r="I167" s="25" t="n">
+      <c r="I167" s="27" t="n">
         <f aca="false">H167/SUMIFS(H:H,A:A,A167)</f>
         <v>0.180871212121212</v>
       </c>
-      <c r="J167" s="29" t="n">
+      <c r="J167" s="32" t="n">
         <f aca="false">ROUND(I167*SUMIF(A:A,A167,D:D),0)</f>
         <v>579</v>
       </c>
@@ -17417,11 +17444,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A167,B:B,B167)/COUNTIFS(B:B,B167,A:A,A167),0)</f>
         <v>275</v>
       </c>
-      <c r="L167" s="25" t="n">
+      <c r="L167" s="27" t="n">
         <f aca="false">K167/SUMIF(A:A,A167,K:K)</f>
         <v>0.127314814814815</v>
       </c>
-      <c r="M167" s="1" t="n">
+      <c r="M167" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A167,J:J)*L167,0)</f>
         <v>407</v>
       </c>
@@ -17442,7 +17469,7 @@
       <c r="A168" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B168" s="27" t="s">
+      <c r="B168" s="30" t="s">
         <v>249</v>
       </c>
       <c r="C168" s="1" t="s">
@@ -17460,15 +17487,15 @@
       <c r="G168" s="1" t="n">
         <v>7120</v>
       </c>
-      <c r="H168" s="28" t="n">
+      <c r="H168" s="31" t="n">
         <f aca="false">ROUND(D168*IF(ISNUMBER(SEARCH("Labour",B168)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B168)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B168)),ISNUMBER(SEARCH("RefUK",B168))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B168)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B168)),ISNUMBER(SEARCH("Lib Dem",B168))),National!$L$8,National!$L$9))))),0)</f>
         <v>344</v>
       </c>
-      <c r="I168" s="25" t="n">
+      <c r="I168" s="27" t="n">
         <f aca="false">H168/SUMIFS(H:H,A:A,A168)</f>
         <v>0.162878787878788</v>
       </c>
-      <c r="J168" s="29" t="n">
+      <c r="J168" s="32" t="n">
         <f aca="false">ROUND(I168*SUMIF(A:A,A168,D:D),0)</f>
         <v>521</v>
       </c>
@@ -17476,11 +17503,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A168,B:B,B168)/COUNTIFS(B:B,B168,A:A,A168),0)</f>
         <v>275</v>
       </c>
-      <c r="L168" s="25" t="n">
+      <c r="L168" s="27" t="n">
         <f aca="false">K168/SUMIF(A:A,A168,K:K)</f>
         <v>0.127314814814815</v>
       </c>
-      <c r="M168" s="1" t="n">
+      <c r="M168" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A168,J:J)*L168,0)</f>
         <v>407</v>
       </c>
@@ -17501,7 +17528,7 @@
       <c r="A169" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B169" s="27" t="s">
+      <c r="B169" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C169" s="1" t="s">
@@ -17519,15 +17546,15 @@
       <c r="G169" s="1" t="n">
         <v>7120</v>
       </c>
-      <c r="H169" s="28" t="n">
+      <c r="H169" s="31" t="n">
         <f aca="false">ROUND(D169*IF(ISNUMBER(SEARCH("Labour",B169)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B169)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B169)),ISNUMBER(SEARCH("RefUK",B169))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B169)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B169)),ISNUMBER(SEARCH("Lib Dem",B169))),National!$L$8,National!$L$9))))),0)</f>
         <v>328</v>
       </c>
-      <c r="I169" s="25" t="n">
+      <c r="I169" s="27" t="n">
         <f aca="false">H169/SUMIFS(H:H,A:A,A169)</f>
         <v>0.15530303030303</v>
       </c>
-      <c r="J169" s="29" t="n">
+      <c r="J169" s="32" t="n">
         <f aca="false">ROUND(I169*SUMIF(A:A,A169,D:D),0)</f>
         <v>497</v>
       </c>
@@ -17535,11 +17562,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A169,B:B,B169)/COUNTIFS(B:B,B169,A:A,A169),0)</f>
         <v>246</v>
       </c>
-      <c r="L169" s="25" t="n">
+      <c r="L169" s="27" t="n">
         <f aca="false">K169/SUMIF(A:A,A169,K:K)</f>
         <v>0.113888888888889</v>
       </c>
-      <c r="M169" s="1" t="n">
+      <c r="M169" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A169,J:J)*L169,0)</f>
         <v>364</v>
       </c>
@@ -17560,7 +17587,7 @@
       <c r="A170" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B170" s="27" t="s">
+      <c r="B170" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C170" s="1" t="s">
@@ -17578,15 +17605,15 @@
       <c r="G170" s="1" t="n">
         <v>7120</v>
       </c>
-      <c r="H170" s="28" t="n">
+      <c r="H170" s="31" t="n">
         <f aca="false">ROUND(D170*IF(ISNUMBER(SEARCH("Labour",B170)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B170)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B170)),ISNUMBER(SEARCH("RefUK",B170))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B170)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B170)),ISNUMBER(SEARCH("Lib Dem",B170))),National!$L$8,National!$L$9))))),0)</f>
         <v>320</v>
       </c>
-      <c r="I170" s="25" t="n">
+      <c r="I170" s="27" t="n">
         <f aca="false">H170/SUMIFS(H:H,A:A,A170)</f>
         <v>0.151515151515152</v>
       </c>
-      <c r="J170" s="29" t="n">
+      <c r="J170" s="32" t="n">
         <f aca="false">ROUND(I170*SUMIF(A:A,A170,D:D),0)</f>
         <v>485</v>
       </c>
@@ -17594,11 +17621,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A170,B:B,B170)/COUNTIFS(B:B,B170,A:A,A170),0)</f>
         <v>246</v>
       </c>
-      <c r="L170" s="25" t="n">
+      <c r="L170" s="27" t="n">
         <f aca="false">K170/SUMIF(A:A,A170,K:K)</f>
         <v>0.113888888888889</v>
       </c>
-      <c r="M170" s="1" t="n">
+      <c r="M170" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A170,J:J)*L170,0)</f>
         <v>364</v>
       </c>
@@ -17619,7 +17646,7 @@
       <c r="A171" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B171" s="30" t="s">
+      <c r="B171" s="33" t="s">
         <v>219</v>
       </c>
       <c r="C171" s="1" t="s">
@@ -17637,15 +17664,15 @@
       <c r="G171" s="1" t="n">
         <v>7120</v>
       </c>
-      <c r="H171" s="28" t="n">
+      <c r="H171" s="31" t="n">
         <f aca="false">ROUND(D171*IF(ISNUMBER(SEARCH("Labour",B171)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B171)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B171)),ISNUMBER(SEARCH("RefUK",B171))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B171)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B171)),ISNUMBER(SEARCH("Lib Dem",B171))),National!$L$8,National!$L$9))))),0)</f>
         <v>527</v>
       </c>
-      <c r="I171" s="25" t="n">
+      <c r="I171" s="27" t="n">
         <f aca="false">H171/SUMIFS(H:H,A:A,A171)</f>
         <v>0.249526515151515</v>
       </c>
-      <c r="J171" s="29" t="n">
+      <c r="J171" s="32" t="n">
         <f aca="false">ROUND(I171*SUMIF(A:A,A171,D:D),0)</f>
         <v>798</v>
       </c>
@@ -17653,11 +17680,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A171,B:B,B171)/COUNTIFS(B:B,B171,A:A,A171),0)</f>
         <v>798</v>
       </c>
-      <c r="L171" s="25" t="n">
+      <c r="L171" s="27" t="n">
         <f aca="false">K171/SUMIF(A:A,A171,K:K)</f>
         <v>0.369444444444444</v>
       </c>
-      <c r="M171" s="1" t="n">
+      <c r="M171" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A171,J:J)*L171,0)</f>
         <v>1182</v>
       </c>
@@ -17678,7 +17705,7 @@
       <c r="A172" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B172" s="27" t="s">
+      <c r="B172" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C172" s="1" t="s">
@@ -17696,15 +17723,15 @@
       <c r="G172" s="1" t="n">
         <v>7120</v>
       </c>
-      <c r="H172" s="28" t="n">
+      <c r="H172" s="31" t="n">
         <f aca="false">ROUND(D172*IF(ISNUMBER(SEARCH("Labour",B172)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B172)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B172)),ISNUMBER(SEARCH("RefUK",B172))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B172)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B172)),ISNUMBER(SEARCH("Lib Dem",B172))),National!$L$8,National!$L$9))))),0)</f>
         <v>211</v>
       </c>
-      <c r="I172" s="25" t="n">
+      <c r="I172" s="27" t="n">
         <f aca="false">H172/SUMIFS(H:H,A:A,A172)</f>
         <v>0.099905303030303</v>
       </c>
-      <c r="J172" s="29" t="n">
+      <c r="J172" s="32" t="n">
         <f aca="false">ROUND(I172*SUMIF(A:A,A172,D:D),0)</f>
         <v>320</v>
       </c>
@@ -17712,11 +17739,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A172,B:B,B172)/COUNTIFS(B:B,B172,A:A,A172),0)</f>
         <v>320</v>
       </c>
-      <c r="L172" s="25" t="n">
+      <c r="L172" s="27" t="n">
         <f aca="false">K172/SUMIF(A:A,A172,K:K)</f>
         <v>0.148148148148148</v>
       </c>
-      <c r="M172" s="1" t="n">
+      <c r="M172" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A172,J:J)*L172,0)</f>
         <v>474</v>
       </c>
@@ -17737,7 +17764,7 @@
       <c r="A173" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B173" s="27" t="s">
+      <c r="B173" s="30" t="s">
         <v>249</v>
       </c>
       <c r="C173" s="1" t="s">
@@ -17755,15 +17782,15 @@
       <c r="G173" s="1" t="n">
         <v>10149</v>
       </c>
-      <c r="H173" s="28" t="n">
+      <c r="H173" s="31" t="n">
         <f aca="false">ROUND(D173*IF(ISNUMBER(SEARCH("Labour",B173)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B173)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B173)),ISNUMBER(SEARCH("RefUK",B173))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B173)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B173)),ISNUMBER(SEARCH("Lib Dem",B173))),National!$L$8,National!$L$9))))),0)</f>
         <v>790</v>
       </c>
-      <c r="I173" s="25" t="n">
+      <c r="I173" s="27" t="n">
         <f aca="false">H173/SUMIFS(H:H,A:A,A173)</f>
         <v>0.149225538345297</v>
       </c>
-      <c r="J173" s="29" t="n">
+      <c r="J173" s="32" t="n">
         <f aca="false">ROUND(I173*SUMIF(A:A,A173,D:D),0)</f>
         <v>1355</v>
       </c>
@@ -17771,11 +17798,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A173,B:B,B173)/COUNTIFS(B:B,B173,A:A,A173),0)</f>
         <v>437</v>
       </c>
-      <c r="L173" s="25" t="n">
+      <c r="L173" s="27" t="n">
         <f aca="false">K173/SUMIF(A:A,A173,K:K)</f>
         <v>0.0969602840026625</v>
       </c>
-      <c r="M173" s="1" t="n">
+      <c r="M173" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A173,J:J)*L173,0)</f>
         <v>881</v>
       </c>
@@ -17796,7 +17823,7 @@
       <c r="A174" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B174" s="27" t="s">
+      <c r="B174" s="30" t="s">
         <v>249</v>
       </c>
       <c r="C174" s="1" t="s">
@@ -17814,15 +17841,15 @@
       <c r="G174" s="1" t="n">
         <v>10149</v>
       </c>
-      <c r="H174" s="28" t="n">
+      <c r="H174" s="31" t="n">
         <f aca="false">ROUND(D174*IF(ISNUMBER(SEARCH("Labour",B174)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B174)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B174)),ISNUMBER(SEARCH("RefUK",B174))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B174)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B174)),ISNUMBER(SEARCH("Lib Dem",B174))),National!$L$8,National!$L$9))))),0)</f>
         <v>782</v>
       </c>
-      <c r="I174" s="25" t="n">
+      <c r="I174" s="27" t="n">
         <f aca="false">H174/SUMIFS(H:H,A:A,A174)</f>
         <v>0.147714393653192</v>
       </c>
-      <c r="J174" s="29" t="n">
+      <c r="J174" s="32" t="n">
         <f aca="false">ROUND(I174*SUMIF(A:A,A174,D:D),0)</f>
         <v>1342</v>
       </c>
@@ -17830,11 +17857,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A174,B:B,B174)/COUNTIFS(B:B,B174,A:A,A174),0)</f>
         <v>437</v>
       </c>
-      <c r="L174" s="25" t="n">
+      <c r="L174" s="27" t="n">
         <f aca="false">K174/SUMIF(A:A,A174,K:K)</f>
         <v>0.0969602840026625</v>
       </c>
-      <c r="M174" s="1" t="n">
+      <c r="M174" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A174,J:J)*L174,0)</f>
         <v>881</v>
       </c>
@@ -17855,7 +17882,7 @@
       <c r="A175" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B175" s="27" t="s">
+      <c r="B175" s="30" t="s">
         <v>249</v>
       </c>
       <c r="C175" s="1" t="s">
@@ -17873,15 +17900,15 @@
       <c r="G175" s="1" t="n">
         <v>10149</v>
       </c>
-      <c r="H175" s="28" t="n">
+      <c r="H175" s="31" t="n">
         <f aca="false">ROUND(D175*IF(ISNUMBER(SEARCH("Labour",B175)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B175)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B175)),ISNUMBER(SEARCH("RefUK",B175))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B175)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B175)),ISNUMBER(SEARCH("Lib Dem",B175))),National!$L$8,National!$L$9))))),0)</f>
         <v>721</v>
       </c>
-      <c r="I175" s="25" t="n">
+      <c r="I175" s="27" t="n">
         <f aca="false">H175/SUMIFS(H:H,A:A,A175)</f>
         <v>0.136191915375897</v>
       </c>
-      <c r="J175" s="29" t="n">
+      <c r="J175" s="32" t="n">
         <f aca="false">ROUND(I175*SUMIF(A:A,A175,D:D),0)</f>
         <v>1237</v>
       </c>
@@ -17889,11 +17916,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A175,B:B,B175)/COUNTIFS(B:B,B175,A:A,A175),0)</f>
         <v>437</v>
       </c>
-      <c r="L175" s="25" t="n">
+      <c r="L175" s="27" t="n">
         <f aca="false">K175/SUMIF(A:A,A175,K:K)</f>
         <v>0.0969602840026625</v>
       </c>
-      <c r="M175" s="1" t="n">
+      <c r="M175" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A175,J:J)*L175,0)</f>
         <v>881</v>
       </c>
@@ -17914,7 +17941,7 @@
       <c r="A176" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B176" s="27" t="s">
+      <c r="B176" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C176" s="1" t="s">
@@ -17932,15 +17959,15 @@
       <c r="G176" s="1" t="n">
         <v>10149</v>
       </c>
-      <c r="H176" s="28" t="n">
+      <c r="H176" s="31" t="n">
         <f aca="false">ROUND(D176*IF(ISNUMBER(SEARCH("Labour",B176)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B176)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B176)),ISNUMBER(SEARCH("RefUK",B176))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B176)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B176)),ISNUMBER(SEARCH("Lib Dem",B176))),National!$L$8,National!$L$9))))),0)</f>
         <v>644</v>
       </c>
-      <c r="I176" s="25" t="n">
+      <c r="I176" s="27" t="n">
         <f aca="false">H176/SUMIFS(H:H,A:A,A176)</f>
         <v>0.121647147714394</v>
       </c>
-      <c r="J176" s="29" t="n">
+      <c r="J176" s="32" t="n">
         <f aca="false">ROUND(I176*SUMIF(A:A,A176,D:D),0)</f>
         <v>1105</v>
       </c>
@@ -17948,11 +17975,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A176,B:B,B176)/COUNTIFS(B:B,B176,A:A,A176),0)</f>
         <v>325</v>
       </c>
-      <c r="L176" s="25" t="n">
+      <c r="L176" s="27" t="n">
         <f aca="false">K176/SUMIF(A:A,A176,K:K)</f>
         <v>0.0721100510317284</v>
       </c>
-      <c r="M176" s="1" t="n">
+      <c r="M176" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A176,J:J)*L176,0)</f>
         <v>655</v>
       </c>
@@ -17973,7 +18000,7 @@
       <c r="A177" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B177" s="27" t="s">
+      <c r="B177" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C177" s="1" t="s">
@@ -17991,15 +18018,15 @@
       <c r="G177" s="1" t="n">
         <v>10149</v>
       </c>
-      <c r="H177" s="28" t="n">
+      <c r="H177" s="31" t="n">
         <f aca="false">ROUND(D177*IF(ISNUMBER(SEARCH("Labour",B177)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B177)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B177)),ISNUMBER(SEARCH("RefUK",B177))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B177)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B177)),ISNUMBER(SEARCH("Lib Dem",B177))),National!$L$8,National!$L$9))))),0)</f>
         <v>534</v>
       </c>
-      <c r="I177" s="25" t="n">
+      <c r="I177" s="27" t="n">
         <f aca="false">H177/SUMIFS(H:H,A:A,A177)</f>
         <v>0.10086890819796</v>
       </c>
-      <c r="J177" s="29" t="n">
+      <c r="J177" s="32" t="n">
         <f aca="false">ROUND(I177*SUMIF(A:A,A177,D:D),0)</f>
         <v>916</v>
       </c>
@@ -18007,11 +18034,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A177,B:B,B177)/COUNTIFS(B:B,B177,A:A,A177),0)</f>
         <v>325</v>
       </c>
-      <c r="L177" s="25" t="n">
+      <c r="L177" s="27" t="n">
         <f aca="false">K177/SUMIF(A:A,A177,K:K)</f>
         <v>0.0721100510317284</v>
       </c>
-      <c r="M177" s="1" t="n">
+      <c r="M177" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A177,J:J)*L177,0)</f>
         <v>655</v>
       </c>
@@ -18032,7 +18059,7 @@
       <c r="A178" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B178" s="27" t="s">
+      <c r="B178" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C178" s="1" t="s">
@@ -18050,15 +18077,15 @@
       <c r="G178" s="1" t="n">
         <v>10149</v>
       </c>
-      <c r="H178" s="28" t="n">
+      <c r="H178" s="31" t="n">
         <f aca="false">ROUND(D178*IF(ISNUMBER(SEARCH("Labour",B178)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B178)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B178)),ISNUMBER(SEARCH("RefUK",B178))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B178)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B178)),ISNUMBER(SEARCH("Lib Dem",B178))),National!$L$8,National!$L$9))))),0)</f>
         <v>528</v>
       </c>
-      <c r="I178" s="25" t="n">
+      <c r="I178" s="27" t="n">
         <f aca="false">H178/SUMIFS(H:H,A:A,A178)</f>
         <v>0.0997355496788818</v>
       </c>
-      <c r="J178" s="29" t="n">
+      <c r="J178" s="32" t="n">
         <f aca="false">ROUND(I178*SUMIF(A:A,A178,D:D),0)</f>
         <v>906</v>
       </c>
@@ -18066,11 +18093,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A178,B:B,B178)/COUNTIFS(B:B,B178,A:A,A178),0)</f>
         <v>325</v>
       </c>
-      <c r="L178" s="25" t="n">
+      <c r="L178" s="27" t="n">
         <f aca="false">K178/SUMIF(A:A,A178,K:K)</f>
         <v>0.0721100510317284</v>
       </c>
-      <c r="M178" s="1" t="n">
+      <c r="M178" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A178,J:J)*L178,0)</f>
         <v>655</v>
       </c>
@@ -18091,7 +18118,7 @@
       <c r="A179" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B179" s="30" t="s">
+      <c r="B179" s="33" t="s">
         <v>219</v>
       </c>
       <c r="C179" s="1" t="s">
@@ -18109,15 +18136,15 @@
       <c r="G179" s="1" t="n">
         <v>10149</v>
       </c>
-      <c r="H179" s="28" t="n">
+      <c r="H179" s="31" t="n">
         <f aca="false">ROUND(D179*IF(ISNUMBER(SEARCH("Labour",B179)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B179)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B179)),ISNUMBER(SEARCH("RefUK",B179))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B179)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B179)),ISNUMBER(SEARCH("Lib Dem",B179))),National!$L$8,National!$L$9))))),0)</f>
         <v>857</v>
       </c>
-      <c r="I179" s="25" t="n">
+      <c r="I179" s="27" t="n">
         <f aca="false">H179/SUMIFS(H:H,A:A,A179)</f>
         <v>0.16188137514167</v>
       </c>
-      <c r="J179" s="29" t="n">
+      <c r="J179" s="32" t="n">
         <f aca="false">ROUND(I179*SUMIF(A:A,A179,D:D),0)</f>
         <v>1470</v>
       </c>
@@ -18125,11 +18152,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A179,B:B,B179)/COUNTIFS(B:B,B179,A:A,A179),0)</f>
         <v>1470</v>
       </c>
-      <c r="L179" s="25" t="n">
+      <c r="L179" s="27" t="n">
         <f aca="false">K179/SUMIF(A:A,A179,K:K)</f>
         <v>0.32615930774351</v>
       </c>
-      <c r="M179" s="1" t="n">
+      <c r="M179" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A179,J:J)*L179,0)</f>
         <v>2962</v>
       </c>
@@ -18150,7 +18177,7 @@
       <c r="A180" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B180" s="27" t="s">
+      <c r="B180" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C180" s="1" t="s">
@@ -18168,15 +18195,15 @@
       <c r="G180" s="1" t="n">
         <v>10149</v>
       </c>
-      <c r="H180" s="28" t="n">
+      <c r="H180" s="31" t="n">
         <f aca="false">ROUND(D180*IF(ISNUMBER(SEARCH("Labour",B180)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B180)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B180)),ISNUMBER(SEARCH("RefUK",B180))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B180)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B180)),ISNUMBER(SEARCH("Lib Dem",B180))),National!$L$8,National!$L$9))))),0)</f>
         <v>438</v>
       </c>
-      <c r="I180" s="25" t="n">
+      <c r="I180" s="27" t="n">
         <f aca="false">H180/SUMIFS(H:H,A:A,A180)</f>
         <v>0.0827351718927087</v>
       </c>
-      <c r="J180" s="29" t="n">
+      <c r="J180" s="32" t="n">
         <f aca="false">ROUND(I180*SUMIF(A:A,A180,D:D),0)</f>
         <v>751</v>
       </c>
@@ -18184,11 +18211,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A180,B:B,B180)/COUNTIFS(B:B,B180,A:A,A180),0)</f>
         <v>751</v>
       </c>
-      <c r="L180" s="25" t="n">
+      <c r="L180" s="27" t="n">
         <f aca="false">K180/SUMIF(A:A,A180,K:K)</f>
         <v>0.166629687153317</v>
       </c>
-      <c r="M180" s="1" t="n">
+      <c r="M180" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A180,J:J)*L180,0)</f>
         <v>1513</v>
       </c>
@@ -18209,7 +18236,7 @@
       <c r="A181" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B181" s="27" t="s">
+      <c r="B181" s="30" t="s">
         <v>249</v>
       </c>
       <c r="C181" s="1" t="s">
@@ -18227,15 +18254,15 @@
       <c r="G181" s="1" t="n">
         <v>7143</v>
       </c>
-      <c r="H181" s="28" t="n">
+      <c r="H181" s="31" t="n">
         <f aca="false">ROUND(D181*IF(ISNUMBER(SEARCH("Labour",B181)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B181)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B181)),ISNUMBER(SEARCH("RefUK",B181))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B181)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B181)),ISNUMBER(SEARCH("Lib Dem",B181))),National!$L$8,National!$L$9))))),0)</f>
         <v>390</v>
       </c>
-      <c r="I181" s="25" t="n">
+      <c r="I181" s="27" t="n">
         <f aca="false">H181/SUMIFS(H:H,A:A,A181)</f>
         <v>0.173487544483986</v>
       </c>
-      <c r="J181" s="29" t="n">
+      <c r="J181" s="32" t="n">
         <f aca="false">ROUND(I181*SUMIF(A:A,A181,D:D),0)</f>
         <v>641</v>
       </c>
@@ -18243,11 +18270,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A181,B:B,B181)/COUNTIFS(B:B,B181,A:A,A181),0)</f>
         <v>309</v>
       </c>
-      <c r="L181" s="25" t="n">
+      <c r="L181" s="27" t="n">
         <f aca="false">K181/SUMIF(A:A,A181,K:K)</f>
         <v>0.13570487483531</v>
       </c>
-      <c r="M181" s="1" t="n">
+      <c r="M181" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A181,J:J)*L181,0)</f>
         <v>501</v>
       </c>
@@ -18268,7 +18295,7 @@
       <c r="A182" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B182" s="27" t="s">
+      <c r="B182" s="30" t="s">
         <v>249</v>
       </c>
       <c r="C182" s="1" t="s">
@@ -18286,15 +18313,15 @@
       <c r="G182" s="1" t="n">
         <v>7143</v>
       </c>
-      <c r="H182" s="28" t="n">
+      <c r="H182" s="31" t="n">
         <f aca="false">ROUND(D182*IF(ISNUMBER(SEARCH("Labour",B182)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B182)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B182)),ISNUMBER(SEARCH("RefUK",B182))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B182)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B182)),ISNUMBER(SEARCH("Lib Dem",B182))),National!$L$8,National!$L$9))))),0)</f>
         <v>362</v>
       </c>
-      <c r="I182" s="25" t="n">
+      <c r="I182" s="27" t="n">
         <f aca="false">H182/SUMIFS(H:H,A:A,A182)</f>
         <v>0.161032028469751</v>
       </c>
-      <c r="J182" s="29" t="n">
+      <c r="J182" s="32" t="n">
         <f aca="false">ROUND(I182*SUMIF(A:A,A182,D:D),0)</f>
         <v>595</v>
       </c>
@@ -18302,11 +18329,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A182,B:B,B182)/COUNTIFS(B:B,B182,A:A,A182),0)</f>
         <v>309</v>
       </c>
-      <c r="L182" s="25" t="n">
+      <c r="L182" s="27" t="n">
         <f aca="false">K182/SUMIF(A:A,A182,K:K)</f>
         <v>0.13570487483531</v>
       </c>
-      <c r="M182" s="1" t="n">
+      <c r="M182" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A182,J:J)*L182,0)</f>
         <v>501</v>
       </c>
@@ -18327,7 +18354,7 @@
       <c r="A183" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B183" s="27" t="s">
+      <c r="B183" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C183" s="1" t="s">
@@ -18345,15 +18372,15 @@
       <c r="G183" s="1" t="n">
         <v>7143</v>
       </c>
-      <c r="H183" s="28" t="n">
+      <c r="H183" s="31" t="n">
         <f aca="false">ROUND(D183*IF(ISNUMBER(SEARCH("Labour",B183)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B183)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B183)),ISNUMBER(SEARCH("RefUK",B183))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B183)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B183)),ISNUMBER(SEARCH("Lib Dem",B183))),National!$L$8,National!$L$9))))),0)</f>
         <v>522</v>
       </c>
-      <c r="I183" s="25" t="n">
+      <c r="I183" s="27" t="n">
         <f aca="false">H183/SUMIFS(H:H,A:A,A183)</f>
         <v>0.23220640569395</v>
       </c>
-      <c r="J183" s="29" t="n">
+      <c r="J183" s="32" t="n">
         <f aca="false">ROUND(I183*SUMIF(A:A,A183,D:D),0)</f>
         <v>857</v>
       </c>
@@ -18361,11 +18388,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A183,B:B,B183)/COUNTIFS(B:B,B183,A:A,A183),0)</f>
         <v>400</v>
       </c>
-      <c r="L183" s="25" t="n">
+      <c r="L183" s="27" t="n">
         <f aca="false">K183/SUMIF(A:A,A183,K:K)</f>
         <v>0.175669740887132</v>
       </c>
-      <c r="M183" s="1" t="n">
+      <c r="M183" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A183,J:J)*L183,0)</f>
         <v>649</v>
       </c>
@@ -18386,7 +18413,7 @@
       <c r="A184" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B184" s="27" t="s">
+      <c r="B184" s="30" t="s">
         <v>241</v>
       </c>
       <c r="C184" s="1" t="s">
@@ -18404,15 +18431,15 @@
       <c r="G184" s="1" t="n">
         <v>7143</v>
       </c>
-      <c r="H184" s="28" t="n">
+      <c r="H184" s="31" t="n">
         <f aca="false">ROUND(D184*IF(ISNUMBER(SEARCH("Labour",B184)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B184)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B184)),ISNUMBER(SEARCH("RefUK",B184))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B184)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B184)),ISNUMBER(SEARCH("Lib Dem",B184))),National!$L$8,National!$L$9))))),0)</f>
         <v>451</v>
       </c>
-      <c r="I184" s="25" t="n">
+      <c r="I184" s="27" t="n">
         <f aca="false">H184/SUMIFS(H:H,A:A,A184)</f>
         <v>0.200622775800712</v>
       </c>
-      <c r="J184" s="29" t="n">
+      <c r="J184" s="32" t="n">
         <f aca="false">ROUND(I184*SUMIF(A:A,A184,D:D),0)</f>
         <v>741</v>
       </c>
@@ -18420,11 +18447,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A184,B:B,B184)/COUNTIFS(B:B,B184,A:A,A184),0)</f>
         <v>400</v>
       </c>
-      <c r="L184" s="25" t="n">
+      <c r="L184" s="27" t="n">
         <f aca="false">K184/SUMIF(A:A,A184,K:K)</f>
         <v>0.175669740887132</v>
       </c>
-      <c r="M184" s="1" t="n">
+      <c r="M184" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A184,J:J)*L184,0)</f>
         <v>649</v>
       </c>
@@ -18445,7 +18472,7 @@
       <c r="A185" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B185" s="30" t="s">
+      <c r="B185" s="33" t="s">
         <v>219</v>
       </c>
       <c r="C185" s="1" t="s">
@@ -18463,15 +18490,15 @@
       <c r="G185" s="1" t="n">
         <v>7143</v>
       </c>
-      <c r="H185" s="28" t="n">
+      <c r="H185" s="31" t="n">
         <f aca="false">ROUND(D185*IF(ISNUMBER(SEARCH("Labour",B185)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B185)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B185)),ISNUMBER(SEARCH("RefUK",B185))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B185)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B185)),ISNUMBER(SEARCH("Lib Dem",B185))),National!$L$8,National!$L$9))))),0)</f>
         <v>287</v>
       </c>
-      <c r="I185" s="25" t="n">
+      <c r="I185" s="27" t="n">
         <f aca="false">H185/SUMIFS(H:H,A:A,A185)</f>
         <v>0.127669039145907</v>
       </c>
-      <c r="J185" s="29" t="n">
+      <c r="J185" s="32" t="n">
         <f aca="false">ROUND(I185*SUMIF(A:A,A185,D:D),0)</f>
         <v>471</v>
       </c>
@@ -18479,11 +18506,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A185,B:B,B185)/COUNTIFS(B:B,B185,A:A,A185),0)</f>
         <v>471</v>
       </c>
-      <c r="L185" s="25" t="n">
+      <c r="L185" s="27" t="n">
         <f aca="false">K185/SUMIF(A:A,A185,K:K)</f>
         <v>0.206851119894598</v>
       </c>
-      <c r="M185" s="1" t="n">
+      <c r="M185" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A185,J:J)*L185,0)</f>
         <v>764</v>
       </c>
@@ -18504,7 +18531,7 @@
       <c r="A186" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B186" s="27" t="s">
+      <c r="B186" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C186" s="1" t="s">
@@ -18522,15 +18549,15 @@
       <c r="G186" s="1" t="n">
         <v>7143</v>
       </c>
-      <c r="H186" s="28" t="n">
+      <c r="H186" s="31" t="n">
         <f aca="false">ROUND(D186*IF(ISNUMBER(SEARCH("Labour",B186)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B186)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B186)),ISNUMBER(SEARCH("RefUK",B186))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B186)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B186)),ISNUMBER(SEARCH("Lib Dem",B186))),National!$L$8,National!$L$9))))),0)</f>
         <v>151</v>
       </c>
-      <c r="I186" s="25" t="n">
+      <c r="I186" s="27" t="n">
         <f aca="false">H186/SUMIFS(H:H,A:A,A186)</f>
         <v>0.0671708185053381</v>
       </c>
-      <c r="J186" s="29" t="n">
+      <c r="J186" s="32" t="n">
         <f aca="false">ROUND(I186*SUMIF(A:A,A186,D:D),0)</f>
         <v>248</v>
       </c>
@@ -18538,11 +18565,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A186,B:B,B186)/COUNTIFS(B:B,B186,A:A,A186),0)</f>
         <v>248</v>
       </c>
-      <c r="L186" s="25" t="n">
+      <c r="L186" s="27" t="n">
         <f aca="false">K186/SUMIF(A:A,A186,K:K)</f>
         <v>0.108915239350022</v>
       </c>
-      <c r="M186" s="1" t="n">
+      <c r="M186" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A186,J:J)*L186,0)</f>
         <v>402</v>
       </c>
@@ -18563,7 +18590,7 @@
       <c r="A187" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B187" s="27" t="s">
+      <c r="B187" s="30" t="s">
         <v>297</v>
       </c>
       <c r="C187" s="1" t="s">
@@ -18581,15 +18608,15 @@
       <c r="G187" s="1" t="n">
         <v>7143</v>
       </c>
-      <c r="H187" s="28" t="n">
+      <c r="H187" s="31" t="n">
         <f aca="false">ROUND(D187*IF(ISNUMBER(SEARCH("Labour",B187)),National!$L$4,IF(ISNUMBER(SEARCH("Conservative",B187)),National!$L$5,IF(OR(ISNUMBER(SEARCH("Reform",B187)),ISNUMBER(SEARCH("RefUK",B187))),National!$L$6,IF(ISNUMBER(SEARCH("Green",B187)),National!$L$7,IF(OR(ISNUMBER(SEARCH("Liberal Democrat",B187)),ISNUMBER(SEARCH("Lib Dem",B187))),National!$L$8,National!$L$9))))),0)</f>
         <v>85</v>
       </c>
-      <c r="I187" s="25" t="n">
+      <c r="I187" s="27" t="n">
         <f aca="false">H187/SUMIFS(H:H,A:A,A187)</f>
         <v>0.0378113879003559</v>
       </c>
-      <c r="J187" s="29" t="n">
+      <c r="J187" s="32" t="n">
         <f aca="false">ROUND(I187*SUMIF(A:A,A187,D:D),0)</f>
         <v>140</v>
       </c>
@@ -18597,11 +18624,11 @@
         <f aca="false">ROUND(AVERAGEIFS(J:J,A:A,A187,B:B,B187)/COUNTIFS(B:B,B187,A:A,A187),0)</f>
         <v>140</v>
       </c>
-      <c r="L187" s="25" t="n">
+      <c r="L187" s="27" t="n">
         <f aca="false">K187/SUMIF(A:A,A187,K:K)</f>
         <v>0.0614844093104963</v>
       </c>
-      <c r="M187" s="1" t="n">
+      <c r="M187" s="29" t="n">
         <f aca="false">ROUND(SUMIF(A:A,A187,J:J)*L187,0)</f>
         <v>227</v>
       </c>
@@ -18829,7 +18856,7 @@
   <dimension ref="A1:D145"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="4" style="33" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="4" style="36" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18842,7 +18869,7 @@
       <c r="C1" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="36" t="s">
         <v>435</v>
       </c>
     </row>
@@ -18856,7 +18883,7 @@
       <c r="C2" s="24" t="n">
         <v>360.527946808952</v>
       </c>
-      <c r="D2" s="33" t="n">
+      <c r="D2" s="36" t="n">
         <v>0.185718120905711</v>
       </c>
     </row>
@@ -18870,7 +18897,7 @@
       <c r="C3" s="24" t="n">
         <v>338.19781283489</v>
       </c>
-      <c r="D3" s="33" t="n">
+      <c r="D3" s="36" t="n">
         <v>0.174215238652222</v>
       </c>
     </row>
@@ -18884,7 +18911,7 @@
       <c r="C4" s="24" t="n">
         <v>352.807231473231</v>
       </c>
-      <c r="D4" s="33" t="n">
+      <c r="D4" s="36" t="n">
         <v>0.18174096252759</v>
       </c>
     </row>
@@ -18898,7 +18925,7 @@
       <c r="C5" s="24" t="n">
         <v>287.814156900925</v>
       </c>
-      <c r="D5" s="33" t="n">
+      <c r="D5" s="36" t="n">
         <v>0.148261195457412</v>
       </c>
     </row>
@@ -18912,7 +18939,7 @@
       <c r="C6" s="24" t="n">
         <v>126.560809724739</v>
       </c>
-      <c r="D6" s="33" t="n">
+      <c r="D6" s="36" t="n">
         <v>0.0651950451287457</v>
       </c>
     </row>
@@ -18926,7 +18953,7 @@
       <c r="C7" s="24" t="n">
         <v>475.356282121029</v>
       </c>
-      <c r="D7" s="33" t="n">
+      <c r="D7" s="36" t="n">
         <v>0.24486943732832</v>
       </c>
     </row>
@@ -18940,7 +18967,7 @@
       <c r="C8" s="24" t="n">
         <v>1165.97888283737</v>
       </c>
-      <c r="D8" s="33" t="n">
+      <c r="D8" s="36" t="n">
         <v>0.156273354961736</v>
       </c>
     </row>
@@ -18954,7 +18981,7 @@
       <c r="C9" s="24" t="n">
         <v>1634.60572548016</v>
       </c>
-      <c r="D9" s="33" t="n">
+      <c r="D9" s="36" t="n">
         <v>0.219082287441457</v>
       </c>
     </row>
@@ -18968,7 +18995,7 @@
       <c r="C10" s="24" t="n">
         <v>1489.2735865392</v>
       </c>
-      <c r="D10" s="33" t="n">
+      <c r="D10" s="36" t="n">
         <v>0.199603769202087</v>
       </c>
     </row>
@@ -18982,7 +19009,7 @@
       <c r="C11" s="24" t="n">
         <v>1155.96838469631</v>
       </c>
-      <c r="D11" s="33" t="n">
+      <c r="D11" s="36" t="n">
         <v>0.154931671889796</v>
       </c>
     </row>
@@ -18996,7 +19023,7 @@
       <c r="C12" s="24" t="n">
         <v>499.87533960075</v>
       </c>
-      <c r="D12" s="33" t="n">
+      <c r="D12" s="36" t="n">
         <v>0.0669970936282744</v>
       </c>
     </row>
@@ -19010,7 +19037,7 @@
       <c r="C13" s="24" t="n">
         <v>1515.44769987671</v>
       </c>
-      <c r="D13" s="33" t="n">
+      <c r="D13" s="36" t="n">
         <v>0.20311182287665</v>
       </c>
     </row>
@@ -19024,7 +19051,7 @@
       <c r="C14" s="24" t="n">
         <v>586.13211991833</v>
       </c>
-      <c r="D14" s="33" t="n">
+      <c r="D14" s="36" t="n">
         <v>0.17246006228266</v>
       </c>
     </row>
@@ -19038,7 +19065,7 @@
       <c r="C15" s="24" t="n">
         <v>651.614137203626</v>
       </c>
-      <c r="D15" s="33" t="n">
+      <c r="D15" s="36" t="n">
         <v>0.191727105318947</v>
       </c>
     </row>
@@ -19052,7 +19079,7 @@
       <c r="C16" s="24" t="n">
         <v>645.971188087718</v>
       </c>
-      <c r="D16" s="33" t="n">
+      <c r="D16" s="36" t="n">
         <v>0.190066757211556</v>
       </c>
     </row>
@@ -19066,7 +19093,7 @@
       <c r="C17" s="24" t="n">
         <v>511.697574922317</v>
       </c>
-      <c r="D17" s="33" t="n">
+      <c r="D17" s="36" t="n">
         <v>0.150558880228719</v>
       </c>
     </row>
@@ -19080,7 +19107,7 @@
       <c r="C18" s="24" t="n">
         <v>226.082278774795</v>
       </c>
-      <c r="D18" s="33" t="n">
+      <c r="D18" s="36" t="n">
         <v>0.0665211179417018</v>
       </c>
     </row>
@@ -19094,7 +19121,7 @@
       <c r="C19" s="24" t="n">
         <v>777.156929558383</v>
       </c>
-      <c r="D19" s="33" t="n">
+      <c r="D19" s="36" t="n">
         <v>0.228666077016416</v>
       </c>
     </row>
@@ -19108,7 +19135,7 @@
       <c r="C20" s="24" t="n">
         <v>356.867485268003</v>
       </c>
-      <c r="D20" s="33" t="n">
+      <c r="D20" s="36" t="n">
         <v>0.184523594210349</v>
       </c>
     </row>
@@ -19122,7 +19149,7 @@
       <c r="C21" s="24" t="n">
         <v>335.77479747641</v>
       </c>
-      <c r="D21" s="33" t="n">
+      <c r="D21" s="36" t="n">
         <v>0.17361730903859</v>
       </c>
     </row>
@@ -19136,7 +19163,7 @@
       <c r="C22" s="24" t="n">
         <v>354.806786697755</v>
       </c>
-      <c r="D22" s="33" t="n">
+      <c r="D22" s="36" t="n">
         <v>0.183458079635714</v>
       </c>
     </row>
@@ -19150,7 +19177,7 @@
       <c r="C23" s="24" t="n">
         <v>286.420370169987</v>
       </c>
-      <c r="D23" s="33" t="n">
+      <c r="D23" s="36" t="n">
         <v>0.148097874815168</v>
       </c>
     </row>
@@ -19164,7 +19191,7 @@
       <c r="C24" s="24" t="n">
         <v>127.516958873924</v>
       </c>
-      <c r="D24" s="33" t="n">
+      <c r="D24" s="36" t="n">
         <v>0.0659345234450797</v>
       </c>
     </row>
@@ -19178,7 +19205,7 @@
       <c r="C25" s="24" t="n">
         <v>472.607391279307</v>
       </c>
-      <c r="D25" s="33" t="n">
+      <c r="D25" s="36" t="n">
         <v>0.2443686188551</v>
       </c>
     </row>
@@ -19192,7 +19219,7 @@
       <c r="C26" s="24" t="n">
         <v>927.876080431862</v>
       </c>
-      <c r="D26" s="33" t="n">
+      <c r="D26" s="36" t="n">
         <v>0.169937764385988</v>
       </c>
     </row>
@@ -19206,7 +19233,7 @@
       <c r="C27" s="24" t="n">
         <v>1055.39261025115</v>
       </c>
-      <c r="D27" s="33" t="n">
+      <c r="D27" s="36" t="n">
         <v>0.19329204030359</v>
       </c>
     </row>
@@ -19220,7 +19247,7 @@
       <c r="C28" s="24" t="n">
         <v>1047.73938994028</v>
       </c>
-      <c r="D28" s="33" t="n">
+      <c r="D28" s="36" t="n">
         <v>0.191890375601361</v>
       </c>
     </row>
@@ -19234,7 +19261,7 @@
       <c r="C29" s="24" t="n">
         <v>824.386274452057</v>
       </c>
-      <c r="D29" s="33" t="n">
+      <c r="D29" s="36" t="n">
         <v>0.150983911995739</v>
       </c>
     </row>
@@ -19248,7 +19275,7 @@
       <c r="C30" s="24" t="n">
         <v>366.160706967011</v>
       </c>
-      <c r="D30" s="33" t="n">
+      <c r="D30" s="36" t="n">
         <v>0.0670612523161555</v>
       </c>
     </row>
@@ -19262,7 +19289,7 @@
       <c r="C31" s="24" t="n">
         <v>1238.53842444329</v>
       </c>
-      <c r="D31" s="33" t="n">
+      <c r="D31" s="36" t="n">
         <v>0.226834655397167</v>
       </c>
     </row>
@@ -19276,7 +19303,7 @@
       <c r="C32" s="24" t="n">
         <v>963.414885197876</v>
       </c>
-      <c r="D32" s="33" t="n">
+      <c r="D32" s="36" t="n">
         <v>0.15783918755408</v>
       </c>
     </row>
@@ -19290,7 +19317,7 @@
       <c r="C33" s="24" t="n">
         <v>1314.09086272256</v>
       </c>
-      <c r="D33" s="33" t="n">
+      <c r="D33" s="36" t="n">
         <v>0.215291498326568</v>
       </c>
     </row>
@@ -19304,7 +19331,7 @@
       <c r="C34" s="24" t="n">
         <v>1209.9214248615</v>
       </c>
-      <c r="D34" s="33" t="n">
+      <c r="D34" s="36" t="n">
         <v>0.1982251028488</v>
       </c>
     </row>
@@ -19318,7 +19345,7 @@
       <c r="C35" s="24" t="n">
         <v>940.825338747684</v>
       </c>
-      <c r="D35" s="33" t="n">
+      <c r="D35" s="36" t="n">
         <v>0.15413827353075</v>
       </c>
     </row>
@@ -19332,7 +19359,7 @@
       <c r="C36" s="24" t="n">
         <v>408.86854434517</v>
       </c>
-      <c r="D36" s="33" t="n">
+      <c r="D36" s="36" t="n">
         <v>0.0669861757871906</v>
       </c>
     </row>
@@ -19346,7 +19373,7 @@
       <c r="C37" s="24" t="n">
         <v>1266.65393262598</v>
       </c>
-      <c r="D37" s="33" t="n">
+      <c r="D37" s="36" t="n">
         <v>0.207519761952612</v>
       </c>
     </row>
@@ -19360,7 +19387,7 @@
       <c r="C38" s="24" t="n">
         <v>1183.23643253647</v>
       </c>
-      <c r="D38" s="33" t="n">
+      <c r="D38" s="36" t="n">
         <v>0.157133695010925</v>
       </c>
     </row>
@@ -19374,7 +19401,7 @@
       <c r="C39" s="24" t="n">
         <v>1620.33580204033</v>
       </c>
-      <c r="D39" s="33" t="n">
+      <c r="D39" s="36" t="n">
         <v>0.215180453146872</v>
       </c>
     </row>
@@ -19388,7 +19415,7 @@
       <c r="C40" s="24" t="n">
         <v>1497.92000030454</v>
       </c>
-      <c r="D40" s="33" t="n">
+      <c r="D40" s="36" t="n">
         <v>0.198923645356366</v>
       </c>
     </row>
@@ -19402,7 +19429,7 @@
       <c r="C41" s="24" t="n">
         <v>1159.47102047941</v>
       </c>
-      <c r="D41" s="33" t="n">
+      <c r="D41" s="36" t="n">
         <v>0.153977650363129</v>
       </c>
     </row>
@@ -19416,7 +19443,7 @@
       <c r="C42" s="24" t="n">
         <v>506.434288887098</v>
       </c>
-      <c r="D42" s="33" t="n">
+      <c r="D42" s="36" t="n">
         <v>0.0672544293810078</v>
       </c>
     </row>
@@ -19430,7 +19457,7 @@
       <c r="C43" s="24" t="n">
         <v>1562.72788463747</v>
       </c>
-      <c r="D43" s="33" t="n">
+      <c r="D43" s="36" t="n">
         <v>0.2075301267417</v>
       </c>
     </row>
@@ -19444,7 +19471,7 @@
       <c r="C44" s="24" t="n">
         <v>774.051740319585</v>
       </c>
-      <c r="D44" s="33" t="n">
+      <c r="D44" s="36" t="n">
         <v>0.199608861507454</v>
       </c>
     </row>
@@ -19458,7 +19485,7 @@
       <c r="C45" s="24" t="n">
         <v>605.280671958169</v>
       </c>
-      <c r="D45" s="33" t="n">
+      <c r="D45" s="36" t="n">
         <v>0.156086963608083</v>
       </c>
     </row>
@@ -19472,7 +19499,7 @@
       <c r="C46" s="24" t="n">
         <v>679.760286129533</v>
       </c>
-      <c r="D46" s="33" t="n">
+      <c r="D46" s="36" t="n">
         <v>0.175293419993185</v>
       </c>
     </row>
@@ -19486,7 +19513,7 @@
       <c r="C47" s="24" t="n">
         <v>567.183123235218</v>
       </c>
-      <c r="D47" s="33" t="n">
+      <c r="D47" s="36" t="n">
         <v>0.146262544992768</v>
       </c>
     </row>
@@ -19500,7 +19527,7 @@
       <c r="C48" s="24" t="n">
         <v>249.48012705819</v>
       </c>
-      <c r="D48" s="33" t="n">
+      <c r="D48" s="36" t="n">
         <v>0.0643347744561103</v>
       </c>
     </row>
@@ -19514,7 +19541,7 @@
       <c r="C49" s="24" t="n">
         <v>1002.08662038124</v>
       </c>
-      <c r="D49" s="33" t="n">
+      <c r="D49" s="36" t="n">
         <v>0.2584134354424</v>
       </c>
     </row>
@@ -19528,7 +19555,7 @@
       <c r="C50" s="24" t="n">
         <v>1064.82790682281</v>
       </c>
-      <c r="D50" s="33" t="n">
+      <c r="D50" s="36" t="n">
         <v>0.176237470201896</v>
       </c>
     </row>
@@ -19542,7 +19569,7 @@
       <c r="C51" s="24" t="n">
         <v>1151.16797907744</v>
       </c>
-      <c r="D51" s="33" t="n">
+      <c r="D51" s="36" t="n">
         <v>0.190527437447971</v>
       </c>
     </row>
@@ -19556,7 +19583,7 @@
       <c r="C52" s="24" t="n">
         <v>1136.04419118881</v>
       </c>
-      <c r="D52" s="33" t="n">
+      <c r="D52" s="36" t="n">
         <v>0.188024330513711</v>
       </c>
     </row>
@@ -19570,7 +19597,7 @@
       <c r="C53" s="24" t="n">
         <v>911.292012530443</v>
       </c>
-      <c r="D53" s="33" t="n">
+      <c r="D53" s="36" t="n">
         <v>0.150826061070059</v>
       </c>
     </row>
@@ -19584,7 +19611,7 @@
       <c r="C54" s="24" t="n">
         <v>396.912215325491</v>
       </c>
-      <c r="D54" s="33" t="n">
+      <c r="D54" s="36" t="n">
         <v>0.0656921219597927</v>
       </c>
     </row>
@@ -19598,7 +19625,7 @@
       <c r="C55" s="24" t="n">
         <v>1381.7620039458</v>
       </c>
-      <c r="D55" s="33" t="n">
+      <c r="D55" s="36" t="n">
         <v>0.22869257880657</v>
       </c>
     </row>
@@ -19612,7 +19639,7 @@
       <c r="C56" s="24" t="n">
         <v>1079.26107575782</v>
       </c>
-      <c r="D56" s="33" t="n">
+      <c r="D56" s="36" t="n">
         <v>0.177160292553738</v>
       </c>
     </row>
@@ -19626,7 +19653,7 @@
       <c r="C57" s="24" t="n">
         <v>1130.68533485535</v>
       </c>
-      <c r="D57" s="33" t="n">
+      <c r="D57" s="36" t="n">
         <v>0.185601565004597</v>
       </c>
     </row>
@@ -19640,7 +19667,7 @@
       <c r="C58" s="24" t="n">
         <v>1142.34989312844</v>
       </c>
-      <c r="D58" s="33" t="n">
+      <c r="D58" s="36" t="n">
         <v>0.187516297781111</v>
       </c>
     </row>
@@ -19654,7 +19681,7 @@
       <c r="C59" s="24" t="n">
         <v>913.972731156138</v>
       </c>
-      <c r="D59" s="33" t="n">
+      <c r="D59" s="36" t="n">
         <v>0.150028274043022</v>
       </c>
     </row>
@@ -19668,7 +19695,7 @@
       <c r="C60" s="24" t="n">
         <v>402.946648964337</v>
       </c>
-      <c r="D60" s="33" t="n">
+      <c r="D60" s="36" t="n">
         <v>0.0661435382203011</v>
       </c>
     </row>
@@ -19682,7 +19709,7 @@
       <c r="C61" s="24" t="n">
         <v>1422.7875534347</v>
       </c>
-      <c r="D61" s="33" t="n">
+      <c r="D61" s="36" t="n">
         <v>0.233550032397231</v>
       </c>
     </row>
@@ -19696,7 +19723,7 @@
       <c r="C62" s="24" t="n">
         <v>705.247043665063</v>
       </c>
-      <c r="D62" s="33" t="n">
+      <c r="D62" s="36" t="n">
         <v>0.164095642649641</v>
       </c>
     </row>
@@ -19710,7 +19737,7 @@
       <c r="C63" s="24" t="n">
         <v>875.376093254611</v>
       </c>
-      <c r="D63" s="33" t="n">
+      <c r="D63" s="36" t="n">
         <v>0.203680970906653</v>
       </c>
     </row>
@@ -19724,7 +19751,7 @@
       <c r="C64" s="24" t="n">
         <v>835.262847506184</v>
       </c>
-      <c r="D64" s="33" t="n">
+      <c r="D64" s="36" t="n">
         <v>0.194347491384863</v>
       </c>
     </row>
@@ -19738,7 +19765,7 @@
       <c r="C65" s="24" t="n">
         <v>655.302020204681</v>
       </c>
-      <c r="D65" s="33" t="n">
+      <c r="D65" s="36" t="n">
         <v>0.152474522369163</v>
       </c>
     </row>
@@ -19752,7 +19779,7 @@
       <c r="C66" s="24" t="n">
         <v>287.305208518691</v>
       </c>
-      <c r="D66" s="33" t="n">
+      <c r="D66" s="36" t="n">
         <v>0.0668496709797681</v>
       </c>
     </row>
@@ -19766,7 +19793,7 @@
       <c r="C67" s="24" t="n">
         <v>939.287229265264</v>
       </c>
-      <c r="D67" s="33" t="n">
+      <c r="D67" s="36" t="n">
         <v>0.218551701709912</v>
       </c>
     </row>
@@ -19780,7 +19807,7 @@
       <c r="C68" s="24" t="n">
         <v>575.511084325886</v>
       </c>
-      <c r="D68" s="33" t="n">
+      <c r="D68" s="36" t="n">
         <v>0.169436031068668</v>
       </c>
     </row>
@@ -19794,7 +19821,7 @@
       <c r="C69" s="24" t="n">
         <v>668.926181742822</v>
       </c>
-      <c r="D69" s="33" t="n">
+      <c r="D69" s="36" t="n">
         <v>0.196938339502498</v>
       </c>
     </row>
@@ -19808,7 +19835,7 @@
       <c r="C70" s="24" t="n">
         <v>652.043040446558</v>
       </c>
-      <c r="D70" s="33" t="n">
+      <c r="D70" s="36" t="n">
         <v>0.191967779367133</v>
       </c>
     </row>
@@ -19822,7 +19849,7 @@
       <c r="C71" s="24" t="n">
         <v>514.71131115506</v>
       </c>
-      <c r="D71" s="33" t="n">
+      <c r="D71" s="36" t="n">
         <v>0.151535989633312</v>
       </c>
     </row>
@@ -19836,7 +19863,7 @@
       <c r="C72" s="24" t="n">
         <v>226.475737964202</v>
       </c>
-      <c r="D72" s="33" t="n">
+      <c r="D72" s="36" t="n">
         <v>0.0666766483202485</v>
       </c>
     </row>
@@ -19850,7 +19877,7 @@
       <c r="C73" s="24" t="n">
         <v>758.960154441223</v>
       </c>
-      <c r="D73" s="33" t="n">
+      <c r="D73" s="36" t="n">
         <v>0.223445212108141</v>
       </c>
     </row>
@@ -19864,7 +19891,7 @@
       <c r="C74" s="24" t="n">
         <v>1051.58537104833</v>
       </c>
-      <c r="D74" s="33" t="n">
+      <c r="D74" s="36" t="n">
         <v>0.181685051721868</v>
       </c>
     </row>
@@ -19878,7 +19905,7 @@
       <c r="C75" s="24" t="n">
         <v>1055.40054654156</v>
       </c>
-      <c r="D75" s="33" t="n">
+      <c r="D75" s="36" t="n">
         <v>0.182344209195811</v>
       </c>
     </row>
@@ -19892,7 +19919,7 @@
       <c r="C76" s="24" t="n">
         <v>1072.91329898334</v>
       </c>
-      <c r="D76" s="33" t="n">
+      <c r="D76" s="36" t="n">
         <v>0.185369931520197</v>
       </c>
     </row>
@@ -19906,7 +19933,7 @@
       <c r="C77" s="24" t="n">
         <v>866.65099212323</v>
       </c>
-      <c r="D77" s="33" t="n">
+      <c r="D77" s="36" t="n">
         <v>0.14973347353791</v>
       </c>
     </row>
@@ -19920,7 +19947,7 @@
       <c r="C78" s="24" t="n">
         <v>379.097338590059</v>
       </c>
-      <c r="D78" s="33" t="n">
+      <c r="D78" s="36" t="n">
         <v>0.0654976014935379</v>
       </c>
     </row>
@@ -19934,7 +19961,7 @@
       <c r="C79" s="24" t="n">
         <v>1362.31002589975</v>
       </c>
-      <c r="D79" s="33" t="n">
+      <c r="D79" s="36" t="n">
         <v>0.235369732530676</v>
       </c>
     </row>
@@ -19948,7 +19975,7 @@
       <c r="C80" s="24" t="n">
         <v>1010.19601513613</v>
       </c>
-      <c r="D80" s="33" t="n">
+      <c r="D80" s="36" t="n">
         <v>0.182342676869598</v>
       </c>
     </row>
@@ -19962,7 +19989,7 @@
       <c r="C81" s="24" t="n">
         <v>999.263903926681</v>
       </c>
-      <c r="D81" s="33" t="n">
+      <c r="D81" s="36" t="n">
         <v>0.180369405948014</v>
       </c>
     </row>
@@ -19976,7 +20003,7 @@
       <c r="C82" s="24" t="n">
         <v>1023.09508083479</v>
       </c>
-      <c r="D82" s="33" t="n">
+      <c r="D82" s="36" t="n">
         <v>0.184670987547296</v>
       </c>
     </row>
@@ -19990,7 +20017,7 @@
       <c r="C83" s="24" t="n">
         <v>827.143565066292</v>
       </c>
-      <c r="D83" s="33" t="n">
+      <c r="D83" s="36" t="n">
         <v>0.149301293560661</v>
       </c>
     </row>
@@ -20004,7 +20031,7 @@
       <c r="C84" s="24" t="n">
         <v>362.586101144983</v>
       </c>
-      <c r="D84" s="33" t="n">
+      <c r="D84" s="36" t="n">
         <v>0.065447615401232</v>
       </c>
     </row>
@@ -20018,7 +20045,7 @@
       <c r="C85" s="24" t="n">
         <v>1317.81177471817</v>
       </c>
-      <c r="D85" s="33" t="n">
+      <c r="D85" s="36" t="n">
         <v>0.237868020673199</v>
       </c>
     </row>
@@ -20032,7 +20059,7 @@
       <c r="C86" s="24" t="n">
         <v>801.484164854835</v>
       </c>
-      <c r="D86" s="33" t="n">
+      <c r="D86" s="36" t="n">
         <v>0.192848235535227</v>
       </c>
     </row>
@@ -20046,7 +20073,7 @@
       <c r="C87" s="24" t="n">
         <v>688.893018071589</v>
       </c>
-      <c r="D87" s="33" t="n">
+      <c r="D87" s="36" t="n">
         <v>0.165757239922145</v>
       </c>
     </row>
@@ -20060,7 +20087,7 @@
       <c r="C88" s="24" t="n">
         <v>741.397798595303</v>
       </c>
-      <c r="D88" s="33" t="n">
+      <c r="D88" s="36" t="n">
         <v>0.178390620249749</v>
       </c>
     </row>
@@ -20074,7 +20101,7 @@
       <c r="C89" s="24" t="n">
         <v>613.848971549703</v>
       </c>
-      <c r="D89" s="33" t="n">
+      <c r="D89" s="36" t="n">
         <v>0.147700598763439</v>
       </c>
     </row>
@@ -20088,7 +20115,7 @@
       <c r="C90" s="24" t="n">
         <v>268.615081178121</v>
       </c>
-      <c r="D90" s="33" t="n">
+      <c r="D90" s="36" t="n">
         <v>0.0646325239036191</v>
       </c>
     </row>
@@ -20102,7 +20129,7 @@
       <c r="C91" s="24" t="n">
         <v>1041.79673465656</v>
       </c>
-      <c r="D91" s="33" t="n">
+      <c r="D91" s="36" t="n">
         <v>0.250670781625821</v>
       </c>
     </row>
@@ -20116,7 +20143,7 @@
       <c r="C92" s="24" t="n">
         <v>906.274586364994</v>
       </c>
-      <c r="D92" s="33" t="n">
+      <c r="D92" s="36" t="n">
         <v>0.172973089983962</v>
       </c>
     </row>
@@ -20130,7 +20157,7 @@
       <c r="C93" s="24" t="n">
         <v>1014.40764453746</v>
       </c>
-      <c r="D93" s="33" t="n">
+      <c r="D93" s="36" t="n">
         <v>0.193611547117057</v>
       </c>
     </row>
@@ -20144,7 +20171,7 @@
       <c r="C94" s="24" t="n">
         <v>996.394277828526</v>
       </c>
-      <c r="D94" s="33" t="n">
+      <c r="D94" s="36" t="n">
         <v>0.190173485686739</v>
       </c>
     </row>
@@ -20158,7 +20185,7 @@
       <c r="C95" s="24" t="n">
         <v>792.56546407976</v>
       </c>
-      <c r="D95" s="33" t="n">
+      <c r="D95" s="36" t="n">
         <v>0.1512703758872</v>
       </c>
     </row>
@@ -20172,7 +20199,7 @@
       <c r="C96" s="24" t="n">
         <v>347.471736083945</v>
       </c>
-      <c r="D96" s="33" t="n">
+      <c r="D96" s="36" t="n">
         <v>0.0663190392589535</v>
       </c>
     </row>
@@ -20186,7 +20213,7 @@
       <c r="C97" s="24" t="n">
         <v>1182.28269923459</v>
       </c>
-      <c r="D97" s="33" t="n">
+      <c r="D97" s="36" t="n">
         <v>0.225652462066088</v>
       </c>
     </row>
@@ -20200,7 +20227,7 @@
       <c r="C98" s="24" t="n">
         <v>918.909442370645</v>
       </c>
-      <c r="D98" s="33" t="n">
+      <c r="D98" s="36" t="n">
         <v>0.17361602733954</v>
       </c>
     </row>
@@ -20214,7 +20241,7 @@
       <c r="C99" s="24" t="n">
         <v>977.505374703948</v>
       </c>
-      <c r="D99" s="33" t="n">
+      <c r="D99" s="36" t="n">
         <v>0.18468696917655</v>
       </c>
     </row>
@@ -20228,7 +20255,7 @@
       <c r="C100" s="24" t="n">
         <v>1007.823321219</v>
       </c>
-      <c r="D100" s="33" t="n">
+      <c r="D100" s="36" t="n">
         <v>0.19041515215991</v>
       </c>
     </row>
@@ -20242,7 +20269,7 @@
       <c r="C101" s="24" t="n">
         <v>794.485876495925</v>
       </c>
-      <c r="D101" s="33" t="n">
+      <c r="D101" s="36" t="n">
         <v>0.15010780746658</v>
       </c>
     </row>
@@ -20256,7 +20283,7 @@
       <c r="C102" s="24" t="n">
         <v>355.940444731023</v>
       </c>
-      <c r="D102" s="33" t="n">
+      <c r="D102" s="36" t="n">
         <v>0.067250332986287</v>
       </c>
     </row>
@@ -20270,7 +20297,7 @@
       <c r="C103" s="24" t="n">
         <v>1238.10405069044</v>
       </c>
-      <c r="D103" s="33" t="n">
+      <c r="D103" s="36" t="n">
         <v>0.233923710871134</v>
       </c>
     </row>
@@ -20284,7 +20311,7 @@
       <c r="C104" s="24" t="n">
         <v>301.84680738326</v>
       </c>
-      <c r="D104" s="33" t="n">
+      <c r="D104" s="36" t="n">
         <v>0.169627181575755</v>
       </c>
     </row>
@@ -20298,7 +20325,7 @@
       <c r="C105" s="24" t="n">
         <v>336.46381984861</v>
       </c>
-      <c r="D105" s="33" t="n">
+      <c r="D105" s="36" t="n">
         <v>0.189080712689683</v>
       </c>
     </row>
@@ -20312,7 +20339,7 @@
       <c r="C106" s="24" t="n">
         <v>341.794911991461</v>
       </c>
-      <c r="D106" s="33" t="n">
+      <c r="D106" s="36" t="n">
         <v>0.192076597068093</v>
       </c>
     </row>
@@ -20326,7 +20353,7 @@
       <c r="C107" s="24" t="n">
         <v>267.640765195637</v>
       </c>
-      <c r="D107" s="33" t="n">
+      <c r="D107" s="36" t="n">
         <v>0.150404601156739</v>
       </c>
     </row>
@@ -20340,7 +20367,7 @@
       <c r="C108" s="24" t="n">
         <v>120.698583598033</v>
       </c>
-      <c r="D108" s="33" t="n">
+      <c r="D108" s="36" t="n">
         <v>0.0678283157387321</v>
       </c>
     </row>
@@ -20354,7 +20381,7 @@
       <c r="C109" s="24" t="n">
         <v>411.027037291483</v>
       </c>
-      <c r="D109" s="33" t="n">
+      <c r="D109" s="36" t="n">
         <v>0.230982591770999</v>
       </c>
     </row>
@@ -20368,7 +20395,7 @@
       <c r="C110" s="24" t="n">
         <v>1082.95998530472</v>
       </c>
-      <c r="D110" s="33" t="n">
+      <c r="D110" s="36" t="n">
         <v>0.174085252955782</v>
       </c>
     </row>
@@ -20382,7 +20409,7 @@
       <c r="C111" s="24" t="n">
         <v>1181.14481360215</v>
       </c>
-      <c r="D111" s="33" t="n">
+      <c r="D111" s="36" t="n">
         <v>0.189868412908612</v>
       </c>
     </row>
@@ -20396,7 +20423,7 @@
       <c r="C112" s="24" t="n">
         <v>1177.36434855757</v>
       </c>
-      <c r="D112" s="33" t="n">
+      <c r="D112" s="36" t="n">
         <v>0.189260705123923</v>
       </c>
     </row>
@@ -20410,7 +20437,7 @@
       <c r="C113" s="24" t="n">
         <v>936.806927201351</v>
       </c>
-      <c r="D113" s="33" t="n">
+      <c r="D113" s="36" t="n">
         <v>0.150591225073462</v>
       </c>
     </row>
@@ -20424,7 +20451,7 @@
       <c r="C114" s="24" t="n">
         <v>412.695996292608</v>
       </c>
-      <c r="D114" s="33" t="n">
+      <c r="D114" s="36" t="n">
         <v>0.0663406662142019</v>
       </c>
     </row>
@@ -20438,7 +20465,7 @@
       <c r="C115" s="24" t="n">
         <v>1429.88792101227</v>
       </c>
-      <c r="D115" s="33" t="n">
+      <c r="D115" s="36" t="n">
         <v>0.229853737724019</v>
       </c>
     </row>
@@ -20452,7 +20479,7 @@
       <c r="C116" s="24" t="n">
         <v>1015.3552419376</v>
       </c>
-      <c r="D116" s="33" t="n">
+      <c r="D116" s="36" t="n">
         <v>0.180493693018285</v>
       </c>
     </row>
@@ -20466,7 +20493,7 @@
       <c r="C117" s="24" t="n">
         <v>1015.84508269471</v>
       </c>
-      <c r="D117" s="33" t="n">
+      <c r="D117" s="36" t="n">
         <v>0.180580769111056</v>
       </c>
     </row>
@@ -20480,7 +20507,7 @@
       <c r="C118" s="24" t="n">
         <v>1041.1002150389</v>
       </c>
-      <c r="D118" s="33" t="n">
+      <c r="D118" s="36" t="n">
         <v>0.185070224541227</v>
       </c>
     </row>
@@ -20494,7 +20521,7 @@
       <c r="C119" s="24" t="n">
         <v>839.119507246155</v>
       </c>
-      <c r="D119" s="33" t="n">
+      <c r="D119" s="36" t="n">
         <v>0.149165309333037</v>
       </c>
     </row>
@@ -20508,7 +20535,7 @@
       <c r="C120" s="24" t="n">
         <v>370.550270275282</v>
       </c>
-      <c r="D120" s="33" t="n">
+      <c r="D120" s="36" t="n">
         <v>0.0658705288242554</v>
       </c>
     </row>
@@ -20522,7 +20549,7 @@
       <c r="C121" s="24" t="n">
         <v>1343.46304260201</v>
       </c>
-      <c r="D121" s="33" t="n">
+      <c r="D121" s="36" t="n">
         <v>0.23881947517214</v>
       </c>
     </row>
@@ -20536,7 +20563,7 @@
       <c r="C122" s="24" t="n">
         <v>977.552875260162</v>
       </c>
-      <c r="D122" s="33" t="n">
+      <c r="D122" s="36" t="n">
         <v>0.167728806235539</v>
       </c>
     </row>
@@ -20550,7 +20577,7 @@
       <c r="C123" s="24" t="n">
         <v>1175.20197608028</v>
       </c>
-      <c r="D123" s="33" t="n">
+      <c r="D123" s="36" t="n">
         <v>0.201641496355</v>
       </c>
     </row>
@@ -20564,7 +20591,7 @@
       <c r="C124" s="24" t="n">
         <v>1121.90848909806</v>
       </c>
-      <c r="D124" s="33" t="n">
+      <c r="D124" s="36" t="n">
         <v>0.192497384381233</v>
       </c>
     </row>
@@ -20578,7 +20605,7 @@
       <c r="C125" s="24" t="n">
         <v>887.658477207183</v>
       </c>
-      <c r="D125" s="33" t="n">
+      <c r="D125" s="36" t="n">
         <v>0.152304699310708</v>
       </c>
     </row>
@@ -20592,7 +20619,7 @@
       <c r="C126" s="24" t="n">
         <v>385.999329760854</v>
       </c>
-      <c r="D126" s="33" t="n">
+      <c r="D126" s="36" t="n">
         <v>0.0662298771013032</v>
       </c>
     </row>
@@ -20606,7 +20633,7 @@
       <c r="C127" s="24" t="n">
         <v>1279.85409094458</v>
       </c>
-      <c r="D127" s="33" t="n">
+      <c r="D127" s="36" t="n">
         <v>0.219597736616216</v>
       </c>
     </row>
@@ -20620,7 +20647,7 @@
       <c r="C128" s="24" t="n">
         <v>700.118158529561</v>
       </c>
-      <c r="D128" s="33" t="n">
+      <c r="D128" s="36" t="n">
         <v>0.177857985651585</v>
       </c>
     </row>
@@ -20634,7 +20661,7 @@
       <c r="C129" s="24" t="n">
         <v>733.239936649622</v>
       </c>
-      <c r="D129" s="33" t="n">
+      <c r="D129" s="36" t="n">
         <v>0.186272240682486</v>
       </c>
     </row>
@@ -20648,7 +20675,7 @@
       <c r="C130" s="24" t="n">
         <v>736.356356978635</v>
       </c>
-      <c r="D130" s="33" t="n">
+      <c r="D130" s="36" t="n">
         <v>0.18706393596336</v>
       </c>
     </row>
@@ -20662,7 +20689,7 @@
       <c r="C131" s="24" t="n">
         <v>591.684842704685</v>
       </c>
-      <c r="D131" s="33" t="n">
+      <c r="D131" s="36" t="n">
         <v>0.150311590953525</v>
       </c>
     </row>
@@ -20676,7 +20703,7 @@
       <c r="C132" s="24" t="n">
         <v>259.210312336603</v>
       </c>
-      <c r="D132" s="33" t="n">
+      <c r="D132" s="36" t="n">
         <v>0.065849776142265</v>
       </c>
     </row>
@@ -20690,7 +20717,7 @@
       <c r="C133" s="24" t="n">
         <v>915.779056850298</v>
       </c>
-      <c r="D133" s="33" t="n">
+      <c r="D133" s="36" t="n">
         <v>0.232644470606779</v>
       </c>
     </row>
@@ -20704,7 +20731,7 @@
       <c r="C134" s="24" t="n">
         <v>1034.14765986637</v>
       </c>
-      <c r="D134" s="33" t="n">
+      <c r="D134" s="36" t="n">
         <v>0.178877994218476</v>
       </c>
     </row>
@@ -20718,7 +20745,7 @@
       <c r="C135" s="24" t="n">
         <v>1056.26986377139</v>
       </c>
-      <c r="D135" s="33" t="n">
+      <c r="D135" s="36" t="n">
         <v>0.182704503348453</v>
       </c>
     </row>
@@ -20732,7 +20759,7 @@
       <c r="C136" s="24" t="n">
         <v>1076.66989221733</v>
       </c>
-      <c r="D136" s="33" t="n">
+      <c r="D136" s="36" t="n">
         <v>0.186233125335453</v>
       </c>
     </row>
@@ -20746,7 +20773,7 @@
       <c r="C137" s="24" t="n">
         <v>864.563621840276</v>
       </c>
-      <c r="D137" s="33" t="n">
+      <c r="D137" s="36" t="n">
         <v>0.149544801531566</v>
       </c>
     </row>
@@ -20760,7 +20787,7 @@
       <c r="C138" s="24" t="n">
         <v>381.705995415724</v>
       </c>
-      <c r="D138" s="33" t="n">
+      <c r="D138" s="36" t="n">
         <v>0.0660242298957138</v>
       </c>
     </row>
@@ -20774,7 +20801,7 @@
       <c r="C139" s="24" t="n">
         <v>1367.94471048568</v>
       </c>
-      <c r="D139" s="33" t="n">
+      <c r="D139" s="36" t="n">
         <v>0.236615345670338</v>
       </c>
     </row>
@@ -20788,7 +20815,7 @@
       <c r="C140" s="24" t="n">
         <v>693.278625395239</v>
       </c>
-      <c r="D140" s="33" t="n">
+      <c r="D140" s="36" t="n">
         <v>0.172039385208514</v>
       </c>
     </row>
@@ -20802,7 +20829,7 @@
       <c r="C141" s="24" t="n">
         <v>791.095392422185</v>
       </c>
-      <c r="D141" s="33" t="n">
+      <c r="D141" s="36" t="n">
         <v>0.196312939658295</v>
       </c>
     </row>
@@ -20816,7 +20843,7 @@
       <c r="C142" s="24" t="n">
         <v>766.323475678671</v>
       </c>
-      <c r="D142" s="33" t="n">
+      <c r="D142" s="36" t="n">
         <v>0.190165706538911</v>
       </c>
     </row>
@@ -20830,7 +20857,7 @@
       <c r="C143" s="24" t="n">
         <v>610.691377128436</v>
       </c>
-      <c r="D143" s="33" t="n">
+      <c r="D143" s="36" t="n">
         <v>0.151545086239202</v>
       </c>
     </row>
@@ -20844,7 +20871,7 @@
       <c r="C144" s="24" t="n">
         <v>266.087787270853</v>
       </c>
-      <c r="D144" s="33" t="n">
+      <c r="D144" s="36" t="n">
         <v>0.0660305649946637</v>
       </c>
     </row>
@@ -20858,7 +20885,7 @@
       <c r="C145" s="24" t="n">
         <v>902.290273409186</v>
       </c>
-      <c r="D145" s="33" t="n">
+      <c r="D145" s="36" t="n">
         <v>0.223906317360415</v>
       </c>
     </row>
